--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/Desktop/OfertasTec/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{05723E70-F8A6-4E05-B9EC-5024AC390ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92270EEF-993F-42E0-A73E-010DFE83797C}"/>
+  <xr:revisionPtr revIDLastSave="693" documentId="13_ncr:1_{05723E70-F8A6-4E05-B9EC-5024AC390ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65724605-F4D3-4945-8460-436861B7F766}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Renomear" sheetId="1" r:id="rId1"/>
     <sheet name="Como usar" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos Renomear'!$A$1:$I$287</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="509">
   <si>
     <t>#</t>
   </si>
@@ -1108,13 +1111,469 @@
   </si>
   <si>
     <t>Vou usar os dados pra atualizar o site automaticamente.</t>
+  </si>
+  <si>
+    <t>Pen drive</t>
+  </si>
+  <si>
+    <t>https://meli.la/2qiZA87</t>
+  </si>
+  <si>
+    <t>https://meli.la/11j9MNb</t>
+  </si>
+  <si>
+    <t>https://meli.la/2CViyMj</t>
+  </si>
+  <si>
+    <t>https://meli.la/16wgc76</t>
+  </si>
+  <si>
+    <t>https://meli.la/1HWTTfy</t>
+  </si>
+  <si>
+    <t>https://meli.la/2zCrUDN</t>
+  </si>
+  <si>
+    <t>https://meli.la/29Wfdp7</t>
+  </si>
+  <si>
+    <t>Pen Drive 128gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 128gb De Armazenamento Pc Notebook Cor Prateado</t>
+  </si>
+  <si>
+    <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 32gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
+  </si>
+  <si>
+    <t>Pen Drive 64gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
+  </si>
+  <si>
+    <t>Pendrive Twist preto 64gb multilaser modelo PD590</t>
+  </si>
+  <si>
+    <t>Pendrive Sandisk Cruzer Blade 32gb Usb 2.0 Sdcz50-032g-b35 Cor Preto Sem tampa</t>
+  </si>
+  <si>
+    <t>Pen Drive 32gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
+  </si>
+  <si>
+    <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Ótima De Armazenamento Pc Notebook Haixia Cor Prateado</t>
+  </si>
+  <si>
+    <t>https://meli.la/1BhCm1B</t>
+  </si>
+  <si>
+    <t>https://meli.la/2UUu5Ti</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Dv34H3</t>
+  </si>
+  <si>
+    <t>https://meli.la/1zAUW82</t>
+  </si>
+  <si>
+    <t>https://meli.la/1LuoL3b</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Q1hTC1</t>
+  </si>
+  <si>
+    <t>https://meli.la/2EC1D2e</t>
+  </si>
+  <si>
+    <t>https://meli.la/22nV3bJ</t>
+  </si>
+  <si>
+    <t>https://meli.la/1qNb23D</t>
+  </si>
+  <si>
+    <t>Pendrive Kapbom 16gb Usb 2.0 Metal Prateado Compatível Wind</t>
+  </si>
+  <si>
+    <t>Pen Drive 8gb Usb Compacto Alto Desempenho E Velocidade</t>
+  </si>
+  <si>
+    <t>Pendrive 2tb Usb 3.0 Metalico</t>
+  </si>
+  <si>
+    <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 32gb De Armazenamento Pc Notebook Cor Prateado</t>
+  </si>
+  <si>
+    <t>Pen Drive 16gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
+  </si>
+  <si>
+    <t>Pendrive Flash Drive 2 Em 1 Usb C E Usb 3.0 32gb Metal Pro</t>
+  </si>
+  <si>
+    <t>Pendrive Altomex AL-U-32 memória 32gb pc notebook usb cor preto liso</t>
+  </si>
+  <si>
+    <t>Pendrive Kingston Datatraveler Exodia M 256gb Dtxm/256gb 3.2 Cor Verde</t>
+  </si>
+  <si>
+    <t>Kingston USB Datatraveler Exodia S 64Gb USB-A 3.2 Gen 1</t>
+  </si>
+  <si>
+    <t>RHEAD RED HIGH END STUDIOS</t>
+  </si>
+  <si>
+    <t>Gurumania</t>
+  </si>
+  <si>
+    <t>WMIX ELETRÔNICOS</t>
+  </si>
+  <si>
+    <t>SanDisk</t>
+  </si>
+  <si>
+    <t>Haixia</t>
+  </si>
+  <si>
+    <t>Kapbom</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Pen Drive Celular Mini Pequeno Hrebos</t>
+  </si>
+  <si>
+    <t>Altomex</t>
+  </si>
+  <si>
+    <t>https://meli.la/2LbfSKF</t>
+  </si>
+  <si>
+    <t>https://meli.la/2YZWcPv</t>
+  </si>
+  <si>
+    <t>https://meli.la/11UGXL4</t>
+  </si>
+  <si>
+    <t>https://meli.la/1XfkXY4</t>
+  </si>
+  <si>
+    <t>https://meli.la/15oUo1F</t>
+  </si>
+  <si>
+    <t>https://meli.la/23sKPyN</t>
+  </si>
+  <si>
+    <t>https://meli.la/2LoeExa</t>
+  </si>
+  <si>
+    <t>Pendrive Kingston Datatraveler Exodia Dtx/64 64gb 3.2 Gen 1</t>
+  </si>
+  <si>
+    <t>Pendrive Sandisk Ultra Shift Preto 32gb Usb 3.2</t>
+  </si>
+  <si>
+    <t>SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido</t>
+  </si>
+  <si>
+    <t>Pendrive 64gb Usb 3.0 Tipo C Metal Plug &amp; Play Android Vers</t>
+  </si>
+  <si>
+    <t>Pen Drive Sandisk Usb 3.2 Geração 1 Ultra Luxe 128gb</t>
+  </si>
+  <si>
+    <t>Pendrive SanDisk Cruzer Blade SDCZ50-016G-B35 16GB 2.0 Liso azul-elétrico</t>
+  </si>
+  <si>
+    <t>Pen Drive SanDisk Ultra Shift 128 GB USB 3.0 Violeta</t>
+  </si>
+  <si>
+    <t>https://meli.la/1iL54rx</t>
+  </si>
+  <si>
+    <t>https://meli.la/1j345xd</t>
+  </si>
+  <si>
+    <t>https://meli.la/1e35itv</t>
+  </si>
+  <si>
+    <t>https://meli.la/1qjgyca</t>
+  </si>
+  <si>
+    <t>https://meli.la/2bUd8Qi</t>
+  </si>
+  <si>
+    <t>https://meli.la/1rPATiL</t>
+  </si>
+  <si>
+    <t>https://meli.la/2Z5fhDF</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Ny9BQg</t>
+  </si>
+  <si>
+    <t>https://meli.la/1MHXAZo</t>
+  </si>
+  <si>
+    <t>https://meli.la/2u6BAdS</t>
+  </si>
+  <si>
+    <t>https://meli.la/2KYJowg</t>
+  </si>
+  <si>
+    <t>https://meli.la/2niAQ49</t>
+  </si>
+  <si>
+    <t>Kapbom Ka-a-16 Kit C/ 2 Pen-drive De 16 Gb Penmax Usb 2.0 Pc</t>
+  </si>
+  <si>
+    <t>Pendrive Altomex Al-u-4 4 4gb 2.0 Preto</t>
+  </si>
+  <si>
+    <t>Pen Drive 64gb Usb 3.0 De Duplo 2 Em 1 Usb/usb-c 140mb/s</t>
+  </si>
+  <si>
+    <t>Pendrive Sandisk Cruzer Blade 32gb 2.0 Usb Original Lacrado</t>
+  </si>
+  <si>
+    <t>Pendrive SanDisk Cruzer Blade 8GB 2.0 preto e vermelho</t>
+  </si>
+  <si>
+    <t>Pen Drive 16gb Multilaser Twist - Pd588</t>
+  </si>
+  <si>
+    <t>Pen Drive 32gb Madeira Redondo Ecológico Personalizado Cor Marrom-claro</t>
+  </si>
+  <si>
+    <t>Pen Drive 32gb Ultra Flair Usb 3.0 Metal 150mbs Z73 Sandisk</t>
+  </si>
+  <si>
+    <t>Pendrive 32gb 2 Em 1 Usb 3.0 Tipo-c Para Celular Pc Tablet</t>
+  </si>
+  <si>
+    <t>Pendrive Altomex 128gb Usb 2.0 Al-u-128 Alta Velocidade - Preto</t>
+  </si>
+  <si>
+    <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 128gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
+  </si>
+  <si>
+    <t>Pendrive Sandisk Ultra Shift 256gb Usb 3.2 Gen 1 100mbs Roxo Violeta</t>
+  </si>
+  <si>
+    <t>https://meli.la/1Z5VJQ6</t>
+  </si>
+  <si>
+    <t>https://meli.la/1fheaUW</t>
+  </si>
+  <si>
+    <t>https://meli.la/1vKzJM3</t>
+  </si>
+  <si>
+    <t>https://meli.la/2NPo4eJ</t>
+  </si>
+  <si>
+    <t>https://meli.la/1NCrcA6</t>
+  </si>
+  <si>
+    <t>https://meli.la/2ASehEZ</t>
+  </si>
+  <si>
+    <t>https://meli.la/13C2HTp</t>
+  </si>
+  <si>
+    <t>https://meli.la/2e1VX7E</t>
+  </si>
+  <si>
+    <t>Mouse pad pequeno</t>
+  </si>
+  <si>
+    <t>Mousepad De Escritório Pequeno Preto Tecido Simples Fortrek</t>
+  </si>
+  <si>
+    <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Grafite Desenho impresso Courino</t>
+  </si>
+  <si>
+    <t>Mouse Pad Com Apoio Ergonômico Em Espuma Para Punho Antiderrapante Confortável Para Escritório Gamer Estudo Trabalho Preto Megalodonte</t>
+  </si>
+  <si>
+    <t>Mousepad Mp-04pt Simples - Hoopso</t>
+  </si>
+  <si>
+    <t>Mousepad Gamer Speed Havit Pequeno Com Alta Qualidade Cor Preto</t>
+  </si>
+  <si>
+    <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Caramelo</t>
+  </si>
+  <si>
+    <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Azul</t>
+  </si>
+  <si>
+    <t>Mouse Pad Ziphome Preto 23x22.5cm Borracha Tecido Antiderrapante</t>
+  </si>
+  <si>
+    <t>https://meli.la/2Pn152u</t>
+  </si>
+  <si>
+    <t>https://meli.la/1XfeDjK</t>
+  </si>
+  <si>
+    <t>https://meli.la/2M889UE</t>
+  </si>
+  <si>
+    <t>https://meli.la/2K3HSeC</t>
+  </si>
+  <si>
+    <t>https://meli.la/1iM9KwJ</t>
+  </si>
+  <si>
+    <t>https://meli.la/2jgnzuA</t>
+  </si>
+  <si>
+    <t>Mouse Pad Pequeno 20x20cm Couro Sintetico Kit 2 Tapete Mesas Cor Quadrado MARFIM Desenho impresso Liso</t>
+  </si>
+  <si>
+    <t>Tapete Para Mouse Preto Liso Notebook E Escritório Borracha</t>
+  </si>
+  <si>
+    <t>Mousepad 20x20cm Couro Sintetico Slim Premium Impermeavel</t>
+  </si>
+  <si>
+    <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Rosa Desenho impresso Courino</t>
+  </si>
+  <si>
+    <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Bege</t>
+  </si>
+  <si>
+    <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Branco</t>
+  </si>
+  <si>
+    <t>Validação</t>
+  </si>
+  <si>
+    <t>https://meli.la/2cGbTdT</t>
+  </si>
+  <si>
+    <t>https://meli.la/1NTtrP5</t>
+  </si>
+  <si>
+    <t>https://meli.la/2PLvtPH</t>
+  </si>
+  <si>
+    <t>https://meli.la/2gbZpAz</t>
+  </si>
+  <si>
+    <t>https://meli.la/1NTUn6u</t>
+  </si>
+  <si>
+    <t>Fone Bluetooth 5.3 Tws Sem Fio Anti Ruido A Prova Dagua Compatível Iphone 7 8 X Xr 11 12 13 14 15 16 17 Xs Pro Max Plus Samsung S20 S23 S24 Xiaomi Motorola Android Prova DAgua Wireless Premium</t>
+  </si>
+  <si>
+    <t>Fone De Ouvido Bluetooth In Ear Touch À Prova D'água Inova</t>
+  </si>
+  <si>
+    <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Azul</t>
+  </si>
+  <si>
+    <t>Fone de Ouvido Ows Bluetooth Design Aberto Kaidi 794 Cor Preto</t>
+  </si>
+  <si>
+    <t>Fone Sem Fio Bluetooth 5.4 Compativel Iphone Ipx4 Microfone</t>
+  </si>
+  <si>
+    <t>https://meli.la/1KFgyz2</t>
+  </si>
+  <si>
+    <t>https://meli.la/1XARpGa</t>
+  </si>
+  <si>
+    <t>https://meli.la/18AJ4f6</t>
+  </si>
+  <si>
+    <t>https://meli.la/2GHMGcW</t>
+  </si>
+  <si>
+    <t>https://meli.la/1jGZwC3</t>
+  </si>
+  <si>
+    <t>https://meli.la/2G3uu5c</t>
+  </si>
+  <si>
+    <t>https://meli.la/1A65TWL</t>
+  </si>
+  <si>
+    <t>Fone de Ouvido TWS B Basto Fone-TWS Bluetooth Sem Fio Com Cancelamento de Ruído e Microfone</t>
+  </si>
+  <si>
+    <t>Fone Bluetooth 5.4 Sem Fio Tws Kaidi Kd780 Graves Potentes</t>
+  </si>
+  <si>
+    <t>Fone De Ouvido Bluetooth 5.1 Sem Fio Tws Wireless Bateria Longa Duração E Conexão Rápida Coolmusic</t>
+  </si>
+  <si>
+    <t>Fone Qcy N30 Anc Bluetooth 5.4 Multiponto Ipx4 Cor Preto</t>
+  </si>
+  <si>
+    <t>Fone De Ouvido Esportivos Sem Fio Bluetooth Impermeável Ipx6</t>
+  </si>
+  <si>
+    <t>Fone de Ouvido Eardbud AIWA AWS-EB-04-B Bluetooth IPX4 ANC 26 Horas de bateria</t>
+  </si>
+  <si>
+    <t>Fone De Ouvido Bluetooth Redmi Buds 6 Play Xiaomi Sem Fio Cor Preto</t>
+  </si>
+  <si>
+    <t>https://meli.la/1HyuGqq</t>
+  </si>
+  <si>
+    <t>https://meli.la/2gZQECx</t>
+  </si>
+  <si>
+    <t>https://meli.la/1LM6zpe</t>
+  </si>
+  <si>
+    <t>https://meli.la/1ECoJrH</t>
+  </si>
+  <si>
+    <t>https://meli.la/2B1DT57</t>
+  </si>
+  <si>
+    <t>https://meli.la/2bjhTN4</t>
+  </si>
+  <si>
+    <t>https://meli.la/2UKmjJK</t>
+  </si>
+  <si>
+    <t>https://meli.la/2mZP8Mf</t>
+  </si>
+  <si>
+    <t>https://meli.la/18G4RGk</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Dual Bluetooth 2.4GHz USB Recarregável Silencioso Para Notebook PC</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Bluetooth Recarregável Hrebos IF-216 Prateado USB Para Windows</t>
+  </si>
+  <si>
+    <t>Mouse sem fio Logitech M280 com Pilha Inclusa - Cinza</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Logitech M196 Com Conexão Bluetooth - Branco</t>
+  </si>
+  <si>
+    <t>Mouse sem fio Logitech M185 - Cinza</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Preto Z3700 V0l79aa Hp</t>
+  </si>
+  <si>
+    <t>Mouse Oriente Sem Fio 1600 Dpi Maxprint Branco</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Compacto Lenovo 300 Cinza Claro Gy51l15677</t>
+  </si>
+  <si>
+    <t>Mouse Sem Fio Multilaser Office - Design Ergonômico e Conexão 2.4GHz - MO251</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1172,8 +1631,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1191,12 +1691,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1210,6 +1704,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1242,7 +1754,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1250,28 +1762,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1279,6 +1817,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFE000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1288,6 +1831,443 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>30009</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40BFD6AF-2AA5-D3C9-4774-D62397ADB9F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="30889575"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2437580</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>184354</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6342830</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>1090</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A05A0F-50D9-F2B7-5594-ECD904ABC224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6718709" y="31913870"/>
+          <a:ext cx="3905250" cy="4861539"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC84B47-27C5-CF6D-DF61-CB9DBC0A23CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="36261675"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>26892</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C799D10F-3A70-56CD-41AF-1C8D372BF96B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="41414700"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4413250</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>177699</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="AutoShape 6" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E14386CC-53BB-8ED3-41AD-E060719A4BD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4990353" y="39033823"/>
+          <a:ext cx="3905250" cy="4674994"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>26894</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1031" name="AutoShape 7" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4471EFF-4EA2-F67F-9D89-3FA554A7530C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="46567725"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>243</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3905250</xdr:colOff>
+      <xdr:row>267</xdr:row>
+      <xdr:rowOff>185170</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1032" name="AutoShape 8" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CEDEFC-15EC-34F6-6168-D106A7729DB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="46948725"/>
+          <a:ext cx="3905250" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>271</xdr:row>
+      <xdr:rowOff>26895</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1033" name="AutoShape 9" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C3E7364-BD21-61D8-5459-69BB19FBEA2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="51720750"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3905250</xdr:colOff>
+      <xdr:row>294</xdr:row>
+      <xdr:rowOff>185167</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1034" name="AutoShape 10" descr="SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE6B2A92-3BB5-A5B5-505C-49B010D202EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4276725" y="52101750"/>
+          <a:ext cx="3905250" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1579,20 +2559,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I144"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA1972"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="187.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="181.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="s">
+        <v>466</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +2586,7 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1618,8 +2602,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="20"/>
       <c r="B2">
         <v>1</v>
       </c>
@@ -1629,7 +2613,7 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1639,8 +2623,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="20"/>
       <c r="B3">
         <v>2</v>
       </c>
@@ -1650,7 +2634,7 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1660,8 +2644,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="20"/>
       <c r="B4">
         <v>3</v>
       </c>
@@ -1671,7 +2655,7 @@
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -1681,8 +2665,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
       <c r="B5" s="5">
         <v>4</v>
       </c>
@@ -1692,7 +2676,7 @@
       <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
@@ -1702,8 +2686,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="20"/>
       <c r="B6">
         <v>5</v>
       </c>
@@ -1713,7 +2697,7 @@
       <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1723,8 +2707,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="20"/>
       <c r="B7">
         <v>6</v>
       </c>
@@ -1734,7 +2718,7 @@
       <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="4" t="s">
@@ -1744,8 +2728,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="21"/>
       <c r="B8">
         <v>7</v>
       </c>
@@ -1755,7 +2739,7 @@
       <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -1765,8 +2749,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="20"/>
       <c r="B9">
         <v>8</v>
       </c>
@@ -1776,7 +2760,7 @@
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -1786,18 +2770,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
       <c r="B10">
         <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -1807,8 +2791,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
       <c r="B11">
         <v>10</v>
       </c>
@@ -1818,7 +2802,7 @@
       <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G11" s="4" t="s">
@@ -1828,8 +2812,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="20"/>
       <c r="B12">
         <v>11</v>
       </c>
@@ -1839,7 +2823,7 @@
       <c r="D12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1849,8 +2833,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="20"/>
       <c r="B13">
         <v>12</v>
       </c>
@@ -1860,7 +2844,7 @@
       <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1870,8 +2854,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="20"/>
       <c r="B14">
         <v>13</v>
       </c>
@@ -1881,7 +2865,7 @@
       <c r="D14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -1891,8 +2875,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="20"/>
       <c r="B15">
         <v>14</v>
       </c>
@@ -1902,7 +2886,7 @@
       <c r="D15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="4" t="s">
@@ -1912,29 +2896,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16">
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="12" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="5"/>
+      <c r="G16" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="I16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="20"/>
       <c r="B17">
         <v>16</v>
       </c>
@@ -1944,7 +2930,7 @@
       <c r="D17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -1954,8 +2940,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="20"/>
       <c r="B18">
         <v>17</v>
       </c>
@@ -1965,7 +2951,7 @@
       <c r="D18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -1975,8 +2961,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="20"/>
       <c r="B19">
         <v>18</v>
       </c>
@@ -1986,7 +2972,7 @@
       <c r="D19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>55</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -1996,8 +2982,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
       <c r="B20" s="5">
         <v>19</v>
       </c>
@@ -2007,7 +2993,7 @@
       <c r="D20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2015,18 +3001,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
       <c r="B21">
         <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>59</v>
       </c>
       <c r="G21" t="s">
@@ -2036,8 +3022,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
       <c r="B22" s="5">
         <v>21</v>
       </c>
@@ -2047,7 +3033,7 @@
       <c r="D22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -2055,8 +3041,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="20"/>
       <c r="B23">
         <v>22</v>
       </c>
@@ -2066,7 +3052,7 @@
       <c r="D23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>63</v>
       </c>
       <c r="G23" t="s">
@@ -2076,29 +3062,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="5"/>
       <c r="B24" s="5">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="6" t="s">
         <v>64</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G24" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
       <c r="B25" s="5">
         <v>24</v>
       </c>
@@ -2108,7 +3096,7 @@
       <c r="D25" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2116,8 +3104,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="21"/>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="20"/>
       <c r="B26">
         <v>25</v>
       </c>
@@ -2127,7 +3115,7 @@
       <c r="D26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="4" t="s">
@@ -2137,8 +3125,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="20"/>
       <c r="B27">
         <v>26</v>
       </c>
@@ -2148,7 +3136,7 @@
       <c r="D27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G27" t="s">
@@ -2158,8 +3146,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="20"/>
       <c r="B28">
         <v>27</v>
       </c>
@@ -2169,7 +3157,7 @@
       <c r="D28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G28" s="4" t="s">
@@ -2179,8 +3167,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
       <c r="B29" s="5">
         <v>28</v>
       </c>
@@ -2190,18 +3178,20 @@
       <c r="D29" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
         <v>73</v>
       </c>
+      <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="20"/>
       <c r="B30">
         <v>29</v>
       </c>
@@ -2211,7 +3201,7 @@
       <c r="D30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G30" s="4" t="s">
@@ -2221,8 +3211,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="21"/>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="20"/>
       <c r="B31">
         <v>30</v>
       </c>
@@ -2232,7 +3222,7 @@
       <c r="D31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>81</v>
       </c>
       <c r="G31" s="4" t="s">
@@ -2242,8 +3232,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="21"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="20"/>
       <c r="B32">
         <v>31</v>
       </c>
@@ -2253,7 +3243,7 @@
       <c r="D32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>83</v>
       </c>
       <c r="G32" s="4" t="s">
@@ -2263,8 +3253,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="5"/>
       <c r="B33" s="5">
         <v>32</v>
       </c>
@@ -2274,18 +3264,20 @@
       <c r="D33" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>85</v>
       </c>
+      <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="20"/>
       <c r="B34">
         <v>33</v>
       </c>
@@ -2295,7 +3287,7 @@
       <c r="D34" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G34" s="4" t="s">
@@ -2305,8 +3297,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="20"/>
       <c r="B35">
         <v>34</v>
       </c>
@@ -2316,7 +3308,7 @@
       <c r="D35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>88</v>
       </c>
       <c r="G35" s="4" t="s">
@@ -2326,8 +3318,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="20"/>
       <c r="B36">
         <v>35</v>
       </c>
@@ -2337,7 +3329,7 @@
       <c r="D36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>90</v>
       </c>
       <c r="G36" s="4" t="s">
@@ -2347,8 +3339,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="20"/>
       <c r="B37">
         <v>36</v>
       </c>
@@ -2358,7 +3350,7 @@
       <c r="D37" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>93</v>
       </c>
       <c r="G37" t="s">
@@ -2368,7 +3360,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="20"/>
       <c r="B38">
         <v>37</v>
       </c>
@@ -2378,7 +3371,7 @@
       <c r="D38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G38" s="4" t="s">
@@ -2388,7 +3381,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="20"/>
       <c r="B39">
         <v>38</v>
       </c>
@@ -2398,7 +3392,7 @@
       <c r="D39" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="8" t="s">
         <v>99</v>
       </c>
       <c r="G39" s="4" t="s">
@@ -2408,7 +3402,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="20"/>
       <c r="B40">
         <v>39</v>
       </c>
@@ -2418,7 +3413,7 @@
       <c r="D40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G40" s="4" t="s">
@@ -2428,7 +3423,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="20"/>
       <c r="B41">
         <v>40</v>
       </c>
@@ -2438,7 +3434,7 @@
       <c r="D41" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="8" t="s">
         <v>104</v>
       </c>
       <c r="G41" s="4" t="s">
@@ -2448,7 +3444,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="5"/>
       <c r="B42" s="5">
         <v>41</v>
       </c>
@@ -2458,7 +3455,7 @@
       <c r="D42" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="10"/>
+      <c r="E42" s="9"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -2466,7 +3463,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="20"/>
       <c r="B43">
         <v>42</v>
       </c>
@@ -2476,7 +3474,7 @@
       <c r="D43" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>108</v>
       </c>
       <c r="G43" s="4" t="s">
@@ -2486,17 +3484,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="5"/>
       <c r="B44" s="5">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="9"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -2504,7 +3503,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="20"/>
       <c r="B45">
         <v>44</v>
       </c>
@@ -2514,7 +3514,7 @@
       <c r="D45" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>113</v>
       </c>
       <c r="G45" t="s">
@@ -2524,7 +3524,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="20"/>
       <c r="B46">
         <v>45</v>
       </c>
@@ -2534,7 +3535,7 @@
       <c r="D46" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>116</v>
       </c>
       <c r="G46" s="4" t="s">
@@ -2544,27 +3545,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B47">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="6" t="s">
         <v>117</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="F47" s="5"/>
+      <c r="G47" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="20"/>
       <c r="B48">
         <v>47</v>
       </c>
@@ -2574,7 +3579,7 @@
       <c r="D48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="8" t="s">
         <v>120</v>
       </c>
       <c r="G48" t="s">
@@ -2584,7 +3589,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="5"/>
       <c r="B49" s="5">
         <v>48</v>
       </c>
@@ -2594,7 +3600,7 @@
       <c r="D49" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="10"/>
+      <c r="E49" s="9"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -2602,7 +3608,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="20"/>
       <c r="B50">
         <v>49</v>
       </c>
@@ -2612,7 +3619,7 @@
       <c r="D50" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="8" t="s">
         <v>124</v>
       </c>
       <c r="G50" t="s">
@@ -2622,7 +3629,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="20"/>
       <c r="B51">
         <v>50</v>
       </c>
@@ -2632,7 +3640,7 @@
       <c r="D51" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="8" t="s">
         <v>127</v>
       </c>
       <c r="G51" s="4" t="s">
@@ -2642,7 +3650,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="20"/>
       <c r="B52">
         <v>51</v>
       </c>
@@ -2652,7 +3661,7 @@
       <c r="D52" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="8" t="s">
         <v>129</v>
       </c>
       <c r="G52" s="4" t="s">
@@ -2662,7 +3671,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="20"/>
       <c r="B53">
         <v>52</v>
       </c>
@@ -2672,7 +3682,7 @@
       <c r="D53" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="8" t="s">
         <v>131</v>
       </c>
       <c r="G53" s="4" t="s">
@@ -2682,7 +3692,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="20"/>
       <c r="B54">
         <v>53</v>
       </c>
@@ -2692,7 +3703,7 @@
       <c r="D54" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="8" t="s">
         <v>134</v>
       </c>
       <c r="G54" s="4" t="s">
@@ -2702,7 +3713,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="20"/>
       <c r="B55">
         <v>54</v>
       </c>
@@ -2712,7 +3724,7 @@
       <c r="D55" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="8" t="s">
         <v>136</v>
       </c>
       <c r="G55" s="4" t="s">
@@ -2722,7 +3734,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="20"/>
       <c r="B56">
         <v>55</v>
       </c>
@@ -2732,7 +3745,7 @@
       <c r="D56" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="8" t="s">
         <v>138</v>
       </c>
       <c r="G56" s="4" t="s">
@@ -2742,7 +3755,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="20"/>
       <c r="B57">
         <v>56</v>
       </c>
@@ -2752,7 +3766,7 @@
       <c r="D57" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="8" t="s">
         <v>141</v>
       </c>
       <c r="G57" s="4" t="s">
@@ -2762,7 +3776,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="20"/>
       <c r="B58">
         <v>57</v>
       </c>
@@ -2772,7 +3787,7 @@
       <c r="D58" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="8" t="s">
         <v>143</v>
       </c>
       <c r="G58" s="4" t="s">
@@ -2782,7 +3797,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="20"/>
       <c r="B59">
         <v>58</v>
       </c>
@@ -2792,7 +3808,7 @@
       <c r="D59" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G59" s="4" t="s">
@@ -2802,7 +3818,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="20"/>
       <c r="B60">
         <v>59</v>
       </c>
@@ -2812,7 +3829,7 @@
       <c r="D60" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="8" t="s">
         <v>149</v>
       </c>
       <c r="G60" s="4" t="s">
@@ -2822,7 +3839,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="20"/>
       <c r="B61">
         <v>60</v>
       </c>
@@ -2832,7 +3850,7 @@
       <c r="D61" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="8" t="s">
         <v>152</v>
       </c>
       <c r="G61" s="4" t="s">
@@ -2842,7 +3860,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="20"/>
       <c r="B62">
         <v>61</v>
       </c>
@@ -2852,7 +3871,7 @@
       <c r="D62" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" s="8" t="s">
         <v>154</v>
       </c>
       <c r="G62" s="4" t="s">
@@ -2862,7 +3881,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="5"/>
       <c r="B63" s="5">
         <v>62</v>
       </c>
@@ -2872,7 +3892,7 @@
       <c r="D63" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E63" s="10"/>
+      <c r="E63" s="9"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -2880,7 +3900,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="20"/>
       <c r="B64">
         <v>63</v>
       </c>
@@ -2890,7 +3911,7 @@
       <c r="D64" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="E64" s="8" t="s">
         <v>157</v>
       </c>
       <c r="G64" s="4" t="s">
@@ -2900,27 +3921,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B65">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5">
         <v>64</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="6" t="s">
         <v>158</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="F65" s="5"/>
+      <c r="G65" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="I65" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H65" s="5"/>
+      <c r="I65" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="20"/>
       <c r="B66">
         <v>65</v>
       </c>
@@ -2930,7 +3955,7 @@
       <c r="D66" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="8" t="s">
         <v>162</v>
       </c>
       <c r="G66" s="4" t="s">
@@ -2940,7 +3965,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="20"/>
       <c r="B67">
         <v>66</v>
       </c>
@@ -2950,7 +3976,7 @@
       <c r="D67" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="8" t="s">
         <v>166</v>
       </c>
       <c r="G67" t="s">
@@ -2960,7 +3986,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="20"/>
       <c r="B68">
         <v>67</v>
       </c>
@@ -2970,7 +3997,7 @@
       <c r="D68" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E68" s="8" t="s">
         <v>168</v>
       </c>
       <c r="G68" s="4" t="s">
@@ -2980,7 +4007,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="20"/>
       <c r="B69">
         <v>68</v>
       </c>
@@ -2990,7 +4018,7 @@
       <c r="D69" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="E69" s="8" t="s">
         <v>170</v>
       </c>
       <c r="G69" s="4" t="s">
@@ -3000,7 +4028,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="20"/>
       <c r="B70">
         <v>69</v>
       </c>
@@ -3010,7 +4039,7 @@
       <c r="D70" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="E70" s="8" t="s">
         <v>173</v>
       </c>
       <c r="G70" s="4" t="s">
@@ -3020,7 +4049,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="5"/>
       <c r="B71" s="5">
         <v>70</v>
       </c>
@@ -3030,7 +4060,7 @@
       <c r="D71" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E71" s="10"/>
+      <c r="E71" s="9"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -3038,7 +4068,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="20"/>
       <c r="B72">
         <v>71</v>
       </c>
@@ -3048,7 +4079,7 @@
       <c r="D72" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E72" s="8" t="s">
         <v>176</v>
       </c>
       <c r="G72" s="4" t="s">
@@ -3058,7 +4089,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="20"/>
       <c r="B73">
         <v>72</v>
       </c>
@@ -3068,7 +4100,7 @@
       <c r="D73" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="8" t="s">
         <v>178</v>
       </c>
       <c r="G73" s="4" t="s">
@@ -3078,7 +4110,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="20"/>
       <c r="B74">
         <v>73</v>
       </c>
@@ -3088,7 +4121,7 @@
       <c r="D74" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G74" s="4" t="s">
@@ -3098,7 +4131,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="20"/>
       <c r="B75">
         <v>74</v>
       </c>
@@ -3108,7 +4142,7 @@
       <c r="D75" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="8" t="s">
         <v>183</v>
       </c>
       <c r="G75" s="4" t="s">
@@ -3118,7 +4152,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="5"/>
       <c r="B76" s="5">
         <v>75</v>
       </c>
@@ -3128,7 +4163,7 @@
       <c r="D76" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E76" s="10"/>
+      <c r="E76" s="9"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -3136,7 +4171,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="20"/>
       <c r="B77">
         <v>76</v>
       </c>
@@ -3146,7 +4182,7 @@
       <c r="D77" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E77" s="9" t="s">
+      <c r="E77" s="8" t="s">
         <v>187</v>
       </c>
       <c r="G77" s="4" t="s">
@@ -3156,7 +4192,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="20"/>
       <c r="B78">
         <v>77</v>
       </c>
@@ -3166,7 +4203,7 @@
       <c r="D78" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="E78" s="8" t="s">
         <v>190</v>
       </c>
       <c r="G78" s="4" t="s">
@@ -3176,7 +4213,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="20"/>
       <c r="B79">
         <v>78</v>
       </c>
@@ -3186,7 +4224,7 @@
       <c r="D79" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="8" t="s">
         <v>193</v>
       </c>
       <c r="G79" s="4" t="s">
@@ -3196,7 +4234,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="5"/>
       <c r="B80" s="5">
         <v>79</v>
       </c>
@@ -3206,7 +4245,7 @@
       <c r="D80" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E80" s="10"/>
+      <c r="E80" s="9"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -3214,7 +4253,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" s="5"/>
       <c r="B81" s="5">
         <v>80</v>
       </c>
@@ -3224,7 +4264,7 @@
       <c r="D81" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E81" s="10"/>
+      <c r="E81" s="9"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -3232,7 +4272,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="20"/>
       <c r="B82">
         <v>81</v>
       </c>
@@ -3242,7 +4283,7 @@
       <c r="D82" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="E82" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G82" s="4" t="s">
@@ -3252,7 +4293,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" s="20"/>
       <c r="B83">
         <v>82</v>
       </c>
@@ -3262,7 +4304,7 @@
       <c r="D83" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="E83" s="8" t="s">
         <v>201</v>
       </c>
       <c r="G83" s="4" t="s">
@@ -3272,7 +4314,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="20"/>
       <c r="B84">
         <v>83</v>
       </c>
@@ -3282,7 +4325,7 @@
       <c r="D84" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="E84" s="8" t="s">
         <v>204</v>
       </c>
       <c r="G84" s="4" t="s">
@@ -3292,7 +4335,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="20"/>
       <c r="B85">
         <v>84</v>
       </c>
@@ -3302,7 +4346,7 @@
       <c r="D85" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="8" t="s">
         <v>207</v>
       </c>
       <c r="G85" s="4" t="s">
@@ -3312,7 +4356,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="20"/>
       <c r="B86">
         <v>85</v>
       </c>
@@ -3322,7 +4367,7 @@
       <c r="D86" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="E86" s="8" t="s">
         <v>209</v>
       </c>
       <c r="G86" s="4" t="s">
@@ -3332,7 +4377,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="20"/>
       <c r="B87">
         <v>86</v>
       </c>
@@ -3342,7 +4388,7 @@
       <c r="D87" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="8" t="s">
         <v>211</v>
       </c>
       <c r="G87" s="4" t="s">
@@ -3352,7 +4398,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" s="20"/>
       <c r="B88">
         <v>87</v>
       </c>
@@ -3362,7 +4409,7 @@
       <c r="D88" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="8" t="s">
         <v>213</v>
       </c>
       <c r="G88" s="4" t="s">
@@ -3372,7 +4419,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" s="20"/>
       <c r="B89">
         <v>88</v>
       </c>
@@ -3382,7 +4430,7 @@
       <c r="D89" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="8" t="s">
         <v>217</v>
       </c>
       <c r="G89" s="4" t="s">
@@ -3392,7 +4440,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" s="20"/>
       <c r="B90">
         <v>89</v>
       </c>
@@ -3402,7 +4451,7 @@
       <c r="D90" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="E90" s="8" t="s">
         <v>220</v>
       </c>
       <c r="G90" s="4" t="s">
@@ -3412,7 +4461,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" s="20"/>
       <c r="B91">
         <v>90</v>
       </c>
@@ -3422,7 +4472,7 @@
       <c r="D91" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E91" s="9" t="s">
+      <c r="E91" s="8" t="s">
         <v>223</v>
       </c>
       <c r="G91" s="4" t="s">
@@ -3432,7 +4482,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" s="20"/>
       <c r="B92">
         <v>91</v>
       </c>
@@ -3442,7 +4493,7 @@
       <c r="D92" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E92" s="8" t="s">
         <v>226</v>
       </c>
       <c r="G92" s="4" t="s">
@@ -3452,7 +4503,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" s="5"/>
       <c r="B93" s="5">
         <v>92</v>
       </c>
@@ -3462,7 +4514,7 @@
       <c r="D93" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="E93" s="10"/>
+      <c r="E93" s="9"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -3470,7 +4522,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" s="20"/>
       <c r="B94">
         <v>93</v>
       </c>
@@ -3480,7 +4533,7 @@
       <c r="D94" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="E94" s="8" t="s">
         <v>230</v>
       </c>
       <c r="G94" s="4" t="s">
@@ -3490,7 +4543,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" s="20"/>
       <c r="B95">
         <v>94</v>
       </c>
@@ -3500,7 +4554,7 @@
       <c r="D95" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="E95" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G95" s="4" t="s">
@@ -3510,7 +4564,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" s="20"/>
       <c r="B96">
         <v>95</v>
       </c>
@@ -3520,7 +4575,7 @@
       <c r="D96" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E96" s="9" t="s">
+      <c r="E96" s="8" t="s">
         <v>235</v>
       </c>
       <c r="G96" s="4" t="s">
@@ -3530,7 +4585,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" s="20"/>
       <c r="B97">
         <v>96</v>
       </c>
@@ -3540,7 +4596,7 @@
       <c r="D97" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" s="8" t="s">
         <v>238</v>
       </c>
       <c r="G97" s="4" t="s">
@@ -3550,7 +4606,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" s="5"/>
       <c r="B98" s="5">
         <v>97</v>
       </c>
@@ -3560,7 +4617,7 @@
       <c r="D98" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E98" s="10"/>
+      <c r="E98" s="9"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -3568,7 +4625,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" s="5"/>
       <c r="B99" s="5">
         <v>98</v>
       </c>
@@ -3578,7 +4636,7 @@
       <c r="D99" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="E99" s="10"/>
+      <c r="E99" s="9"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -3586,7 +4644,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" s="20"/>
       <c r="B100">
         <v>99</v>
       </c>
@@ -3596,7 +4655,7 @@
       <c r="D100" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E100" s="9" t="s">
+      <c r="E100" s="8" t="s">
         <v>243</v>
       </c>
       <c r="G100" s="4" t="s">
@@ -3606,7 +4665,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="20"/>
       <c r="B101">
         <v>100</v>
       </c>
@@ -3616,7 +4676,7 @@
       <c r="D101" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="E101" s="8" t="s">
         <v>246</v>
       </c>
       <c r="G101" s="4" t="s">
@@ -3626,7 +4686,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102" s="20"/>
       <c r="B102">
         <v>101</v>
       </c>
@@ -3636,7 +4697,7 @@
       <c r="D102" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E102" s="9" t="s">
+      <c r="E102" s="8" t="s">
         <v>249</v>
       </c>
       <c r="G102" s="4" t="s">
@@ -3646,27 +4707,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5">
         <v>102</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="6" t="s">
         <v>250</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="F103" s="5"/>
+      <c r="G103" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="I103" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H103" s="5"/>
+      <c r="I103" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" s="20"/>
       <c r="B104">
         <v>103</v>
       </c>
@@ -3676,7 +4741,7 @@
       <c r="D104" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E104" s="9" t="s">
+      <c r="E104" s="8" t="s">
         <v>253</v>
       </c>
       <c r="G104" s="4" t="s">
@@ -3686,7 +4751,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" s="5"/>
       <c r="B105" s="5">
         <v>104</v>
       </c>
@@ -3696,7 +4762,7 @@
       <c r="D105" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E105" s="10"/>
+      <c r="E105" s="9"/>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -3704,7 +4770,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106" s="20"/>
       <c r="B106">
         <v>105</v>
       </c>
@@ -3714,7 +4781,7 @@
       <c r="D106" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E106" s="9" t="s">
+      <c r="E106" s="8" t="s">
         <v>257</v>
       </c>
       <c r="G106" s="4" t="s">
@@ -3724,7 +4791,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107" s="20"/>
       <c r="B107">
         <v>106</v>
       </c>
@@ -3734,7 +4802,7 @@
       <c r="D107" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E107" s="9" t="s">
+      <c r="E107" s="8" t="s">
         <v>260</v>
       </c>
       <c r="G107" s="4" t="s">
@@ -3744,7 +4812,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108" s="20"/>
       <c r="B108">
         <v>107</v>
       </c>
@@ -3754,7 +4823,7 @@
       <c r="D108" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E108" s="9" t="s">
+      <c r="E108" s="8" t="s">
         <v>262</v>
       </c>
       <c r="G108" s="4" t="s">
@@ -3764,7 +4833,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A109" s="5"/>
       <c r="B109" s="5">
         <v>108</v>
       </c>
@@ -3774,7 +4844,7 @@
       <c r="D109" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E109" s="10"/>
+      <c r="E109" s="9"/>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -3782,7 +4852,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" s="20"/>
       <c r="B110">
         <v>109</v>
       </c>
@@ -3792,7 +4863,7 @@
       <c r="D110" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E110" s="9" t="s">
+      <c r="E110" s="8" t="s">
         <v>266</v>
       </c>
       <c r="G110" s="4" t="s">
@@ -3802,7 +4873,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A111" s="20"/>
       <c r="B111">
         <v>110</v>
       </c>
@@ -3812,7 +4884,7 @@
       <c r="D111" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E111" s="9" t="s">
+      <c r="E111" s="8" t="s">
         <v>269</v>
       </c>
       <c r="G111" s="4" t="s">
@@ -3822,7 +4894,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A112" s="20"/>
       <c r="B112">
         <v>111</v>
       </c>
@@ -3832,7 +4905,7 @@
       <c r="D112" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E112" s="9" t="s">
+      <c r="E112" s="8" t="s">
         <v>272</v>
       </c>
       <c r="G112" s="4" t="s">
@@ -3842,25 +4915,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="14">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A113" s="13"/>
+      <c r="B113" s="13">
         <v>112</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="D113" s="15" t="s">
+      <c r="D113" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E113" s="16"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
-      <c r="I113" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E113" s="15"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" s="20"/>
       <c r="B114">
         <v>113</v>
       </c>
@@ -3870,7 +4945,7 @@
       <c r="D114" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E114" s="9" t="s">
+      <c r="E114" s="8" t="s">
         <v>275</v>
       </c>
       <c r="G114" s="4" t="s">
@@ -3880,7 +4955,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" s="20"/>
       <c r="B115">
         <v>114</v>
       </c>
@@ -3890,7 +4966,7 @@
       <c r="D115" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E115" s="9" t="s">
+      <c r="E115" s="8" t="s">
         <v>277</v>
       </c>
       <c r="G115" s="4" t="s">
@@ -3900,7 +4976,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" s="20"/>
       <c r="B116">
         <v>115</v>
       </c>
@@ -3910,7 +4987,7 @@
       <c r="D116" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="E116" s="8" t="s">
         <v>279</v>
       </c>
       <c r="G116" t="s">
@@ -3920,7 +4997,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" s="20"/>
       <c r="B117">
         <v>116</v>
       </c>
@@ -3930,7 +5008,7 @@
       <c r="D117" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E117" s="9" t="s">
+      <c r="E117" s="8" t="s">
         <v>282</v>
       </c>
       <c r="G117" s="4" t="s">
@@ -3940,7 +5018,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="5"/>
       <c r="B118" s="5">
         <v>117</v>
       </c>
@@ -3950,7 +5029,7 @@
       <c r="D118" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E118" s="10"/>
+      <c r="E118" s="9"/>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -3958,7 +5037,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A119" s="20"/>
       <c r="B119">
         <v>118</v>
       </c>
@@ -3968,7 +5048,7 @@
       <c r="D119" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="E119" s="9" t="s">
+      <c r="E119" s="8" t="s">
         <v>287</v>
       </c>
       <c r="G119" s="4" t="s">
@@ -3978,7 +5058,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" s="20"/>
       <c r="B120">
         <v>119</v>
       </c>
@@ -3988,7 +5069,7 @@
       <c r="D120" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="E120" s="8" t="s">
         <v>289</v>
       </c>
       <c r="G120" s="4" t="s">
@@ -3998,7 +5079,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A121" s="20"/>
       <c r="B121">
         <v>120</v>
       </c>
@@ -4008,7 +5090,7 @@
       <c r="D121" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E121" s="9" t="s">
+      <c r="E121" s="8" t="s">
         <v>291</v>
       </c>
       <c r="G121" s="4" t="s">
@@ -4018,7 +5100,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A122" s="5"/>
       <c r="B122" s="5">
         <v>121</v>
       </c>
@@ -4028,7 +5111,7 @@
       <c r="D122" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E122" s="10"/>
+      <c r="E122" s="9"/>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
@@ -4036,7 +5119,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A123" s="20"/>
       <c r="B123">
         <v>122</v>
       </c>
@@ -4046,7 +5130,7 @@
       <c r="D123" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="E123" s="8" t="s">
         <v>294</v>
       </c>
       <c r="G123" s="4" t="s">
@@ -4056,7 +5140,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A124" s="20"/>
       <c r="B124">
         <v>123</v>
       </c>
@@ -4066,7 +5151,7 @@
       <c r="D124" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E124" s="9" t="s">
+      <c r="E124" s="8" t="s">
         <v>296</v>
       </c>
       <c r="G124" t="s">
@@ -4076,29 +5161,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B125" s="17">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A125" s="16"/>
+      <c r="B125" s="16">
         <v>124</v>
       </c>
-      <c r="C125" s="17" t="s">
+      <c r="C125" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="D125" s="18" t="s">
+      <c r="D125" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="E125" s="19" t="s">
+      <c r="E125" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="F125" s="17"/>
-      <c r="G125" s="20" t="s">
+      <c r="F125" s="16"/>
+      <c r="G125" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="H125" s="17"/>
-      <c r="I125" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H125" s="16"/>
+      <c r="I125" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A126" s="20"/>
       <c r="B126">
         <v>125</v>
       </c>
@@ -4108,7 +5195,7 @@
       <c r="D126" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E126" s="9" t="s">
+      <c r="E126" s="8" t="s">
         <v>302</v>
       </c>
       <c r="G126" t="s">
@@ -4118,7 +5205,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A127" s="20"/>
       <c r="B127">
         <v>126</v>
       </c>
@@ -4128,7 +5216,7 @@
       <c r="D127" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E127" s="9" t="s">
+      <c r="E127" s="8" t="s">
         <v>304</v>
       </c>
       <c r="G127" s="4" t="s">
@@ -4138,7 +5226,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A128" s="20"/>
       <c r="B128">
         <v>127</v>
       </c>
@@ -4148,7 +5237,7 @@
       <c r="D128" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E128" s="9" t="s">
+      <c r="E128" s="8" t="s">
         <v>306</v>
       </c>
       <c r="G128" t="s">
@@ -4158,7 +5247,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A129" s="20"/>
       <c r="B129">
         <v>128</v>
       </c>
@@ -4168,7 +5258,7 @@
       <c r="D129" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E129" s="9" t="s">
+      <c r="E129" s="8" t="s">
         <v>308</v>
       </c>
       <c r="G129" s="4" t="s">
@@ -4178,7 +5268,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A130" s="20"/>
       <c r="B130">
         <v>129</v>
       </c>
@@ -4188,7 +5279,7 @@
       <c r="D130" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E130" s="9" t="s">
+      <c r="E130" t="s">
         <v>311</v>
       </c>
       <c r="G130" s="4" t="s">
@@ -4198,7 +5289,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A131" s="20"/>
       <c r="B131">
         <v>130</v>
       </c>
@@ -4208,7 +5300,7 @@
       <c r="D131" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E131" s="9" t="s">
+      <c r="E131" t="s">
         <v>313</v>
       </c>
       <c r="G131" s="4" t="s">
@@ -4218,7 +5310,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A132" s="20"/>
       <c r="B132">
         <v>132</v>
       </c>
@@ -4228,7 +5321,7 @@
       <c r="D132" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E132" s="9" t="s">
+      <c r="E132" s="8" t="s">
         <v>315</v>
       </c>
       <c r="G132" s="4" t="s">
@@ -4238,7 +5331,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A133" s="20"/>
       <c r="B133">
         <v>133</v>
       </c>
@@ -4248,7 +5342,7 @@
       <c r="D133" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E133" s="9" t="s">
+      <c r="E133" s="8" t="s">
         <v>317</v>
       </c>
       <c r="G133" s="4" t="s">
@@ -4258,7 +5352,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A134" s="20"/>
       <c r="B134">
         <v>134</v>
       </c>
@@ -4268,7 +5363,7 @@
       <c r="D134" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E134" s="9" t="s">
+      <c r="E134" s="8" t="s">
         <v>320</v>
       </c>
       <c r="G134" s="4" t="s">
@@ -4278,7 +5373,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A135" s="20"/>
       <c r="B135">
         <v>135</v>
       </c>
@@ -4288,7 +5384,7 @@
       <c r="D135" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E135" s="9" t="s">
+      <c r="E135" s="8" t="s">
         <v>324</v>
       </c>
       <c r="G135" s="4" t="s">
@@ -4301,7 +5397,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A136" s="20"/>
       <c r="B136">
         <v>136</v>
       </c>
@@ -4311,7 +5408,7 @@
       <c r="D136" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E136" s="9" t="s">
+      <c r="E136" s="8" t="s">
         <v>328</v>
       </c>
       <c r="G136" s="4" t="s">
@@ -4321,7 +5418,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A137" s="20"/>
       <c r="B137">
         <v>137</v>
       </c>
@@ -4331,7 +5429,7 @@
       <c r="D137" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E137" s="9" t="s">
+      <c r="E137" s="8" t="s">
         <v>331</v>
       </c>
       <c r="G137" s="4" t="s">
@@ -4341,7 +5439,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A138" s="20"/>
       <c r="B138">
         <v>138</v>
       </c>
@@ -4351,7 +5450,7 @@
       <c r="D138" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E138" s="9" t="s">
+      <c r="E138" s="8" t="s">
         <v>333</v>
       </c>
       <c r="G138" s="4" t="s">
@@ -4361,7 +5460,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" s="20"/>
       <c r="B139">
         <v>139</v>
       </c>
@@ -4371,7 +5471,7 @@
       <c r="D139" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E139" s="9" t="s">
+      <c r="E139" s="8" t="s">
         <v>335</v>
       </c>
       <c r="G139" s="4" t="s">
@@ -4381,7 +5481,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" s="20"/>
       <c r="B140">
         <v>140</v>
       </c>
@@ -4391,7 +5492,7 @@
       <c r="D140" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E140" s="9" t="s">
+      <c r="E140" s="8" t="s">
         <v>337</v>
       </c>
       <c r="G140" s="4" t="s">
@@ -4401,255 +5502,2551 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E142"/>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E143"/>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E144"/>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" s="20"/>
+      <c r="B141">
+        <v>142</v>
+      </c>
+      <c r="C141" t="s">
+        <v>357</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="20"/>
+      <c r="B142">
+        <v>143</v>
+      </c>
+      <c r="C142" t="s">
+        <v>357</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" s="20"/>
+      <c r="B143">
+        <v>144</v>
+      </c>
+      <c r="C143" t="s">
+        <v>357</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" s="20"/>
+      <c r="B144">
+        <v>145</v>
+      </c>
+      <c r="C144" t="s">
+        <v>357</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" s="20"/>
+      <c r="B145">
+        <v>147</v>
+      </c>
+      <c r="C145" t="s">
+        <v>357</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" s="20"/>
+      <c r="B146">
+        <v>148</v>
+      </c>
+      <c r="C146" t="s">
+        <v>357</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" s="20"/>
+      <c r="B147">
+        <v>149</v>
+      </c>
+      <c r="C147" t="s">
+        <v>357</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" s="20"/>
+      <c r="B148">
+        <v>150</v>
+      </c>
+      <c r="C148" t="s">
+        <v>357</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" s="20"/>
+      <c r="B149">
+        <v>151</v>
+      </c>
+      <c r="C149" t="s">
+        <v>357</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" s="20"/>
+      <c r="B150">
+        <v>152</v>
+      </c>
+      <c r="C150" t="s">
+        <v>357</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" s="20"/>
+      <c r="B151">
+        <v>153</v>
+      </c>
+      <c r="C151" t="s">
+        <v>357</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" s="20"/>
+      <c r="B152">
+        <v>154</v>
+      </c>
+      <c r="C152" t="s">
+        <v>357</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="F152" s="8"/>
+      <c r="G152" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="22" x14ac:dyDescent="0.35">
+      <c r="A153" s="20"/>
+      <c r="B153">
+        <v>155</v>
+      </c>
+      <c r="C153" t="s">
+        <v>357</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="F153" s="23"/>
+      <c r="G153" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" s="20"/>
+      <c r="B154">
+        <v>156</v>
+      </c>
+      <c r="C154" t="s">
+        <v>357</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="F154" s="8"/>
+      <c r="G154" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="22" x14ac:dyDescent="0.35">
+      <c r="A155" s="20"/>
+      <c r="B155">
+        <v>157</v>
+      </c>
+      <c r="C155" t="s">
+        <v>357</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="F155" s="23"/>
+      <c r="G155" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5">
+        <v>158</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F156" s="9"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A157" s="20"/>
+      <c r="B157">
+        <v>159</v>
+      </c>
+      <c r="C157" t="s">
+        <v>357</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B158">
+        <v>160</v>
+      </c>
+      <c r="C158" t="s">
+        <v>357</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B159">
+        <v>161</v>
+      </c>
+      <c r="C159" t="s">
+        <v>357</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B160">
+        <v>162</v>
+      </c>
+      <c r="C160" t="s">
+        <v>357</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B161">
+        <v>163</v>
+      </c>
+      <c r="C161" t="s">
+        <v>357</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="F161" s="8"/>
+      <c r="G161" s="8"/>
+      <c r="H161" s="8"/>
+      <c r="I161" s="8"/>
+    </row>
+    <row r="162" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B162">
+        <v>164</v>
+      </c>
+      <c r="C162" t="s">
+        <v>357</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="F162" s="8"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="8"/>
+      <c r="I162" s="8"/>
+      <c r="J162" s="8"/>
+      <c r="K162" s="8"/>
+      <c r="L162" s="8"/>
+      <c r="M162" s="8"/>
+      <c r="N162" s="8"/>
+      <c r="O162" s="8"/>
+      <c r="P162" s="8"/>
+      <c r="Q162" s="8"/>
+      <c r="R162" s="8"/>
+      <c r="S162" s="8"/>
+      <c r="T162" s="8"/>
+      <c r="U162" s="8"/>
+      <c r="V162" s="8"/>
+      <c r="W162" s="8"/>
+      <c r="X162" s="8"/>
+      <c r="Y162" s="8"/>
+      <c r="Z162" s="8"/>
+      <c r="AA162" s="8"/>
+    </row>
+    <row r="163" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A163" s="5"/>
+      <c r="B163" s="5">
+        <v>165</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D163" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="F163" s="9"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="9"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="8"/>
+      <c r="K163" s="8"/>
+      <c r="L163" s="8"/>
+      <c r="M163" s="8"/>
+      <c r="N163" s="8"/>
+      <c r="O163" s="8"/>
+      <c r="P163" s="8"/>
+      <c r="Q163" s="8"/>
+      <c r="R163" s="8"/>
+      <c r="S163" s="8"/>
+      <c r="T163" s="8"/>
+      <c r="U163" s="8"/>
+      <c r="V163" s="8"/>
+      <c r="W163" s="8"/>
+      <c r="X163" s="8"/>
+      <c r="Y163" s="8"/>
+      <c r="Z163" s="8"/>
+      <c r="AA163" s="8"/>
+    </row>
+    <row r="164" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="31"/>
+      <c r="B164" s="31">
+        <v>166</v>
+      </c>
+      <c r="C164" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="D164" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="F164" s="8"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+      <c r="I164" s="8"/>
+      <c r="J164" s="8"/>
+      <c r="K164" s="8"/>
+      <c r="L164" s="8"/>
+      <c r="M164" s="8"/>
+      <c r="N164" s="8"/>
+      <c r="O164" s="8"/>
+      <c r="P164" s="8"/>
+      <c r="Q164" s="8"/>
+      <c r="R164" s="8"/>
+      <c r="S164" s="8"/>
+      <c r="T164" s="8"/>
+      <c r="U164" s="8"/>
+      <c r="V164" s="8"/>
+      <c r="W164" s="8"/>
+      <c r="X164" s="8"/>
+      <c r="Y164" s="8"/>
+      <c r="Z164" s="8"/>
+      <c r="AA164" s="8"/>
+    </row>
+    <row r="165" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A165"/>
+      <c r="B165">
+        <v>167</v>
+      </c>
+      <c r="C165" t="s">
+        <v>357</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F165" s="8"/>
+      <c r="G165" s="8"/>
+      <c r="H165" s="8"/>
+      <c r="I165" s="8"/>
+      <c r="J165" s="8"/>
+      <c r="K165" s="8"/>
+      <c r="L165" s="8"/>
+      <c r="M165" s="8"/>
+      <c r="N165" s="8"/>
+      <c r="O165" s="8"/>
+      <c r="P165" s="8"/>
+      <c r="Q165" s="8"/>
+      <c r="R165" s="8"/>
+      <c r="S165" s="8"/>
+      <c r="T165" s="8"/>
+      <c r="U165" s="8"/>
+      <c r="V165" s="8"/>
+      <c r="W165" s="8"/>
+      <c r="X165" s="8"/>
+      <c r="Y165" s="8"/>
+      <c r="Z165" s="8"/>
+      <c r="AA165" s="8"/>
+    </row>
+    <row r="166" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B166">
+        <v>168</v>
+      </c>
+      <c r="C166" t="s">
+        <v>357</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="F166" s="8"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+      <c r="I166" s="8"/>
+      <c r="J166" s="8"/>
+      <c r="K166" s="8"/>
+      <c r="L166" s="8"/>
+      <c r="M166" s="8"/>
+      <c r="N166" s="8"/>
+      <c r="O166" s="8"/>
+      <c r="P166" s="8"/>
+      <c r="Q166" s="8"/>
+      <c r="R166" s="8"/>
+      <c r="S166" s="8"/>
+      <c r="T166" s="8"/>
+      <c r="U166" s="8"/>
+      <c r="V166" s="8"/>
+      <c r="W166" s="8"/>
+      <c r="X166" s="8"/>
+      <c r="Y166" s="8"/>
+      <c r="Z166" s="8"/>
+      <c r="AA166" s="8"/>
+    </row>
+    <row r="167" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B167">
+        <v>169</v>
+      </c>
+      <c r="C167" t="s">
+        <v>357</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="F167" s="8"/>
+      <c r="G167" s="8"/>
+      <c r="H167" s="8"/>
+      <c r="I167" s="8"/>
+      <c r="J167" s="8"/>
+      <c r="K167" s="8"/>
+      <c r="L167" s="8"/>
+      <c r="M167" s="8"/>
+      <c r="N167" s="8"/>
+      <c r="O167" s="8"/>
+      <c r="P167" s="8"/>
+      <c r="Q167" s="8"/>
+      <c r="R167" s="8"/>
+      <c r="S167" s="8"/>
+      <c r="T167" s="8"/>
+      <c r="U167" s="8"/>
+      <c r="V167" s="8"/>
+      <c r="W167" s="8"/>
+      <c r="X167" s="8"/>
+      <c r="Y167" s="8"/>
+      <c r="Z167" s="8"/>
+      <c r="AA167" s="8"/>
+    </row>
+    <row r="168" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B168">
+        <v>170</v>
+      </c>
+      <c r="C168" t="s">
+        <v>357</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F168" s="8"/>
+      <c r="G168" s="8"/>
+      <c r="H168" s="8"/>
+      <c r="I168" s="8"/>
+      <c r="J168" s="8"/>
+      <c r="K168" s="8"/>
+      <c r="L168" s="8"/>
+      <c r="M168" s="8"/>
+      <c r="N168" s="8"/>
+      <c r="O168" s="8"/>
+      <c r="P168" s="8"/>
+      <c r="Q168" s="8"/>
+      <c r="R168" s="8"/>
+      <c r="S168" s="8"/>
+      <c r="T168" s="8"/>
+      <c r="U168" s="8"/>
+      <c r="V168" s="8"/>
+      <c r="W168" s="8"/>
+      <c r="X168" s="8"/>
+      <c r="Y168" s="8"/>
+      <c r="Z168" s="8"/>
+      <c r="AA168" s="8"/>
+    </row>
+    <row r="169" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B169">
+        <v>171</v>
+      </c>
+      <c r="C169" t="s">
+        <v>357</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+      <c r="I169" s="8"/>
+      <c r="J169" s="8"/>
+      <c r="K169" s="8"/>
+      <c r="L169" s="8"/>
+      <c r="M169" s="8"/>
+      <c r="N169" s="8"/>
+      <c r="O169" s="8"/>
+      <c r="P169" s="8"/>
+      <c r="Q169" s="8"/>
+      <c r="R169" s="8"/>
+      <c r="S169" s="8"/>
+      <c r="T169" s="8"/>
+      <c r="U169" s="8"/>
+      <c r="V169" s="8"/>
+      <c r="W169" s="8"/>
+      <c r="X169" s="8"/>
+      <c r="Y169" s="8"/>
+      <c r="Z169" s="8"/>
+      <c r="AA169" s="8"/>
+    </row>
+    <row r="170" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B170">
+        <v>172</v>
+      </c>
+      <c r="C170" t="s">
+        <v>357</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="8"/>
+      <c r="I170" s="8"/>
+      <c r="J170" s="8"/>
+      <c r="K170" s="8"/>
+      <c r="L170" s="8"/>
+      <c r="M170" s="8"/>
+      <c r="N170" s="8"/>
+      <c r="O170" s="8"/>
+      <c r="P170" s="8"/>
+      <c r="Q170" s="8"/>
+      <c r="R170" s="8"/>
+      <c r="S170" s="8"/>
+      <c r="T170" s="8"/>
+      <c r="U170" s="8"/>
+      <c r="V170" s="8"/>
+      <c r="W170" s="8"/>
+      <c r="X170" s="8"/>
+      <c r="Y170" s="8"/>
+      <c r="Z170" s="8"/>
+      <c r="AA170" s="8"/>
+    </row>
+    <row r="171" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B171">
+        <v>173</v>
+      </c>
+      <c r="C171" t="s">
+        <v>357</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="F171" s="8"/>
+      <c r="G171" s="8"/>
+      <c r="H171" s="8"/>
+      <c r="I171" s="8"/>
+      <c r="J171" s="8"/>
+      <c r="K171" s="8"/>
+      <c r="L171" s="8"/>
+      <c r="M171" s="8"/>
+      <c r="N171" s="8"/>
+      <c r="O171" s="8"/>
+      <c r="P171" s="8"/>
+      <c r="Q171" s="8"/>
+      <c r="R171" s="8"/>
+      <c r="S171" s="8"/>
+      <c r="T171" s="8"/>
+      <c r="U171" s="8"/>
+      <c r="V171" s="8"/>
+      <c r="W171" s="8"/>
+      <c r="X171" s="8"/>
+      <c r="Y171" s="8"/>
+      <c r="Z171" s="8"/>
+      <c r="AA171" s="8"/>
+    </row>
+    <row r="172" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B172">
+        <v>174</v>
+      </c>
+      <c r="C172" t="s">
+        <v>357</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F172" s="8"/>
+      <c r="G172" s="8"/>
+      <c r="H172" s="8"/>
+      <c r="I172" s="8"/>
+      <c r="J172" s="8"/>
+      <c r="K172" s="8"/>
+      <c r="L172" s="8"/>
+      <c r="M172" s="8"/>
+      <c r="N172" s="8"/>
+      <c r="O172" s="8"/>
+      <c r="P172" s="8"/>
+      <c r="Q172" s="8"/>
+      <c r="R172" s="8"/>
+      <c r="S172" s="8"/>
+      <c r="T172" s="8"/>
+      <c r="U172" s="8"/>
+      <c r="V172" s="8"/>
+      <c r="W172" s="8"/>
+      <c r="X172" s="8"/>
+      <c r="Y172" s="8"/>
+      <c r="Z172" s="8"/>
+      <c r="AA172" s="8"/>
+    </row>
+    <row r="173" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B173">
+        <v>175</v>
+      </c>
+      <c r="C173" t="s">
+        <v>357</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="F173" s="8"/>
+      <c r="G173" s="8"/>
+      <c r="H173" s="8"/>
+      <c r="I173" s="8"/>
+      <c r="J173" s="8"/>
+      <c r="K173" s="8"/>
+      <c r="L173" s="8"/>
+      <c r="M173" s="8"/>
+      <c r="N173" s="8"/>
+      <c r="O173" s="8"/>
+      <c r="P173" s="8"/>
+      <c r="Q173" s="8"/>
+      <c r="R173" s="8"/>
+      <c r="S173" s="8"/>
+      <c r="T173" s="8"/>
+      <c r="U173" s="8"/>
+      <c r="V173" s="8"/>
+      <c r="W173" s="8"/>
+      <c r="X173" s="8"/>
+      <c r="Y173" s="8"/>
+      <c r="Z173" s="8"/>
+      <c r="AA173" s="8"/>
+    </row>
+    <row r="174" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B174">
+        <v>176</v>
+      </c>
+      <c r="C174" t="s">
+        <v>357</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F174" s="8"/>
+      <c r="G174" s="8"/>
+      <c r="H174" s="8"/>
+      <c r="I174" s="8"/>
+      <c r="J174" s="8"/>
+      <c r="K174" s="8"/>
+      <c r="L174" s="8"/>
+      <c r="M174" s="8"/>
+      <c r="N174" s="8"/>
+      <c r="O174" s="8"/>
+      <c r="P174" s="8"/>
+      <c r="Q174" s="8"/>
+      <c r="R174" s="8"/>
+      <c r="S174" s="8"/>
+      <c r="T174" s="8"/>
+      <c r="U174" s="8"/>
+      <c r="V174" s="8"/>
+      <c r="W174" s="8"/>
+      <c r="X174" s="8"/>
+      <c r="Y174" s="8"/>
+      <c r="Z174" s="8"/>
+      <c r="AA174" s="8"/>
+    </row>
+    <row r="175" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B175">
+        <v>177</v>
+      </c>
+      <c r="C175" t="s">
+        <v>357</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="F175" s="8"/>
+      <c r="G175" s="8"/>
+      <c r="H175" s="8"/>
+      <c r="I175" s="8"/>
+      <c r="J175" s="8"/>
+      <c r="K175" s="8"/>
+      <c r="L175" s="8"/>
+      <c r="M175" s="8"/>
+      <c r="N175" s="8"/>
+      <c r="O175" s="8"/>
+      <c r="P175" s="8"/>
+      <c r="Q175" s="8"/>
+      <c r="R175" s="8"/>
+      <c r="S175" s="8"/>
+      <c r="T175" s="8"/>
+      <c r="U175" s="8"/>
+      <c r="V175" s="8"/>
+      <c r="W175" s="8"/>
+      <c r="X175" s="8"/>
+      <c r="Y175" s="8"/>
+      <c r="Z175" s="8"/>
+      <c r="AA175" s="8"/>
+    </row>
+    <row r="176" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B176">
+        <v>178</v>
+      </c>
+      <c r="C176" t="s">
+        <v>357</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="F176" s="8"/>
+      <c r="G176" s="8"/>
+      <c r="H176" s="8"/>
+      <c r="I176" s="8"/>
+      <c r="J176" s="8"/>
+      <c r="K176" s="8"/>
+      <c r="L176" s="8"/>
+      <c r="M176" s="8"/>
+      <c r="N176" s="8"/>
+      <c r="O176" s="8"/>
+      <c r="P176" s="8"/>
+      <c r="Q176" s="8"/>
+      <c r="R176" s="8"/>
+      <c r="S176" s="8"/>
+      <c r="T176" s="8"/>
+      <c r="U176" s="8"/>
+      <c r="V176" s="8"/>
+      <c r="W176" s="8"/>
+      <c r="X176" s="8"/>
+      <c r="Y176" s="8"/>
+      <c r="Z176" s="8"/>
+      <c r="AA176" s="8"/>
+    </row>
+    <row r="177" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B177">
+        <v>179</v>
+      </c>
+      <c r="C177" t="s">
+        <v>445</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="F177" s="8"/>
+      <c r="G177" s="8"/>
+      <c r="H177" s="8"/>
+      <c r="I177" s="8"/>
+      <c r="J177" s="8"/>
+      <c r="K177" s="8"/>
+      <c r="L177" s="8"/>
+      <c r="M177" s="8"/>
+      <c r="N177" s="8"/>
+      <c r="O177" s="8"/>
+      <c r="P177" s="8"/>
+      <c r="Q177" s="8"/>
+      <c r="R177" s="8"/>
+      <c r="S177" s="8"/>
+      <c r="T177" s="8"/>
+      <c r="U177" s="8"/>
+      <c r="V177" s="8"/>
+      <c r="W177" s="8"/>
+      <c r="X177" s="8"/>
+      <c r="Y177" s="8"/>
+      <c r="Z177" s="8"/>
+      <c r="AA177" s="8"/>
+    </row>
+    <row r="178" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B178">
+        <v>180</v>
+      </c>
+      <c r="C178" t="s">
+        <v>445</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="F178" s="8"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="8"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="8"/>
+      <c r="L178" s="8"/>
+      <c r="M178" s="8"/>
+      <c r="N178" s="8"/>
+      <c r="O178" s="8"/>
+      <c r="P178" s="8"/>
+      <c r="Q178" s="8"/>
+      <c r="R178" s="8"/>
+      <c r="S178" s="8"/>
+      <c r="T178" s="8"/>
+      <c r="U178" s="8"/>
+      <c r="V178" s="8"/>
+      <c r="W178" s="8"/>
+      <c r="X178" s="8"/>
+      <c r="Y178" s="8"/>
+      <c r="Z178" s="8"/>
+      <c r="AA178" s="8"/>
+    </row>
+    <row r="179" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B179">
+        <v>181</v>
+      </c>
+      <c r="C179" t="s">
+        <v>445</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F179" s="8"/>
+      <c r="G179" s="8"/>
+      <c r="H179" s="8"/>
+      <c r="I179" s="8"/>
+      <c r="J179" s="8"/>
+      <c r="K179" s="8"/>
+      <c r="L179" s="8"/>
+      <c r="M179" s="8"/>
+      <c r="N179" s="8"/>
+      <c r="O179" s="8"/>
+      <c r="P179" s="8"/>
+      <c r="Q179" s="8"/>
+      <c r="R179" s="8"/>
+      <c r="S179" s="8"/>
+      <c r="T179" s="8"/>
+      <c r="U179" s="8"/>
+      <c r="V179" s="8"/>
+      <c r="W179" s="8"/>
+      <c r="X179" s="8"/>
+      <c r="Y179" s="8"/>
+      <c r="Z179" s="8"/>
+      <c r="AA179" s="8"/>
+    </row>
+    <row r="180" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B180">
+        <v>182</v>
+      </c>
+      <c r="C180" t="s">
+        <v>445</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="F180" s="8"/>
+      <c r="G180" s="8"/>
+      <c r="H180" s="8"/>
+      <c r="I180" s="8"/>
+      <c r="J180" s="8"/>
+      <c r="K180" s="8"/>
+      <c r="L180" s="8"/>
+      <c r="M180" s="8"/>
+      <c r="N180" s="8"/>
+      <c r="O180" s="8"/>
+      <c r="P180" s="8"/>
+      <c r="Q180" s="8"/>
+      <c r="R180" s="8"/>
+      <c r="S180" s="8"/>
+      <c r="T180" s="8"/>
+      <c r="U180" s="8"/>
+      <c r="V180" s="8"/>
+      <c r="W180" s="8"/>
+      <c r="X180" s="8"/>
+      <c r="Y180" s="8"/>
+      <c r="Z180" s="8"/>
+      <c r="AA180" s="8"/>
+    </row>
+    <row r="181" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B181">
+        <v>183</v>
+      </c>
+      <c r="C181" t="s">
+        <v>445</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="F181" s="8"/>
+      <c r="G181" s="8"/>
+      <c r="H181" s="8"/>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8"/>
+      <c r="K181" s="8"/>
+      <c r="L181" s="8"/>
+      <c r="M181" s="8"/>
+      <c r="N181" s="8"/>
+      <c r="O181" s="8"/>
+      <c r="P181" s="8"/>
+      <c r="Q181" s="8"/>
+      <c r="R181" s="8"/>
+      <c r="S181" s="8"/>
+      <c r="T181" s="8"/>
+      <c r="U181" s="8"/>
+      <c r="V181" s="8"/>
+      <c r="W181" s="8"/>
+      <c r="X181" s="8"/>
+      <c r="Y181" s="8"/>
+      <c r="Z181" s="8"/>
+      <c r="AA181" s="8"/>
+    </row>
+    <row r="182" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B182">
+        <v>184</v>
+      </c>
+      <c r="C182" t="s">
+        <v>445</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8"/>
+      <c r="H182" s="8"/>
+      <c r="I182" s="8"/>
+      <c r="J182" s="8"/>
+      <c r="K182" s="8"/>
+      <c r="L182" s="8"/>
+      <c r="M182" s="8"/>
+      <c r="N182" s="8"/>
+      <c r="O182" s="8"/>
+      <c r="P182" s="8"/>
+      <c r="Q182" s="8"/>
+      <c r="R182" s="8"/>
+      <c r="S182" s="8"/>
+      <c r="T182" s="8"/>
+      <c r="U182" s="8"/>
+      <c r="V182" s="8"/>
+      <c r="W182" s="8"/>
+      <c r="X182" s="8"/>
+      <c r="Y182" s="8"/>
+      <c r="Z182" s="8"/>
+      <c r="AA182" s="8"/>
+    </row>
+    <row r="183" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B183">
+        <v>185</v>
+      </c>
+      <c r="C183" t="s">
+        <v>445</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F183" s="8"/>
+      <c r="G183" s="8"/>
+      <c r="H183" s="8"/>
+      <c r="I183" s="8"/>
+      <c r="J183" s="8"/>
+      <c r="K183" s="8"/>
+      <c r="L183" s="8"/>
+      <c r="M183" s="8"/>
+      <c r="N183" s="8"/>
+      <c r="O183" s="8"/>
+      <c r="P183" s="8"/>
+      <c r="Q183" s="8"/>
+      <c r="R183" s="8"/>
+      <c r="S183" s="8"/>
+      <c r="T183" s="8"/>
+      <c r="U183" s="8"/>
+      <c r="V183" s="8"/>
+      <c r="W183" s="8"/>
+      <c r="X183" s="8"/>
+      <c r="Y183" s="8"/>
+      <c r="Z183" s="8"/>
+      <c r="AA183" s="8"/>
+    </row>
+    <row r="184" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B184">
+        <v>186</v>
+      </c>
+      <c r="C184" t="s">
+        <v>445</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="F184" s="8"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8"/>
+      <c r="K184" s="8"/>
+      <c r="L184" s="8"/>
+      <c r="M184" s="8"/>
+      <c r="N184" s="8"/>
+      <c r="O184" s="8"/>
+      <c r="P184" s="8"/>
+      <c r="Q184" s="8"/>
+      <c r="R184" s="8"/>
+      <c r="S184" s="8"/>
+      <c r="T184" s="8"/>
+      <c r="U184" s="8"/>
+      <c r="V184" s="8"/>
+      <c r="W184" s="8"/>
+      <c r="X184" s="8"/>
+      <c r="Y184" s="8"/>
+      <c r="Z184" s="8"/>
+      <c r="AA184" s="8"/>
+    </row>
+    <row r="185" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B185">
+        <v>187</v>
+      </c>
+      <c r="C185" t="s">
+        <v>445</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="F185" s="8"/>
+      <c r="G185" s="8"/>
+      <c r="H185" s="8"/>
+      <c r="I185" s="8"/>
+      <c r="J185" s="8"/>
+      <c r="K185" s="8"/>
+      <c r="L185" s="8"/>
+      <c r="M185" s="8"/>
+      <c r="N185" s="8"/>
+      <c r="O185" s="8"/>
+      <c r="P185" s="8"/>
+      <c r="Q185" s="8"/>
+      <c r="R185" s="8"/>
+      <c r="S185" s="8"/>
+      <c r="T185" s="8"/>
+      <c r="U185" s="8"/>
+      <c r="V185" s="8"/>
+      <c r="W185" s="8"/>
+      <c r="X185" s="8"/>
+      <c r="Y185" s="8"/>
+      <c r="Z185" s="8"/>
+      <c r="AA185" s="8"/>
+    </row>
+    <row r="186" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B186">
+        <v>188</v>
+      </c>
+      <c r="C186" t="s">
+        <v>445</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="F186" s="8"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8"/>
+      <c r="K186" s="8"/>
+      <c r="L186" s="8"/>
+      <c r="M186" s="8"/>
+      <c r="N186" s="8"/>
+      <c r="O186" s="8"/>
+      <c r="P186" s="8"/>
+      <c r="Q186" s="8"/>
+      <c r="R186" s="8"/>
+      <c r="S186" s="8"/>
+      <c r="T186" s="8"/>
+      <c r="U186" s="8"/>
+      <c r="V186" s="8"/>
+      <c r="W186" s="8"/>
+      <c r="X186" s="8"/>
+      <c r="Y186" s="8"/>
+      <c r="Z186" s="8"/>
+      <c r="AA186" s="8"/>
+    </row>
+    <row r="187" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B187">
+        <v>189</v>
+      </c>
+      <c r="C187" t="s">
+        <v>445</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="F187" s="8"/>
+      <c r="G187" s="8"/>
+      <c r="H187" s="8"/>
+      <c r="I187" s="8"/>
+      <c r="J187" s="8"/>
+      <c r="K187" s="8"/>
+      <c r="L187" s="8"/>
+      <c r="M187" s="8"/>
+      <c r="N187" s="8"/>
+      <c r="O187" s="8"/>
+      <c r="P187" s="8"/>
+      <c r="Q187" s="8"/>
+      <c r="R187" s="8"/>
+      <c r="S187" s="8"/>
+      <c r="T187" s="8"/>
+      <c r="U187" s="8"/>
+      <c r="V187" s="8"/>
+      <c r="W187" s="8"/>
+      <c r="X187" s="8"/>
+      <c r="Y187" s="8"/>
+      <c r="Z187" s="8"/>
+      <c r="AA187" s="8"/>
+    </row>
+    <row r="188" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B188">
+        <v>190</v>
+      </c>
+      <c r="C188" t="s">
+        <v>445</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F188" s="8"/>
+      <c r="G188" s="8"/>
+      <c r="H188" s="8"/>
+      <c r="I188" s="8"/>
+      <c r="J188" s="8"/>
+      <c r="K188" s="8"/>
+      <c r="L188" s="8"/>
+      <c r="M188" s="8"/>
+      <c r="N188" s="8"/>
+      <c r="O188" s="8"/>
+      <c r="P188" s="8"/>
+      <c r="Q188" s="8"/>
+      <c r="R188" s="8"/>
+      <c r="S188" s="8"/>
+      <c r="T188" s="8"/>
+      <c r="U188" s="8"/>
+      <c r="V188" s="8"/>
+      <c r="W188" s="8"/>
+      <c r="X188" s="8"/>
+      <c r="Y188" s="8"/>
+      <c r="Z188" s="8"/>
+      <c r="AA188" s="8"/>
+    </row>
+    <row r="189" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B189">
+        <v>191</v>
+      </c>
+      <c r="C189" t="s">
+        <v>445</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="F189" s="8"/>
+      <c r="G189" s="8"/>
+      <c r="H189" s="8"/>
+      <c r="I189" s="8"/>
+      <c r="J189" s="8"/>
+      <c r="K189" s="8"/>
+      <c r="L189" s="8"/>
+      <c r="M189" s="8"/>
+      <c r="N189" s="8"/>
+      <c r="O189" s="8"/>
+      <c r="P189" s="8"/>
+      <c r="Q189" s="8"/>
+      <c r="R189" s="8"/>
+      <c r="S189" s="8"/>
+      <c r="T189" s="8"/>
+      <c r="U189" s="8"/>
+      <c r="V189" s="8"/>
+      <c r="W189" s="8"/>
+      <c r="X189" s="8"/>
+      <c r="Y189" s="8"/>
+      <c r="Z189" s="8"/>
+      <c r="AA189" s="8"/>
+    </row>
+    <row r="190" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B190">
+        <v>192</v>
+      </c>
+      <c r="C190" t="s">
+        <v>445</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="F190" s="8"/>
+      <c r="G190" s="8"/>
+      <c r="H190" s="8"/>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8"/>
+      <c r="K190" s="8"/>
+      <c r="L190" s="8"/>
+      <c r="M190" s="8"/>
+      <c r="N190" s="8"/>
+      <c r="O190" s="8"/>
+      <c r="P190" s="8"/>
+      <c r="Q190" s="8"/>
+      <c r="R190" s="8"/>
+      <c r="S190" s="8"/>
+      <c r="T190" s="8"/>
+      <c r="U190" s="8"/>
+      <c r="V190" s="8"/>
+      <c r="W190" s="8"/>
+      <c r="X190" s="8"/>
+      <c r="Y190" s="8"/>
+      <c r="Z190" s="8"/>
+      <c r="AA190" s="8"/>
+    </row>
+    <row r="191" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B191">
+        <v>193</v>
+      </c>
+      <c r="C191" t="s">
+        <v>215</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="F191" s="8"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="8"/>
+      <c r="L191" s="8"/>
+      <c r="M191" s="8"/>
+      <c r="N191" s="8"/>
+      <c r="O191" s="8"/>
+      <c r="P191" s="8"/>
+      <c r="Q191" s="8"/>
+      <c r="R191" s="8"/>
+      <c r="S191" s="8"/>
+      <c r="T191" s="8"/>
+      <c r="U191" s="8"/>
+      <c r="V191" s="8"/>
+      <c r="W191" s="8"/>
+      <c r="X191" s="8"/>
+      <c r="Y191" s="8"/>
+      <c r="Z191" s="8"/>
+      <c r="AA191" s="8"/>
+    </row>
+    <row r="192" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B192">
+        <v>194</v>
+      </c>
+      <c r="C192" t="s">
+        <v>215</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="J192" s="8"/>
+      <c r="K192" s="8"/>
+      <c r="L192" s="8"/>
+      <c r="M192" s="8"/>
+      <c r="N192" s="8"/>
+      <c r="O192" s="8"/>
+      <c r="P192" s="8"/>
+      <c r="Q192" s="8"/>
+      <c r="R192" s="8"/>
+      <c r="S192" s="8"/>
+      <c r="T192" s="8"/>
+      <c r="U192" s="8"/>
+      <c r="V192" s="8"/>
+      <c r="W192" s="8"/>
+      <c r="X192" s="8"/>
+      <c r="Y192" s="8"/>
+      <c r="Z192" s="8"/>
+      <c r="AA192" s="8"/>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B193">
+        <v>195</v>
+      </c>
+      <c r="C193" t="s">
+        <v>215</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B194">
+        <v>196</v>
+      </c>
+      <c r="C194" t="s">
+        <v>215</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B195">
+        <v>197</v>
+      </c>
+      <c r="C195" t="s">
+        <v>215</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B196">
+        <v>198</v>
+      </c>
+      <c r="C196" t="s">
+        <v>215</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B197">
+        <v>199</v>
+      </c>
+      <c r="C197" t="s">
+        <v>215</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B198">
+        <v>200</v>
+      </c>
+      <c r="C198" t="s">
+        <v>215</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B199">
+        <v>201</v>
+      </c>
+      <c r="C199" t="s">
+        <v>215</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B200">
+        <v>202</v>
+      </c>
+      <c r="C200" t="s">
+        <v>215</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B201">
+        <v>203</v>
+      </c>
+      <c r="C201" t="s">
+        <v>215</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B202">
+        <v>204</v>
+      </c>
+      <c r="C202" t="s">
+        <v>215</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B203">
+        <v>205</v>
+      </c>
+      <c r="C203" t="s">
+        <v>8</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B204">
+        <v>206</v>
+      </c>
+      <c r="C204" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B205">
+        <v>207</v>
+      </c>
+      <c r="C205" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B206">
+        <v>208</v>
+      </c>
+      <c r="C206" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B207">
+        <v>209</v>
+      </c>
+      <c r="C207" t="s">
+        <v>8</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B208">
+        <v>210</v>
+      </c>
+      <c r="C208" t="s">
+        <v>8</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B209">
+        <v>211</v>
+      </c>
+      <c r="C209" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="E209" s="8" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B210">
+        <v>212</v>
+      </c>
+      <c r="C210" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E210" s="8" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B211">
+        <v>213</v>
+      </c>
+      <c r="C211" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B212">
+        <v>214</v>
+      </c>
+      <c r="E212" s="25"/>
+    </row>
+    <row r="213" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B213">
+        <v>215</v>
+      </c>
+      <c r="E213" s="25"/>
+    </row>
+    <row r="214" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B214">
+        <v>216</v>
+      </c>
+      <c r="E214" s="27"/>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B215">
+        <v>217</v>
+      </c>
+      <c r="E215" s="27"/>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B216">
+        <v>218</v>
+      </c>
+      <c r="E216" s="25"/>
+    </row>
+    <row r="217" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B217">
+        <v>219</v>
+      </c>
+      <c r="E217" s="26"/>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B218">
+        <v>220</v>
+      </c>
+      <c r="E218" s="25"/>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B219">
+        <v>221</v>
+      </c>
+      <c r="E219" s="25"/>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B220">
+        <v>222</v>
+      </c>
+      <c r="E220" s="25"/>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B221">
+        <v>223</v>
+      </c>
+      <c r="E221" s="25"/>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B222">
+        <v>224</v>
+      </c>
+      <c r="E222" s="25"/>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B223">
+        <v>225</v>
+      </c>
+      <c r="E223" s="25"/>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B224">
+        <v>226</v>
+      </c>
+      <c r="E224" s="25"/>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B225">
+        <v>227</v>
+      </c>
+      <c r="E225" s="25"/>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B226">
+        <v>228</v>
+      </c>
+      <c r="E226" s="25"/>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B227">
+        <v>229</v>
+      </c>
+      <c r="E227" s="25"/>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B228">
+        <v>230</v>
+      </c>
+      <c r="E228" s="25"/>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B229">
+        <v>231</v>
+      </c>
+      <c r="E229" s="25"/>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B230">
+        <v>232</v>
+      </c>
+      <c r="E230" s="25"/>
+    </row>
+    <row r="231" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B231">
+        <v>233</v>
+      </c>
+      <c r="E231" s="25"/>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B232">
+        <v>234</v>
+      </c>
+      <c r="E232" s="25"/>
+    </row>
+    <row r="233" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B233">
+        <v>235</v>
+      </c>
+      <c r="E233" s="25"/>
+    </row>
+    <row r="234" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B234">
+        <v>236</v>
+      </c>
+      <c r="E234" s="25"/>
+    </row>
+    <row r="235" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B235">
+        <v>237</v>
+      </c>
+      <c r="E235" s="25"/>
+    </row>
+    <row r="236" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B236">
+        <v>238</v>
+      </c>
+      <c r="E236" s="25"/>
+    </row>
+    <row r="237" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B237">
+        <v>239</v>
+      </c>
+      <c r="E237" s="25"/>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B238">
+        <v>240</v>
+      </c>
+      <c r="E238" s="25"/>
+    </row>
+    <row r="239" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B239">
+        <v>241</v>
+      </c>
+      <c r="E239" s="25"/>
+    </row>
+    <row r="240" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B240">
+        <v>242</v>
+      </c>
+      <c r="E240" s="25"/>
+    </row>
+    <row r="241" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B241">
+        <v>243</v>
+      </c>
+      <c r="E241" s="27"/>
+    </row>
+    <row r="242" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B242">
+        <v>244</v>
+      </c>
+      <c r="E242" s="27"/>
+    </row>
+    <row r="243" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B243">
+        <v>245</v>
+      </c>
+      <c r="E243" s="25"/>
+    </row>
+    <row r="244" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B244">
+        <v>246</v>
+      </c>
+      <c r="E244" s="26"/>
+    </row>
+    <row r="245" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B245">
+        <v>247</v>
+      </c>
+      <c r="E245" s="25"/>
+    </row>
+    <row r="246" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B246">
+        <v>248</v>
+      </c>
+      <c r="E246" s="25"/>
+    </row>
+    <row r="247" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B247">
+        <v>249</v>
+      </c>
+      <c r="E247" s="25"/>
+    </row>
+    <row r="248" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B248">
+        <v>250</v>
+      </c>
+      <c r="E248" s="25"/>
+    </row>
+    <row r="249" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B249">
+        <v>251</v>
+      </c>
+      <c r="E249" s="25"/>
+    </row>
+    <row r="250" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B250">
+        <v>252</v>
+      </c>
+      <c r="E250" s="25"/>
+    </row>
+    <row r="251" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B251">
+        <v>253</v>
+      </c>
+      <c r="E251" s="25"/>
+    </row>
+    <row r="252" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B252">
+        <v>254</v>
+      </c>
+      <c r="E252" s="25"/>
+    </row>
+    <row r="253" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B253">
+        <v>255</v>
+      </c>
+      <c r="E253" s="25"/>
+    </row>
+    <row r="254" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B254">
+        <v>256</v>
+      </c>
+      <c r="E254" s="25"/>
+    </row>
+    <row r="255" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B255">
+        <v>257</v>
+      </c>
+      <c r="E255" s="25"/>
+    </row>
+    <row r="256" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B256">
+        <v>258</v>
+      </c>
+      <c r="E256" s="25"/>
+    </row>
+    <row r="257" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B257">
+        <v>259</v>
+      </c>
+      <c r="E257" s="25"/>
+    </row>
+    <row r="258" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B258">
+        <v>260</v>
+      </c>
+      <c r="E258" s="25"/>
+    </row>
+    <row r="259" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B259">
+        <v>261</v>
+      </c>
+      <c r="E259" s="25"/>
+    </row>
+    <row r="260" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B260">
+        <v>262</v>
+      </c>
+      <c r="E260" s="25"/>
+    </row>
+    <row r="261" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B261">
+        <v>263</v>
+      </c>
+      <c r="E261" s="25"/>
+    </row>
+    <row r="262" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B262">
+        <v>264</v>
+      </c>
+      <c r="E262" s="25"/>
+    </row>
+    <row r="263" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B263">
+        <v>265</v>
+      </c>
+      <c r="E263" s="25"/>
+    </row>
+    <row r="264" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B264">
+        <v>266</v>
+      </c>
+      <c r="E264" s="25"/>
+    </row>
+    <row r="265" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B265">
+        <v>267</v>
+      </c>
+      <c r="E265" s="25"/>
+    </row>
+    <row r="266" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B266">
+        <v>268</v>
+      </c>
+      <c r="E266" s="25"/>
+    </row>
+    <row r="267" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B267">
+        <v>269</v>
+      </c>
+      <c r="E267" s="25"/>
+    </row>
+    <row r="268" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B268">
+        <v>270</v>
+      </c>
+      <c r="E268" s="27"/>
+    </row>
+    <row r="269" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B269">
+        <v>271</v>
+      </c>
+      <c r="E269" s="27"/>
+    </row>
+    <row r="270" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B270">
+        <v>272</v>
+      </c>
+      <c r="E270" s="25"/>
+    </row>
+    <row r="271" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B271">
+        <v>273</v>
+      </c>
+      <c r="E271" s="26"/>
+    </row>
+    <row r="272" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B272">
+        <v>274</v>
+      </c>
+      <c r="E272" s="25"/>
+    </row>
+    <row r="273" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B273">
+        <v>275</v>
+      </c>
+      <c r="E273" s="25"/>
+    </row>
+    <row r="274" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B274">
+        <v>276</v>
+      </c>
+      <c r="E274" s="25"/>
+    </row>
+    <row r="275" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B275">
+        <v>277</v>
+      </c>
+      <c r="E275" s="25"/>
+    </row>
+    <row r="276" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B276">
+        <v>278</v>
+      </c>
+      <c r="E276" s="25"/>
+    </row>
+    <row r="277" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B277">
+        <v>279</v>
+      </c>
+      <c r="E277" s="25"/>
+    </row>
+    <row r="278" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B278">
+        <v>280</v>
+      </c>
+      <c r="E278" s="25"/>
+    </row>
+    <row r="279" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B279">
+        <v>281</v>
+      </c>
+      <c r="E279" s="25"/>
+    </row>
+    <row r="280" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B280">
+        <v>282</v>
+      </c>
+      <c r="E280" s="25"/>
+    </row>
+    <row r="281" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B281">
+        <v>283</v>
+      </c>
+      <c r="E281" s="25"/>
+    </row>
+    <row r="282" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B282">
+        <v>284</v>
+      </c>
+      <c r="E282" s="25"/>
+    </row>
+    <row r="283" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B283">
+        <v>285</v>
+      </c>
+      <c r="E283" s="25"/>
+    </row>
+    <row r="284" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B284">
+        <v>286</v>
+      </c>
+      <c r="E284" s="25"/>
+    </row>
+    <row r="285" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B285">
+        <v>287</v>
+      </c>
+      <c r="E285" s="25"/>
+    </row>
+    <row r="286" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B286">
+        <v>288</v>
+      </c>
+      <c r="E286" s="25"/>
+    </row>
+    <row r="287" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B287">
+        <v>289</v>
+      </c>
+      <c r="E287" s="25"/>
+    </row>
+    <row r="288" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E288" s="25"/>
+    </row>
+    <row r="290" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="E290" s="25"/>
+    </row>
+    <row r="291" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="E291" s="25"/>
+    </row>
+    <row r="294" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D294" s="25"/>
+      <c r="E294" s="25"/>
+    </row>
+    <row r="295" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D295" s="25"/>
+      <c r="E295" s="24"/>
+    </row>
+    <row r="296" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="E296" s="28"/>
+    </row>
+    <row r="297" spans="4:5" ht="22" x14ac:dyDescent="0.35">
+      <c r="E297" s="29"/>
+    </row>
+    <row r="1972" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B1972">
+        <v>163</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="D26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="D41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="D42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="D43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="D44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="D45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="D46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="D47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="D49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="D50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="D51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="D54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="D57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D191" r:id="rId1" xr:uid="{CFFFF2DC-D421-4D0E-9212-0F6A995F7DD6}"/>
+    <hyperlink ref="D190" r:id="rId2" xr:uid="{01778D0D-B1DB-480D-AC18-55B0FC59F262}"/>
+    <hyperlink ref="D189" r:id="rId3" xr:uid="{B9302863-C0B5-4199-946D-57A70FF237B6}"/>
+    <hyperlink ref="D188" r:id="rId4" xr:uid="{DBC304CB-488D-423B-BE5F-C4199EB7340D}"/>
+    <hyperlink ref="D187" r:id="rId5" xr:uid="{45F6019F-32E3-486D-A5BB-71F1D79C6E54}"/>
+    <hyperlink ref="D186" r:id="rId6" xr:uid="{2AC61109-74B8-4765-999C-37CBAACA5B3B}"/>
+    <hyperlink ref="D185" r:id="rId7" xr:uid="{77EC23EF-260E-455D-8E7C-B6028D288CFF}"/>
+    <hyperlink ref="D182" r:id="rId8" xr:uid="{27258975-DB48-4F92-A31B-110E491A5757}"/>
+    <hyperlink ref="D179" r:id="rId9" xr:uid="{57933E71-4E04-41CB-A331-3E17098E9D76}"/>
+    <hyperlink ref="D181" r:id="rId10" xr:uid="{F4C3E4C6-3EF1-4B09-81B3-B9AA68CA76D8}"/>
+    <hyperlink ref="D183" r:id="rId11" xr:uid="{F8C23F9D-1B11-4028-94B3-D89CA6FD5CD5}"/>
+    <hyperlink ref="D184" r:id="rId12" xr:uid="{DE118D8C-9084-489B-9D7C-F8E21736F36B}"/>
+    <hyperlink ref="D180" r:id="rId13" xr:uid="{DB96D8CF-6671-4E79-9587-4DD8D2D64198}"/>
+    <hyperlink ref="D178" r:id="rId14" xr:uid="{C39C1533-FA62-44E4-8FDE-E2DD3A24C916}"/>
+    <hyperlink ref="D177" r:id="rId15" xr:uid="{E3ED0536-D48B-4949-A006-C36972C5B159}"/>
+    <hyperlink ref="D165" r:id="rId16" xr:uid="{11143684-8ACE-4743-9513-78EF7BADD26D}"/>
+    <hyperlink ref="D166" r:id="rId17" xr:uid="{F690BA2C-9EC4-40EA-86AE-F79C4DE0BEF7}"/>
+    <hyperlink ref="D167" r:id="rId18" xr:uid="{3413C4EB-7D2F-4D9F-9AD6-233A8F2D13E3}"/>
+    <hyperlink ref="D168" r:id="rId19" xr:uid="{81785379-F352-4F27-B2CF-8DA363EFEF0A}"/>
+    <hyperlink ref="D169" r:id="rId20" xr:uid="{4340214D-547D-4B16-AC7F-C9781B2A7D2E}"/>
+    <hyperlink ref="D170" r:id="rId21" xr:uid="{528CB70E-4E9B-4309-8FB9-7C49BD0F6BC3}"/>
+    <hyperlink ref="D171" r:id="rId22" xr:uid="{65678029-7B7F-4138-8198-6A7EA6E83C77}"/>
+    <hyperlink ref="D173" r:id="rId23" xr:uid="{E2143BB4-3EB0-48EA-9A38-A784B6EC8F87}"/>
+    <hyperlink ref="D172" r:id="rId24" xr:uid="{514E2A68-9F69-4F68-8263-7644324A8C76}"/>
+    <hyperlink ref="D174" r:id="rId25" xr:uid="{DF24CCFA-081C-45BC-8533-5FDA4DDDA9DF}"/>
+    <hyperlink ref="D175" r:id="rId26" xr:uid="{9975BC69-DF68-4181-AE8C-A551090D97E2}"/>
+    <hyperlink ref="D176" r:id="rId27" xr:uid="{D2048B28-BFF4-42C1-AB54-F860D9CC39C1}"/>
+    <hyperlink ref="D158" r:id="rId28" xr:uid="{6229870A-E2BF-4F5C-8BDE-F88F1E0B1AB9}"/>
+    <hyperlink ref="D159" r:id="rId29" xr:uid="{186BD832-9F3D-49EA-97F2-8BF86FEC2A35}"/>
+    <hyperlink ref="D160" r:id="rId30" xr:uid="{EDDD7818-B33F-443B-8415-CEA961F08147}"/>
+    <hyperlink ref="D161" r:id="rId31" xr:uid="{C89FA074-94A8-4ABC-A234-9A434BC3899E}"/>
+    <hyperlink ref="D162" r:id="rId32" xr:uid="{19360AB6-4406-4BB7-8A83-EC5BB16F4E37}"/>
+    <hyperlink ref="D163" r:id="rId33" xr:uid="{30D13A12-999B-4FC9-A0DC-EA1CBECEBFC8}"/>
+    <hyperlink ref="D164" r:id="rId34" xr:uid="{34BF1F92-5181-424E-BC40-36C507FB92D5}"/>
+    <hyperlink ref="D154" r:id="rId35" xr:uid="{2A937861-C332-455B-92C0-17D1EF515E80}"/>
+    <hyperlink ref="D157" r:id="rId36" xr:uid="{DCE91B0E-8B9E-4E24-BE18-10F3A5EB6C56}"/>
+    <hyperlink ref="D156" r:id="rId37" xr:uid="{E72D43A9-7FE8-4F78-9352-F6FDE58C50F1}"/>
+    <hyperlink ref="D155" r:id="rId38" xr:uid="{4CE9D94F-0B5D-4AF6-A9A8-D1A656B1C64E}"/>
+    <hyperlink ref="D153" r:id="rId39" xr:uid="{2342A86E-78AF-4833-9CA0-42CB060F7ADA}"/>
+    <hyperlink ref="D152" r:id="rId40" xr:uid="{B92B52F4-41E4-4017-8E04-50E572957723}"/>
+    <hyperlink ref="D151" r:id="rId41" xr:uid="{1D3E3A6F-8A4C-4345-AE5C-DD6455553F0E}"/>
+    <hyperlink ref="D150" r:id="rId42" xr:uid="{45720C7C-5D13-421D-BAE9-75B1E7D6FD6A}"/>
+    <hyperlink ref="D149" r:id="rId43" xr:uid="{5D11D4C5-B971-4C2F-9240-7F2ED270B661}"/>
+    <hyperlink ref="D148" r:id="rId44" xr:uid="{FEDA49B7-54E5-4C54-9A0F-1347C6B2B1AF}"/>
+    <hyperlink ref="D141" r:id="rId45" xr:uid="{1C363057-3C6C-48BE-A4F7-0A694CD97BC9}"/>
+    <hyperlink ref="D142" r:id="rId46" xr:uid="{4BBA221E-3538-4F85-A4EB-27D9D406992E}"/>
+    <hyperlink ref="D143" r:id="rId47" xr:uid="{BA35E436-6089-42C2-B729-86D8ED489D4B}"/>
+    <hyperlink ref="D144" r:id="rId48" xr:uid="{11A5CF90-B54E-4772-940D-B8DDDD22ABC7}"/>
+    <hyperlink ref="D145" r:id="rId49" xr:uid="{D0F5BFB3-5267-4012-A966-133A63FB8C05}"/>
+    <hyperlink ref="D146" r:id="rId50" xr:uid="{FA43C216-EBC4-457D-AEA6-1C9298BBA7BE}"/>
+    <hyperlink ref="D147" r:id="rId51" xr:uid="{01C77430-7F78-4905-8851-1B106736AADF}"/>
+    <hyperlink ref="D140" r:id="rId52" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D139" r:id="rId53" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D138" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D137" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D136" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D135" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D134" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D133" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D132" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D131" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D130" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D129" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D128" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D127" r:id="rId65" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D126" r:id="rId66" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D125" r:id="rId67" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D124" r:id="rId68" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D123" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D122" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D121" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D120" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D119" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D118" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D117" r:id="rId75" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D116" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D115" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D114" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D113" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D112" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D111" r:id="rId81" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D110" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D109" r:id="rId83" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D108" r:id="rId84" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D107" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D106" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D105" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D104" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D103" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D102" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D101" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D100" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D99" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D98" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D96" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D95" r:id="rId97" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D94" r:id="rId98" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D93" r:id="rId99" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D92" r:id="rId100" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D91" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D90" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D89" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D88" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D87" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D86" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D85" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D84" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D83" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D82" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D81" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D80" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D79" r:id="rId113" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D78" r:id="rId114" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D77" r:id="rId115" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D76" r:id="rId116" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D75" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D74" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D73" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D72" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D71" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D70" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D69" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D68" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D67" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D66" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D65" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D64" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D63" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D62" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D61" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="D60" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D59" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="D58" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="D57" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D56" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="D55" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D54" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="D53" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="D52" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D51" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D50" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="D49" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="D48" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="D47" r:id="rId145" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D46" r:id="rId146" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="D45" r:id="rId147" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="D44" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="D43" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="D42" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="D41" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="D40" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="D39" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="D38" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="D37" r:id="rId155" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="D36" r:id="rId156" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="D35" r:id="rId157" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="D34" r:id="rId158" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="D33" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="D32" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="D31" r:id="rId161" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D30" r:id="rId162" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="D29" r:id="rId163" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="D28" r:id="rId164" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D27" r:id="rId165" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="D26" r:id="rId166" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="D25" r:id="rId167" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="D24" r:id="rId168" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="D23" r:id="rId169" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="D22" r:id="rId170" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="D21" r:id="rId171" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D20" r:id="rId172" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="D19" r:id="rId173" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D18" r:id="rId174" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="D17" r:id="rId175" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="D16" r:id="rId176" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="D15" r:id="rId177" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="D14" r:id="rId178" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D13" r:id="rId179" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="D12" r:id="rId180" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="D11" r:id="rId181" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="D10" r:id="rId182" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D9" r:id="rId183" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D8" r:id="rId184" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D7" r:id="rId185" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D6" r:id="rId186" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D5" r:id="rId187" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D4" r:id="rId188" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D3" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D2" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D192" r:id="rId191" xr:uid="{03A3D1C7-0B5A-4304-8534-E4818E3B2F0C}"/>
+    <hyperlink ref="D193" r:id="rId192" xr:uid="{49B23470-2B21-4F35-882B-4B88F8B8F247}"/>
+    <hyperlink ref="D195" r:id="rId193" xr:uid="{E505664C-1B1B-4E51-8CD7-6F7D28CE4906}"/>
+    <hyperlink ref="D194" r:id="rId194" xr:uid="{C695E934-1325-419E-A371-A1F9D6BC7895}"/>
+    <hyperlink ref="D196" r:id="rId195" xr:uid="{1E1C5FE9-B576-4CE4-BF18-B75EE0D1F17E}"/>
+    <hyperlink ref="D197" r:id="rId196" xr:uid="{CE3B27B4-A2CB-486A-B515-4C2D597FEFB3}"/>
+    <hyperlink ref="D198" r:id="rId197" xr:uid="{D5481884-6230-4128-9F71-42454249BD7A}"/>
+    <hyperlink ref="D199" r:id="rId198" xr:uid="{65D95D72-19F4-4F71-A7B5-BB738AF49015}"/>
+    <hyperlink ref="D201" r:id="rId199" xr:uid="{5BCD670A-337E-4F25-B6B9-A5A1804832B9}"/>
+    <hyperlink ref="D200" r:id="rId200" xr:uid="{D2A807ED-657E-4420-A256-F5FE13A942D2}"/>
+    <hyperlink ref="D202" r:id="rId201" xr:uid="{81650AFE-C99D-4413-B3C7-5F812D9495E1}"/>
+    <hyperlink ref="D203" r:id="rId202" xr:uid="{0082804D-A559-443C-BA72-D4DDC7282821}"/>
+    <hyperlink ref="D204" r:id="rId203" xr:uid="{C7902020-0F8F-4ABF-95F8-37F9C3CE5B7A}"/>
+    <hyperlink ref="D206" r:id="rId204" xr:uid="{7102A362-7E98-4356-A773-1AAB1182AFA0}"/>
+    <hyperlink ref="D207" r:id="rId205" xr:uid="{DC3559C8-E5F4-4735-AE65-FF11AEEB3D6E}"/>
+    <hyperlink ref="D208" r:id="rId206" xr:uid="{216FBC87-D581-4BE8-ABF2-FB0EC4BC1073}"/>
+    <hyperlink ref="D209" r:id="rId207" xr:uid="{398F5E2A-33AF-4DE0-A5CA-3C1943B83E4E}"/>
+    <hyperlink ref="D210" r:id="rId208" xr:uid="{5F12E7F7-042B-47B3-A9B3-7A88C8CF2AEC}"/>
+    <hyperlink ref="D211" r:id="rId209" xr:uid="{D5809BD0-8A04-4C6A-99C0-99F54DFB26A1}"/>
+    <hyperlink ref="D205" r:id="rId210" xr:uid="{B1939160-4325-4E98-A9D5-E8A2BDC9E7B9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId211"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>356</v>
       </c>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/Desktop/OfertasTec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_F9695CA42DBBB00D7708F6DF240B1251B879C294" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6D98F19-8F14-412B-AD16-EB05E3675314}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_F9695CA42DBBB00D7708F6DF240B1251B879C294" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AB0688C-7B48-48BA-BC41-00E7B9218022}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,7 +1792,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1873,29 +1873,13 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7499,19 +7483,19 @@
       <c r="E253" s="20"/>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B254" s="29"/>
+      <c r="B254" s="58"/>
       <c r="E254" s="20"/>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B255" s="29"/>
+      <c r="B255" s="58"/>
       <c r="E255" s="20"/>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B256" s="29"/>
+      <c r="B256" s="58"/>
       <c r="E256" s="20"/>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B257" s="29"/>
+      <c r="B257" s="58"/>
       <c r="E257" s="20"/>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.25">
@@ -7636,6 +7620,7 @@
       <c r="E1974"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I253" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/Desktop/OfertasTec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_AAE99CEC2896977288487518AB0B1651B879BB5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5C98F01-509B-46DF-A0FE-F6C415968AC0}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_AAE99CEC2896977288487518AB0B1651B879BB5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B3FAF33-F3FF-4810-A5F4-7472D876727C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Renomear" sheetId="1" r:id="rId1"/>
@@ -1792,7 +1792,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1875,7 +1875,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1892,6 +1891,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2179,6 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA1974"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2222,7 +2226,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="29">
         <v>1</v>
@@ -2245,7 +2249,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="29">
         <v>2</v>
@@ -2268,7 +2272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="29">
         <v>3</v>
@@ -2291,7 +2295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="55">
         <v>4</v>
@@ -2312,7 +2316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="29">
         <v>5</v>
@@ -2335,7 +2339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="29">
         <v>6</v>
@@ -2358,7 +2362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="29">
         <v>7</v>
@@ -2381,7 +2385,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="29">
         <v>8</v>
@@ -2404,7 +2408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="29">
         <v>9</v>
@@ -2427,7 +2431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="55">
         <v>10</v>
@@ -2452,7 +2456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="29">
         <v>11</v>
@@ -2475,7 +2479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="29">
         <v>12</v>
@@ -2498,7 +2502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="29">
         <v>13</v>
@@ -2521,7 +2525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="29">
         <v>14</v>
@@ -2544,7 +2548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="55">
         <v>15</v>
@@ -2567,7 +2571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="56">
         <v>16</v>
@@ -2592,7 +2596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="29">
         <v>17</v>
@@ -2615,7 +2619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="29">
         <v>18</v>
@@ -2638,7 +2642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="55">
         <v>19</v>
@@ -2657,7 +2661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="29">
         <v>20</v>
@@ -2680,7 +2684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="55">
         <v>21</v>
@@ -2699,7 +2703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="29">
         <v>22</v>
@@ -2722,7 +2726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="55">
         <v>23</v>
@@ -2745,7 +2749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="55">
         <v>24</v>
@@ -2764,7 +2768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="29">
         <v>25</v>
@@ -2787,7 +2791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="29">
         <v>26</v>
@@ -2810,7 +2814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="29">
         <v>27</v>
@@ -2833,7 +2837,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="47"/>
       <c r="B29" s="48">
         <v>28</v>
@@ -2856,7 +2860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="29">
         <v>29</v>
@@ -2879,7 +2883,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="29">
         <v>30</v>
@@ -2902,7 +2906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="56">
         <v>31</v>
@@ -2927,7 +2931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="55">
         <v>32</v>
@@ -2950,7 +2954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="29">
         <v>33</v>
@@ -2973,7 +2977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="47"/>
       <c r="B35" s="48">
         <v>34</v>
@@ -2996,7 +3000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="29">
         <v>35</v>
@@ -3019,7 +3023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="29">
         <v>36</v>
@@ -3042,7 +3046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="29">
         <v>37</v>
@@ -3065,7 +3069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="29">
         <v>38</v>
@@ -3088,7 +3092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="29">
         <v>39</v>
@@ -3111,7 +3115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="29">
         <v>40</v>
@@ -3134,7 +3138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="55">
         <v>41</v>
@@ -3153,7 +3157,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="29">
         <v>42</v>
@@ -3176,7 +3180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="55">
         <v>43</v>
@@ -3195,7 +3199,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="29">
         <v>44</v>
@@ -3218,7 +3222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="29">
         <v>45</v>
@@ -3241,7 +3245,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="55">
         <v>46</v>
@@ -3264,7 +3268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="29">
         <v>47</v>
@@ -3287,7 +3291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="55">
         <v>48</v>
@@ -3306,7 +3310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="29">
         <v>49</v>
@@ -3329,7 +3333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="29">
         <v>50</v>
@@ -3352,7 +3356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="29">
         <v>51</v>
@@ -3375,7 +3379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="29">
         <v>52</v>
@@ -3398,7 +3402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="29">
         <v>53</v>
@@ -3421,7 +3425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="29">
         <v>54</v>
@@ -3444,7 +3448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="29">
         <v>55</v>
@@ -3897,7 +3901,6 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="60"/>
       <c r="B76" s="37">
         <v>75</v>
       </c>
@@ -4189,7 +4192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="29">
         <v>88</v>
@@ -4212,7 +4215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="29">
         <v>89</v>
@@ -4235,7 +4238,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" s="29">
         <v>90</v>
@@ -4258,7 +4261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="29">
         <v>91</v>
@@ -4281,7 +4284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="55">
         <v>92</v>
@@ -4300,7 +4303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="29">
         <v>93</v>
@@ -4323,7 +4326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" s="29">
         <v>94</v>
@@ -4346,7 +4349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="29">
         <v>95</v>
@@ -4369,7 +4372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="29">
         <v>96</v>
@@ -4392,7 +4395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="55">
         <v>97</v>
@@ -4411,7 +4414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="55">
         <v>98</v>
@@ -4430,7 +4433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="29">
         <v>99</v>
@@ -4453,7 +4456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="B101" s="29">
         <v>100</v>
@@ -4476,7 +4479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="B102" s="29">
         <v>101</v>
@@ -4499,7 +4502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="55">
         <v>102</v>
@@ -4522,7 +4525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="29">
         <v>103</v>
@@ -4545,7 +4548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="55">
         <v>104</v>
@@ -4564,7 +4567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="B106" s="29">
         <v>105</v>
@@ -4587,7 +4590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="B107" s="29">
         <v>106</v>
@@ -4610,7 +4613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" s="29">
         <v>107</v>
@@ -4633,7 +4636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="55">
         <v>108</v>
@@ -4652,7 +4655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="B110" s="29">
         <v>109</v>
@@ -4675,7 +4678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="B111" s="29">
         <v>110</v>
@@ -4698,7 +4701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="16"/>
       <c r="B112" s="29">
         <v>111</v>
@@ -4721,7 +4724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9"/>
       <c r="B113" s="56">
         <v>112</v>
@@ -4740,7 +4743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="B114" s="29">
         <v>113</v>
@@ -4763,7 +4766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="B115" s="29">
         <v>114</v>
@@ -4786,7 +4789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16"/>
       <c r="B116" s="29">
         <v>115</v>
@@ -4809,7 +4812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="16"/>
       <c r="B117" s="29">
         <v>116</v>
@@ -4832,7 +4835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="55">
         <v>117</v>
@@ -4851,7 +4854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" s="29">
         <v>118</v>
@@ -4874,7 +4877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="16"/>
       <c r="B120" s="29">
         <v>119</v>
@@ -4897,7 +4900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="16"/>
       <c r="B121" s="29">
         <v>120</v>
@@ -4920,7 +4923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="55">
         <v>121</v>
@@ -4939,7 +4942,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="B123" s="29">
         <v>122</v>
@@ -4962,7 +4965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="16"/>
       <c r="B124" s="29">
         <v>123</v>
@@ -4985,7 +4988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="29">
         <v>124</v>
@@ -5008,7 +5011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" s="29">
         <v>125</v>
@@ -5031,7 +5034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" s="29">
         <v>126</v>
@@ -5054,7 +5057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="16"/>
       <c r="B128" s="29">
         <v>127</v>
@@ -5077,7 +5080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="16"/>
       <c r="B129" s="29">
         <v>128</v>
@@ -5100,7 +5103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" s="29">
         <v>129</v>
@@ -5123,7 +5126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" s="29">
         <v>130</v>
@@ -5146,7 +5149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="16"/>
       <c r="B132" s="29">
         <v>131</v>
@@ -5169,7 +5172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="16"/>
       <c r="B133" s="29">
         <v>132</v>
@@ -5192,7 +5195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" s="29">
         <v>133</v>
@@ -5215,7 +5218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="B135" s="29">
         <v>134</v>
@@ -5238,7 +5241,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="16"/>
       <c r="B136" s="29">
         <v>135</v>
@@ -5261,7 +5264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="16"/>
       <c r="B137" s="29">
         <v>136</v>
@@ -5284,7 +5287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="B138" s="33">
         <v>137</v>
@@ -5309,7 +5312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" s="29">
         <v>138</v>
@@ -5332,7 +5335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="16"/>
       <c r="B140" s="29">
         <v>139</v>
@@ -5355,7 +5358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:9" s="57" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16"/>
       <c r="B141" s="29">
         <v>140</v>
@@ -5375,7 +5378,7 @@
       </c>
       <c r="H141" s="29"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" s="29">
         <v>141</v>
@@ -5395,7 +5398,7 @@
       </c>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" s="29">
         <v>142</v>
@@ -5415,7 +5418,7 @@
       </c>
       <c r="H143" s="29"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="16"/>
       <c r="B144" s="29">
         <v>143</v>
@@ -5435,7 +5438,7 @@
       </c>
       <c r="H144" s="29"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9"/>
       <c r="B145" s="56">
         <v>144</v>
@@ -5457,7 +5460,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" s="29">
         <v>145</v>
@@ -5477,7 +5480,7 @@
       </c>
       <c r="H146" s="29"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" s="29">
         <v>146</v>
@@ -5497,7 +5500,7 @@
       </c>
       <c r="H147" s="29"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="16"/>
       <c r="B148" s="29">
         <v>147</v>
@@ -5517,7 +5520,7 @@
       </c>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="16"/>
       <c r="B149" s="29">
         <v>148</v>
@@ -5537,7 +5540,7 @@
       </c>
       <c r="H149" s="29"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9"/>
       <c r="B150" s="56">
         <v>149</v>
@@ -5559,7 +5562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:9" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B151" s="48">
         <v>150</v>
       </c>
@@ -5578,7 +5581,7 @@
       </c>
       <c r="H151" s="48"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="16"/>
       <c r="B152" s="29">
         <v>151</v>
@@ -5598,7 +5601,7 @@
       </c>
       <c r="H152" s="29"/>
     </row>
-    <row r="153" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="16"/>
       <c r="B153" s="29">
         <v>152</v>
@@ -5618,7 +5621,7 @@
       </c>
       <c r="H153" s="29"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" s="29">
         <v>153</v>
@@ -5638,7 +5641,7 @@
       </c>
       <c r="H154" s="29"/>
     </row>
-    <row r="155" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9"/>
       <c r="B155" s="56">
         <v>154</v>
@@ -5660,7 +5663,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="B156" s="55">
         <v>155</v>
@@ -5679,7 +5682,7 @@
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16"/>
       <c r="B157" s="29">
         <v>156</v>
@@ -5697,7 +5700,7 @@
       <c r="G157" s="29"/>
       <c r="H157" s="29"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B158" s="29">
         <v>157</v>
       </c>
@@ -5714,7 +5717,7 @@
       <c r="G158" s="29"/>
       <c r="H158" s="29"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B159" s="56">
         <v>158</v>
       </c>
@@ -5733,7 +5736,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B160" s="56">
         <v>159</v>
       </c>
@@ -5752,7 +5755,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B161" s="29">
         <v>160</v>
       </c>
@@ -5770,7 +5773,7 @@
       <c r="H161" s="31"/>
       <c r="I161" s="5"/>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B162" s="56">
         <v>161</v>
       </c>
@@ -5808,7 +5811,7 @@
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="B163" s="55">
         <v>162</v>
@@ -5845,7 +5848,7 @@
       <c r="Z163" s="5"/>
       <c r="AA163" s="5"/>
     </row>
-    <row r="164" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="26"/>
       <c r="B164" s="56">
         <v>163</v>
@@ -5884,7 +5887,7 @@
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
     </row>
-    <row r="165" spans="1:27" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B165" s="29">
         <v>164</v>
       </c>
@@ -5920,7 +5923,7 @@
       <c r="Z165" s="5"/>
       <c r="AA165" s="5"/>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B166" s="29">
         <v>165</v>
       </c>
@@ -5956,7 +5959,7 @@
       <c r="Z166" s="5"/>
       <c r="AA166" s="5"/>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B167" s="29">
         <v>166</v>
       </c>
@@ -5992,7 +5995,7 @@
       <c r="Z167" s="5"/>
       <c r="AA167" s="5"/>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B168" s="29">
         <v>167</v>
       </c>
@@ -6028,7 +6031,7 @@
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B169" s="56">
         <v>168</v>
       </c>
@@ -6066,7 +6069,7 @@
       <c r="Z169" s="5"/>
       <c r="AA169" s="5"/>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B170" s="29">
         <v>169</v>
       </c>
@@ -6102,7 +6105,7 @@
       <c r="Z170" s="5"/>
       <c r="AA170" s="5"/>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B171" s="29">
         <v>170</v>
       </c>
@@ -6138,7 +6141,7 @@
       <c r="Z171" s="5"/>
       <c r="AA171" s="5"/>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B172" s="56">
         <v>171</v>
       </c>
@@ -6176,7 +6179,7 @@
       <c r="Z172" s="5"/>
       <c r="AA172" s="5"/>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B173" s="56">
         <v>172</v>
       </c>
@@ -6214,7 +6217,7 @@
       <c r="Z173" s="5"/>
       <c r="AA173" s="5"/>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B174" s="55">
         <v>173</v>
       </c>
@@ -6252,7 +6255,7 @@
       <c r="Z174" s="5"/>
       <c r="AA174" s="5"/>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B175" s="29">
         <v>174</v>
       </c>
@@ -6288,7 +6291,7 @@
       <c r="Z175" s="5"/>
       <c r="AA175" s="5"/>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B176" s="29">
         <v>175</v>
       </c>
@@ -6324,7 +6327,7 @@
       <c r="Z176" s="5"/>
       <c r="AA176" s="5"/>
     </row>
-    <row r="177" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B177" s="29">
         <v>176</v>
       </c>
@@ -6360,7 +6363,7 @@
       <c r="Z177" s="5"/>
       <c r="AA177" s="5"/>
     </row>
-    <row r="178" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B178" s="29">
         <v>177</v>
       </c>
@@ -6396,7 +6399,7 @@
       <c r="Z178" s="5"/>
       <c r="AA178" s="5"/>
     </row>
-    <row r="179" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B179" s="29">
         <v>178</v>
       </c>
@@ -6432,7 +6435,7 @@
       <c r="Z179" s="5"/>
       <c r="AA179" s="5"/>
     </row>
-    <row r="180" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B180" s="56">
         <v>179</v>
       </c>
@@ -6470,7 +6473,7 @@
       <c r="Z180" s="5"/>
       <c r="AA180" s="5"/>
     </row>
-    <row r="181" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B181" s="29">
         <v>180</v>
       </c>
@@ -6506,7 +6509,7 @@
       <c r="Z181" s="5"/>
       <c r="AA181" s="5"/>
     </row>
-    <row r="182" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B182" s="29">
         <v>181</v>
       </c>
@@ -6542,7 +6545,7 @@
       <c r="Z182" s="5"/>
       <c r="AA182" s="5"/>
     </row>
-    <row r="183" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B183" s="29">
         <v>182</v>
       </c>
@@ -6578,7 +6581,7 @@
       <c r="Z183" s="5"/>
       <c r="AA183" s="5"/>
     </row>
-    <row r="184" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B184" s="29">
         <v>183</v>
       </c>
@@ -6614,7 +6617,7 @@
       <c r="Z184" s="5"/>
       <c r="AA184" s="5"/>
     </row>
-    <row r="185" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B185" s="29">
         <v>184</v>
       </c>
@@ -6650,7 +6653,7 @@
       <c r="Z185" s="5"/>
       <c r="AA185" s="5"/>
     </row>
-    <row r="186" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B186" s="29">
         <v>185</v>
       </c>
@@ -6686,7 +6689,7 @@
       <c r="Z186" s="5"/>
       <c r="AA186" s="5"/>
     </row>
-    <row r="187" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B187" s="29">
         <v>186</v>
       </c>
@@ -6722,7 +6725,7 @@
       <c r="Z187" s="5"/>
       <c r="AA187" s="5"/>
     </row>
-    <row r="188" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B188" s="29">
         <v>187</v>
       </c>
@@ -6758,7 +6761,7 @@
       <c r="Z188" s="5"/>
       <c r="AA188" s="5"/>
     </row>
-    <row r="189" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B189" s="29">
         <v>188</v>
       </c>
@@ -6794,7 +6797,7 @@
       <c r="Z189" s="5"/>
       <c r="AA189" s="5"/>
     </row>
-    <row r="190" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B190" s="29">
         <v>189</v>
       </c>
@@ -6830,7 +6833,7 @@
       <c r="Z190" s="5"/>
       <c r="AA190" s="5"/>
     </row>
-    <row r="191" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B191" s="29">
         <v>190</v>
       </c>
@@ -6866,7 +6869,7 @@
       <c r="Z191" s="5"/>
       <c r="AA191" s="5"/>
     </row>
-    <row r="192" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B192" s="29">
         <v>191</v>
       </c>
@@ -6901,7 +6904,7 @@
       <c r="Z192" s="5"/>
       <c r="AA192" s="5"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B193" s="29">
         <v>192</v>
       </c>
@@ -6918,7 +6921,7 @@
       <c r="G193" s="29"/>
       <c r="H193" s="29"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B194" s="56">
         <v>193</v>
       </c>
@@ -6937,7 +6940,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B195" s="29">
         <v>194</v>
       </c>
@@ -6954,7 +6957,7 @@
       <c r="G195" s="29"/>
       <c r="H195" s="29"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B196" s="29">
         <v>195</v>
       </c>
@@ -6971,7 +6974,7 @@
       <c r="G196" s="29"/>
       <c r="H196" s="29"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B197" s="29">
         <v>196</v>
       </c>
@@ -6988,7 +6991,7 @@
       <c r="G197" s="29"/>
       <c r="H197" s="29"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B198" s="29">
         <v>197</v>
       </c>
@@ -7005,7 +7008,7 @@
       <c r="G198" s="29"/>
       <c r="H198" s="29"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B199" s="29">
         <v>198</v>
       </c>
@@ -7022,7 +7025,7 @@
       <c r="G199" s="29"/>
       <c r="H199" s="29"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B200" s="29">
         <v>199</v>
       </c>
@@ -7039,7 +7042,7 @@
       <c r="G200" s="29"/>
       <c r="H200" s="29"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B201" s="56">
         <v>200</v>
       </c>
@@ -7058,7 +7061,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B202" s="29">
         <v>201</v>
       </c>
@@ -7075,8 +7078,7 @@
       <c r="G202" s="29"/>
       <c r="H202" s="29"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="60"/>
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B203" s="55">
         <v>202</v>
       </c>
@@ -7094,7 +7096,7 @@
       <c r="H203" s="55"/>
       <c r="I203" s="3"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="16"/>
       <c r="B204" s="29">
         <v>203</v>
@@ -7112,7 +7114,7 @@
       <c r="G204" s="29"/>
       <c r="H204" s="29"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="16"/>
       <c r="B205" s="29">
         <v>204</v>
@@ -7130,7 +7132,7 @@
       <c r="G205" s="29"/>
       <c r="H205" s="29"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="16"/>
       <c r="B206" s="29">
         <v>205</v>
@@ -7148,7 +7150,7 @@
       <c r="G206" s="29"/>
       <c r="H206" s="29"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="16"/>
       <c r="B207" s="29">
         <v>206</v>
@@ -7166,7 +7168,7 @@
       <c r="G207" s="29"/>
       <c r="H207" s="29"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="16"/>
       <c r="B208" s="29">
         <v>207</v>
@@ -7184,7 +7186,7 @@
       <c r="G208" s="29"/>
       <c r="H208" s="29"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="16"/>
       <c r="B209" s="56">
         <v>208</v>
@@ -7204,7 +7206,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="16"/>
       <c r="B210" s="29">
         <v>209</v>
@@ -7222,7 +7224,7 @@
       <c r="G210" s="29"/>
       <c r="H210" s="29"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="16"/>
       <c r="B211" s="29">
         <v>210</v>
@@ -7240,253 +7242,253 @@
       <c r="G211" s="29"/>
       <c r="H211" s="29"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B212" s="29">
         <v>211</v>
       </c>
       <c r="E212" s="20"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B213" s="29">
         <v>212</v>
       </c>
       <c r="E213" s="20"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B214" s="29">
         <v>213</v>
       </c>
       <c r="E214" s="22"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B215" s="29">
         <v>214</v>
       </c>
       <c r="E215" s="22"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B216" s="29">
         <v>215</v>
       </c>
       <c r="E216" s="20"/>
     </row>
-    <row r="217" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B217" s="29">
         <v>216</v>
       </c>
       <c r="E217" s="21"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B218" s="29">
         <v>217</v>
       </c>
       <c r="E218" s="20"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B219" s="29">
         <v>218</v>
       </c>
       <c r="E219" s="20"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B220" s="29">
         <v>219</v>
       </c>
       <c r="E220" s="20"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B221" s="29">
         <v>220</v>
       </c>
       <c r="E221" s="20"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B222" s="29">
         <v>221</v>
       </c>
       <c r="E222" s="20"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B223" s="29">
         <v>222</v>
       </c>
       <c r="E223" s="20"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B224" s="29">
         <v>223</v>
       </c>
       <c r="E224" s="20"/>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B225" s="29">
         <v>224</v>
       </c>
       <c r="E225" s="20"/>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B226" s="29">
         <v>225</v>
       </c>
       <c r="E226" s="20"/>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B227" s="29">
         <v>226</v>
       </c>
       <c r="E227" s="20"/>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B228" s="29">
         <v>227</v>
       </c>
       <c r="E228" s="20"/>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B229" s="29">
         <v>228</v>
       </c>
       <c r="E229" s="20"/>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B230" s="29">
         <v>229</v>
       </c>
       <c r="E230" s="20"/>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B231" s="29">
         <v>230</v>
       </c>
       <c r="E231" s="20"/>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B232" s="29">
         <v>231</v>
       </c>
       <c r="E232" s="20"/>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B233" s="29">
         <v>232</v>
       </c>
       <c r="E233" s="20"/>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B234" s="29">
         <v>233</v>
       </c>
       <c r="E234" s="20"/>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B235" s="29">
         <v>234</v>
       </c>
       <c r="E235" s="20"/>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B236" s="29">
         <v>235</v>
       </c>
       <c r="E236" s="20"/>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B237" s="29">
         <v>236</v>
       </c>
       <c r="E237" s="20"/>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B238" s="29">
         <v>237</v>
       </c>
       <c r="E238" s="20"/>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B239" s="29">
         <v>238</v>
       </c>
       <c r="E239" s="20"/>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B240" s="29">
         <v>239</v>
       </c>
       <c r="E240" s="20"/>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B241" s="29">
         <v>240</v>
       </c>
       <c r="E241" s="22"/>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B242" s="29">
         <v>241</v>
       </c>
       <c r="E242" s="22"/>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B243" s="29">
         <v>242</v>
       </c>
       <c r="E243" s="20"/>
     </row>
-    <row r="244" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:5" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B244" s="29">
         <v>243</v>
       </c>
       <c r="E244" s="21"/>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B245" s="29">
         <v>244</v>
       </c>
       <c r="E245" s="20"/>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B246" s="29">
         <v>245</v>
       </c>
       <c r="E246" s="20"/>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B247" s="29">
         <v>246</v>
       </c>
       <c r="E247" s="20"/>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B248" s="29">
         <v>247</v>
       </c>
       <c r="E248" s="20"/>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B249" s="29">
         <v>248</v>
       </c>
       <c r="E249" s="20"/>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B250" s="29">
         <v>249</v>
       </c>
       <c r="E250" s="20"/>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B251" s="29">
         <v>250</v>
       </c>
       <c r="E251" s="20"/>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B252" s="29">
         <v>251</v>
       </c>
       <c r="E252" s="20"/>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B253" s="29">
         <v>252</v>
       </c>
@@ -7624,7 +7626,15 @@
       <c r="D1974" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I253" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I253" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Teclado com fio"/>
+        <filter val="Teclado gamer com fio"/>
+        <filter val="Teclado sem fio"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/Desktop/OfertasTec/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\capta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_AAE99CEC2896977288487518AB0B1651B879BB5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B3FAF33-F3FF-4810-A5F4-7472D876727C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89D0BAA-3B10-4B36-BCAA-7441DE47A05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Renomear" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="511">
   <si>
     <t>Validação</t>
   </si>
@@ -626,6 +626,9 @@
     <t>https://meli.la/1ouDkYa</t>
   </si>
   <si>
+    <t>Teclado Gamer Magnético 8000hz Attack Shark Com Fio X68 He</t>
+  </si>
+  <si>
     <t>https://meli.la/2wUJ3fr</t>
   </si>
   <si>
@@ -887,7 +890,7 @@
     <t>TECHSTORE-QKZ</t>
   </si>
   <si>
-    <t>Fone gamer (headset)</t>
+    <t>Fone gamer (headset com fio)</t>
   </si>
   <si>
     <t>https://meli.la/1zm1HFa</t>
@@ -1289,7 +1292,7 @@
     <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 128gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
   </si>
   <si>
-    <t>Mouse pad pequeno</t>
+    <t>Mousepad simples</t>
   </si>
   <si>
     <t>https://meli.la/1Z5VJQ6</t>
@@ -1554,9 +1557,6 @@
   </si>
   <si>
     <t>Vou usar os dados pra atualizar o site automaticamente.</t>
-  </si>
-  <si>
-    <t>Teclado Gamer Magnético 8000hz Attack Shark Com Fio X68 He</t>
   </si>
 </sst>
 </file>
@@ -1893,10 +1893,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2182,7 +2178,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA1974"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2226,7 +2221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="29">
         <v>1</v>
@@ -2249,7 +2244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="29">
         <v>2</v>
@@ -2272,7 +2267,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="29">
         <v>3</v>
@@ -2295,7 +2290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="55">
         <v>4</v>
@@ -2316,7 +2311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="29">
         <v>5</v>
@@ -2339,7 +2334,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="29">
         <v>6</v>
@@ -2362,7 +2357,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="29">
         <v>7</v>
@@ -2385,7 +2380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="29">
         <v>8</v>
@@ -2408,7 +2403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="29">
         <v>9</v>
@@ -2431,7 +2426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="55">
         <v>10</v>
@@ -2456,7 +2451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="29">
         <v>11</v>
@@ -2479,7 +2474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="29">
         <v>12</v>
@@ -2502,7 +2497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="29">
         <v>13</v>
@@ -2525,7 +2520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15" s="29">
         <v>14</v>
@@ -2548,7 +2543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="55">
         <v>15</v>
@@ -2571,7 +2566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="56">
         <v>16</v>
@@ -2596,7 +2591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="29">
         <v>17</v>
@@ -2619,7 +2614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="29">
         <v>18</v>
@@ -2642,7 +2637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="55">
         <v>19</v>
@@ -2661,7 +2656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="29">
         <v>20</v>
@@ -2684,7 +2679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="55">
         <v>21</v>
@@ -2703,7 +2698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="29">
         <v>22</v>
@@ -2726,7 +2721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="55">
         <v>23</v>
@@ -2749,7 +2744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="55">
         <v>24</v>
@@ -2768,7 +2763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="29">
         <v>25</v>
@@ -2791,7 +2786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="29">
         <v>26</v>
@@ -2814,7 +2809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="29">
         <v>27</v>
@@ -2837,7 +2832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="47"/>
       <c r="B29" s="48">
         <v>28</v>
@@ -2860,7 +2855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="29">
         <v>29</v>
@@ -2883,7 +2878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="29">
         <v>30</v>
@@ -2906,7 +2901,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="56">
         <v>31</v>
@@ -2931,7 +2926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="55">
         <v>32</v>
@@ -2954,7 +2949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="29">
         <v>33</v>
@@ -2977,7 +2972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="47"/>
       <c r="B35" s="48">
         <v>34</v>
@@ -3000,7 +2995,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="29">
         <v>35</v>
@@ -3023,7 +3018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="29">
         <v>36</v>
@@ -3046,7 +3041,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="29">
         <v>37</v>
@@ -3069,7 +3064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="29">
         <v>38</v>
@@ -3092,7 +3087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="29">
         <v>39</v>
@@ -3115,7 +3110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="29">
         <v>40</v>
@@ -3138,7 +3133,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="55">
         <v>41</v>
@@ -3157,7 +3152,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="29">
         <v>42</v>
@@ -3180,7 +3175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="55">
         <v>43</v>
@@ -3199,7 +3194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="29">
         <v>44</v>
@@ -3222,7 +3217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="29">
         <v>45</v>
@@ -3245,7 +3240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="55">
         <v>46</v>
@@ -3268,7 +3263,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="29">
         <v>47</v>
@@ -3291,7 +3286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="55">
         <v>48</v>
@@ -3310,7 +3305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="29">
         <v>49</v>
@@ -3333,7 +3328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="29">
         <v>50</v>
@@ -3356,7 +3351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="29">
         <v>51</v>
@@ -3379,7 +3374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="29">
         <v>52</v>
@@ -3402,7 +3397,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="29">
         <v>53</v>
@@ -3425,7 +3420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="29">
         <v>54</v>
@@ -3448,7 +3443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="29">
         <v>55</v>
@@ -4020,7 +4015,7 @@
         <v>199</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>510</v>
+        <v>200</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -4038,14 +4033,14 @@
         <v>184</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F82" s="29"/>
       <c r="G82" s="32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H82" s="29"/>
       <c r="I82" t="s">
@@ -4061,14 +4056,14 @@
         <v>184</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F83" s="33"/>
       <c r="G83" s="36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H83" s="33" t="s">
         <v>35</v>
@@ -4086,14 +4081,14 @@
         <v>184</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F84" s="29"/>
       <c r="G84" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H84" s="29"/>
       <c r="I84" t="s">
@@ -4109,14 +4104,14 @@
         <v>184</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F85" s="29"/>
       <c r="G85" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H85" s="29"/>
       <c r="I85" t="s">
@@ -4132,10 +4127,10 @@
         <v>184</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F86" s="29"/>
       <c r="G86" s="32" t="s">
@@ -4155,10 +4150,10 @@
         <v>184</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F87" s="29"/>
       <c r="G87" s="32" t="s">
@@ -4178,122 +4173,122 @@
         <v>184</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F88" s="29"/>
       <c r="G88" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H88" s="29"/>
       <c r="I88" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="29">
         <v>88</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F89" s="29"/>
       <c r="G89" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H89" s="29"/>
       <c r="I89" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="29">
         <v>89</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F90" s="29"/>
       <c r="G90" s="32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H90" s="29"/>
       <c r="I90" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" s="29">
         <v>90</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F91" s="29"/>
       <c r="G91" s="32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H91" s="29"/>
       <c r="I91" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="29">
         <v>91</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F92" s="29"/>
       <c r="G92" s="32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H92" s="29"/>
       <c r="I92" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="55">
         <v>92</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="3"/>
@@ -4303,19 +4298,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="29">
         <v>93</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F94" s="29"/>
       <c r="G94" s="32" t="s">
@@ -4326,85 +4321,85 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" s="29">
         <v>94</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F95" s="29"/>
       <c r="G95" s="32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H95" s="29"/>
       <c r="I95" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="29">
         <v>95</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F96" s="29"/>
       <c r="G96" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H96" s="29"/>
       <c r="I96" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="29">
         <v>96</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F97" s="29"/>
       <c r="G97" s="32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H97" s="29"/>
       <c r="I97" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="55">
         <v>97</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="3"/>
@@ -4414,16 +4409,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="55">
         <v>98</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="3"/>
@@ -4433,131 +4428,131 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="29">
         <v>99</v>
       </c>
       <c r="C100" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F100" s="29"/>
       <c r="G100" s="32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H100" s="29"/>
       <c r="I100" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="B101" s="29">
         <v>100</v>
       </c>
       <c r="C101" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D101" s="30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F101" s="29"/>
       <c r="G101" s="32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H101" s="29"/>
       <c r="I101" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="B102" s="29">
         <v>101</v>
       </c>
       <c r="C102" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E102" s="31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F102" s="29"/>
       <c r="G102" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H102" s="29"/>
       <c r="I102" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="55">
         <v>102</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="29">
         <v>103</v>
       </c>
       <c r="C104" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E104" s="31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F104" s="29"/>
       <c r="G104" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H104" s="29"/>
       <c r="I104" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="55">
         <v>104</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="3"/>
@@ -4567,85 +4562,85 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="B106" s="29">
         <v>105</v>
       </c>
       <c r="C106" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E106" s="31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F106" s="29"/>
       <c r="G106" s="32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H106" s="29"/>
       <c r="I106" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="B107" s="29">
         <v>106</v>
       </c>
       <c r="C107" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F107" s="29"/>
       <c r="G107" s="32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H107" s="29"/>
       <c r="I107" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" s="29">
         <v>107</v>
       </c>
       <c r="C108" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E108" s="31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F108" s="29"/>
       <c r="G108" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H108" s="29"/>
       <c r="I108" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="55">
         <v>108</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="3"/>
@@ -4655,85 +4650,85 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="B110" s="29">
         <v>109</v>
       </c>
       <c r="C110" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E110" s="31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F110" s="29"/>
       <c r="G110" s="32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H110" s="29"/>
       <c r="I110" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="B111" s="29">
         <v>110</v>
       </c>
       <c r="C111" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E111" s="31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F111" s="29"/>
       <c r="G111" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H111" s="29"/>
       <c r="I111" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="16"/>
       <c r="B112" s="29">
         <v>111</v>
       </c>
       <c r="C112" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E112" s="31" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F112" s="29"/>
       <c r="G112" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H112" s="29"/>
       <c r="I112" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="9"/>
       <c r="B113" s="56">
         <v>112</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E113" s="11"/>
       <c r="F113" s="9"/>
@@ -4743,108 +4738,108 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="B114" s="29">
         <v>113</v>
       </c>
       <c r="C114" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F114" s="29"/>
       <c r="G114" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H114" s="29"/>
       <c r="I114" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="B115" s="29">
         <v>114</v>
       </c>
       <c r="C115" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F115" s="29"/>
       <c r="G115" s="32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H115" s="29"/>
       <c r="I115" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="16"/>
       <c r="B116" s="29">
         <v>115</v>
       </c>
       <c r="C116" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F116" s="29"/>
       <c r="G116" s="29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H116" s="29"/>
       <c r="I116" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="16"/>
       <c r="B117" s="29">
         <v>116</v>
       </c>
       <c r="C117" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D117" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E117" s="31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F117" s="29"/>
       <c r="G117" s="32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H117" s="29"/>
       <c r="I117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="55">
         <v>117</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="3"/>
@@ -4854,19 +4849,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" s="29">
         <v>118</v>
       </c>
       <c r="C119" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D119" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E119" s="31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F119" s="29"/>
       <c r="G119" s="32" t="s">
@@ -4877,19 +4872,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="16"/>
       <c r="B120" s="29">
         <v>119</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E120" s="31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F120" s="29"/>
       <c r="G120" s="32" t="s">
@@ -4900,19 +4895,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="16"/>
       <c r="B121" s="29">
         <v>120</v>
       </c>
       <c r="C121" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E121" s="31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F121" s="29"/>
       <c r="G121" s="32" t="s">
@@ -4923,16 +4918,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="55">
         <v>121</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="3"/>
@@ -4942,88 +4937,88 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="B123" s="29">
         <v>122</v>
       </c>
       <c r="C123" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E123" s="31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F123" s="29"/>
       <c r="G123" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H123" s="29"/>
       <c r="I123" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="16"/>
       <c r="B124" s="29">
         <v>123</v>
       </c>
       <c r="C124" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E124" s="31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F124" s="29"/>
       <c r="G124" s="29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H124" s="29"/>
       <c r="I124" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="29">
         <v>124</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F125" s="12"/>
       <c r="G125" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H125" s="12"/>
       <c r="I125" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" s="29">
         <v>125</v>
       </c>
       <c r="C126" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D126" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E126" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F126" s="29"/>
       <c r="G126" s="29" t="s">
@@ -5034,19 +5029,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" s="29">
         <v>126</v>
       </c>
       <c r="C127" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D127" s="30" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" s="29"/>
       <c r="G127" s="32" t="s">
@@ -5057,19 +5052,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="16"/>
       <c r="B128" s="29">
         <v>127</v>
       </c>
       <c r="C128" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D128" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E128" s="31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F128" s="29"/>
       <c r="G128" s="29" t="s">
@@ -5080,42 +5075,42 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="16"/>
       <c r="B129" s="29">
         <v>128</v>
       </c>
       <c r="C129" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D129" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E129" s="31" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F129" s="29"/>
       <c r="G129" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H129" s="29"/>
       <c r="I129" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" s="29">
         <v>129</v>
       </c>
       <c r="C130" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D130" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E130" s="29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F130" s="29"/>
       <c r="G130" s="32" t="s">
@@ -5126,19 +5121,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" s="29">
         <v>130</v>
       </c>
       <c r="C131" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D131" s="30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E131" s="29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F131" s="29"/>
       <c r="G131" s="32" t="s">
@@ -5149,19 +5144,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="16"/>
       <c r="B132" s="29">
         <v>131</v>
       </c>
       <c r="C132" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D132" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F132" s="29"/>
       <c r="G132" s="32" t="s">
@@ -5172,265 +5167,263 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="16"/>
       <c r="B133" s="29">
         <v>132</v>
       </c>
       <c r="C133" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D133" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E133" s="31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F133" s="29"/>
       <c r="G133" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H133" s="29"/>
       <c r="I133" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" s="29">
         <v>133</v>
       </c>
       <c r="C134" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D134" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E134" s="31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F134" s="29"/>
       <c r="G134" s="32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H134" s="29"/>
       <c r="I134" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="B135" s="29">
         <v>134</v>
       </c>
       <c r="C135" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D135" s="30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E135" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F135" s="29"/>
       <c r="G135" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H135" s="29"/>
       <c r="I135" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="16"/>
       <c r="B136" s="29">
         <v>135</v>
       </c>
       <c r="C136" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E136" s="31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F136" s="29"/>
       <c r="G136" s="32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H136" s="29"/>
       <c r="I136" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="16"/>
       <c r="B137" s="29">
         <v>136</v>
       </c>
       <c r="C137" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D137" s="30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E137" s="31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F137" s="29"/>
       <c r="G137" s="32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H137" s="29"/>
       <c r="I137" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
-      <c r="B138" s="33">
+      <c r="B138" s="29">
         <v>137</v>
       </c>
-      <c r="C138" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="D138" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="E138" s="35" t="s">
+      <c r="C138" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="D138" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="F138" s="33"/>
-      <c r="G138" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="H138" s="33" t="s">
-        <v>35</v>
-      </c>
+      <c r="E138" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="F138" s="29"/>
+      <c r="G138" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="H138" s="29"/>
       <c r="I138" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" s="29">
         <v>138</v>
       </c>
       <c r="C139" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D139" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E139" s="31" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F139" s="29"/>
       <c r="G139" s="32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H139" s="29"/>
       <c r="I139" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="16"/>
       <c r="B140" s="29">
         <v>139</v>
       </c>
       <c r="C140" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D140" s="30" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E140" s="31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F140" s="29"/>
       <c r="G140" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H140" s="29"/>
       <c r="I140" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:9" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" s="57" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16"/>
       <c r="B141" s="29">
         <v>140</v>
       </c>
       <c r="C141" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D141" s="41" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E141" s="31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F141" s="29"/>
       <c r="G141" s="32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H141" s="29"/>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" s="29">
         <v>141</v>
       </c>
       <c r="C142" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D142" s="41" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E142" s="31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F142" s="29"/>
       <c r="G142" s="32" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" s="29">
         <v>142</v>
       </c>
       <c r="C143" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D143" s="41" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E143" s="31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F143" s="29"/>
       <c r="G143" s="32" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H143" s="29"/>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="16"/>
       <c r="B144" s="29">
         <v>143</v>
       </c>
       <c r="C144" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D144" s="41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E144" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F144" s="29"/>
       <c r="G144" s="32" t="s">
@@ -5438,101 +5431,101 @@
       </c>
       <c r="H144" s="29"/>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="9"/>
       <c r="B145" s="56">
         <v>144</v>
       </c>
       <c r="C145" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E145" s="39" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F145" s="37"/>
       <c r="G145" s="40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H145" s="37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" s="29">
         <v>145</v>
       </c>
       <c r="C146" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D146" s="41" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E146" s="31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F146" s="29"/>
       <c r="G146" s="32" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H146" s="29"/>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" s="29">
         <v>146</v>
       </c>
       <c r="C147" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D147" s="41" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E147" s="31" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F147" s="29"/>
       <c r="G147" s="32" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H147" s="29"/>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="16"/>
       <c r="B148" s="29">
         <v>147</v>
       </c>
       <c r="C148" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D148" s="41" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E148" s="31" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F148" s="29"/>
       <c r="G148" s="32" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="16"/>
       <c r="B149" s="29">
         <v>148</v>
       </c>
       <c r="C149" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D149" s="41" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F149" s="29"/>
       <c r="G149" s="32" t="s">
@@ -5540,195 +5533,195 @@
       </c>
       <c r="H149" s="29"/>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="9"/>
       <c r="B150" s="56">
         <v>149</v>
       </c>
       <c r="C150" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D150" s="43" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E150" s="39" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F150" s="37"/>
       <c r="G150" s="40" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H150" s="37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:9" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B151" s="48">
         <v>150</v>
       </c>
       <c r="C151" s="48" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D151" s="54" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E151" s="50" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F151" s="48"/>
       <c r="G151" s="51" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H151" s="48"/>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="16"/>
       <c r="B152" s="29">
         <v>151</v>
       </c>
       <c r="C152" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D152" s="41" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E152" s="31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F152" s="31"/>
       <c r="G152" s="32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H152" s="29"/>
     </row>
-    <row r="153" spans="1:9" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="16"/>
       <c r="B153" s="29">
         <v>152</v>
       </c>
       <c r="C153" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D153" s="41" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F153" s="44"/>
       <c r="G153" s="32" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H153" s="29"/>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" s="29">
         <v>153</v>
       </c>
       <c r="C154" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D154" s="41" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F154" s="31"/>
       <c r="G154" s="32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H154" s="29"/>
     </row>
-    <row r="155" spans="1:9" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9"/>
       <c r="B155" s="56">
         <v>154</v>
       </c>
       <c r="C155" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D155" s="43" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E155" s="39" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F155" s="45"/>
       <c r="G155" s="40" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H155" s="37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="B156" s="55">
         <v>155</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="16"/>
       <c r="B157" s="29">
         <v>156</v>
       </c>
       <c r="C157" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D157" s="41" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E157" s="31" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F157" s="29"/>
       <c r="G157" s="29"/>
       <c r="H157" s="29"/>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B158" s="29">
         <v>157</v>
       </c>
       <c r="C158" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D158" s="41" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E158" s="31" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F158" s="29"/>
       <c r="G158" s="29"/>
       <c r="H158" s="29"/>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B159" s="56">
         <v>158</v>
       </c>
       <c r="C159" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D159" s="43" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E159" s="39" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F159" s="37"/>
       <c r="G159" s="37"/>
@@ -5736,18 +5729,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B160" s="56">
         <v>159</v>
       </c>
       <c r="C160" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D160" s="43" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E160" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F160" s="37"/>
       <c r="G160" s="37"/>
@@ -5755,36 +5748,36 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B161" s="29">
         <v>160</v>
       </c>
       <c r="C161" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D161" s="41" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E161" s="31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F161" s="31"/>
       <c r="G161" s="31"/>
       <c r="H161" s="31"/>
       <c r="I161" s="5"/>
     </row>
-    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B162" s="56">
         <v>161</v>
       </c>
       <c r="C162" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D162" s="43" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E162" s="39" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F162" s="39"/>
       <c r="G162" s="39"/>
@@ -5811,19 +5804,19 @@
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
     </row>
-    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="B163" s="55">
         <v>162</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
@@ -5848,19 +5841,19 @@
       <c r="Z163" s="5"/>
       <c r="AA163" s="5"/>
     </row>
-    <row r="164" spans="1:27" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="26"/>
       <c r="B164" s="56">
         <v>163</v>
       </c>
       <c r="C164" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D164" s="43" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E164" s="39" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F164" s="39"/>
       <c r="G164" s="39"/>
@@ -5887,18 +5880,18 @@
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
     </row>
-    <row r="165" spans="1:27" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B165" s="29">
         <v>164</v>
       </c>
       <c r="C165" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D165" s="41" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E165" s="31" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F165" s="31"/>
       <c r="G165" s="31"/>
@@ -5923,18 +5916,18 @@
       <c r="Z165" s="5"/>
       <c r="AA165" s="5"/>
     </row>
-    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B166" s="29">
         <v>165</v>
       </c>
       <c r="C166" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D166" s="41" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E166" s="31" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F166" s="31"/>
       <c r="G166" s="31"/>
@@ -5959,18 +5952,18 @@
       <c r="Z166" s="5"/>
       <c r="AA166" s="5"/>
     </row>
-    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B167" s="29">
         <v>166</v>
       </c>
       <c r="C167" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D167" s="41" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E167" s="31" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F167" s="31"/>
       <c r="G167" s="31"/>
@@ -5995,18 +5988,18 @@
       <c r="Z167" s="5"/>
       <c r="AA167" s="5"/>
     </row>
-    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B168" s="29">
         <v>167</v>
       </c>
       <c r="C168" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D168" s="41" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E168" s="31" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F168" s="31"/>
       <c r="G168" s="31"/>
@@ -6031,18 +6024,18 @@
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
     </row>
-    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B169" s="56">
         <v>168</v>
       </c>
       <c r="C169" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D169" s="43" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E169" s="39" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F169" s="39"/>
       <c r="G169" s="39"/>
@@ -6069,18 +6062,18 @@
       <c r="Z169" s="5"/>
       <c r="AA169" s="5"/>
     </row>
-    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B170" s="29">
         <v>169</v>
       </c>
       <c r="C170" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D170" s="41" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E170" s="31" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F170" s="31"/>
       <c r="G170" s="31"/>
@@ -6105,18 +6098,18 @@
       <c r="Z170" s="5"/>
       <c r="AA170" s="5"/>
     </row>
-    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B171" s="29">
         <v>170</v>
       </c>
       <c r="C171" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D171" s="41" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E171" s="31" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F171" s="31"/>
       <c r="G171" s="31"/>
@@ -6141,18 +6134,18 @@
       <c r="Z171" s="5"/>
       <c r="AA171" s="5"/>
     </row>
-    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B172" s="56">
         <v>171</v>
       </c>
       <c r="C172" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D172" s="43" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E172" s="39" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F172" s="39"/>
       <c r="G172" s="39"/>
@@ -6179,18 +6172,18 @@
       <c r="Z172" s="5"/>
       <c r="AA172" s="5"/>
     </row>
-    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B173" s="56">
         <v>172</v>
       </c>
       <c r="C173" s="37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D173" s="43" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E173" s="39" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F173" s="39"/>
       <c r="G173" s="39"/>
@@ -6217,18 +6210,18 @@
       <c r="Z173" s="5"/>
       <c r="AA173" s="5"/>
     </row>
-    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B174" s="55">
         <v>173</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D174" s="46" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F174" s="35"/>
       <c r="G174" s="35"/>
@@ -6255,18 +6248,18 @@
       <c r="Z174" s="5"/>
       <c r="AA174" s="5"/>
     </row>
-    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B175" s="29">
         <v>174</v>
       </c>
       <c r="C175" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D175" s="41" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E175" s="31" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F175" s="31"/>
       <c r="G175" s="31"/>
@@ -6291,18 +6284,18 @@
       <c r="Z175" s="5"/>
       <c r="AA175" s="5"/>
     </row>
-    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B176" s="29">
         <v>175</v>
       </c>
       <c r="C176" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D176" s="41" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E176" s="31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F176" s="31"/>
       <c r="G176" s="31"/>
@@ -6327,18 +6320,18 @@
       <c r="Z176" s="5"/>
       <c r="AA176" s="5"/>
     </row>
-    <row r="177" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B177" s="29">
         <v>176</v>
       </c>
       <c r="C177" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D177" s="41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E177" s="31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F177" s="31"/>
       <c r="G177" s="31"/>
@@ -6363,18 +6356,18 @@
       <c r="Z177" s="5"/>
       <c r="AA177" s="5"/>
     </row>
-    <row r="178" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B178" s="29">
         <v>177</v>
       </c>
       <c r="C178" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D178" s="41" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E178" s="31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F178" s="31"/>
       <c r="G178" s="31"/>
@@ -6399,18 +6392,18 @@
       <c r="Z178" s="5"/>
       <c r="AA178" s="5"/>
     </row>
-    <row r="179" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B179" s="29">
         <v>178</v>
       </c>
       <c r="C179" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D179" s="41" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E179" s="31" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F179" s="31"/>
       <c r="G179" s="31"/>
@@ -6435,18 +6428,18 @@
       <c r="Z179" s="5"/>
       <c r="AA179" s="5"/>
     </row>
-    <row r="180" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B180" s="56">
         <v>179</v>
       </c>
       <c r="C180" s="37" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D180" s="43" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E180" s="39" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F180" s="39"/>
       <c r="G180" s="39"/>
@@ -6473,18 +6466,18 @@
       <c r="Z180" s="5"/>
       <c r="AA180" s="5"/>
     </row>
-    <row r="181" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B181" s="29">
         <v>180</v>
       </c>
       <c r="C181" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D181" s="41" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E181" s="31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
@@ -6509,18 +6502,18 @@
       <c r="Z181" s="5"/>
       <c r="AA181" s="5"/>
     </row>
-    <row r="182" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B182" s="29">
         <v>181</v>
       </c>
       <c r="C182" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D182" s="41" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E182" s="31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
@@ -6545,18 +6538,18 @@
       <c r="Z182" s="5"/>
       <c r="AA182" s="5"/>
     </row>
-    <row r="183" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B183" s="29">
         <v>182</v>
       </c>
       <c r="C183" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D183" s="41" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E183" s="31" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
@@ -6581,18 +6574,18 @@
       <c r="Z183" s="5"/>
       <c r="AA183" s="5"/>
     </row>
-    <row r="184" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B184" s="29">
         <v>183</v>
       </c>
       <c r="C184" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D184" s="41" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E184" s="31" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
@@ -6617,18 +6610,18 @@
       <c r="Z184" s="5"/>
       <c r="AA184" s="5"/>
     </row>
-    <row r="185" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B185" s="29">
         <v>184</v>
       </c>
       <c r="C185" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D185" s="41" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E185" s="31" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
@@ -6653,18 +6646,18 @@
       <c r="Z185" s="5"/>
       <c r="AA185" s="5"/>
     </row>
-    <row r="186" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B186" s="29">
         <v>185</v>
       </c>
       <c r="C186" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D186" s="41" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E186" s="31" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
@@ -6689,18 +6682,18 @@
       <c r="Z186" s="5"/>
       <c r="AA186" s="5"/>
     </row>
-    <row r="187" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B187" s="29">
         <v>186</v>
       </c>
       <c r="C187" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D187" s="41" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E187" s="31" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
@@ -6725,18 +6718,18 @@
       <c r="Z187" s="5"/>
       <c r="AA187" s="5"/>
     </row>
-    <row r="188" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B188" s="29">
         <v>187</v>
       </c>
       <c r="C188" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D188" s="41" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E188" s="31" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
@@ -6761,18 +6754,18 @@
       <c r="Z188" s="5"/>
       <c r="AA188" s="5"/>
     </row>
-    <row r="189" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B189" s="29">
         <v>188</v>
       </c>
       <c r="C189" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D189" s="41" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E189" s="31" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
@@ -6797,18 +6790,18 @@
       <c r="Z189" s="5"/>
       <c r="AA189" s="5"/>
     </row>
-    <row r="190" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B190" s="29">
         <v>189</v>
       </c>
       <c r="C190" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D190" s="41" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E190" s="31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
@@ -6833,18 +6826,18 @@
       <c r="Z190" s="5"/>
       <c r="AA190" s="5"/>
     </row>
-    <row r="191" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B191" s="29">
         <v>190</v>
       </c>
       <c r="C191" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D191" s="41" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E191" s="31" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
@@ -6869,18 +6862,18 @@
       <c r="Z191" s="5"/>
       <c r="AA191" s="5"/>
     </row>
-    <row r="192" spans="2:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B192" s="29">
         <v>191</v>
       </c>
       <c r="C192" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D192" s="41" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E192" s="31" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F192" s="29"/>
       <c r="G192" s="29"/>
@@ -6904,35 +6897,35 @@
       <c r="Z192" s="5"/>
       <c r="AA192" s="5"/>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B193" s="29">
         <v>192</v>
       </c>
       <c r="C193" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D193" s="41" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E193" s="31" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F193" s="29"/>
       <c r="G193" s="29"/>
       <c r="H193" s="29"/>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B194" s="56">
         <v>193</v>
       </c>
       <c r="C194" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D194" s="43" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E194" s="39" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F194" s="37"/>
       <c r="G194" s="37"/>
@@ -6940,120 +6933,120 @@
         <v>53</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B195" s="29">
         <v>194</v>
       </c>
       <c r="C195" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D195" s="41" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E195" s="31" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F195" s="29"/>
       <c r="G195" s="29"/>
       <c r="H195" s="29"/>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B196" s="29">
         <v>195</v>
       </c>
       <c r="C196" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D196" s="41" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E196" s="31" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F196" s="29"/>
       <c r="G196" s="29"/>
       <c r="H196" s="29"/>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B197" s="29">
         <v>196</v>
       </c>
       <c r="C197" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D197" s="41" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E197" s="31" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F197" s="29"/>
       <c r="G197" s="29"/>
       <c r="H197" s="29"/>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B198" s="29">
         <v>197</v>
       </c>
       <c r="C198" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D198" s="41" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E198" s="31" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F198" s="29"/>
       <c r="G198" s="29"/>
       <c r="H198" s="29"/>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B199" s="29">
         <v>198</v>
       </c>
       <c r="C199" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D199" s="41" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E199" s="31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F199" s="29"/>
       <c r="G199" s="29"/>
       <c r="H199" s="29"/>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B200" s="29">
         <v>199</v>
       </c>
       <c r="C200" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D200" s="41" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E200" s="31" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F200" s="29"/>
       <c r="G200" s="29"/>
       <c r="H200" s="29"/>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B201" s="56">
         <v>200</v>
       </c>
       <c r="C201" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D201" s="43" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E201" s="39" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F201" s="37"/>
       <c r="G201" s="37"/>
@@ -7061,24 +7054,24 @@
         <v>53</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B202" s="29">
         <v>201</v>
       </c>
       <c r="C202" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D202" s="41" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E202" s="31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F202" s="29"/>
       <c r="G202" s="29"/>
       <c r="H202" s="29"/>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B203" s="55">
         <v>202</v>
       </c>
@@ -7086,17 +7079,17 @@
         <v>9</v>
       </c>
       <c r="D203" s="58" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E203" s="59" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F203" s="55"/>
       <c r="G203" s="55"/>
       <c r="H203" s="55"/>
       <c r="I203" s="3"/>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="16"/>
       <c r="B204" s="29">
         <v>203</v>
@@ -7105,16 +7098,16 @@
         <v>9</v>
       </c>
       <c r="D204" s="41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E204" s="31" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F204" s="29"/>
       <c r="G204" s="29"/>
       <c r="H204" s="29"/>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="16"/>
       <c r="B205" s="29">
         <v>204</v>
@@ -7123,16 +7116,16 @@
         <v>9</v>
       </c>
       <c r="D205" s="41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E205" s="31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F205" s="29"/>
       <c r="G205" s="29"/>
       <c r="H205" s="29"/>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="16"/>
       <c r="B206" s="29">
         <v>205</v>
@@ -7141,16 +7134,16 @@
         <v>9</v>
       </c>
       <c r="D206" s="41" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E206" s="31" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F206" s="29"/>
       <c r="G206" s="29"/>
       <c r="H206" s="29"/>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="16"/>
       <c r="B207" s="29">
         <v>206</v>
@@ -7159,16 +7152,16 @@
         <v>9</v>
       </c>
       <c r="D207" s="41" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E207" s="31" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F207" s="29"/>
       <c r="G207" s="29"/>
       <c r="H207" s="29"/>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="16"/>
       <c r="B208" s="29">
         <v>207</v>
@@ -7177,16 +7170,16 @@
         <v>9</v>
       </c>
       <c r="D208" s="41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E208" s="31" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F208" s="29"/>
       <c r="G208" s="29"/>
       <c r="H208" s="29"/>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="16"/>
       <c r="B209" s="56">
         <v>208</v>
@@ -7195,10 +7188,10 @@
         <v>9</v>
       </c>
       <c r="D209" s="43" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E209" s="39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F209" s="37"/>
       <c r="G209" s="37"/>
@@ -7206,7 +7199,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="16"/>
       <c r="B210" s="29">
         <v>209</v>
@@ -7215,16 +7208,16 @@
         <v>9</v>
       </c>
       <c r="D210" s="41" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E210" s="31" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F210" s="29"/>
       <c r="G210" s="29"/>
       <c r="H210" s="29"/>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="16"/>
       <c r="B211" s="29">
         <v>210</v>
@@ -7233,262 +7226,262 @@
         <v>9</v>
       </c>
       <c r="D211" s="41" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E211" s="31" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F211" s="29"/>
       <c r="G211" s="29"/>
       <c r="H211" s="29"/>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B212" s="29">
         <v>211</v>
       </c>
       <c r="E212" s="20"/>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B213" s="29">
         <v>212</v>
       </c>
       <c r="E213" s="20"/>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B214" s="29">
         <v>213</v>
       </c>
       <c r="E214" s="22"/>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B215" s="29">
         <v>214</v>
       </c>
       <c r="E215" s="22"/>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B216" s="29">
         <v>215</v>
       </c>
       <c r="E216" s="20"/>
     </row>
-    <row r="217" spans="1:8" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B217" s="29">
         <v>216</v>
       </c>
       <c r="E217" s="21"/>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B218" s="29">
         <v>217</v>
       </c>
       <c r="E218" s="20"/>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B219" s="29">
         <v>218</v>
       </c>
       <c r="E219" s="20"/>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B220" s="29">
         <v>219</v>
       </c>
       <c r="E220" s="20"/>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B221" s="29">
         <v>220</v>
       </c>
       <c r="E221" s="20"/>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B222" s="29">
         <v>221</v>
       </c>
       <c r="E222" s="20"/>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B223" s="29">
         <v>222</v>
       </c>
       <c r="E223" s="20"/>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B224" s="29">
         <v>223</v>
       </c>
       <c r="E224" s="20"/>
     </row>
-    <row r="225" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B225" s="29">
         <v>224</v>
       </c>
       <c r="E225" s="20"/>
     </row>
-    <row r="226" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B226" s="29">
         <v>225</v>
       </c>
       <c r="E226" s="20"/>
     </row>
-    <row r="227" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B227" s="29">
         <v>226</v>
       </c>
       <c r="E227" s="20"/>
     </row>
-    <row r="228" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" s="29">
         <v>227</v>
       </c>
       <c r="E228" s="20"/>
     </row>
-    <row r="229" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B229" s="29">
         <v>228</v>
       </c>
       <c r="E229" s="20"/>
     </row>
-    <row r="230" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B230" s="29">
         <v>229</v>
       </c>
       <c r="E230" s="20"/>
     </row>
-    <row r="231" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B231" s="29">
         <v>230</v>
       </c>
       <c r="E231" s="20"/>
     </row>
-    <row r="232" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B232" s="29">
         <v>231</v>
       </c>
       <c r="E232" s="20"/>
     </row>
-    <row r="233" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B233" s="29">
         <v>232</v>
       </c>
       <c r="E233" s="20"/>
     </row>
-    <row r="234" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B234" s="29">
         <v>233</v>
       </c>
       <c r="E234" s="20"/>
     </row>
-    <row r="235" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B235" s="29">
         <v>234</v>
       </c>
       <c r="E235" s="20"/>
     </row>
-    <row r="236" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B236" s="29">
         <v>235</v>
       </c>
       <c r="E236" s="20"/>
     </row>
-    <row r="237" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" s="29">
         <v>236</v>
       </c>
       <c r="E237" s="20"/>
     </row>
-    <row r="238" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B238" s="29">
         <v>237</v>
       </c>
       <c r="E238" s="20"/>
     </row>
-    <row r="239" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B239" s="29">
         <v>238</v>
       </c>
       <c r="E239" s="20"/>
     </row>
-    <row r="240" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B240" s="29">
         <v>239</v>
       </c>
       <c r="E240" s="20"/>
     </row>
-    <row r="241" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B241" s="29">
         <v>240</v>
       </c>
       <c r="E241" s="22"/>
     </row>
-    <row r="242" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B242" s="29">
         <v>241</v>
       </c>
       <c r="E242" s="22"/>
     </row>
-    <row r="243" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B243" s="29">
         <v>242</v>
       </c>
       <c r="E243" s="20"/>
     </row>
-    <row r="244" spans="2:5" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B244" s="29">
         <v>243</v>
       </c>
       <c r="E244" s="21"/>
     </row>
-    <row r="245" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B245" s="29">
         <v>244</v>
       </c>
       <c r="E245" s="20"/>
     </row>
-    <row r="246" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B246" s="29">
         <v>245</v>
       </c>
       <c r="E246" s="20"/>
     </row>
-    <row r="247" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B247" s="29">
         <v>246</v>
       </c>
       <c r="E247" s="20"/>
     </row>
-    <row r="248" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B248" s="29">
         <v>247</v>
       </c>
       <c r="E248" s="20"/>
     </row>
-    <row r="249" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B249" s="29">
         <v>248</v>
       </c>
       <c r="E249" s="20"/>
     </row>
-    <row r="250" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B250" s="29">
         <v>249</v>
       </c>
       <c r="E250" s="20"/>
     </row>
-    <row r="251" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B251" s="29">
         <v>250</v>
       </c>
       <c r="E251" s="20"/>
     </row>
-    <row r="252" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B252" s="29">
         <v>251</v>
       </c>
       <c r="E252" s="20"/>
     </row>
-    <row r="253" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B253" s="29">
         <v>252</v>
       </c>
@@ -7626,15 +7619,6 @@
       <c r="D1974" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I253" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Teclado com fio"/>
-        <filter val="Teclado gamer com fio"/>
-        <filter val="Teclado sem fio"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -7861,92 +7845,92 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -1387,31 +1387,31 @@
     </row>
     <row r="21">
       <c r="A21" s="16" t="n"/>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="40" t="inlineStr">
         <is>
           <t>https://meli.la/2eiaX1o</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Sem Fio</t>
         </is>
       </c>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H21" s="36" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1453,31 +1453,35 @@
     </row>
     <row r="23">
       <c r="A23" s="16" t="n"/>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>https://meli.la/1ViXRN7</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Branco</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H23" s="28" t="n"/>
+      <c r="H23" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1581,31 +1585,35 @@
     </row>
     <row r="27">
       <c r="A27" s="16" t="n"/>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>https://meli.la/2iuRXex</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 4K</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H27" s="28" t="n"/>
+      <c r="H27" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1684,31 +1692,31 @@
     </row>
     <row r="30">
       <c r="A30" s="16" t="n"/>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>https://meli.la/2kvFciT</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Paw3104 7200 DPI</t>
         </is>
       </c>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="39" t="inlineStr">
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="31" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H30" s="36" t="inlineStr">
+      <c r="H30" s="28" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1721,31 +1729,35 @@
     </row>
     <row r="31">
       <c r="A31" s="16" t="n"/>
-      <c r="B31" s="28" t="n">
+      <c r="B31" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>https://meli.la/241na5E</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="38" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="31" t="inlineStr">
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="39" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H31" s="28" t="n"/>
+      <c r="H31" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>⬜</t>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1638c87186bceadf/Desktop/OfertasTec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_93A9383EEBD1B033BA28AB930C480551B8790B43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55CA5FCD-1CCD-422A-B807-540CC12946D0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_93A9383EEBA1B11C24EAF462A72A0351B8790B92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA84F889-8952-4C31-985B-4A6260B183E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="515">
   <si>
     <t>Validação</t>
   </si>
@@ -377,6 +377,9 @@
     <t>https://meli.la/321ZTMv</t>
   </si>
   <si>
+    <t>Mouse Gamer M711 Cobra Chroma Redragon Com fio Para Jogos 12.400 DPI Com Led RGB Preto</t>
+  </si>
+  <si>
     <t>https://meli.la/2nikVNt</t>
   </si>
   <si>
@@ -410,6 +413,9 @@
     <t>https://meli.la/23wdZ7w</t>
   </si>
   <si>
+    <t>Mouse Gamer 6 Botões 12.800 Dpi Sensor Instantâneo Kp-mu026</t>
+  </si>
+  <si>
     <t>https://meli.la/15mY31Y</t>
   </si>
   <si>
@@ -1563,12 +1569,6 @@
   </si>
   <si>
     <t>Vou usar os dados pra atualizar o site automaticamente.</t>
-  </si>
-  <si>
-    <t>Mouse Gamer M711 Cobra Chroma Redragon Com fio Para Jogos 12.400 DPI Com Led RGB Preto</t>
-  </si>
-  <si>
-    <t>Mouse Gamer 6 Botões 12.800 Dpi Sensor Instantâneo Kp-mu026</t>
   </si>
 </sst>
 </file>
@@ -2533,7 +2533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="28">
         <v>14</v>
@@ -3208,7 +3208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="28">
         <v>43</v>
@@ -3220,7 +3220,7 @@
         <v>116</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>513</v>
+        <v>117</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
@@ -3229,7 +3229,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="28">
         <v>44</v>
@@ -3238,21 +3238,21 @@
         <v>115</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" s="28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H45" s="28"/>
       <c r="I45" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="28">
         <v>45</v>
@@ -3261,10 +3261,10 @@
         <v>115</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="31" t="s">
@@ -3275,7 +3275,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="36">
         <v>46</v>
@@ -3284,10 +3284,10 @@
         <v>115</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F47" s="36"/>
       <c r="G47" s="39" t="s">
@@ -3300,7 +3300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="36">
         <v>47</v>
@@ -3309,14 +3309,14 @@
         <v>115</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F48" s="36"/>
       <c r="G48" s="36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H48" s="36" t="s">
         <v>53</v>
@@ -3325,7 +3325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="36">
         <v>48</v>
@@ -3334,10 +3334,10 @@
         <v>115</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>514</v>
+        <v>129</v>
       </c>
       <c r="F49" s="36"/>
       <c r="G49" s="36"/>
@@ -3348,7 +3348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="28">
         <v>49</v>
@@ -3357,21 +3357,21 @@
         <v>115</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F50" s="28"/>
       <c r="G50" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H50" s="28"/>
       <c r="I50" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="28">
         <v>50</v>
@@ -3380,10 +3380,10 @@
         <v>115</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="31" t="s">
@@ -3394,7 +3394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="36">
         <v>51</v>
@@ -3403,14 +3403,14 @@
         <v>115</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H52" s="36" t="s">
         <v>53</v>
@@ -3419,7 +3419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="28">
         <v>52</v>
@@ -3428,21 +3428,21 @@
         <v>115</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E53" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F53" s="28"/>
       <c r="G53" s="31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H53" s="28"/>
       <c r="I53" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="28">
         <v>53</v>
@@ -3451,21 +3451,21 @@
         <v>115</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F54" s="28"/>
       <c r="G54" s="31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H54" s="28"/>
       <c r="I54" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="36">
         <v>54</v>
@@ -3474,10 +3474,10 @@
         <v>115</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="39" t="s">
@@ -3490,7 +3490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="36">
         <v>55</v>
@@ -3499,10 +3499,10 @@
         <v>115</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F56" s="36"/>
       <c r="G56" s="39" t="s">
@@ -3515,111 +3515,113 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
-      <c r="B57" s="28">
+      <c r="B57" s="36">
         <v>56</v>
       </c>
-      <c r="C57" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E57" s="30" t="s">
+      <c r="C57" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="F57" s="28"/>
-      <c r="G57" s="31" t="s">
+      <c r="D57" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E57" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="36"/>
+      <c r="G57" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="H57" s="28"/>
+      <c r="H57" s="36" t="s">
+        <v>53</v>
+      </c>
       <c r="I57" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="28">
         <v>57</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F58" s="28"/>
       <c r="G58" s="31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H58" s="28"/>
       <c r="I58" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="28">
         <v>58</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E59" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F59" s="28"/>
       <c r="G59" s="31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H59" s="28"/>
       <c r="I59" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="28">
         <v>59</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F60" s="28"/>
       <c r="G60" s="31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H60" s="28"/>
       <c r="I60" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="B61" s="28">
         <v>60</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F61" s="28"/>
       <c r="G61" s="31" t="s">
@@ -3630,19 +3632,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="B62" s="28">
         <v>61</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F62" s="28"/>
       <c r="G62" s="31" t="s">
@@ -3653,16 +3655,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="54">
         <v>62</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="3"/>
@@ -3672,19 +3674,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="B64" s="28">
         <v>63</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F64" s="28"/>
       <c r="G64" s="31" t="s">
@@ -3695,46 +3697,46 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="54">
+      <c r="B65" s="28">
         <v>64</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="18" t="s">
+      <c r="C65" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D65" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="H65" s="3"/>
+      <c r="E65" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" s="28"/>
+      <c r="G65" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H65" s="28"/>
       <c r="I65" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="B66" s="28">
         <v>65</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F66" s="28"/>
       <c r="G66" s="31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H66" s="28"/>
       <c r="I66" t="s">
@@ -3747,13 +3749,13 @@
         <v>66</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F67" s="28"/>
       <c r="G67" s="28" t="s">
@@ -3770,13 +3772,13 @@
         <v>67</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F68" s="28"/>
       <c r="G68" s="31" t="s">
@@ -3793,17 +3795,17 @@
         <v>68</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E69" s="30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F69" s="28"/>
       <c r="G69" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H69" s="28"/>
       <c r="I69" t="s">
@@ -3816,17 +3818,17 @@
         <v>69</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F70" s="28"/>
       <c r="G70" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H70" s="28"/>
       <c r="I70" t="s">
@@ -3839,10 +3841,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="3"/>
@@ -3858,13 +3860,13 @@
         <v>71</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F72" s="28"/>
       <c r="G72" s="31" t="s">
@@ -3881,17 +3883,17 @@
         <v>72</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F73" s="28"/>
       <c r="G73" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H73" s="28"/>
       <c r="I73" t="s">
@@ -3904,13 +3906,13 @@
         <v>73</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E74" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F74" s="28"/>
       <c r="G74" s="31" t="s">
@@ -3927,17 +3929,17 @@
         <v>74</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E75" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F75" s="28"/>
       <c r="G75" s="31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H75" s="28"/>
       <c r="I75" t="s">
@@ -3949,10 +3951,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="36"/>
@@ -3970,17 +3972,17 @@
         <v>76</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E77" s="30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F77" s="28"/>
       <c r="G77" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H77" s="28"/>
       <c r="I77" t="s">
@@ -3993,17 +3995,17 @@
         <v>77</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E78" s="30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F78" s="28"/>
       <c r="G78" s="31" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H78" s="28"/>
       <c r="I78" t="s">
@@ -4016,17 +4018,17 @@
         <v>78</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F79" s="28"/>
       <c r="G79" s="31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H79" s="28"/>
       <c r="I79" t="s">
@@ -4039,10 +4041,10 @@
         <v>79</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="3"/>
@@ -4058,13 +4060,13 @@
         <v>80</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -4079,17 +4081,17 @@
         <v>81</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F82" s="28"/>
       <c r="G82" s="31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H82" s="28"/>
       <c r="I82" t="s">
@@ -4102,17 +4104,17 @@
         <v>82</v>
       </c>
       <c r="C83" s="32" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E83" s="34" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H83" s="32" t="s">
         <v>35</v>
@@ -4127,17 +4129,17 @@
         <v>83</v>
       </c>
       <c r="C84" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E84" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F84" s="28"/>
       <c r="G84" s="31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H84" s="28"/>
       <c r="I84" t="s">
@@ -4150,17 +4152,17 @@
         <v>84</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E85" s="30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F85" s="28"/>
       <c r="G85" s="31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H85" s="28"/>
       <c r="I85" t="s">
@@ -4173,13 +4175,13 @@
         <v>85</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F86" s="28"/>
       <c r="G86" s="31" t="s">
@@ -4196,13 +4198,13 @@
         <v>86</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F87" s="28"/>
       <c r="G87" s="31" t="s">
@@ -4219,17 +4221,17 @@
         <v>87</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F88" s="28"/>
       <c r="G88" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H88" s="28"/>
       <c r="I88" t="s">
@@ -4242,17 +4244,17 @@
         <v>88</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F89" s="28"/>
       <c r="G89" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H89" s="28"/>
       <c r="I89" t="s">
@@ -4265,17 +4267,17 @@
         <v>89</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E90" s="30" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F90" s="28"/>
       <c r="G90" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H90" s="28"/>
       <c r="I90" t="s">
@@ -4288,17 +4290,17 @@
         <v>90</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E91" s="30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F91" s="28"/>
       <c r="G91" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H91" s="28"/>
       <c r="I91" t="s">
@@ -4311,17 +4313,17 @@
         <v>91</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E92" s="30" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F92" s="28"/>
       <c r="G92" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H92" s="28"/>
       <c r="I92" t="s">
@@ -4334,10 +4336,10 @@
         <v>92</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="3"/>
@@ -4353,13 +4355,13 @@
         <v>93</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F94" s="28"/>
       <c r="G94" s="31" t="s">
@@ -4376,17 +4378,17 @@
         <v>94</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F95" s="28"/>
       <c r="G95" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H95" s="28"/>
       <c r="I95" t="s">
@@ -4399,17 +4401,17 @@
         <v>95</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E96" s="30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F96" s="28"/>
       <c r="G96" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H96" s="28"/>
       <c r="I96" t="s">
@@ -4422,17 +4424,17 @@
         <v>96</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F97" s="28"/>
       <c r="G97" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H97" s="28"/>
       <c r="I97" t="s">
@@ -4445,10 +4447,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="3"/>
@@ -4464,10 +4466,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="3"/>
@@ -4483,17 +4485,17 @@
         <v>99</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F100" s="28"/>
       <c r="G100" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H100" s="28"/>
       <c r="I100" t="s">
@@ -4506,17 +4508,17 @@
         <v>100</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D101" s="29" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E101" s="30" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F101" s="28"/>
       <c r="G101" s="31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H101" s="28"/>
       <c r="I101" t="s">
@@ -4529,17 +4531,17 @@
         <v>101</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E102" s="30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F102" s="28"/>
       <c r="G102" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H102" s="28"/>
       <c r="I102" t="s">
@@ -4552,17 +4554,17 @@
         <v>102</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
@@ -4575,17 +4577,17 @@
         <v>103</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E104" s="30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F104" s="28"/>
       <c r="G104" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H104" s="28"/>
       <c r="I104" t="s">
@@ -4598,10 +4600,10 @@
         <v>104</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="3"/>
@@ -4617,17 +4619,17 @@
         <v>105</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E106" s="30" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F106" s="28"/>
       <c r="G106" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H106" s="28"/>
       <c r="I106" t="s">
@@ -4640,17 +4642,17 @@
         <v>106</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D107" s="29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E107" s="30" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F107" s="28"/>
       <c r="G107" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H107" s="28"/>
       <c r="I107" t="s">
@@ -4663,17 +4665,17 @@
         <v>107</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D108" s="29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E108" s="30" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F108" s="28"/>
       <c r="G108" s="31" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H108" s="28"/>
       <c r="I108" t="s">
@@ -4686,10 +4688,10 @@
         <v>108</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="3"/>
@@ -4705,17 +4707,17 @@
         <v>109</v>
       </c>
       <c r="C110" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D110" s="29" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E110" s="30" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F110" s="28"/>
       <c r="G110" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H110" s="28"/>
       <c r="I110" t="s">
@@ -4728,17 +4730,17 @@
         <v>110</v>
       </c>
       <c r="C111" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D111" s="29" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E111" s="30" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F111" s="28"/>
       <c r="G111" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H111" s="28"/>
       <c r="I111" t="s">
@@ -4751,17 +4753,17 @@
         <v>111</v>
       </c>
       <c r="C112" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E112" s="30" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F112" s="28"/>
       <c r="G112" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H112" s="28"/>
       <c r="I112" t="s">
@@ -4774,10 +4776,10 @@
         <v>112</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E113" s="11"/>
       <c r="F113" s="9"/>
@@ -4793,17 +4795,17 @@
         <v>113</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E114" s="30" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F114" s="28"/>
       <c r="G114" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H114" s="28"/>
       <c r="I114" t="s">
@@ -4816,17 +4818,17 @@
         <v>114</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E115" s="30" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F115" s="28"/>
       <c r="G115" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H115" s="28"/>
       <c r="I115" t="s">
@@ -4839,17 +4841,17 @@
         <v>115</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E116" s="30" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F116" s="28"/>
       <c r="G116" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H116" s="28"/>
       <c r="I116" t="s">
@@ -4862,17 +4864,17 @@
         <v>116</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E117" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F117" s="28"/>
       <c r="G117" s="31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H117" s="28"/>
       <c r="I117" t="s">
@@ -4885,10 +4887,10 @@
         <v>117</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="3"/>
@@ -4904,13 +4906,13 @@
         <v>118</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E119" s="30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F119" s="28"/>
       <c r="G119" s="31" t="s">
@@ -4927,17 +4929,17 @@
         <v>119</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E120" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F120" s="28"/>
       <c r="G120" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H120" s="28"/>
       <c r="I120" t="s">
@@ -4950,13 +4952,13 @@
         <v>120</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E121" s="30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F121" s="28"/>
       <c r="G121" s="31" t="s">
@@ -4973,10 +4975,10 @@
         <v>121</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="3"/>
@@ -4992,17 +4994,17 @@
         <v>122</v>
       </c>
       <c r="C123" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E123" s="30" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F123" s="28"/>
       <c r="G123" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H123" s="28"/>
       <c r="I123" t="s">
@@ -5015,17 +5017,17 @@
         <v>123</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E124" s="30" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F124" s="28"/>
       <c r="G124" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H124" s="28"/>
       <c r="I124" t="s">
@@ -5038,17 +5040,17 @@
         <v>124</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F125" s="12"/>
       <c r="G125" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H125" s="12"/>
       <c r="I125" s="12" t="s">
@@ -5061,13 +5063,13 @@
         <v>125</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E126" s="30" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F126" s="28"/>
       <c r="G126" s="28" t="s">
@@ -5084,17 +5086,17 @@
         <v>126</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F127" s="28"/>
       <c r="G127" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H127" s="28"/>
       <c r="I127" t="s">
@@ -5107,17 +5109,17 @@
         <v>127</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F128" s="28"/>
       <c r="G128" s="28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H128" s="28"/>
       <c r="I128" t="s">
@@ -5130,17 +5132,17 @@
         <v>128</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F129" s="28"/>
       <c r="G129" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H129" s="28"/>
       <c r="I129" t="s">
@@ -5153,17 +5155,17 @@
         <v>129</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F130" s="28"/>
       <c r="G130" s="31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H130" s="28"/>
       <c r="I130" t="s">
@@ -5176,17 +5178,17 @@
         <v>130</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F131" s="28"/>
       <c r="G131" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H131" s="28"/>
       <c r="I131" t="s">
@@ -5199,13 +5201,13 @@
         <v>131</v>
       </c>
       <c r="C132" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E132" s="30" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F132" s="28"/>
       <c r="G132" s="31" t="s">
@@ -5222,17 +5224,17 @@
         <v>132</v>
       </c>
       <c r="C133" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E133" s="30" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F133" s="28"/>
       <c r="G133" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H133" s="28"/>
       <c r="I133" t="s">
@@ -5245,17 +5247,17 @@
         <v>133</v>
       </c>
       <c r="C134" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F134" s="28"/>
       <c r="G134" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H134" s="28"/>
       <c r="I134" t="s">
@@ -5268,17 +5270,17 @@
         <v>134</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E135" s="30" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F135" s="28"/>
       <c r="G135" s="31" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H135" s="28"/>
       <c r="I135" t="s">
@@ -5291,17 +5293,17 @@
         <v>135</v>
       </c>
       <c r="C136" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E136" s="30" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F136" s="28"/>
       <c r="G136" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H136" s="28"/>
       <c r="I136" t="s">
@@ -5314,17 +5316,17 @@
         <v>136</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E137" s="30" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F137" s="28"/>
       <c r="G137" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H137" s="28"/>
       <c r="I137" t="s">
@@ -5337,17 +5339,17 @@
         <v>137</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E138" s="30" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F138" s="28"/>
       <c r="G138" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H138" s="28"/>
       <c r="I138" t="s">
@@ -5360,17 +5362,17 @@
         <v>138</v>
       </c>
       <c r="C139" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E139" s="30" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F139" s="28"/>
       <c r="G139" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H139" s="28"/>
       <c r="I139" t="s">
@@ -5383,17 +5385,17 @@
         <v>139</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E140" s="30" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F140" s="28"/>
       <c r="G140" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H140" s="28"/>
       <c r="I140" t="s">
@@ -5406,17 +5408,17 @@
         <v>140</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D141" s="40" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E141" s="30" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F141" s="28"/>
       <c r="G141" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H141" s="28"/>
     </row>
@@ -5426,17 +5428,17 @@
         <v>141</v>
       </c>
       <c r="C142" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D142" s="40" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E142" s="30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F142" s="28"/>
       <c r="G142" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H142" s="28"/>
     </row>
@@ -5446,17 +5448,17 @@
         <v>142</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D143" s="40" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E143" s="30" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F143" s="28"/>
       <c r="G143" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H143" s="28"/>
     </row>
@@ -5466,13 +5468,13 @@
         <v>143</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D144" s="40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E144" s="30" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F144" s="28"/>
       <c r="G144" s="31" t="s">
@@ -5486,17 +5488,17 @@
         <v>144</v>
       </c>
       <c r="C145" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D145" s="42" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E145" s="38" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F145" s="36"/>
       <c r="G145" s="39" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H145" s="36" t="s">
         <v>53</v>
@@ -5508,17 +5510,17 @@
         <v>145</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D146" s="40" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E146" s="30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F146" s="28"/>
       <c r="G146" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H146" s="28"/>
     </row>
@@ -5528,17 +5530,17 @@
         <v>146</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D147" s="40" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E147" s="30" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F147" s="28"/>
       <c r="G147" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H147" s="28"/>
     </row>
@@ -5548,17 +5550,17 @@
         <v>147</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E148" s="30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F148" s="28"/>
       <c r="G148" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H148" s="28"/>
     </row>
@@ -5568,13 +5570,13 @@
         <v>148</v>
       </c>
       <c r="C149" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D149" s="40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E149" s="30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F149" s="28"/>
       <c r="G149" s="31" t="s">
@@ -5588,17 +5590,17 @@
         <v>149</v>
       </c>
       <c r="C150" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D150" s="42" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E150" s="38" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F150" s="36"/>
       <c r="G150" s="39" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H150" s="36" t="s">
         <v>53</v>
@@ -5609,17 +5611,17 @@
         <v>150</v>
       </c>
       <c r="C151" s="47" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D151" s="53" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E151" s="49" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F151" s="47"/>
       <c r="G151" s="50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H151" s="47"/>
     </row>
@@ -5629,17 +5631,17 @@
         <v>151</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D152" s="40" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E152" s="30" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F152" s="30"/>
       <c r="G152" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H152" s="28"/>
     </row>
@@ -5649,17 +5651,17 @@
         <v>152</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D153" s="40" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F153" s="43"/>
       <c r="G153" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H153" s="28"/>
     </row>
@@ -5669,17 +5671,17 @@
         <v>153</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D154" s="40" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F154" s="30"/>
       <c r="G154" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H154" s="28"/>
     </row>
@@ -5689,17 +5691,17 @@
         <v>154</v>
       </c>
       <c r="C155" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D155" s="42" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E155" s="38" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F155" s="44"/>
       <c r="G155" s="39" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H155" s="36" t="s">
         <v>53</v>
@@ -5711,13 +5713,13 @@
         <v>155</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="3"/>
@@ -5730,13 +5732,13 @@
         <v>156</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D157" s="40" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F157" s="28"/>
       <c r="G157" s="28"/>
@@ -5747,13 +5749,13 @@
         <v>157</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D158" s="40" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F158" s="28"/>
       <c r="G158" s="28"/>
@@ -5764,13 +5766,13 @@
         <v>158</v>
       </c>
       <c r="C159" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D159" s="42" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E159" s="38" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F159" s="36"/>
       <c r="G159" s="36"/>
@@ -5783,13 +5785,13 @@
         <v>159</v>
       </c>
       <c r="C160" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D160" s="42" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E160" s="38" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F160" s="36"/>
       <c r="G160" s="36"/>
@@ -5802,13 +5804,13 @@
         <v>160</v>
       </c>
       <c r="C161" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D161" s="40" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F161" s="30"/>
       <c r="G161" s="30"/>
@@ -5820,13 +5822,13 @@
         <v>161</v>
       </c>
       <c r="C162" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D162" s="42" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E162" s="38" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F162" s="38"/>
       <c r="G162" s="38"/>
@@ -5859,13 +5861,13 @@
         <v>162</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
@@ -5896,13 +5898,13 @@
         <v>163</v>
       </c>
       <c r="C164" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D164" s="42" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E164" s="38" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F164" s="38"/>
       <c r="G164" s="38"/>
@@ -5934,13 +5936,13 @@
         <v>164</v>
       </c>
       <c r="C165" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D165" s="40" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F165" s="30"/>
       <c r="G165" s="30"/>
@@ -5970,13 +5972,13 @@
         <v>165</v>
       </c>
       <c r="C166" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D166" s="40" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F166" s="30"/>
       <c r="G166" s="30"/>
@@ -6006,13 +6008,13 @@
         <v>166</v>
       </c>
       <c r="C167" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D167" s="40" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F167" s="30"/>
       <c r="G167" s="30"/>
@@ -6042,13 +6044,13 @@
         <v>167</v>
       </c>
       <c r="C168" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D168" s="40" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F168" s="30"/>
       <c r="G168" s="30"/>
@@ -6078,13 +6080,13 @@
         <v>168</v>
       </c>
       <c r="C169" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D169" s="42" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E169" s="38" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F169" s="38"/>
       <c r="G169" s="38"/>
@@ -6116,13 +6118,13 @@
         <v>169</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D170" s="40" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F170" s="30"/>
       <c r="G170" s="30"/>
@@ -6152,13 +6154,13 @@
         <v>170</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D171" s="40" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F171" s="30"/>
       <c r="G171" s="30"/>
@@ -6188,13 +6190,13 @@
         <v>171</v>
       </c>
       <c r="C172" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E172" s="38" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F172" s="38"/>
       <c r="G172" s="38"/>
@@ -6226,13 +6228,13 @@
         <v>172</v>
       </c>
       <c r="C173" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D173" s="42" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E173" s="38" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F173" s="38"/>
       <c r="G173" s="38"/>
@@ -6264,13 +6266,13 @@
         <v>173</v>
       </c>
       <c r="C174" s="32" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D174" s="45" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E174" s="34" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F174" s="34"/>
       <c r="G174" s="34"/>
@@ -6302,13 +6304,13 @@
         <v>174</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D175" s="40" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F175" s="30"/>
       <c r="G175" s="30"/>
@@ -6338,13 +6340,13 @@
         <v>175</v>
       </c>
       <c r="C176" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D176" s="40" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F176" s="30"/>
       <c r="G176" s="30"/>
@@ -6374,13 +6376,13 @@
         <v>176</v>
       </c>
       <c r="C177" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D177" s="40" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F177" s="30"/>
       <c r="G177" s="30"/>
@@ -6410,13 +6412,13 @@
         <v>177</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D178" s="40" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F178" s="30"/>
       <c r="G178" s="30"/>
@@ -6446,13 +6448,13 @@
         <v>178</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D179" s="40" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F179" s="30"/>
       <c r="G179" s="30"/>
@@ -6482,13 +6484,13 @@
         <v>179</v>
       </c>
       <c r="C180" s="36" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D180" s="42" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E180" s="38" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F180" s="38"/>
       <c r="G180" s="38"/>
@@ -6520,13 +6522,13 @@
         <v>180</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D181" s="40" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F181" s="30"/>
       <c r="G181" s="30"/>
@@ -6556,13 +6558,13 @@
         <v>181</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D182" s="40" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F182" s="30"/>
       <c r="G182" s="30"/>
@@ -6592,13 +6594,13 @@
         <v>182</v>
       </c>
       <c r="C183" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D183" s="40" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F183" s="30"/>
       <c r="G183" s="30"/>
@@ -6628,13 +6630,13 @@
         <v>183</v>
       </c>
       <c r="C184" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D184" s="40" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F184" s="30"/>
       <c r="G184" s="30"/>
@@ -6664,13 +6666,13 @@
         <v>184</v>
       </c>
       <c r="C185" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D185" s="40" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F185" s="30"/>
       <c r="G185" s="30"/>
@@ -6700,13 +6702,13 @@
         <v>185</v>
       </c>
       <c r="C186" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D186" s="40" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F186" s="30"/>
       <c r="G186" s="30"/>
@@ -6736,13 +6738,13 @@
         <v>186</v>
       </c>
       <c r="C187" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D187" s="40" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F187" s="30"/>
       <c r="G187" s="30"/>
@@ -6772,13 +6774,13 @@
         <v>187</v>
       </c>
       <c r="C188" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D188" s="40" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F188" s="30"/>
       <c r="G188" s="30"/>
@@ -6808,13 +6810,13 @@
         <v>188</v>
       </c>
       <c r="C189" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D189" s="40" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F189" s="30"/>
       <c r="G189" s="30"/>
@@ -6844,13 +6846,13 @@
         <v>189</v>
       </c>
       <c r="C190" s="28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D190" s="40" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F190" s="30"/>
       <c r="G190" s="30"/>
@@ -6880,13 +6882,13 @@
         <v>190</v>
       </c>
       <c r="C191" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D191" s="40" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F191" s="30"/>
       <c r="G191" s="30"/>
@@ -6916,13 +6918,13 @@
         <v>191</v>
       </c>
       <c r="C192" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D192" s="40" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F192" s="28"/>
       <c r="G192" s="28"/>
@@ -6951,13 +6953,13 @@
         <v>192</v>
       </c>
       <c r="C193" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D193" s="40" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F193" s="28"/>
       <c r="G193" s="28"/>
@@ -6968,13 +6970,13 @@
         <v>193</v>
       </c>
       <c r="C194" s="36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D194" s="42" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E194" s="38" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F194" s="36"/>
       <c r="G194" s="36"/>
@@ -6987,13 +6989,13 @@
         <v>194</v>
       </c>
       <c r="C195" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D195" s="40" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F195" s="28"/>
       <c r="G195" s="28"/>
@@ -7004,13 +7006,13 @@
         <v>195</v>
       </c>
       <c r="C196" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D196" s="40" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E196" s="30" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F196" s="28"/>
       <c r="G196" s="28"/>
@@ -7021,13 +7023,13 @@
         <v>196</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D197" s="40" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E197" s="30" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F197" s="28"/>
       <c r="G197" s="28"/>
@@ -7038,13 +7040,13 @@
         <v>197</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D198" s="40" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F198" s="28"/>
       <c r="G198" s="28"/>
@@ -7055,13 +7057,13 @@
         <v>198</v>
       </c>
       <c r="C199" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D199" s="40" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F199" s="28"/>
       <c r="G199" s="28"/>
@@ -7072,13 +7074,13 @@
         <v>199</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D200" s="40" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F200" s="28"/>
       <c r="G200" s="28"/>
@@ -7089,13 +7091,13 @@
         <v>200</v>
       </c>
       <c r="C201" s="36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D201" s="42" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E201" s="38" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F201" s="36"/>
       <c r="G201" s="36"/>
@@ -7108,13 +7110,13 @@
         <v>201</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D202" s="40" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F202" s="28"/>
       <c r="G202" s="28"/>
@@ -7128,10 +7130,10 @@
         <v>9</v>
       </c>
       <c r="D203" s="57" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E203" s="58" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F203" s="54"/>
       <c r="G203" s="54"/>
@@ -7147,10 +7149,10 @@
         <v>9</v>
       </c>
       <c r="D204" s="40" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F204" s="28"/>
       <c r="G204" s="28"/>
@@ -7165,10 +7167,10 @@
         <v>9</v>
       </c>
       <c r="D205" s="40" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F205" s="28"/>
       <c r="G205" s="28"/>
@@ -7183,10 +7185,10 @@
         <v>9</v>
       </c>
       <c r="D206" s="40" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F206" s="28"/>
       <c r="G206" s="28"/>
@@ -7201,10 +7203,10 @@
         <v>9</v>
       </c>
       <c r="D207" s="40" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F207" s="28"/>
       <c r="G207" s="28"/>
@@ -7219,10 +7221,10 @@
         <v>9</v>
       </c>
       <c r="D208" s="40" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F208" s="28"/>
       <c r="G208" s="28"/>
@@ -7237,10 +7239,10 @@
         <v>9</v>
       </c>
       <c r="D209" s="42" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E209" s="38" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F209" s="36"/>
       <c r="G209" s="36"/>
@@ -7257,10 +7259,10 @@
         <v>9</v>
       </c>
       <c r="D210" s="40" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F210" s="28"/>
       <c r="G210" s="28"/>
@@ -7275,10 +7277,10 @@
         <v>9</v>
       </c>
       <c r="D211" s="40" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F211" s="28"/>
       <c r="G211" s="28"/>
@@ -7671,7 +7673,7 @@
   <autoFilter ref="A1:I253" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Mouse gamer com fio"/>
+        <filter val="Teclado com fio"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7901,92 +7903,92 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -698,7 +698,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA1974"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="1">
       <c r="A67" s="16" t="n"/>
       <c r="B67" s="36" t="n">
         <v>66</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="1">
       <c r="A68" s="16" t="n"/>
       <c r="B68" s="28" t="n">
         <v>67</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69" s="16" t="n"/>
       <c r="B69" s="32" t="n">
         <v>68</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70" s="16" t="n"/>
       <c r="B70" s="36" t="n">
         <v>69</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71" s="3" t="n"/>
       <c r="B71" s="28" t="n">
         <v>70</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" s="16" t="n"/>
       <c r="B72" s="28" t="n">
         <v>71</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73" s="16" t="n"/>
       <c r="B73" s="28" t="n">
         <v>72</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="1">
       <c r="A74" s="16" t="n"/>
       <c r="B74" s="28" t="n">
         <v>73</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" s="16" t="n"/>
       <c r="B89" s="28" t="n">
         <v>88</v>
@@ -3681,40 +3681,44 @@
         </is>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="16" t="n"/>
-      <c r="B90" s="28" t="n">
+      <c r="B90" s="36" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="28" t="inlineStr">
+      <c r="C90" s="36" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D90" s="29" t="inlineStr">
+      <c r="D90" s="37" t="inlineStr">
         <is>
           <t>https://meli.la/1vyVnBY</t>
         </is>
       </c>
-      <c r="E90" s="30" t="inlineStr">
+      <c r="E90" s="38" t="inlineStr">
         <is>
           <t>Fones de ouvido Bluetooth esportivos sem fio Ipx7 5.3.650 mAh, Bluetooth 5.3, cancelamento de ruído Enc, tela LED, resistência à água IPX7, para negócios, entretenimento e corrida</t>
         </is>
       </c>
-      <c r="F90" s="28" t="n"/>
-      <c r="G90" s="31" t="inlineStr">
+      <c r="F90" s="36" t="n"/>
+      <c r="G90" s="39" t="inlineStr">
         <is>
           <t>MerttoBX28</t>
         </is>
       </c>
-      <c r="H90" s="28" t="n"/>
+      <c r="H90" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="91" hidden="1">
+    <row r="91">
       <c r="A91" s="16" t="n"/>
       <c r="B91" s="28" t="n">
         <v>90</v>
@@ -3747,7 +3751,7 @@
         </is>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92">
       <c r="A92" s="16" t="n"/>
       <c r="B92" s="28" t="n">
         <v>91</v>
@@ -3780,7 +3784,7 @@
         </is>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="A93" s="3" t="n"/>
       <c r="B93" s="54" t="n">
         <v>92</v>
@@ -3805,7 +3809,7 @@
         </is>
       </c>
     </row>
-    <row r="94" hidden="1">
+    <row r="94">
       <c r="A94" s="16" t="n"/>
       <c r="B94" s="28" t="n">
         <v>93</v>
@@ -3838,7 +3842,7 @@
         </is>
       </c>
     </row>
-    <row r="95" hidden="1">
+    <row r="95">
       <c r="A95" s="16" t="n"/>
       <c r="B95" s="28" t="n">
         <v>94</v>
@@ -3871,40 +3875,44 @@
         </is>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96">
       <c r="A96" s="16" t="n"/>
-      <c r="B96" s="28" t="n">
+      <c r="B96" s="36" t="n">
         <v>95</v>
       </c>
-      <c r="C96" s="28" t="inlineStr">
+      <c r="C96" s="36" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D96" s="29" t="inlineStr">
+      <c r="D96" s="37" t="inlineStr">
         <is>
           <t>https://meli.la/1G18uM3</t>
         </is>
       </c>
-      <c r="E96" s="30" t="inlineStr">
+      <c r="E96" s="38" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Jbl Tune Flex 2 Preto</t>
         </is>
       </c>
-      <c r="F96" s="28" t="n"/>
-      <c r="G96" s="31" t="inlineStr">
+      <c r="F96" s="36" t="n"/>
+      <c r="G96" s="39" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H96" s="28" t="n"/>
+      <c r="H96" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="97" hidden="1">
+    <row r="97">
       <c r="A97" s="16" t="n"/>
       <c r="B97" s="28" t="n">
         <v>96</v>
@@ -3937,7 +3945,7 @@
         </is>
       </c>
     </row>
-    <row r="98" hidden="1">
+    <row r="98">
       <c r="A98" s="3" t="n"/>
       <c r="B98" s="54" t="n">
         <v>97</v>
@@ -3962,32 +3970,36 @@
         </is>
       </c>
     </row>
-    <row r="99" hidden="1">
+    <row r="99">
       <c r="A99" s="3" t="n"/>
-      <c r="B99" s="54" t="n">
+      <c r="B99" s="28" t="n">
         <v>98</v>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="28" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="29" t="inlineStr">
         <is>
           <t>https://meli.la/2L2DTy9</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
+      <c r="E99" s="30" t="inlineStr">
+        <is>
+          <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Branco</t>
+        </is>
+      </c>
+      <c r="F99" s="28" t="n"/>
+      <c r="G99" s="28" t="n"/>
+      <c r="H99" s="28" t="n"/>
       <c r="I99" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" s="16" t="n"/>
       <c r="B100" s="28" t="n">
         <v>99</v>
@@ -4020,40 +4032,44 @@
         </is>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="A101" s="16" t="n"/>
-      <c r="B101" s="28" t="n">
+      <c r="B101" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="C101" s="28" t="inlineStr">
+      <c r="C101" s="32" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D101" s="29" t="inlineStr">
+      <c r="D101" s="33" t="inlineStr">
         <is>
           <t>https://meli.la/1c6vAL2</t>
         </is>
       </c>
-      <c r="E101" s="30" t="inlineStr">
+      <c r="E101" s="34" t="inlineStr">
         <is>
           <t>Fone De Ouvido Aberto Indicador De Bateria Ipx7 Para Corrida,fone De Ouvido Bluetooth Com Ear Clip Tws Ows Hifi Esportivo 72h Bateria Ipx7 Prova D'água E Suor Enc Cancelamento Ruído</t>
         </is>
       </c>
-      <c r="F101" s="28" t="n"/>
-      <c r="G101" s="31" t="inlineStr">
+      <c r="F101" s="32" t="n"/>
+      <c r="G101" s="35" t="inlineStr">
         <is>
           <t>Inova Cases</t>
         </is>
       </c>
-      <c r="H101" s="28" t="n"/>
+      <c r="H101" s="32" t="inlineStr">
+        <is>
+          <t>fora do ar</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="102" hidden="1">
+    <row r="102">
       <c r="A102" s="16" t="n"/>
       <c r="B102" s="28" t="n">
         <v>101</v>
@@ -4086,66 +4102,70 @@
         </is>
       </c>
     </row>
-    <row r="103" hidden="1">
+    <row r="103">
       <c r="A103" s="3" t="n"/>
-      <c r="B103" s="54" t="n">
+      <c r="B103" s="28" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="28" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="29" t="inlineStr">
         <is>
           <t>https://meli.la/1N2GQcc</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="30" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Sem Fio Wave Buds 2 JBL JBLWBUDS2BLK Preto</t>
         </is>
       </c>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="18" t="inlineStr">
+      <c r="F103" s="28" t="n"/>
+      <c r="G103" s="31" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H103" s="3" t="n"/>
+      <c r="H103" s="28" t="n"/>
       <c r="I103" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="104" hidden="1">
+    <row r="104">
       <c r="A104" s="16" t="n"/>
-      <c r="B104" s="28" t="n">
+      <c r="B104" s="32" t="n">
         <v>103</v>
       </c>
-      <c r="C104" s="28" t="inlineStr">
+      <c r="C104" s="32" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D104" s="29" t="inlineStr">
+      <c r="D104" s="33" t="inlineStr">
         <is>
           <t>https://meli.la/2wA6HkN</t>
         </is>
       </c>
-      <c r="E104" s="30" t="inlineStr">
+      <c r="E104" s="34" t="inlineStr">
         <is>
           <t>Basike Fone De Ouvido Sem Fio Esportivo Bluetooth5.4 TWS, Corrida Gancho, à prova d'água, Com Gan, Tela LED Dupla, Suporta chamadas de voz, adequadas para Android e IOS, Cor Branco</t>
         </is>
       </c>
-      <c r="F104" s="28" t="n"/>
-      <c r="G104" s="31" t="inlineStr">
+      <c r="F104" s="32" t="n"/>
+      <c r="G104" s="35" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H104" s="28" t="n"/>
+      <c r="H104" s="32" t="inlineStr">
+        <is>
+          <t>fora do ar</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -7129,28 +7149,32 @@
       <c r="Z190" s="5" t="n"/>
       <c r="AA190" s="5" t="n"/>
     </row>
-    <row r="191" hidden="1">
-      <c r="B191" s="28" t="n">
+    <row r="191">
+      <c r="B191" s="32" t="n">
         <v>190</v>
       </c>
-      <c r="C191" s="28" t="inlineStr">
+      <c r="C191" s="32" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D191" s="40" t="inlineStr">
+      <c r="D191" s="45" t="inlineStr">
         <is>
           <t>https://meli.la/2cGbTdT</t>
         </is>
       </c>
-      <c r="E191" s="30" t="inlineStr">
+      <c r="E191" s="34" t="inlineStr">
         <is>
           <t>Fone Bluetooth 5.3 Tws Sem Fio Anti Ruido A Prova Dagua Compatível Iphone 7 8 X Xr 11 12 13 14 15 16 17 Xs Pro Max Plus Samsung S20 S23 S24 Xiaomi Motorola Android Prova DAgua Wireless Premium</t>
         </is>
       </c>
-      <c r="F191" s="30" t="n"/>
-      <c r="G191" s="30" t="n"/>
-      <c r="H191" s="30" t="n"/>
+      <c r="F191" s="34" t="n"/>
+      <c r="G191" s="34" t="n"/>
+      <c r="H191" s="34" t="inlineStr">
+        <is>
+          <t>fora do ar</t>
+        </is>
+      </c>
       <c r="I191" s="5" t="n"/>
       <c r="J191" s="5" t="n"/>
       <c r="K191" s="5" t="n"/>
@@ -7171,7 +7195,7 @@
       <c r="Z191" s="5" t="n"/>
       <c r="AA191" s="5" t="n"/>
     </row>
-    <row r="192" hidden="1">
+    <row r="192">
       <c r="B192" s="28" t="n">
         <v>191</v>
       </c>
@@ -7212,7 +7236,7 @@
       <c r="Z192" s="5" t="n"/>
       <c r="AA192" s="5" t="n"/>
     </row>
-    <row r="193" hidden="1">
+    <row r="193">
       <c r="B193" s="28" t="n">
         <v>192</v>
       </c>
@@ -7235,34 +7259,34 @@
       <c r="G193" s="28" t="n"/>
       <c r="H193" s="28" t="n"/>
     </row>
-    <row r="194" hidden="1">
-      <c r="B194" s="55" t="n">
+    <row r="194">
+      <c r="B194" s="28" t="n">
         <v>193</v>
       </c>
-      <c r="C194" s="36" t="inlineStr">
+      <c r="C194" s="28" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D194" s="42" t="inlineStr">
+      <c r="D194" s="40" t="inlineStr">
         <is>
           <t>https://meli.la/2gbZpAz</t>
         </is>
       </c>
-      <c r="E194" s="38" t="inlineStr">
+      <c r="E194" s="30" t="inlineStr">
         <is>
           <t>Fone de Ouvido Ows Bluetooth Design Aberto Kaidi 794 Cor Preto</t>
         </is>
       </c>
-      <c r="F194" s="36" t="n"/>
-      <c r="G194" s="36" t="n"/>
-      <c r="H194" s="36" t="inlineStr">
+      <c r="F194" s="28" t="n"/>
+      <c r="G194" s="28" t="n"/>
+      <c r="H194" s="28" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="195" hidden="1">
+    <row r="195">
       <c r="B195" s="28" t="n">
         <v>194</v>
       </c>
@@ -7285,7 +7309,7 @@
       <c r="G195" s="28" t="n"/>
       <c r="H195" s="28" t="n"/>
     </row>
-    <row r="196" hidden="1">
+    <row r="196">
       <c r="B196" s="28" t="n">
         <v>195</v>
       </c>
@@ -7308,7 +7332,7 @@
       <c r="G196" s="28" t="n"/>
       <c r="H196" s="28" t="n"/>
     </row>
-    <row r="197" hidden="1">
+    <row r="197">
       <c r="B197" s="28" t="n">
         <v>196</v>
       </c>
@@ -7331,7 +7355,7 @@
       <c r="G197" s="28" t="n"/>
       <c r="H197" s="28" t="n"/>
     </row>
-    <row r="198" hidden="1">
+    <row r="198">
       <c r="B198" s="28" t="n">
         <v>197</v>
       </c>
@@ -7354,7 +7378,7 @@
       <c r="G198" s="28" t="n"/>
       <c r="H198" s="28" t="n"/>
     </row>
-    <row r="199" hidden="1">
+    <row r="199">
       <c r="B199" s="28" t="n">
         <v>198</v>
       </c>
@@ -7377,78 +7401,86 @@
       <c r="G199" s="28" t="n"/>
       <c r="H199" s="28" t="n"/>
     </row>
-    <row r="200" hidden="1">
-      <c r="B200" s="28" t="n">
+    <row r="200">
+      <c r="B200" s="36" t="n">
         <v>199</v>
       </c>
-      <c r="C200" s="28" t="inlineStr">
+      <c r="C200" s="36" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D200" s="40" t="inlineStr">
+      <c r="D200" s="42" t="inlineStr">
         <is>
           <t>https://meli.la/1jGZwC3</t>
         </is>
       </c>
-      <c r="E200" s="30" t="inlineStr">
+      <c r="E200" s="38" t="inlineStr">
         <is>
           <t>Fone De Ouvido Esportivos Sem Fio Bluetooth Impermeável Ipx6</t>
         </is>
       </c>
-      <c r="F200" s="28" t="n"/>
-      <c r="G200" s="28" t="n"/>
-      <c r="H200" s="28" t="n"/>
-    </row>
-    <row r="201" hidden="1">
-      <c r="B201" s="55" t="n">
+      <c r="F200" s="36" t="n"/>
+      <c r="G200" s="36" t="n"/>
+      <c r="H200" s="36" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="C201" s="36" t="inlineStr">
+      <c r="C201" s="28" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D201" s="42" t="inlineStr">
+      <c r="D201" s="40" t="inlineStr">
         <is>
           <t>https://meli.la/2G3uu5c</t>
         </is>
       </c>
-      <c r="E201" s="38" t="inlineStr">
+      <c r="E201" s="30" t="inlineStr">
         <is>
           <t>Fone de Ouvido Eardbud AIWA AWS-EB-04-B Bluetooth IPX4 ANC 26 Horas de bateria</t>
         </is>
       </c>
-      <c r="F201" s="36" t="n"/>
-      <c r="G201" s="36" t="n"/>
-      <c r="H201" s="36" t="inlineStr">
+      <c r="F201" s="28" t="n"/>
+      <c r="G201" s="28" t="n"/>
+      <c r="H201" s="28" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="202" hidden="1">
-      <c r="B202" s="28" t="n">
+    <row r="202">
+      <c r="B202" s="32" t="n">
         <v>201</v>
       </c>
-      <c r="C202" s="28" t="inlineStr">
+      <c r="C202" s="32" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D202" s="40" t="inlineStr">
+      <c r="D202" s="45" t="inlineStr">
         <is>
           <t>https://meli.la/1A65TWL</t>
         </is>
       </c>
-      <c r="E202" s="30" t="inlineStr">
+      <c r="E202" s="34" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Redmi Buds 6 Play Xiaomi Sem Fio Cor Preto</t>
         </is>
       </c>
-      <c r="F202" s="28" t="n"/>
-      <c r="G202" s="28" t="n"/>
-      <c r="H202" s="28" t="n"/>
+      <c r="F202" s="32" t="n"/>
+      <c r="G202" s="32" t="n"/>
+      <c r="H202" s="32" t="inlineStr">
+        <is>
+          <t>fora do ar</t>
+        </is>
+      </c>
     </row>
     <row r="203" hidden="1">
       <c r="B203" s="54" t="n">
@@ -9735,7 +9767,7 @@
   <autoFilter ref="A1:I253">
     <filterColumn colId="2" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="Teclado sem fio"/>
+        <filter val="Fone sem fio (bluetooth)"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9952,6 +9984,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -9962,7 +9995,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
   </cols>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos Renomear" sheetId="1" state="visible" r:id="rId1"/>
@@ -248,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -271,7 +271,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -698,7 +697,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA1974"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -712,7 +711,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Validação</t>
         </is>
@@ -760,31 +759,31 @@
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="16" t="n"/>
-      <c r="B2" s="28" t="n">
+      <c r="B2" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/16Zu7aQ</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Rosa</t>
         </is>
       </c>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H2" s="28" t="n"/>
+      <c r="H2" s="27" t="n"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -793,31 +792,31 @@
     </row>
     <row r="3" hidden="1">
       <c r="A3" s="16" t="n"/>
-      <c r="B3" s="28" t="n">
+      <c r="B3" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1FKVJ3z</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech Pebble 2 M350s Grafite</t>
         </is>
       </c>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="31" t="inlineStr">
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H3" s="28" t="n"/>
+      <c r="H3" s="27" t="n"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -826,31 +825,31 @@
     </row>
     <row r="4" hidden="1">
       <c r="A4" s="16" t="n"/>
-      <c r="B4" s="28" t="n">
+      <c r="B4" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1LJWhVZ</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Mouse Intelbras MSI50 Silencioso Preto</t>
         </is>
       </c>
-      <c r="F4" s="28" t="n"/>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>Intelbras</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n"/>
+      <c r="H4" s="27" t="n"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -859,7 +858,7 @@
     </row>
     <row r="5" hidden="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="54" t="n">
+      <c r="B5" s="53" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -888,31 +887,31 @@
     </row>
     <row r="6" hidden="1">
       <c r="A6" s="16" t="n"/>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/24v9AsX</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Azul Claro</t>
         </is>
       </c>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H6" s="28" t="n"/>
+      <c r="H6" s="27" t="n"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -921,31 +920,31 @@
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="16" t="n"/>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2Ax6kZC</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M280 Sem Fio Preto</t>
         </is>
       </c>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H7" s="28" t="n"/>
+      <c r="H7" s="27" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -954,31 +953,31 @@
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="17" t="n"/>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2QtqWZq</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M190 Sem Fio Cinza</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H8" s="28" t="n"/>
+      <c r="H8" s="27" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -987,31 +986,31 @@
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="16" t="n"/>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2QUUhTR</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Cinza e Preto</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H9" s="28" t="n"/>
+      <c r="H9" s="27" t="n"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1020,31 +1019,31 @@
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="16" t="n"/>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2rqAKxH</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Preto</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H10" s="28" t="n"/>
+      <c r="H10" s="27" t="n"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1053,31 +1052,31 @@
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="16" t="n"/>
-      <c r="B11" s="54" t="n">
+      <c r="B11" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/1zHhNjb</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>Mouse USB 1200 DPI Ergonômico</t>
         </is>
       </c>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>Eduimports</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -1090,31 +1089,31 @@
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="16" t="n"/>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2BdXdPm</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Mouse HP 150 USB Preto</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="31" t="inlineStr">
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="H12" s="28" t="n"/>
+      <c r="H12" s="27" t="n"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1123,31 +1122,31 @@
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="16" t="n"/>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1jy5H8M</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Mouse HP 100 USB 1600 DPI</t>
         </is>
       </c>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="31" t="inlineStr">
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="H13" s="28" t="n"/>
+      <c r="H13" s="27" t="n"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1156,31 +1155,31 @@
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="16" t="n"/>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2F8AUwW</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1600 DPI Preto</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="31" t="inlineStr">
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>Megalodonte</t>
         </is>
       </c>
-      <c r="H14" s="28" t="n"/>
+      <c r="H14" s="27" t="n"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1189,31 +1188,31 @@
     </row>
     <row r="15" hidden="1" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="16" t="n"/>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1zquXcb</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1200 DPI Ergonômico</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>Exbom</t>
         </is>
       </c>
-      <c r="H15" s="28" t="n"/>
+      <c r="H15" s="27" t="n"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1222,31 +1221,31 @@
     </row>
     <row r="16" hidden="1" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="3" t="n"/>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/12UNNBe</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1000 DPI Preto</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="59" t="inlineStr">
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="58" t="inlineStr">
         <is>
           <t>Grupo Ecommshops Pró</t>
         </is>
       </c>
-      <c r="H16" s="28" t="n"/>
+      <c r="H16" s="27" t="n"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1255,31 +1254,31 @@
     </row>
     <row r="17" hidden="1">
       <c r="A17" s="9" t="n"/>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1G5EfHd</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Mouse Dell MS116 USB</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="31" t="inlineStr">
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1292,31 +1291,31 @@
     </row>
     <row r="18" hidden="1">
       <c r="A18" s="16" t="n"/>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1a7Rfrt</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Mouse Multilaser Classic Box 1200 DPI</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
-      <c r="G18" s="31" t="inlineStr">
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H18" s="28" t="n"/>
+      <c r="H18" s="27" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1325,31 +1324,31 @@
     </row>
     <row r="19" hidden="1">
       <c r="A19" s="16" t="n"/>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/28xQ9VT</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Mouse Logitech M90 Com Fio</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H19" s="28" t="n"/>
+      <c r="H19" s="27" t="n"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1358,27 +1357,27 @@
     </row>
     <row r="20" hidden="1">
       <c r="A20" s="16" t="n"/>
-      <c r="B20" s="28" t="n">
+      <c r="B20" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1cvqKkQ</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Mouse Óptico com Fio Usb Black 03950 - MS-71 Exbom</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="28" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1387,31 +1386,31 @@
     </row>
     <row r="21" hidden="1">
       <c r="A21" s="16" t="n"/>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D21" s="40" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2eiaX1o</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Sem Fio</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1424,27 +1423,27 @@
     </row>
     <row r="22" hidden="1">
       <c r="A22" s="16" t="n"/>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1ieF2X8</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 1K Preto Preto - M916-PRO-1K</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="27" t="n"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1453,31 +1452,31 @@
     </row>
     <row r="23" hidden="1">
       <c r="A23" s="16" t="n"/>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D23" s="37" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1ViXRN7</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Branco</t>
         </is>
       </c>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="36" t="inlineStr">
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H23" s="36" t="inlineStr">
+      <c r="H23" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1490,31 +1489,31 @@
     </row>
     <row r="24" hidden="1">
       <c r="A24" s="16" t="n"/>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/15QeaEY</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Tri Mode 18000 DPI</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>Fire Phoenix</t>
         </is>
       </c>
-      <c r="H24" s="28" t="n"/>
+      <c r="H24" s="27" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1523,23 +1522,23 @@
     </row>
     <row r="25" hidden="1">
       <c r="A25" s="16" t="n"/>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D25" s="37" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2bq5uLu</t>
         </is>
       </c>
-      <c r="E25" s="38" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="inlineStr">
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1552,31 +1551,31 @@
     </row>
     <row r="26" hidden="1">
       <c r="A26" s="16" t="n"/>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Bwj698</t>
         </is>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 12000 DPI</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="31" t="inlineStr">
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H26" s="28" t="n"/>
+      <c r="H26" s="27" t="n"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1585,31 +1584,31 @@
     </row>
     <row r="27" hidden="1">
       <c r="A27" s="16" t="n"/>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="35" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D27" s="37" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2iuRXex</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 4K</t>
         </is>
       </c>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="36" t="inlineStr">
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="35" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H27" s="36" t="inlineStr">
+      <c r="H27" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1622,31 +1621,31 @@
     </row>
     <row r="28" hidden="1">
       <c r="A28" s="16" t="n"/>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="35" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="36" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/13eJLNw</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr">
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Shinka 3200 DPI Sem Fio</t>
         </is>
       </c>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="39" t="inlineStr">
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="38" t="inlineStr">
         <is>
           <t>Shinka</t>
         </is>
       </c>
-      <c r="H28" s="36" t="inlineStr">
+      <c r="H28" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1659,32 +1658,32 @@
     </row>
     <row r="29" hidden="1">
       <c r="A29" s="16" t="n"/>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="46" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D29" s="51" t="inlineStr">
+      <c r="D29" s="50" t="inlineStr">
         <is>
           <t>https://meli.la/2iuRXex</t>
         </is>
       </c>
-      <c r="E29" s="52" t="inlineStr">
+      <c r="E29" s="51" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 4K Preto</t>
         </is>
       </c>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="inlineStr">
+      <c r="F29" s="45" t="n"/>
+      <c r="G29" s="45" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H29" s="46" t="n"/>
-      <c r="I29" s="46" t="inlineStr">
+      <c r="H29" s="45" t="n"/>
+      <c r="I29" s="45" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1692,31 +1691,31 @@
     </row>
     <row r="30" hidden="1">
       <c r="A30" s="16" t="n"/>
-      <c r="B30" s="28" t="n">
+      <c r="B30" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2kvFciT</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Paw3104 7200 DPI</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="31" t="inlineStr">
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1729,31 +1728,31 @@
     </row>
     <row r="31" hidden="1">
       <c r="A31" s="16" t="n"/>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D31" s="37" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/241na5E</t>
         </is>
       </c>
-      <c r="E31" s="38" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro</t>
         </is>
       </c>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="39" t="inlineStr">
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="38" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H31" s="36" t="inlineStr">
+      <c r="H31" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1766,31 +1765,31 @@
     </row>
     <row r="32" hidden="1">
       <c r="A32" s="16" t="n"/>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="35" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="36" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D32" s="37" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2BZocDd</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Fyzu Pro</t>
         </is>
       </c>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="39" t="inlineStr">
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="38" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H32" s="36" t="inlineStr">
+      <c r="H32" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1803,31 +1802,31 @@
     </row>
     <row r="33" hidden="1">
       <c r="A33" s="16" t="n"/>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/19CRJzw</t>
         </is>
       </c>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Fire Phoenix Sem Fio</t>
         </is>
       </c>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="inlineStr">
         <is>
           <t>Fire Phoenix</t>
         </is>
       </c>
-      <c r="H33" s="28" t="n"/>
+      <c r="H33" s="27" t="n"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1836,31 +1835,31 @@
     </row>
     <row r="34" hidden="1">
       <c r="A34" s="16" t="n"/>
-      <c r="B34" s="28" t="n">
+      <c r="B34" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2F4p8Fn</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 3311</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="31" t="inlineStr">
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H34" s="28" t="n"/>
+      <c r="H34" s="27" t="n"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1869,32 +1868,32 @@
     </row>
     <row r="35" hidden="1">
       <c r="A35" s="16" t="n"/>
-      <c r="B35" s="47" t="n">
+      <c r="B35" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="46" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D35" s="48" t="inlineStr">
+      <c r="D35" s="47" t="inlineStr">
         <is>
           <t>https://meli.la/1Bwj698</t>
         </is>
       </c>
-      <c r="E35" s="49" t="inlineStr">
+      <c r="E35" s="48" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 3311 Sem Fio</t>
         </is>
       </c>
-      <c r="F35" s="47" t="n"/>
-      <c r="G35" s="50" t="inlineStr">
+      <c r="F35" s="46" t="n"/>
+      <c r="G35" s="49" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H35" s="47" t="n"/>
-      <c r="I35" s="46" t="inlineStr">
+      <c r="H35" s="46" t="n"/>
+      <c r="I35" s="45" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1902,31 +1901,31 @@
     </row>
     <row r="36" hidden="1">
       <c r="A36" s="16" t="n"/>
-      <c r="B36" s="28" t="n">
+      <c r="B36" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1xnHcCq</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Knup Bluetooth 1600 DPI</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="31" t="inlineStr">
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H36" s="28" t="n"/>
+      <c r="H36" s="27" t="n"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1935,31 +1934,31 @@
     </row>
     <row r="37" hidden="1">
       <c r="A37" s="16" t="n"/>
-      <c r="B37" s="28" t="n">
+      <c r="B37" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="28" t="inlineStr">
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2pnhc6K</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Recarregável Bluetooth</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="inlineStr">
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="inlineStr">
         <is>
           <t>Smailwolf Mouse Gamer</t>
         </is>
       </c>
-      <c r="H37" s="28" t="n"/>
+      <c r="H37" s="27" t="n"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1968,31 +1967,31 @@
     </row>
     <row r="38" hidden="1">
       <c r="A38" s="16" t="n"/>
-      <c r="B38" s="32" t="n">
+      <c r="B38" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D38" s="33" t="inlineStr">
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/12Li269</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>Mouse Gamer Machenike M7 Pro RGB</t>
         </is>
       </c>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>Machenike</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -2005,31 +2004,31 @@
     </row>
     <row r="39" hidden="1">
       <c r="A39" s="16" t="n"/>
-      <c r="B39" s="28" t="n">
+      <c r="B39" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="28" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2UTzmsY</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E39" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Warrior Dash 8 Botões</t>
         </is>
       </c>
-      <c r="F39" s="28" t="n"/>
-      <c r="G39" s="31" t="inlineStr">
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="30" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="H39" s="28" t="n"/>
+      <c r="H39" s="27" t="n"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2038,31 +2037,31 @@
     </row>
     <row r="40" hidden="1">
       <c r="A40" s="16" t="n"/>
-      <c r="B40" s="28" t="n">
+      <c r="B40" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1NTFM66</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Taipan Pro M810</t>
         </is>
       </c>
-      <c r="F40" s="28" t="n"/>
-      <c r="G40" s="31" t="inlineStr">
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H40" s="28" t="n"/>
+      <c r="H40" s="27" t="n"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2071,31 +2070,31 @@
     </row>
     <row r="41" hidden="1">
       <c r="A41" s="16" t="n"/>
-      <c r="B41" s="28" t="n">
+      <c r="B41" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="28" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/28iFCs3</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Recarregável Bluetooth 2.4G</t>
         </is>
       </c>
-      <c r="F41" s="28" t="n"/>
-      <c r="G41" s="31" t="inlineStr">
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H41" s="28" t="n"/>
+      <c r="H41" s="27" t="n"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2104,7 +2103,7 @@
     </row>
     <row r="42" hidden="1">
       <c r="A42" s="16" t="n"/>
-      <c r="B42" s="54" t="n">
+      <c r="B42" s="53" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2129,31 +2128,31 @@
     </row>
     <row r="43" hidden="1">
       <c r="A43" s="16" t="n"/>
-      <c r="B43" s="28" t="n">
+      <c r="B43" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1uhKd3R</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon M991 Sem Fio</t>
         </is>
       </c>
-      <c r="F43" s="28" t="n"/>
-      <c r="G43" s="31" t="inlineStr">
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="30" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H43" s="28" t="n"/>
+      <c r="H43" s="27" t="n"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2162,27 +2161,27 @@
     </row>
     <row r="44" hidden="1">
       <c r="A44" s="16" t="n"/>
-      <c r="B44" s="28" t="n">
+      <c r="B44" s="27" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D44" s="40" t="inlineStr">
+      <c r="D44" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/321ZTMv</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="E44" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer M711 Cobra Chroma Redragon Com fio Para Jogos 12.400 DPI Com Led RGB Preto</t>
         </is>
       </c>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
+      <c r="H44" s="27" t="n"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2191,31 +2190,31 @@
     </row>
     <row r="45" hidden="1">
       <c r="A45" s="16" t="n"/>
-      <c r="B45" s="28" t="n">
+      <c r="B45" s="27" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="28" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2nikVNt</t>
         </is>
       </c>
-      <c r="E45" s="30" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Viper Pro Naja 7200 DPI</t>
         </is>
       </c>
-      <c r="F45" s="28" t="n"/>
-      <c r="G45" s="28" t="inlineStr">
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="inlineStr">
         <is>
           <t>Viper Pro</t>
         </is>
       </c>
-      <c r="H45" s="28" t="n"/>
+      <c r="H45" s="27" t="n"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2224,31 +2223,31 @@
     </row>
     <row r="46" hidden="1">
       <c r="A46" s="16" t="n"/>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D46" s="29" t="inlineStr">
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2BkMNpg</t>
         </is>
       </c>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="E46" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Machenike M7 Pro 12800 DPI</t>
         </is>
       </c>
-      <c r="F46" s="28" t="n"/>
-      <c r="G46" s="31" t="inlineStr">
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="30" t="inlineStr">
         <is>
           <t>Machenike</t>
         </is>
       </c>
-      <c r="H46" s="28" t="n"/>
+      <c r="H46" s="27" t="n"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2257,31 +2256,31 @@
     </row>
     <row r="47" hidden="1">
       <c r="A47" s="3" t="n"/>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="35" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="36" t="inlineStr">
+      <c r="C47" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D47" s="37" t="inlineStr">
+      <c r="D47" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2nK6CGd</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
+      <c r="E47" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon M815 Ultraleve</t>
         </is>
       </c>
-      <c r="F47" s="36" t="n"/>
-      <c r="G47" s="39" t="inlineStr">
+      <c r="F47" s="35" t="n"/>
+      <c r="G47" s="38" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H47" s="36" t="inlineStr">
+      <c r="H47" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2294,31 +2293,31 @@
     </row>
     <row r="48" hidden="1">
       <c r="A48" s="16" t="n"/>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="35" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="36" t="inlineStr">
+      <c r="C48" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D48" s="37" t="inlineStr">
+      <c r="D48" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1GyW82d</t>
         </is>
       </c>
-      <c r="E48" s="38" t="inlineStr">
+      <c r="E48" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Onikuma CW917 Com Fio</t>
         </is>
       </c>
-      <c r="F48" s="36" t="n"/>
-      <c r="G48" s="36" t="inlineStr">
+      <c r="F48" s="35" t="n"/>
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>Onikuma</t>
         </is>
       </c>
-      <c r="H48" s="36" t="inlineStr">
+      <c r="H48" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2331,27 +2330,27 @@
     </row>
     <row r="49" hidden="1">
       <c r="A49" s="3" t="n"/>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="C49" s="36" t="inlineStr">
+      <c r="C49" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D49" s="37" t="inlineStr">
+      <c r="D49" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/23wdZ7w</t>
         </is>
       </c>
-      <c r="E49" s="38" t="inlineStr">
+      <c r="E49" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer 6 Botões 12.800 Dpi Sensor Instantâneo Kp-mu026</t>
         </is>
       </c>
-      <c r="F49" s="36" t="n"/>
-      <c r="G49" s="36" t="n"/>
-      <c r="H49" s="36" t="inlineStr">
+      <c r="F49" s="35" t="n"/>
+      <c r="G49" s="35" t="n"/>
+      <c r="H49" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2364,31 +2363,31 @@
     </row>
     <row r="50" hidden="1">
       <c r="A50" s="16" t="n"/>
-      <c r="B50" s="28" t="n">
+      <c r="B50" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="28" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/15mY31Y</t>
         </is>
       </c>
-      <c r="E50" s="30" t="inlineStr">
+      <c r="E50" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Havit MS1036 RGB 7200 DPI</t>
         </is>
       </c>
-      <c r="F50" s="28" t="n"/>
-      <c r="G50" s="28" t="inlineStr">
+      <c r="F50" s="27" t="n"/>
+      <c r="G50" s="27" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H50" s="28" t="n"/>
+      <c r="H50" s="27" t="n"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2397,31 +2396,31 @@
     </row>
     <row r="51" hidden="1">
       <c r="A51" s="16" t="n"/>
-      <c r="B51" s="28" t="n">
+      <c r="B51" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="C51" s="28" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2n5VFUw</t>
         </is>
       </c>
-      <c r="E51" s="30" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Hive RGB 16000 DPI</t>
         </is>
       </c>
-      <c r="F51" s="28" t="n"/>
-      <c r="G51" s="31" t="inlineStr">
+      <c r="F51" s="27" t="n"/>
+      <c r="G51" s="30" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H51" s="28" t="n"/>
+      <c r="H51" s="27" t="n"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2430,31 +2429,31 @@
     </row>
     <row r="52" hidden="1">
       <c r="A52" s="16" t="n"/>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="35" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="36" t="inlineStr">
+      <c r="C52" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D52" s="37" t="inlineStr">
+      <c r="D52" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2BwBjiE</t>
         </is>
       </c>
-      <c r="E52" s="38" t="inlineStr">
+      <c r="E52" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Havit MS959S RGB 8 Botões</t>
         </is>
       </c>
-      <c r="F52" s="36" t="n"/>
-      <c r="G52" s="39" t="inlineStr">
+      <c r="F52" s="35" t="n"/>
+      <c r="G52" s="38" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H52" s="36" t="inlineStr">
+      <c r="H52" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2467,31 +2466,31 @@
     </row>
     <row r="53" hidden="1">
       <c r="A53" s="16" t="n"/>
-      <c r="B53" s="28" t="n">
+      <c r="B53" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="C53" s="28" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1QTQPMY</t>
         </is>
       </c>
-      <c r="E53" s="30" t="inlineStr">
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Rgb Fortrek Crusader White Edition 12800dpi</t>
         </is>
       </c>
-      <c r="F53" s="28" t="n"/>
-      <c r="G53" s="31" t="inlineStr">
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H53" s="28" t="n"/>
+      <c r="H53" s="27" t="n"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2500,31 +2499,31 @@
     </row>
     <row r="54" hidden="1">
       <c r="A54" s="16" t="n"/>
-      <c r="B54" s="28" t="n">
+      <c r="B54" s="27" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="28" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="D54" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2ZyCiGn</t>
         </is>
       </c>
-      <c r="E54" s="30" t="inlineStr">
+      <c r="E54" s="29" t="inlineStr">
         <is>
           <t>Mouse Gamer Fortrek Crusader 12800 Dpi Com Led Switch Huano</t>
         </is>
       </c>
-      <c r="F54" s="28" t="n"/>
-      <c r="G54" s="31" t="inlineStr">
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="30" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H54" s="28" t="n"/>
+      <c r="H54" s="27" t="n"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2533,31 +2532,31 @@
     </row>
     <row r="55" hidden="1">
       <c r="A55" s="16" t="n"/>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="35" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="36" t="inlineStr">
+      <c r="C55" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D55" s="37" t="inlineStr">
+      <c r="D55" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2ms6fTM</t>
         </is>
       </c>
-      <c r="E55" s="38" t="inlineStr">
+      <c r="E55" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Bomber M722 Redragon Preto</t>
         </is>
       </c>
-      <c r="F55" s="36" t="n"/>
-      <c r="G55" s="39" t="inlineStr">
+      <c r="F55" s="35" t="n"/>
+      <c r="G55" s="38" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H55" s="36" t="inlineStr">
+      <c r="H55" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2570,31 +2569,31 @@
     </row>
     <row r="56" hidden="1">
       <c r="A56" s="16" t="n"/>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="36" t="inlineStr">
+      <c r="C56" s="35" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D56" s="37" t="inlineStr">
+      <c r="D56" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/23VvESt</t>
         </is>
       </c>
-      <c r="E56" s="38" t="inlineStr">
+      <c r="E56" s="37" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Devourer Preto M993-rgb</t>
         </is>
       </c>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="39" t="inlineStr">
+      <c r="F56" s="35" t="n"/>
+      <c r="G56" s="38" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H56" s="36" t="inlineStr">
+      <c r="H56" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2607,31 +2606,31 @@
     </row>
     <row r="57" hidden="1">
       <c r="A57" s="16" t="n"/>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C57" s="36" t="inlineStr">
+      <c r="C57" s="35" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D57" s="37" t="inlineStr">
+      <c r="D57" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1Fy7WQv</t>
         </is>
       </c>
-      <c r="E57" s="38" t="inlineStr">
+      <c r="E57" s="37" t="inlineStr">
         <is>
           <t>Teclado Multimídia Com Fio Usb Teclas Silenciosas (abnt2)</t>
         </is>
       </c>
-      <c r="F57" s="36" t="n"/>
-      <c r="G57" s="39" t="inlineStr">
+      <c r="F57" s="35" t="n"/>
+      <c r="G57" s="38" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H57" s="36" t="inlineStr">
+      <c r="H57" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2644,31 +2643,31 @@
     </row>
     <row r="58" hidden="1">
       <c r="A58" s="16" t="n"/>
-      <c r="B58" s="28" t="n">
+      <c r="B58" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D58" s="29" t="inlineStr">
+      <c r="D58" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2e7gPck</t>
         </is>
       </c>
-      <c r="E58" s="30" t="inlineStr">
+      <c r="E58" s="29" t="inlineStr">
         <is>
           <t>Teclado Titanis USB com Fio Preto ABNT2 Ergonômico Plug &amp; Play Numérico PC Toque Suave para Computador Layout Qwerty Prático Ideal para Trabalho Escritório Office</t>
         </is>
       </c>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="31" t="inlineStr">
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="30" t="inlineStr">
         <is>
           <t>Titanis</t>
         </is>
       </c>
-      <c r="H58" s="28" t="n"/>
+      <c r="H58" s="27" t="n"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2677,31 +2676,31 @@
     </row>
     <row r="59" hidden="1">
       <c r="A59" s="16" t="n"/>
-      <c r="B59" s="28" t="n">
+      <c r="B59" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="28" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D59" s="29" t="inlineStr">
+      <c r="D59" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1kFH9iG</t>
         </is>
       </c>
-      <c r="E59" s="30" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>Teclado USB Hoopson TPC-058G com Fio Teclas Grandes Preto ABNT2</t>
         </is>
       </c>
-      <c r="F59" s="28" t="n"/>
-      <c r="G59" s="31" t="inlineStr">
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="30" t="inlineStr">
         <is>
           <t>Hoopson</t>
         </is>
       </c>
-      <c r="H59" s="28" t="n"/>
+      <c r="H59" s="27" t="n"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2710,31 +2709,31 @@
     </row>
     <row r="60" hidden="1">
       <c r="A60" s="16" t="n"/>
-      <c r="B60" s="28" t="n">
+      <c r="B60" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="C60" s="28" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D60" s="29" t="inlineStr">
+      <c r="D60" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/11EgXFE</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E60" s="29" t="inlineStr">
         <is>
           <t>Teclado Usb Com Fio Dgx Padrão Abnt2 Silencioso Ergonômico Preto Com Cabo Usb Escritorio</t>
         </is>
       </c>
-      <c r="F60" s="28" t="n"/>
-      <c r="G60" s="31" t="inlineStr">
+      <c r="F60" s="27" t="n"/>
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>Dgx</t>
         </is>
       </c>
-      <c r="H60" s="28" t="n"/>
+      <c r="H60" s="27" t="n"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2743,31 +2742,31 @@
     </row>
     <row r="61" hidden="1">
       <c r="A61" s="16" t="n"/>
-      <c r="B61" s="28" t="n">
+      <c r="B61" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="28" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D61" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2kFVGHA</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E61" s="29" t="inlineStr">
         <is>
           <t>Teclado Com Fio Usb Kb216 Dell Cor De Teclado Preto Idioma Português Brasil</t>
         </is>
       </c>
-      <c r="F61" s="28" t="n"/>
-      <c r="G61" s="31" t="inlineStr">
+      <c r="F61" s="27" t="n"/>
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="H61" s="28" t="n"/>
+      <c r="H61" s="27" t="n"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2776,31 +2775,31 @@
     </row>
     <row r="62" hidden="1">
       <c r="A62" s="16" t="n"/>
-      <c r="B62" s="28" t="n">
+      <c r="B62" s="27" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="28" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D62" s="29" t="inlineStr">
+      <c r="D62" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2s4v5j3</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E62" s="29" t="inlineStr">
         <is>
           <t>Teclado USB Exbom BK-102 Preto ABNT2 Para PC e Notebook PT-BR</t>
         </is>
       </c>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="31" t="inlineStr">
+      <c r="F62" s="27" t="n"/>
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>Exbom</t>
         </is>
       </c>
-      <c r="H62" s="28" t="n"/>
+      <c r="H62" s="27" t="n"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2809,7 +2808,7 @@
     </row>
     <row r="63" hidden="1">
       <c r="A63" s="3" t="n"/>
-      <c r="B63" s="54" t="n">
+      <c r="B63" s="53" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2834,31 +2833,31 @@
     </row>
     <row r="64" hidden="1">
       <c r="A64" s="16" t="n"/>
-      <c r="B64" s="28" t="n">
+      <c r="B64" s="27" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D64" s="29" t="inlineStr">
+      <c r="D64" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1eE7xym</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E64" s="29" t="inlineStr">
         <is>
           <t>Teclado Com Fio Usb Logitech K120 Com Layout Abnt2 Cor de teclado Preto Idioma Português Brasil QWERTY</t>
         </is>
       </c>
-      <c r="F64" s="28" t="n"/>
-      <c r="G64" s="31" t="inlineStr">
+      <c r="F64" s="27" t="n"/>
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H64" s="28" t="n"/>
+      <c r="H64" s="27" t="n"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2867,31 +2866,31 @@
     </row>
     <row r="65" hidden="1">
       <c r="A65" s="3" t="n"/>
-      <c r="B65" s="28" t="n">
+      <c r="B65" s="27" t="n">
         <v>64</v>
       </c>
-      <c r="C65" s="28" t="inlineStr">
+      <c r="C65" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="D65" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1PK6gym</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>Teclado Bahrein Para Pc Computador Notebook Com Fio Português Brasil Cor Preto</t>
         </is>
       </c>
-      <c r="F65" s="28" t="n"/>
-      <c r="G65" s="31" t="inlineStr">
+      <c r="F65" s="27" t="n"/>
+      <c r="G65" s="30" t="inlineStr">
         <is>
           <t>Rezzet</t>
         </is>
       </c>
-      <c r="H65" s="28" t="n"/>
+      <c r="H65" s="27" t="n"/>
       <c r="I65" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2900,31 +2899,31 @@
     </row>
     <row r="66" hidden="1">
       <c r="A66" s="16" t="n"/>
-      <c r="B66" s="28" t="n">
+      <c r="B66" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="28" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="D66" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1YkqEkr</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E66" s="29" t="inlineStr">
         <is>
           <t>Teclado USB Com Fio B-Max BM-T02 ABNT2 Silencioso Ergonômico Preto</t>
         </is>
       </c>
-      <c r="F66" s="28" t="n"/>
-      <c r="G66" s="31" t="inlineStr">
+      <c r="F66" s="27" t="n"/>
+      <c r="G66" s="30" t="inlineStr">
         <is>
           <t>B-Max</t>
         </is>
       </c>
-      <c r="H66" s="28" t="n"/>
+      <c r="H66" s="27" t="n"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2933,31 +2932,31 @@
     </row>
     <row r="67" hidden="1">
       <c r="A67" s="16" t="n"/>
-      <c r="B67" s="36" t="n">
+      <c r="B67" s="35" t="n">
         <v>66</v>
       </c>
-      <c r="C67" s="36" t="inlineStr">
+      <c r="C67" s="35" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D67" s="37" t="inlineStr">
+      <c r="D67" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1RdrkMP</t>
         </is>
       </c>
-      <c r="E67" s="38" t="inlineStr">
+      <c r="E67" s="37" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Mx Keys Mini Logitech Grafite Americano</t>
         </is>
       </c>
-      <c r="F67" s="36" t="n"/>
-      <c r="G67" s="36" t="inlineStr">
+      <c r="F67" s="35" t="n"/>
+      <c r="G67" s="35" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H67" s="36" t="inlineStr">
+      <c r="H67" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -2970,31 +2969,31 @@
     </row>
     <row r="68" hidden="1">
       <c r="A68" s="16" t="n"/>
-      <c r="B68" s="28" t="n">
+      <c r="B68" s="27" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="28" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D68" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Qx1EEh</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E68" s="29" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Signature Slim K950 Branco Logitech</t>
         </is>
       </c>
-      <c r="F68" s="28" t="n"/>
-      <c r="G68" s="31" t="inlineStr">
+      <c r="F68" s="27" t="n"/>
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H68" s="28" t="n"/>
+      <c r="H68" s="27" t="n"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3003,31 +3002,31 @@
     </row>
     <row r="69" hidden="1">
       <c r="A69" s="16" t="n"/>
-      <c r="B69" s="32" t="n">
+      <c r="B69" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="C69" s="31" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D69" s="33" t="inlineStr">
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/16PdgAV</t>
         </is>
       </c>
-      <c r="E69" s="34" t="inlineStr">
+      <c r="E69" s="33" t="inlineStr">
         <is>
           <t>Teclado Mecânico Aula F75 Preto Sem Fio RGB 75% Tri Mode Bluetooth, 2.4ghz, USB-C, Inglês Us</t>
         </is>
       </c>
-      <c r="F69" s="32" t="n"/>
-      <c r="G69" s="35" t="inlineStr">
+      <c r="F69" s="31" t="n"/>
+      <c r="G69" s="34" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H69" s="32" t="inlineStr">
+      <c r="H69" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -3040,31 +3039,31 @@
     </row>
     <row r="70" hidden="1">
       <c r="A70" s="16" t="n"/>
-      <c r="B70" s="36" t="n">
+      <c r="B70" s="35" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="36" t="inlineStr">
+      <c r="C70" s="35" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D70" s="37" t="inlineStr">
+      <c r="D70" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/138aRrU</t>
         </is>
       </c>
-      <c r="E70" s="38" t="inlineStr">
+      <c r="E70" s="37" t="inlineStr">
         <is>
           <t>Teclado Aula F75 Sem Fio Mecânico Thunder Black Tri Mode Gasket Hot Swapp Inglês US</t>
         </is>
       </c>
-      <c r="F70" s="36" t="n"/>
-      <c r="G70" s="39" t="inlineStr">
+      <c r="F70" s="35" t="n"/>
+      <c r="G70" s="38" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H70" s="36" t="inlineStr">
+      <c r="H70" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -3077,23 +3076,23 @@
     </row>
     <row r="71" hidden="1">
       <c r="A71" s="3" t="n"/>
-      <c r="B71" s="28" t="n">
+      <c r="B71" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="28" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D71" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1gfyU2e</t>
         </is>
       </c>
-      <c r="E71" s="30" t="n"/>
-      <c r="F71" s="28" t="n"/>
-      <c r="G71" s="28" t="n"/>
-      <c r="H71" s="28" t="n"/>
+      <c r="E71" s="29" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3102,31 +3101,31 @@
     </row>
     <row r="72" hidden="1">
       <c r="A72" s="16" t="n"/>
-      <c r="B72" s="28" t="n">
+      <c r="B72" s="27" t="n">
         <v>71</v>
       </c>
-      <c r="C72" s="28" t="inlineStr">
+      <c r="C72" s="27" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="D72" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1uRKdMf</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio Logitech Pebble Keys 2 K380s - Branco</t>
         </is>
       </c>
-      <c r="F72" s="28" t="n"/>
-      <c r="G72" s="31" t="inlineStr">
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H72" s="28" t="n"/>
+      <c r="H72" s="27" t="n"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3135,31 +3134,31 @@
     </row>
     <row r="73" hidden="1">
       <c r="A73" s="16" t="n"/>
-      <c r="B73" s="28" t="n">
+      <c r="B73" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="28" t="inlineStr">
+      <c r="C73" s="27" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="D73" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Y9Djdq</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>Teclado Aula F75 Mecânico Sem Fio Tri Mode Gasket Hot Swapp Cor de teclado Branco Idioma Inglês US</t>
         </is>
       </c>
-      <c r="F73" s="28" t="n"/>
-      <c r="G73" s="31" t="inlineStr">
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="30" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H73" s="28" t="n"/>
+      <c r="H73" s="27" t="n"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3168,31 +3167,31 @@
     </row>
     <row r="74" hidden="1">
       <c r="A74" s="16" t="n"/>
-      <c r="B74" s="28" t="n">
+      <c r="B74" s="27" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="28" t="inlineStr">
+      <c r="C74" s="27" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="D74" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Gkykud</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E74" s="29" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Logitech Signature K650 - Branco</t>
         </is>
       </c>
-      <c r="F74" s="28" t="n"/>
-      <c r="G74" s="31" t="inlineStr">
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="30" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H74" s="28" t="n"/>
+      <c r="H74" s="27" t="n"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3201,31 +3200,31 @@
     </row>
     <row r="75" hidden="1">
       <c r="A75" s="16" t="n"/>
-      <c r="B75" s="28" t="n">
+      <c r="B75" s="27" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="28" t="inlineStr">
+      <c r="C75" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D75" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1s34Rp2</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>Teclado Gamer 60% Membrana Rgb Fio Usb Anti Ghosting Pt-br</t>
         </is>
       </c>
-      <c r="F75" s="28" t="n"/>
-      <c r="G75" s="31" t="inlineStr">
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>Teclado 60 por Cento Barato</t>
         </is>
       </c>
-      <c r="H75" s="28" t="n"/>
+      <c r="H75" s="27" t="n"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3233,23 +3232,23 @@
       </c>
     </row>
     <row r="76" hidden="1">
-      <c r="B76" s="36" t="n">
+      <c r="B76" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="C76" s="36" t="inlineStr">
+      <c r="C76" s="35" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D76" s="37" t="inlineStr">
+      <c r="D76" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2G9hQwo</t>
         </is>
       </c>
-      <c r="E76" s="38" t="n"/>
-      <c r="F76" s="36" t="n"/>
-      <c r="G76" s="36" t="n"/>
-      <c r="H76" s="36" t="inlineStr">
+      <c r="E76" s="37" t="n"/>
+      <c r="F76" s="35" t="n"/>
+      <c r="G76" s="35" t="n"/>
+      <c r="H76" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -3262,31 +3261,31 @@
     </row>
     <row r="77" hidden="1">
       <c r="A77" s="16" t="n"/>
-      <c r="B77" s="28" t="n">
+      <c r="B77" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="28" t="inlineStr">
+      <c r="C77" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D77" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2WCTDDE</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>Teclado Mecânico Gamer Rgb Switch Azul Barulhent 63t Com Fio</t>
         </is>
       </c>
-      <c r="F77" s="28" t="n"/>
-      <c r="G77" s="31" t="inlineStr">
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>T-Wolf</t>
         </is>
       </c>
-      <c r="H77" s="28" t="n"/>
+      <c r="H77" s="27" t="n"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3295,31 +3294,31 @@
     </row>
     <row r="78" hidden="1">
       <c r="A78" s="16" t="n"/>
-      <c r="B78" s="28" t="n">
+      <c r="B78" s="27" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="28" t="inlineStr">
+      <c r="C78" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D78" s="29" t="inlineStr">
+      <c r="D78" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1ivXod3</t>
         </is>
       </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>Bluetooth+2.4g+com Fio Rgb Gamer Teclado Silencioso Para Pc</t>
         </is>
       </c>
-      <c r="F78" s="28" t="n"/>
-      <c r="G78" s="31" t="inlineStr">
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>SPLPLUS</t>
         </is>
       </c>
-      <c r="H78" s="28" t="n"/>
+      <c r="H78" s="27" t="n"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3328,31 +3327,31 @@
     </row>
     <row r="79" hidden="1">
       <c r="A79" s="16" t="n"/>
-      <c r="B79" s="28" t="n">
+      <c r="B79" s="27" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="28" t="inlineStr">
+      <c r="C79" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D79" s="29" t="inlineStr">
+      <c r="D79" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/34bmbbX</t>
         </is>
       </c>
-      <c r="E79" s="30" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>Teclado Mecânico Fio Gamer Rgb 60% Switch Blue Anti Ghosting</t>
         </is>
       </c>
-      <c r="F79" s="28" t="n"/>
-      <c r="G79" s="31" t="inlineStr">
+      <c r="F79" s="27" t="n"/>
+      <c r="G79" s="30" t="inlineStr">
         <is>
           <t>Master Gaming</t>
         </is>
       </c>
-      <c r="H79" s="28" t="n"/>
+      <c r="H79" s="27" t="n"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3361,7 +3360,7 @@
     </row>
     <row r="80" hidden="1">
       <c r="A80" s="3" t="n"/>
-      <c r="B80" s="54" t="n">
+      <c r="B80" s="53" t="n">
         <v>79</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3386,7 +3385,7 @@
     </row>
     <row r="81" hidden="1">
       <c r="A81" s="3" t="n"/>
-      <c r="B81" s="54" t="n">
+      <c r="B81" s="53" t="n">
         <v>80</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3415,31 +3414,31 @@
     </row>
     <row r="82" hidden="1">
       <c r="A82" s="16" t="n"/>
-      <c r="B82" s="28" t="n">
+      <c r="B82" s="27" t="n">
         <v>81</v>
       </c>
-      <c r="C82" s="28" t="inlineStr">
+      <c r="C82" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D82" s="29" t="inlineStr">
+      <c r="D82" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2wUJ3fr</t>
         </is>
       </c>
-      <c r="E82" s="30" t="inlineStr">
+      <c r="E82" s="29" t="inlineStr">
         <is>
           <t>Original Lenovo Teclado Gamer Com Led Rgb Ergonômico Com Fio</t>
         </is>
       </c>
-      <c r="F82" s="28" t="n"/>
-      <c r="G82" s="31" t="inlineStr">
+      <c r="F82" s="27" t="n"/>
+      <c r="G82" s="30" t="inlineStr">
         <is>
           <t>Lenovo Legion</t>
         </is>
       </c>
-      <c r="H82" s="28" t="n"/>
+      <c r="H82" s="27" t="n"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3448,31 +3447,31 @@
     </row>
     <row r="83" hidden="1">
       <c r="A83" s="16" t="n"/>
-      <c r="B83" s="54" t="n">
+      <c r="B83" s="53" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D83" s="33" t="inlineStr">
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/32SsR3d</t>
         </is>
       </c>
-      <c r="E83" s="34" t="inlineStr">
+      <c r="E83" s="33" t="inlineStr">
         <is>
           <t>Teclado Gamer Led Rgb Multimídia Com Fio Pt-br Qwerty Inova</t>
         </is>
       </c>
-      <c r="F83" s="32" t="n"/>
-      <c r="G83" s="35" t="inlineStr">
+      <c r="F83" s="31" t="n"/>
+      <c r="G83" s="34" t="inlineStr">
         <is>
           <t>Inova</t>
         </is>
       </c>
-      <c r="H83" s="32" t="inlineStr">
+      <c r="H83" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -3485,31 +3484,31 @@
     </row>
     <row r="84" hidden="1">
       <c r="A84" s="16" t="n"/>
-      <c r="B84" s="28" t="n">
+      <c r="B84" s="27" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="28" t="inlineStr">
+      <c r="C84" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D84" s="29" t="inlineStr">
+      <c r="D84" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1DNzGQi</t>
         </is>
       </c>
-      <c r="E84" s="30" t="inlineStr">
+      <c r="E84" s="29" t="inlineStr">
         <is>
           <t>Teclado Semi-mecânico Gamer Rgb Usb Shop Finos Pc Console</t>
         </is>
       </c>
-      <c r="F84" s="28" t="n"/>
-      <c r="G84" s="31" t="inlineStr">
+      <c r="F84" s="27" t="n"/>
+      <c r="G84" s="30" t="inlineStr">
         <is>
           <t>Shop Finos</t>
         </is>
       </c>
-      <c r="H84" s="28" t="n"/>
+      <c r="H84" s="27" t="n"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3518,31 +3517,31 @@
     </row>
     <row r="85" hidden="1">
       <c r="A85" s="16" t="n"/>
-      <c r="B85" s="28" t="n">
+      <c r="B85" s="27" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="28" t="inlineStr">
+      <c r="C85" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D85" s="29" t="inlineStr">
+      <c r="D85" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2xBx1Tq</t>
         </is>
       </c>
-      <c r="E85" s="30" t="inlineStr">
+      <c r="E85" s="29" t="inlineStr">
         <is>
           <t>Teclado Pro X Tkl Rapid Gamer Com Fio Branco Logitech G</t>
         </is>
       </c>
-      <c r="F85" s="28" t="n"/>
-      <c r="G85" s="31" t="inlineStr">
+      <c r="F85" s="27" t="n"/>
+      <c r="G85" s="30" t="inlineStr">
         <is>
           <t>Shop Finos</t>
         </is>
       </c>
-      <c r="H85" s="28" t="n"/>
+      <c r="H85" s="27" t="n"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3551,31 +3550,31 @@
     </row>
     <row r="86" hidden="1">
       <c r="A86" s="16" t="n"/>
-      <c r="B86" s="28" t="n">
+      <c r="B86" s="27" t="n">
         <v>85</v>
       </c>
-      <c r="C86" s="28" t="inlineStr">
+      <c r="C86" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D86" s="29" t="inlineStr">
+      <c r="D86" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2NhJeVD</t>
         </is>
       </c>
-      <c r="E86" s="30" t="inlineStr">
+      <c r="E86" s="29" t="inlineStr">
         <is>
           <t>Teclado Gamer Switch Magnético Attack Shark 8000hz X68 He</t>
         </is>
       </c>
-      <c r="F86" s="28" t="n"/>
-      <c r="G86" s="31" t="inlineStr">
+      <c r="F86" s="27" t="n"/>
+      <c r="G86" s="30" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H86" s="28" t="n"/>
+      <c r="H86" s="27" t="n"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3584,31 +3583,31 @@
     </row>
     <row r="87" hidden="1">
       <c r="A87" s="16" t="n"/>
-      <c r="B87" s="28" t="n">
+      <c r="B87" s="27" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="28" t="inlineStr">
+      <c r="C87" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D87" s="29" t="inlineStr">
+      <c r="D87" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2RGpCCn</t>
         </is>
       </c>
-      <c r="E87" s="30" t="inlineStr">
+      <c r="E87" s="29" t="inlineStr">
         <is>
           <t>Teclado E Mouse Mecânico Com Fio De 98 Teclas Para Jogos+rgb</t>
         </is>
       </c>
-      <c r="F87" s="28" t="n"/>
-      <c r="G87" s="31" t="inlineStr">
+      <c r="F87" s="27" t="n"/>
+      <c r="G87" s="30" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H87" s="28" t="n"/>
+      <c r="H87" s="27" t="n"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3617,97 +3616,97 @@
     </row>
     <row r="88" hidden="1">
       <c r="A88" s="16" t="n"/>
-      <c r="B88" s="28" t="n">
+      <c r="B88" s="27" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="28" t="inlineStr">
+      <c r="C88" s="27" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D88" s="29" t="inlineStr">
+      <c r="D88" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1WKzhP5</t>
         </is>
       </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="E88" s="29" t="inlineStr">
         <is>
           <t>Teclado Mecânico Com Fio Conjunto De Mouse Luz De Fundo Rgb</t>
         </is>
       </c>
-      <c r="F88" s="28" t="n"/>
-      <c r="G88" s="31" t="inlineStr">
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="30" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H88" s="28" t="n"/>
+      <c r="H88" s="27" t="n"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" s="16" t="n"/>
-      <c r="B89" s="28" t="n">
+      <c r="B89" s="27" t="n">
         <v>88</v>
       </c>
-      <c r="C89" s="28" t="inlineStr">
+      <c r="C89" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D89" s="29" t="inlineStr">
+      <c r="D89" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1EHHo28</t>
         </is>
       </c>
-      <c r="E89" s="30" t="inlineStr">
+      <c r="E89" s="29" t="inlineStr">
         <is>
           <t>Fone Ouvido Bluetooth 5.4 Sem Fio Estojo De Carregamento Anti Ruido A Prova Dagua Compatível Com Ios Samsung Galaxy Android Tws Wireless Air Premium Microfone Touch Marca Pro Phone See</t>
         </is>
       </c>
-      <c r="F89" s="28" t="n"/>
-      <c r="G89" s="31" t="inlineStr">
+      <c r="F89" s="27" t="n"/>
+      <c r="G89" s="30" t="inlineStr">
         <is>
           <t>PRO PHONE SEE</t>
         </is>
       </c>
-      <c r="H89" s="28" t="n"/>
+      <c r="H89" s="27" t="n"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" s="16" t="n"/>
-      <c r="B90" s="36" t="n">
+      <c r="B90" s="35" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="36" t="inlineStr">
+      <c r="C90" s="35" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D90" s="37" t="inlineStr">
+      <c r="D90" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1vyVnBY</t>
         </is>
       </c>
-      <c r="E90" s="38" t="inlineStr">
+      <c r="E90" s="37" t="inlineStr">
         <is>
           <t>Fones de ouvido Bluetooth esportivos sem fio Ipx7 5.3.650 mAh, Bluetooth 5.3, cancelamento de ruído Enc, tela LED, resistência à água IPX7, para negócios, entretenimento e corrida</t>
         </is>
       </c>
-      <c r="F90" s="36" t="n"/>
-      <c r="G90" s="39" t="inlineStr">
+      <c r="F90" s="35" t="n"/>
+      <c r="G90" s="38" t="inlineStr">
         <is>
           <t>MerttoBX28</t>
         </is>
       </c>
-      <c r="H90" s="36" t="inlineStr">
+      <c r="H90" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -3718,75 +3717,75 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="1">
       <c r="A91" s="16" t="n"/>
-      <c r="B91" s="28" t="n">
+      <c r="B91" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="28" t="inlineStr">
+      <c r="C91" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D91" s="29" t="inlineStr">
+      <c r="D91" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2ZmHugN</t>
         </is>
       </c>
-      <c r="E91" s="30" t="inlineStr">
+      <c r="E91" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Sem Fio Bluetooth Esportivo Gancho De Orelha Beexcellent</t>
         </is>
       </c>
-      <c r="F91" s="28" t="n"/>
-      <c r="G91" s="31" t="inlineStr">
+      <c r="F91" s="27" t="n"/>
+      <c r="G91" s="30" t="inlineStr">
         <is>
           <t>Beexcellent</t>
         </is>
       </c>
-      <c r="H91" s="28" t="n"/>
+      <c r="H91" s="27" t="n"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" s="16" t="n"/>
-      <c r="B92" s="28" t="n">
+      <c r="B92" s="27" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="28" t="inlineStr">
+      <c r="C92" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D92" s="29" t="inlineStr">
+      <c r="D92" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1y3PyiV</t>
         </is>
       </c>
-      <c r="E92" s="30" t="inlineStr">
+      <c r="E92" s="29" t="inlineStr">
         <is>
           <t>Fone de ouvido Tws Philips Tat1109bk/00 preto Ipx4</t>
         </is>
       </c>
-      <c r="F92" s="28" t="n"/>
-      <c r="G92" s="31" t="inlineStr">
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="30" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H92" s="28" t="n"/>
+      <c r="H92" s="27" t="n"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="1">
       <c r="A93" s="3" t="n"/>
-      <c r="B93" s="54" t="n">
+      <c r="B93" s="53" t="n">
         <v>92</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3809,99 +3808,99 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94" s="16" t="n"/>
-      <c r="B94" s="28" t="n">
+      <c r="B94" s="27" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="28" t="inlineStr">
+      <c r="C94" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D94" s="29" t="inlineStr">
+      <c r="D94" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2Kr9VSQ</t>
         </is>
       </c>
-      <c r="E94" s="30" t="inlineStr">
+      <c r="E94" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido In-ear Bluetooth Sem Fio TWS Branco air confortavel wireless charge case</t>
         </is>
       </c>
-      <c r="F94" s="28" t="n"/>
-      <c r="G94" s="31" t="inlineStr">
+      <c r="F94" s="27" t="n"/>
+      <c r="G94" s="30" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H94" s="28" t="n"/>
+      <c r="H94" s="27" t="n"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95" s="16" t="n"/>
-      <c r="B95" s="28" t="n">
+      <c r="B95" s="27" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="28" t="inlineStr">
+      <c r="C95" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D95" s="29" t="inlineStr">
+      <c r="D95" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2haN2CW</t>
         </is>
       </c>
-      <c r="E95" s="30" t="inlineStr">
+      <c r="E95" s="29" t="inlineStr">
         <is>
           <t>Hivi Fone De Ouvido Bluetooth 5.0 Par Sem Fio Duplo Cor Preto</t>
         </is>
       </c>
-      <c r="F95" s="28" t="n"/>
-      <c r="G95" s="31" t="inlineStr">
+      <c r="F95" s="27" t="n"/>
+      <c r="G95" s="30" t="inlineStr">
         <is>
           <t>Hivi ltda</t>
         </is>
       </c>
-      <c r="H95" s="28" t="n"/>
+      <c r="H95" s="27" t="n"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" s="16" t="n"/>
-      <c r="B96" s="36" t="n">
+      <c r="B96" s="35" t="n">
         <v>95</v>
       </c>
-      <c r="C96" s="36" t="inlineStr">
+      <c r="C96" s="35" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D96" s="37" t="inlineStr">
+      <c r="D96" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1G18uM3</t>
         </is>
       </c>
-      <c r="E96" s="38" t="inlineStr">
+      <c r="E96" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Jbl Tune Flex 2 Preto</t>
         </is>
       </c>
-      <c r="F96" s="36" t="n"/>
-      <c r="G96" s="39" t="inlineStr">
+      <c r="F96" s="35" t="n"/>
+      <c r="G96" s="38" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H96" s="36" t="inlineStr">
+      <c r="H96" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -3912,42 +3911,42 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97" s="16" t="n"/>
-      <c r="B97" s="28" t="n">
+      <c r="B97" s="27" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="28" t="inlineStr">
+      <c r="C97" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D97" s="29" t="inlineStr">
+      <c r="D97" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2wu3ra9</t>
         </is>
       </c>
-      <c r="E97" s="30" t="inlineStr">
+      <c r="E97" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Soundcore by Anker P20i Graves Poderosos e Impactantes Bluetooth 5.3 30H de Reprodução Resistência à Água 2 Mics IA para Chamadas Claras Personalização de Som via App Cor Preto</t>
         </is>
       </c>
-      <c r="F97" s="28" t="n"/>
-      <c r="G97" s="31" t="inlineStr">
+      <c r="F97" s="27" t="n"/>
+      <c r="G97" s="30" t="inlineStr">
         <is>
           <t>Soundcore</t>
         </is>
       </c>
-      <c r="H97" s="28" t="n"/>
+      <c r="H97" s="27" t="n"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98" s="3" t="n"/>
-      <c r="B98" s="54" t="n">
+      <c r="B98" s="53" t="n">
         <v>97</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3970,95 +3969,95 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99" s="3" t="n"/>
-      <c r="B99" s="28" t="n">
+      <c r="B99" s="27" t="n">
         <v>98</v>
       </c>
-      <c r="C99" s="28" t="inlineStr">
+      <c r="C99" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D99" s="29" t="inlineStr">
+      <c r="D99" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2L2DTy9</t>
         </is>
       </c>
-      <c r="E99" s="30" t="inlineStr">
+      <c r="E99" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Branco</t>
         </is>
       </c>
-      <c r="F99" s="28" t="n"/>
-      <c r="G99" s="28" t="n"/>
-      <c r="H99" s="28" t="n"/>
+      <c r="F99" s="27" t="n"/>
+      <c r="G99" s="27" t="n"/>
+      <c r="H99" s="27" t="n"/>
       <c r="I99" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" s="16" t="n"/>
-      <c r="B100" s="28" t="n">
+      <c r="B100" s="27" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="28" t="inlineStr">
+      <c r="C100" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D100" s="29" t="inlineStr">
+      <c r="D100" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/19F238V</t>
         </is>
       </c>
-      <c r="E100" s="30" t="inlineStr">
+      <c r="E100" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Sem Fio Stage Hero6 TWS Bluetooth 5.2 Cancelamento De Ruído Ativo 35h IPX5 Para Academia, Corrida e Jogos - Stagesound</t>
         </is>
       </c>
-      <c r="F100" s="28" t="n"/>
-      <c r="G100" s="31" t="inlineStr">
+      <c r="F100" s="27" t="n"/>
+      <c r="G100" s="30" t="inlineStr">
         <is>
           <t>Coolme</t>
         </is>
       </c>
-      <c r="H100" s="28" t="n"/>
+      <c r="H100" s="27" t="n"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="16" t="n"/>
-      <c r="B101" s="32" t="n">
+      <c r="B101" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="C101" s="32" t="inlineStr">
+      <c r="C101" s="31" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D101" s="33" t="inlineStr">
+      <c r="D101" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/1c6vAL2</t>
         </is>
       </c>
-      <c r="E101" s="34" t="inlineStr">
+      <c r="E101" s="33" t="inlineStr">
         <is>
           <t>Fone De Ouvido Aberto Indicador De Bateria Ipx7 Para Corrida,fone De Ouvido Bluetooth Com Ear Clip Tws Ows Hifi Esportivo 72h Bateria Ipx7 Prova D'água E Suor Enc Cancelamento Ruído</t>
         </is>
       </c>
-      <c r="F101" s="32" t="n"/>
-      <c r="G101" s="35" t="inlineStr">
+      <c r="F101" s="31" t="n"/>
+      <c r="G101" s="34" t="inlineStr">
         <is>
           <t>Inova Cases</t>
         </is>
       </c>
-      <c r="H101" s="32" t="inlineStr">
+      <c r="H101" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -4069,99 +4068,99 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102" s="16" t="n"/>
-      <c r="B102" s="28" t="n">
+      <c r="B102" s="27" t="n">
         <v>101</v>
       </c>
-      <c r="C102" s="28" t="inlineStr">
+      <c r="C102" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D102" s="29" t="inlineStr">
+      <c r="D102" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2rbugtv</t>
         </is>
       </c>
-      <c r="E102" s="30" t="inlineStr">
+      <c r="E102" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Ear Cuff Ows Hifi 90 Horas Enc Ipx6</t>
         </is>
       </c>
-      <c r="F102" s="28" t="n"/>
-      <c r="G102" s="31" t="inlineStr">
+      <c r="F102" s="27" t="n"/>
+      <c r="G102" s="30" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H102" s="28" t="n"/>
+      <c r="H102" s="27" t="n"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" s="3" t="n"/>
-      <c r="B103" s="28" t="n">
+      <c r="B103" s="27" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="28" t="inlineStr">
+      <c r="C103" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D103" s="29" t="inlineStr">
+      <c r="D103" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1N2GQcc</t>
         </is>
       </c>
-      <c r="E103" s="30" t="inlineStr">
+      <c r="E103" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Sem Fio Wave Buds 2 JBL JBLWBUDS2BLK Preto</t>
         </is>
       </c>
-      <c r="F103" s="28" t="n"/>
-      <c r="G103" s="31" t="inlineStr">
+      <c r="F103" s="27" t="n"/>
+      <c r="G103" s="30" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H103" s="28" t="n"/>
+      <c r="H103" s="27" t="n"/>
       <c r="I103" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" s="16" t="n"/>
-      <c r="B104" s="32" t="n">
+      <c r="B104" s="31" t="n">
         <v>103</v>
       </c>
-      <c r="C104" s="32" t="inlineStr">
+      <c r="C104" s="31" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D104" s="33" t="inlineStr">
+      <c r="D104" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/2wA6HkN</t>
         </is>
       </c>
-      <c r="E104" s="34" t="inlineStr">
+      <c r="E104" s="33" t="inlineStr">
         <is>
           <t>Basike Fone De Ouvido Sem Fio Esportivo Bluetooth5.4 TWS, Corrida Gancho, à prova d'água, Com Gan, Tela LED Dupla, Suporta chamadas de voz, adequadas para Android e IOS, Cor Branco</t>
         </is>
       </c>
-      <c r="F104" s="32" t="n"/>
-      <c r="G104" s="35" t="inlineStr">
+      <c r="F104" s="31" t="n"/>
+      <c r="G104" s="34" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H104" s="32" t="inlineStr">
+      <c r="H104" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -4172,9 +4171,9 @@
         </is>
       </c>
     </row>
-    <row r="105" hidden="1">
+    <row r="105">
       <c r="A105" s="3" t="n"/>
-      <c r="B105" s="54" t="n">
+      <c r="B105" s="53" t="n">
         <v>104</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4197,380 +4196,400 @@
         </is>
       </c>
     </row>
-    <row r="106" hidden="1">
+    <row r="106">
       <c r="A106" s="16" t="n"/>
-      <c r="B106" s="28" t="n">
+      <c r="B106" s="35" t="n">
         <v>105</v>
       </c>
-      <c r="C106" s="28" t="inlineStr">
+      <c r="C106" s="35" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D106" s="29" t="inlineStr">
+      <c r="D106" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2kNgG1Z</t>
         </is>
       </c>
-      <c r="E106" s="30" t="inlineStr">
+      <c r="E106" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Baseus Encok H17 Com Fio P2 3.5mm Premium Cor Branco</t>
         </is>
       </c>
-      <c r="F106" s="28" t="n"/>
-      <c r="G106" s="31" t="inlineStr">
+      <c r="F106" s="35" t="n"/>
+      <c r="G106" s="38" t="inlineStr">
         <is>
           <t>Baseus</t>
         </is>
       </c>
-      <c r="H106" s="28" t="n"/>
+      <c r="H106" s="35" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="107" hidden="1">
+    <row r="107">
       <c r="A107" s="16" t="n"/>
-      <c r="B107" s="28" t="n">
+      <c r="B107" s="35" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="28" t="inlineStr">
+      <c r="C107" s="35" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D107" s="29" t="inlineStr">
+      <c r="D107" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/2P1K5Eq</t>
         </is>
       </c>
-      <c r="E107" s="30" t="inlineStr">
+      <c r="E107" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Tae1126bk In Ear Com Microfone Philips Cor Preto</t>
         </is>
       </c>
-      <c r="F107" s="28" t="n"/>
-      <c r="G107" s="31" t="inlineStr">
+      <c r="F107" s="35" t="n"/>
+      <c r="G107" s="38" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H107" s="28" t="n"/>
+      <c r="H107" s="35" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="108" hidden="1">
+    <row r="108">
       <c r="A108" s="16" t="n"/>
-      <c r="B108" s="28" t="n">
+      <c r="B108" s="35" t="n">
         <v>107</v>
       </c>
-      <c r="C108" s="28" t="inlineStr">
+      <c r="C108" s="35" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D108" s="29" t="inlineStr">
+      <c r="D108" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1jMCFjN</t>
         </is>
       </c>
-      <c r="E108" s="30" t="inlineStr">
+      <c r="E108" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Com Fio Somic Tone Extra Bass Microfone S603 Preto</t>
         </is>
       </c>
-      <c r="F108" s="28" t="n"/>
-      <c r="G108" s="31" t="inlineStr">
+      <c r="F108" s="35" t="n"/>
+      <c r="G108" s="38" t="inlineStr">
         <is>
           <t>Somic Tone</t>
         </is>
       </c>
-      <c r="H108" s="28" t="n"/>
+      <c r="H108" s="35" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="109" hidden="1">
+    <row r="109">
       <c r="A109" s="3" t="n"/>
-      <c r="B109" s="54" t="n">
+      <c r="B109" s="27" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C109" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Vj6R2V</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="3" t="n"/>
-      <c r="G109" s="3" t="n"/>
-      <c r="H109" s="3" t="n"/>
+      <c r="E109" s="29" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="27" t="n"/>
+      <c r="H109" s="27" t="n"/>
       <c r="I109" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="110" hidden="1">
+    <row r="110">
       <c r="A110" s="16" t="n"/>
-      <c r="B110" s="28" t="n">
+      <c r="B110" s="27" t="n">
         <v>109</v>
       </c>
-      <c r="C110" s="28" t="inlineStr">
+      <c r="C110" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D110" s="29" t="inlineStr">
+      <c r="D110" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2m5Y1hr</t>
         </is>
       </c>
-      <c r="E110" s="30" t="inlineStr">
+      <c r="E110" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Retorno Palco Edx Pro Dj In-ear + Case Cor Cristal</t>
         </is>
       </c>
-      <c r="F110" s="28" t="n"/>
-      <c r="G110" s="31" t="inlineStr">
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="30" t="inlineStr">
         <is>
           <t>Mega digital eletronicos</t>
         </is>
       </c>
-      <c r="H110" s="28" t="n"/>
+      <c r="H110" s="27" t="n"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="111" hidden="1">
+    <row r="111">
       <c r="A111" s="16" t="n"/>
-      <c r="B111" s="28" t="n">
+      <c r="B111" s="27" t="n">
         <v>110</v>
       </c>
-      <c r="C111" s="28" t="inlineStr">
+      <c r="C111" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D111" s="29" t="inlineStr">
+      <c r="D111" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/26bqnka</t>
         </is>
       </c>
-      <c r="E111" s="30" t="inlineStr">
+      <c r="E111" s="29" t="inlineStr">
         <is>
           <t>2pcs Fone De Ouvido 1.2m Com Fio 3.5mm Com Microfone Preto</t>
         </is>
       </c>
-      <c r="F111" s="28" t="n"/>
-      <c r="G111" s="31" t="inlineStr">
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="30" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H111" s="28" t="n"/>
+      <c r="H111" s="27" t="n"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="112" hidden="1">
+    <row r="112">
       <c r="A112" s="16" t="n"/>
-      <c r="B112" s="28" t="n">
+      <c r="B112" s="27" t="n">
         <v>111</v>
       </c>
-      <c r="C112" s="28" t="inlineStr">
+      <c r="C112" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D112" s="29" t="inlineStr">
+      <c r="D112" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/14Hqw6W</t>
         </is>
       </c>
-      <c r="E112" s="30" t="inlineStr">
+      <c r="E112" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Com Fio 3.5mm Com Microfone Cor Preto S6</t>
         </is>
       </c>
-      <c r="F112" s="28" t="n"/>
-      <c r="G112" s="31" t="inlineStr">
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="30" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H112" s="28" t="n"/>
+      <c r="H112" s="27" t="n"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="113" hidden="1">
+    <row r="113">
       <c r="A113" s="9" t="n"/>
-      <c r="B113" s="55" t="n">
+      <c r="B113" s="31" t="n">
         <v>112</v>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="31" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D113" s="10" t="inlineStr">
+      <c r="D113" s="32" t="inlineStr">
         <is>
           <t>https://meli.la/2Kef7ag</t>
         </is>
       </c>
-      <c r="E113" s="11" t="n"/>
-      <c r="F113" s="9" t="n"/>
-      <c r="G113" s="9" t="n"/>
-      <c r="H113" s="9" t="n"/>
+      <c r="E113" s="33" t="n"/>
+      <c r="F113" s="31" t="n"/>
+      <c r="G113" s="31" t="n"/>
+      <c r="H113" s="31" t="inlineStr">
+        <is>
+          <t>fora do ar</t>
+        </is>
+      </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="114" hidden="1">
+    <row r="114">
       <c r="A114" s="16" t="n"/>
-      <c r="B114" s="28" t="n">
+      <c r="B114" s="27" t="n">
         <v>113</v>
       </c>
-      <c r="C114" s="28" t="inlineStr">
+      <c r="C114" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D114" s="29" t="inlineStr">
+      <c r="D114" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1WJac2f</t>
         </is>
       </c>
-      <c r="E114" s="30" t="inlineStr">
+      <c r="E114" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Intra-auricular Com Fio 1.2 Metros Original</t>
         </is>
       </c>
-      <c r="F114" s="28" t="n"/>
-      <c r="G114" s="31" t="inlineStr">
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="30" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H114" s="28" t="n"/>
+      <c r="H114" s="27" t="n"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="115" hidden="1">
+    <row r="115">
       <c r="A115" s="16" t="n"/>
-      <c r="B115" s="28" t="n">
+      <c r="B115" s="35" t="n">
         <v>114</v>
       </c>
-      <c r="C115" s="28" t="inlineStr">
+      <c r="C115" s="35" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D115" s="29" t="inlineStr">
+      <c r="D115" s="36" t="inlineStr">
         <is>
           <t>https://meli.la/1KuHyGK</t>
         </is>
       </c>
-      <c r="E115" s="30" t="inlineStr">
+      <c r="E115" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Taue101bk/00 Com Microfone Philips Cor Preto</t>
         </is>
       </c>
-      <c r="F115" s="28" t="n"/>
-      <c r="G115" s="31" t="inlineStr">
+      <c r="F115" s="35" t="n"/>
+      <c r="G115" s="38" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H115" s="28" t="n"/>
+      <c r="H115" s="35" t="inlineStr">
+        <is>
+          <t>estoque baixo</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="116" hidden="1">
+    <row r="116">
       <c r="A116" s="16" t="n"/>
-      <c r="B116" s="28" t="n">
+      <c r="B116" s="27" t="n">
         <v>115</v>
       </c>
-      <c r="C116" s="28" t="inlineStr">
+      <c r="C116" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D116" s="29" t="inlineStr">
+      <c r="D116" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1CpcDEH</t>
         </is>
       </c>
-      <c r="E116" s="30" t="inlineStr">
+      <c r="E116" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Silicone Com Fio 3.5mm Com Controle E Microfo</t>
         </is>
       </c>
-      <c r="F116" s="28" t="n"/>
-      <c r="G116" s="28" t="inlineStr">
+      <c r="F116" s="27" t="n"/>
+      <c r="G116" s="27" t="inlineStr">
         <is>
           <t>Bemmy</t>
         </is>
       </c>
-      <c r="H116" s="28" t="n"/>
+      <c r="H116" s="27" t="n"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="117" hidden="1">
+    <row r="117">
       <c r="A117" s="16" t="n"/>
-      <c r="B117" s="28" t="n">
+      <c r="B117" s="27" t="n">
         <v>116</v>
       </c>
-      <c r="C117" s="28" t="inlineStr">
+      <c r="C117" s="27" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D117" s="29" t="inlineStr">
+      <c r="D117" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1ttbaqV</t>
         </is>
       </c>
-      <c r="E117" s="30" t="inlineStr">
+      <c r="E117" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido In-Ear QKZ AKX para Música e Jogo com Microfone e Cancelamento de Ruído</t>
         </is>
       </c>
-      <c r="F117" s="28" t="n"/>
-      <c r="G117" s="31" t="inlineStr">
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="30" t="inlineStr">
         <is>
           <t>TECHSTORE-QKZ</t>
         </is>
       </c>
-      <c r="H117" s="28" t="n"/>
+      <c r="H117" s="27" t="n"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4579,7 +4598,7 @@
     </row>
     <row r="118" hidden="1">
       <c r="A118" s="3" t="n"/>
-      <c r="B118" s="54" t="n">
+      <c r="B118" s="53" t="n">
         <v>117</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4604,31 +4623,31 @@
     </row>
     <row r="119" hidden="1">
       <c r="A119" s="16" t="n"/>
-      <c r="B119" s="28" t="n">
+      <c r="B119" s="27" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="28" t="inlineStr">
+      <c r="C119" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D119" s="29" t="inlineStr">
+      <c r="D119" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2unSB1K</t>
         </is>
       </c>
-      <c r="E119" s="30" t="inlineStr">
+      <c r="E119" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Gamer Headset Led Rgb Computador Microfone Pc</t>
         </is>
       </c>
-      <c r="F119" s="28" t="n"/>
-      <c r="G119" s="31" t="inlineStr">
+      <c r="F119" s="27" t="n"/>
+      <c r="G119" s="30" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H119" s="28" t="n"/>
+      <c r="H119" s="27" t="n"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4637,31 +4656,31 @@
     </row>
     <row r="120" hidden="1">
       <c r="A120" s="16" t="n"/>
-      <c r="B120" s="28" t="n">
+      <c r="B120" s="27" t="n">
         <v>119</v>
       </c>
-      <c r="C120" s="28" t="inlineStr">
+      <c r="C120" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D120" s="29" t="inlineStr">
+      <c r="D120" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1Rqma2o</t>
         </is>
       </c>
-      <c r="E120" s="30" t="inlineStr">
+      <c r="E120" s="29" t="inlineStr">
         <is>
           <t>Fone de ouvido Headset over-ear gamer Havit H2232D 2xP2, RGB - Preto</t>
         </is>
       </c>
-      <c r="F120" s="28" t="n"/>
-      <c r="G120" s="31" t="inlineStr">
+      <c r="F120" s="27" t="n"/>
+      <c r="G120" s="30" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H120" s="28" t="n"/>
+      <c r="H120" s="27" t="n"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4670,31 +4689,31 @@
     </row>
     <row r="121" hidden="1">
       <c r="A121" s="16" t="n"/>
-      <c r="B121" s="28" t="n">
+      <c r="B121" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="28" t="inlineStr">
+      <c r="C121" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D121" s="29" t="inlineStr">
+      <c r="D121" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2nSWHED</t>
         </is>
       </c>
-      <c r="E121" s="30" t="inlineStr">
+      <c r="E121" s="29" t="inlineStr">
         <is>
           <t>Fone Headset Gamer Profissional Mento Rgb H270-rgb Redragon Cor Preto</t>
         </is>
       </c>
-      <c r="F121" s="28" t="n"/>
-      <c r="G121" s="31" t="inlineStr">
+      <c r="F121" s="27" t="n"/>
+      <c r="G121" s="30" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H121" s="28" t="n"/>
+      <c r="H121" s="27" t="n"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4703,7 +4722,7 @@
     </row>
     <row r="122" hidden="1">
       <c r="A122" s="3" t="n"/>
-      <c r="B122" s="54" t="n">
+      <c r="B122" s="53" t="n">
         <v>121</v>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4728,31 +4747,31 @@
     </row>
     <row r="123" hidden="1">
       <c r="A123" s="16" t="n"/>
-      <c r="B123" s="28" t="n">
+      <c r="B123" s="27" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="28" t="inlineStr">
+      <c r="C123" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D123" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/15fHoqk</t>
         </is>
       </c>
-      <c r="E123" s="30" t="inlineStr">
+      <c r="E123" s="29" t="inlineStr">
         <is>
           <t>Headset over-ear Gamer Quantum 400 Preto LED JBL</t>
         </is>
       </c>
-      <c r="F123" s="28" t="n"/>
-      <c r="G123" s="31" t="inlineStr">
+      <c r="F123" s="27" t="n"/>
+      <c r="G123" s="30" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H123" s="28" t="n"/>
+      <c r="H123" s="27" t="n"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4761,31 +4780,31 @@
     </row>
     <row r="124" hidden="1">
       <c r="A124" s="16" t="n"/>
-      <c r="B124" s="28" t="n">
+      <c r="B124" s="27" t="n">
         <v>123</v>
       </c>
-      <c r="C124" s="28" t="inlineStr">
+      <c r="C124" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D124" s="29" t="inlineStr">
+      <c r="D124" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1wmU4zZ</t>
         </is>
       </c>
-      <c r="E124" s="30" t="inlineStr">
+      <c r="E124" s="29" t="inlineStr">
         <is>
           <t>Headset Gamer Mancer Twilight S, Rainbow, Drivers 40mm Preto</t>
         </is>
       </c>
-      <c r="F124" s="28" t="n"/>
-      <c r="G124" s="28" t="inlineStr">
+      <c r="F124" s="27" t="n"/>
+      <c r="G124" s="27" t="inlineStr">
         <is>
           <t>Mancer</t>
         </is>
       </c>
-      <c r="H124" s="28" t="n"/>
+      <c r="H124" s="27" t="n"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4794,7 +4813,7 @@
     </row>
     <row r="125" hidden="1">
       <c r="A125" s="12" t="n"/>
-      <c r="B125" s="28" t="n">
+      <c r="B125" s="27" t="n">
         <v>124</v>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -4827,31 +4846,31 @@
     </row>
     <row r="126" hidden="1">
       <c r="A126" s="16" t="n"/>
-      <c r="B126" s="28" t="n">
+      <c r="B126" s="27" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="28" t="inlineStr">
+      <c r="C126" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D126" s="29" t="inlineStr">
+      <c r="D126" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2tidt18</t>
         </is>
       </c>
-      <c r="E126" s="30" t="inlineStr">
+      <c r="E126" s="29" t="inlineStr">
         <is>
           <t>Headset Gamer Redragon Zeus Lite Preto P3 H510-lt Preto</t>
         </is>
       </c>
-      <c r="F126" s="28" t="n"/>
-      <c r="G126" s="28" t="inlineStr">
+      <c r="F126" s="27" t="n"/>
+      <c r="G126" s="27" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H126" s="28" t="n"/>
+      <c r="H126" s="27" t="n"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4860,31 +4879,31 @@
     </row>
     <row r="127" hidden="1">
       <c r="A127" s="16" t="n"/>
-      <c r="B127" s="28" t="n">
+      <c r="B127" s="27" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="28" t="inlineStr">
+      <c r="C127" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D127" s="29" t="inlineStr">
+      <c r="D127" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1eNRNSS</t>
         </is>
       </c>
-      <c r="E127" s="30" t="inlineStr">
+      <c r="E127" s="29" t="inlineStr">
         <is>
           <t>Fone Headset Gamer HAVIT H2230d P2 P3 3,5MM Microfone Removível Consoles PC Preto</t>
         </is>
       </c>
-      <c r="F127" s="28" t="n"/>
-      <c r="G127" s="31" t="inlineStr">
+      <c r="F127" s="27" t="n"/>
+      <c r="G127" s="30" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H127" s="28" t="n"/>
+      <c r="H127" s="27" t="n"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4893,31 +4912,31 @@
     </row>
     <row r="128" hidden="1">
       <c r="A128" s="16" t="n"/>
-      <c r="B128" s="28" t="n">
+      <c r="B128" s="27" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="28" t="inlineStr">
+      <c r="C128" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D128" s="29" t="inlineStr">
+      <c r="D128" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1uLNe2m</t>
         </is>
       </c>
-      <c r="E128" s="30" t="inlineStr">
+      <c r="E128" s="29" t="inlineStr">
         <is>
           <t>Fone Headset Gamer Pro H2 Preto Fortrek</t>
         </is>
       </c>
-      <c r="F128" s="28" t="n"/>
-      <c r="G128" s="28" t="inlineStr">
+      <c r="F128" s="27" t="n"/>
+      <c r="G128" s="27" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H128" s="28" t="n"/>
+      <c r="H128" s="27" t="n"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4926,31 +4945,31 @@
     </row>
     <row r="129" hidden="1">
       <c r="A129" s="16" t="n"/>
-      <c r="B129" s="28" t="n">
+      <c r="B129" s="27" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="28" t="inlineStr">
+      <c r="C129" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D129" s="29" t="inlineStr">
+      <c r="D129" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2UUay16</t>
         </is>
       </c>
-      <c r="E129" s="30" t="inlineStr">
+      <c r="E129" s="29" t="inlineStr">
         <is>
           <t>Fone Nubwo® U3 Headset Gamer 3d Estéreo Ouvido Para Pc Ps4</t>
         </is>
       </c>
-      <c r="F129" s="28" t="n"/>
-      <c r="G129" s="31" t="inlineStr">
+      <c r="F129" s="27" t="n"/>
+      <c r="G129" s="30" t="inlineStr">
         <is>
           <t>Nubwo</t>
         </is>
       </c>
-      <c r="H129" s="28" t="n"/>
+      <c r="H129" s="27" t="n"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4959,31 +4978,31 @@
     </row>
     <row r="130" hidden="1">
       <c r="A130" s="16" t="n"/>
-      <c r="B130" s="28" t="n">
+      <c r="B130" s="27" t="n">
         <v>129</v>
       </c>
-      <c r="C130" s="28" t="inlineStr">
+      <c r="C130" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D130" s="29" t="inlineStr">
+      <c r="D130" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2Z5SEKB</t>
         </is>
       </c>
-      <c r="E130" s="28" t="inlineStr">
+      <c r="E130" s="27" t="inlineStr">
         <is>
           <t>Headset Gamer Profissional Onikuma X25 Fone De Ouvido Over-ear Compatível com Ps4/ps5/xbox/one/series/pc com Luz Led RGB Plug 3.5mm com Microfone Flexível Incorporado Cabo De 2.2m Confortável</t>
         </is>
       </c>
-      <c r="F130" s="28" t="n"/>
-      <c r="G130" s="31" t="inlineStr">
+      <c r="F130" s="27" t="n"/>
+      <c r="G130" s="30" t="inlineStr">
         <is>
           <t>Onikuma</t>
         </is>
       </c>
-      <c r="H130" s="28" t="n"/>
+      <c r="H130" s="27" t="n"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4992,31 +5011,31 @@
     </row>
     <row r="131" hidden="1">
       <c r="A131" s="16" t="n"/>
-      <c r="B131" s="28" t="n">
+      <c r="B131" s="27" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="28" t="inlineStr">
+      <c r="C131" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D131" s="29" t="inlineStr">
+      <c r="D131" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1dZBv92</t>
         </is>
       </c>
-      <c r="E131" s="28" t="inlineStr">
+      <c r="E131" s="27" t="inlineStr">
         <is>
           <t>Headset Gamer Havit H2002d Fone de ouvido over-ear gamer Vermelho Compatível com PS4/PS5/xbox/One/Series/pc</t>
         </is>
       </c>
-      <c r="F131" s="28" t="n"/>
-      <c r="G131" s="31" t="inlineStr">
+      <c r="F131" s="27" t="n"/>
+      <c r="G131" s="30" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H131" s="28" t="n"/>
+      <c r="H131" s="27" t="n"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5025,31 +5044,31 @@
     </row>
     <row r="132" hidden="1">
       <c r="A132" s="16" t="n"/>
-      <c r="B132" s="28" t="n">
+      <c r="B132" s="27" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="28" t="inlineStr">
+      <c r="C132" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D132" s="29" t="inlineStr">
+      <c r="D132" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2rBnTKy</t>
         </is>
       </c>
-      <c r="E132" s="30" t="inlineStr">
+      <c r="E132" s="29" t="inlineStr">
         <is>
           <t>Headset Fone Gamer Redragon Pandora 2 Rgb, H350rgb-1 Cor Preto</t>
         </is>
       </c>
-      <c r="F132" s="28" t="n"/>
-      <c r="G132" s="31" t="inlineStr">
+      <c r="F132" s="27" t="n"/>
+      <c r="G132" s="30" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H132" s="28" t="n"/>
+      <c r="H132" s="27" t="n"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5058,31 +5077,31 @@
     </row>
     <row r="133" hidden="1">
       <c r="A133" s="16" t="n"/>
-      <c r="B133" s="28" t="n">
+      <c r="B133" s="27" t="n">
         <v>132</v>
       </c>
-      <c r="C133" s="28" t="inlineStr">
+      <c r="C133" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D133" s="29" t="inlineStr">
+      <c r="D133" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1D1stad</t>
         </is>
       </c>
-      <c r="E133" s="30" t="inlineStr">
+      <c r="E133" s="29" t="inlineStr">
         <is>
           <t>Headset Fifine Ampligame H6 Rgb 7.1 Surround Gamer Cor Preto</t>
         </is>
       </c>
-      <c r="F133" s="28" t="n"/>
-      <c r="G133" s="31" t="inlineStr">
+      <c r="F133" s="27" t="n"/>
+      <c r="G133" s="30" t="inlineStr">
         <is>
           <t>Fifine</t>
         </is>
       </c>
-      <c r="H133" s="28" t="n"/>
+      <c r="H133" s="27" t="n"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5091,31 +5110,31 @@
     </row>
     <row r="134" hidden="1">
       <c r="A134" s="16" t="n"/>
-      <c r="B134" s="28" t="n">
+      <c r="B134" s="27" t="n">
         <v>133</v>
       </c>
-      <c r="C134" s="28" t="inlineStr">
+      <c r="C134" s="27" t="inlineStr">
         <is>
           <t>Fone gamer (headset com fio)</t>
         </is>
       </c>
-      <c r="D134" s="29" t="inlineStr">
+      <c r="D134" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1ZVVbE5</t>
         </is>
       </c>
-      <c r="E134" s="30" t="inlineStr">
+      <c r="E134" s="29" t="inlineStr">
         <is>
           <t>Headset Gamer Mizar ELG, 3D Surround 7.1, Drivers de 50mm, Microfone Omnidirecional, Earpads de Malha Esportiva, Iluminação RGB, Preto, HGMZ</t>
         </is>
       </c>
-      <c r="F134" s="28" t="n"/>
-      <c r="G134" s="31" t="inlineStr">
+      <c r="F134" s="27" t="n"/>
+      <c r="G134" s="30" t="inlineStr">
         <is>
           <t>ELG</t>
         </is>
       </c>
-      <c r="H134" s="28" t="n"/>
+      <c r="H134" s="27" t="n"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5124,31 +5143,31 @@
     </row>
     <row r="135" hidden="1">
       <c r="A135" s="16" t="n"/>
-      <c r="B135" s="28" t="n">
+      <c r="B135" s="27" t="n">
         <v>134</v>
       </c>
-      <c r="C135" s="28" t="inlineStr">
+      <c r="C135" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D135" s="29" t="inlineStr">
+      <c r="D135" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1xR2nNz</t>
         </is>
       </c>
-      <c r="E135" s="30" t="inlineStr">
+      <c r="E135" s="29" t="inlineStr">
         <is>
           <t>Cabo Carregador Usb Tipo C 6a Carregamento Rápido Alta Velocidade Compatível Celulares Smartphones Tablets Resistência Premium Para Xiaomi Samsung Ios Motorola 1 Metro Branco Ezsias Armarinhos</t>
         </is>
       </c>
-      <c r="F135" s="28" t="n"/>
-      <c r="G135" s="31" t="inlineStr">
+      <c r="F135" s="27" t="n"/>
+      <c r="G135" s="30" t="inlineStr">
         <is>
           <t>Ezsias Armarinhos</t>
         </is>
       </c>
-      <c r="H135" s="28" t="n"/>
+      <c r="H135" s="27" t="n"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5157,31 +5176,31 @@
     </row>
     <row r="136" hidden="1">
       <c r="A136" s="16" t="n"/>
-      <c r="B136" s="28" t="n">
+      <c r="B136" s="27" t="n">
         <v>135</v>
       </c>
-      <c r="C136" s="28" t="inlineStr">
+      <c r="C136" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D136" s="29" t="inlineStr">
+      <c r="D136" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1s6goJ3</t>
         </is>
       </c>
-      <c r="E136" s="30" t="inlineStr">
+      <c r="E136" s="29" t="inlineStr">
         <is>
           <t>Cabo Usb X Tipo C Turbo 60w - 2 Metros Celular Notebook 3.1</t>
         </is>
       </c>
-      <c r="F136" s="28" t="n"/>
-      <c r="G136" s="31" t="inlineStr">
+      <c r="F136" s="27" t="n"/>
+      <c r="G136" s="30" t="inlineStr">
         <is>
           <t>Hrebos</t>
         </is>
       </c>
-      <c r="H136" s="28" t="n"/>
+      <c r="H136" s="27" t="n"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5190,31 +5209,31 @@
     </row>
     <row r="137" hidden="1">
       <c r="A137" s="16" t="n"/>
-      <c r="B137" s="28" t="n">
+      <c r="B137" s="27" t="n">
         <v>136</v>
       </c>
-      <c r="C137" s="28" t="inlineStr">
+      <c r="C137" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D137" s="29" t="inlineStr">
+      <c r="D137" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1G4ky69</t>
         </is>
       </c>
-      <c r="E137" s="30" t="inlineStr">
+      <c r="E137" s="29" t="inlineStr">
         <is>
           <t>Cabo Usb Turbo Tipo C Philips Original Carregamento Rapido 1.2 Metro Nylon DLC2628N Cor Vermelho</t>
         </is>
       </c>
-      <c r="F137" s="28" t="n"/>
-      <c r="G137" s="31" t="inlineStr">
+      <c r="F137" s="27" t="n"/>
+      <c r="G137" s="30" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H137" s="28" t="n"/>
+      <c r="H137" s="27" t="n"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5223,31 +5242,31 @@
     </row>
     <row r="138" hidden="1">
       <c r="A138" s="16" t="n"/>
-      <c r="B138" s="28" t="n">
+      <c r="B138" s="27" t="n">
         <v>137</v>
       </c>
-      <c r="C138" s="28" t="inlineStr">
+      <c r="C138" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D138" s="29" t="inlineStr">
+      <c r="D138" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1FATBkB</t>
         </is>
       </c>
-      <c r="E138" s="30" t="inlineStr">
+      <c r="E138" s="29" t="inlineStr">
         <is>
           <t>Cabo Usb Entrada Tipo C A 60w Turbo Ultra Rápido 2 Metros Longo Nylon Blindado Plus Max Trançado Reforçado Resistente Compatível Com Carregador De Celular Pd Qc Usbc Carga E Dados Marca Pro Phone See</t>
         </is>
       </c>
-      <c r="F138" s="28" t="n"/>
-      <c r="G138" s="31" t="inlineStr">
+      <c r="F138" s="27" t="n"/>
+      <c r="G138" s="30" t="inlineStr">
         <is>
           <t>PRO PHONE SEE</t>
         </is>
       </c>
-      <c r="H138" s="28" t="n"/>
+      <c r="H138" s="27" t="n"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5256,31 +5275,31 @@
     </row>
     <row r="139" hidden="1">
       <c r="A139" s="16" t="n"/>
-      <c r="B139" s="28" t="n">
+      <c r="B139" s="27" t="n">
         <v>138</v>
       </c>
-      <c r="C139" s="28" t="inlineStr">
+      <c r="C139" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D139" s="29" t="inlineStr">
+      <c r="D139" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/2z251cg</t>
         </is>
       </c>
-      <c r="E139" s="30" t="inlineStr">
+      <c r="E139" s="29" t="inlineStr">
         <is>
           <t>Cabo Usb Carregador Celular Usb C Tipo C 3 Metros Turbo 4.0</t>
         </is>
       </c>
-      <c r="F139" s="28" t="n"/>
-      <c r="G139" s="31" t="inlineStr">
+      <c r="F139" s="27" t="n"/>
+      <c r="G139" s="30" t="inlineStr">
         <is>
           <t>Hrebos</t>
         </is>
       </c>
-      <c r="H139" s="28" t="n"/>
+      <c r="H139" s="27" t="n"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5289,176 +5308,176 @@
     </row>
     <row r="140" hidden="1">
       <c r="A140" s="16" t="n"/>
-      <c r="B140" s="28" t="n">
+      <c r="B140" s="27" t="n">
         <v>139</v>
       </c>
-      <c r="C140" s="28" t="inlineStr">
+      <c r="C140" s="27" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D140" s="29" t="inlineStr">
+      <c r="D140" s="28" t="inlineStr">
         <is>
           <t>https://meli.la/1rbUMsD</t>
         </is>
       </c>
-      <c r="E140" s="30" t="inlineStr">
+      <c r="E140" s="29" t="inlineStr">
         <is>
           <t>Cabo Usb Tipo C 2 Metros Carregador Turbo Compatível Com Motorola Moto G Samsung Galaxy Xiaomi Redmi iPhone 15 16 17 Pro Max Carplay Ps5 Super Rápido</t>
         </is>
       </c>
-      <c r="F140" s="28" t="n"/>
-      <c r="G140" s="31" t="inlineStr">
+      <c r="F140" s="27" t="n"/>
+      <c r="G140" s="30" t="inlineStr">
         <is>
           <t>rgbsgames e pipas</t>
         </is>
       </c>
-      <c r="H140" s="28" t="n"/>
+      <c r="H140" s="27" t="n"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="141" hidden="1" customFormat="1" s="56">
+    <row r="141" hidden="1" customFormat="1" s="55">
       <c r="A141" s="16" t="n"/>
-      <c r="B141" s="28" t="n">
+      <c r="B141" s="27" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="28" t="inlineStr">
+      <c r="C141" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D141" s="40" t="inlineStr">
+      <c r="D141" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2qiZA87</t>
         </is>
       </c>
-      <c r="E141" s="30" t="inlineStr">
+      <c r="E141" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 128gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 128gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F141" s="28" t="n"/>
-      <c r="G141" s="31" t="inlineStr">
+      <c r="F141" s="27" t="n"/>
+      <c r="G141" s="30" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H141" s="28" t="n"/>
+      <c r="H141" s="27" t="n"/>
     </row>
     <row r="142" hidden="1">
       <c r="A142" s="16" t="n"/>
-      <c r="B142" s="28" t="n">
+      <c r="B142" s="27" t="n">
         <v>141</v>
       </c>
-      <c r="C142" s="28" t="inlineStr">
+      <c r="C142" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D142" s="40" t="inlineStr">
+      <c r="D142" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2CViyMj</t>
         </is>
       </c>
-      <c r="E142" s="30" t="inlineStr">
+      <c r="E142" s="29" t="inlineStr">
         <is>
           <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 32gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
         </is>
       </c>
-      <c r="F142" s="28" t="n"/>
-      <c r="G142" s="31" t="inlineStr">
+      <c r="F142" s="27" t="n"/>
+      <c r="G142" s="30" t="inlineStr">
         <is>
           <t>Gurumania</t>
         </is>
       </c>
-      <c r="H142" s="28" t="n"/>
+      <c r="H142" s="27" t="n"/>
     </row>
     <row r="143" hidden="1">
       <c r="A143" s="16" t="n"/>
-      <c r="B143" s="28" t="n">
+      <c r="B143" s="27" t="n">
         <v>142</v>
       </c>
-      <c r="C143" s="28" t="inlineStr">
+      <c r="C143" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D143" s="40" t="inlineStr">
+      <c r="D143" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/16wgc76</t>
         </is>
       </c>
-      <c r="E143" s="30" t="inlineStr">
+      <c r="E143" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 64gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F143" s="28" t="n"/>
-      <c r="G143" s="31" t="inlineStr">
+      <c r="F143" s="27" t="n"/>
+      <c r="G143" s="30" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H143" s="28" t="n"/>
+      <c r="H143" s="27" t="n"/>
     </row>
     <row r="144" hidden="1">
       <c r="A144" s="16" t="n"/>
-      <c r="B144" s="28" t="n">
+      <c r="B144" s="27" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="28" t="inlineStr">
+      <c r="C144" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D144" s="40" t="inlineStr">
+      <c r="D144" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/11j9MNb</t>
         </is>
       </c>
-      <c r="E144" s="30" t="inlineStr">
+      <c r="E144" s="29" t="inlineStr">
         <is>
           <t>Pendrive Twist preto 64gb multilaser modelo PD590</t>
         </is>
       </c>
-      <c r="F144" s="28" t="n"/>
-      <c r="G144" s="31" t="inlineStr">
+      <c r="F144" s="27" t="n"/>
+      <c r="G144" s="30" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H144" s="28" t="n"/>
+      <c r="H144" s="27" t="n"/>
     </row>
     <row r="145" hidden="1">
       <c r="A145" s="9" t="n"/>
-      <c r="B145" s="55" t="n">
+      <c r="B145" s="54" t="n">
         <v>144</v>
       </c>
-      <c r="C145" s="36" t="inlineStr">
+      <c r="C145" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D145" s="42" t="inlineStr">
+      <c r="D145" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1HWTTfy</t>
         </is>
       </c>
-      <c r="E145" s="38" t="inlineStr">
+      <c r="E145" s="37" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Cruzer Blade 32gb Usb 2.0 Sdcz50-032g-b35 Cor Preto Sem tampa</t>
         </is>
       </c>
-      <c r="F145" s="36" t="n"/>
-      <c r="G145" s="39" t="inlineStr">
+      <c r="F145" s="35" t="n"/>
+      <c r="G145" s="38" t="inlineStr">
         <is>
           <t>SanDisk</t>
         </is>
       </c>
-      <c r="H145" s="36" t="inlineStr">
+      <c r="H145" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5466,286 +5485,286 @@
     </row>
     <row r="146" hidden="1">
       <c r="A146" s="16" t="n"/>
-      <c r="B146" s="28" t="n">
+      <c r="B146" s="27" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="28" t="inlineStr">
+      <c r="C146" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D146" s="40" t="inlineStr">
+      <c r="D146" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2zCrUDN</t>
         </is>
       </c>
-      <c r="E146" s="30" t="inlineStr">
+      <c r="E146" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F146" s="28" t="n"/>
-      <c r="G146" s="31" t="inlineStr">
+      <c r="F146" s="27" t="n"/>
+      <c r="G146" s="30" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H146" s="28" t="n"/>
+      <c r="H146" s="27" t="n"/>
     </row>
     <row r="147" hidden="1">
       <c r="A147" s="16" t="n"/>
-      <c r="B147" s="28" t="n">
+      <c r="B147" s="27" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="28" t="inlineStr">
+      <c r="C147" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D147" s="40" t="inlineStr">
+      <c r="D147" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/29Wfdp7</t>
         </is>
       </c>
-      <c r="E147" s="30" t="inlineStr">
+      <c r="E147" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Ótima De Armazenamento Pc Notebook Haixia Cor Prateado</t>
         </is>
       </c>
-      <c r="F147" s="28" t="n"/>
-      <c r="G147" s="31" t="inlineStr">
+      <c r="F147" s="27" t="n"/>
+      <c r="G147" s="30" t="inlineStr">
         <is>
           <t>Haixia</t>
         </is>
       </c>
-      <c r="H147" s="28" t="n"/>
+      <c r="H147" s="27" t="n"/>
     </row>
     <row r="148" hidden="1">
       <c r="A148" s="16" t="n"/>
-      <c r="B148" s="28" t="n">
+      <c r="B148" s="27" t="n">
         <v>147</v>
       </c>
-      <c r="C148" s="28" t="inlineStr">
+      <c r="C148" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D148" s="40" t="inlineStr">
+      <c r="D148" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1BhCm1B</t>
         </is>
       </c>
-      <c r="E148" s="30" t="inlineStr">
+      <c r="E148" s="29" t="inlineStr">
         <is>
           <t>Pendrive Kapbom 16gb Usb 2.0 Metal Prateado Compatível Wind</t>
         </is>
       </c>
-      <c r="F148" s="28" t="n"/>
-      <c r="G148" s="31" t="inlineStr">
+      <c r="F148" s="27" t="n"/>
+      <c r="G148" s="30" t="inlineStr">
         <is>
           <t>Kapbom</t>
         </is>
       </c>
-      <c r="H148" s="28" t="n"/>
+      <c r="H148" s="27" t="n"/>
     </row>
     <row r="149" hidden="1">
       <c r="A149" s="16" t="n"/>
-      <c r="B149" s="28" t="n">
+      <c r="B149" s="27" t="n">
         <v>148</v>
       </c>
-      <c r="C149" s="28" t="inlineStr">
+      <c r="C149" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D149" s="40" t="inlineStr">
+      <c r="D149" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2UUu5Ti</t>
         </is>
       </c>
-      <c r="E149" s="30" t="inlineStr">
+      <c r="E149" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 8gb Usb Compacto Alto Desempenho E Velocidade</t>
         </is>
       </c>
-      <c r="F149" s="28" t="n"/>
-      <c r="G149" s="31" t="inlineStr">
+      <c r="F149" s="27" t="n"/>
+      <c r="G149" s="30" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H149" s="28" t="n"/>
+      <c r="H149" s="27" t="n"/>
     </row>
     <row r="150" hidden="1">
       <c r="A150" s="9" t="n"/>
-      <c r="B150" s="55" t="n">
+      <c r="B150" s="54" t="n">
         <v>149</v>
       </c>
-      <c r="C150" s="36" t="inlineStr">
+      <c r="C150" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D150" s="42" t="inlineStr">
+      <c r="D150" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1Dv34H3</t>
         </is>
       </c>
-      <c r="E150" s="38" t="inlineStr">
+      <c r="E150" s="37" t="inlineStr">
         <is>
           <t>Pendrive 2tb Usb 3.0 Metalico</t>
         </is>
       </c>
-      <c r="F150" s="36" t="n"/>
-      <c r="G150" s="39" t="inlineStr">
+      <c r="F150" s="35" t="n"/>
+      <c r="G150" s="38" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
-      <c r="H150" s="36" t="inlineStr">
+      <c r="H150" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="151" hidden="1" customFormat="1" s="46">
-      <c r="B151" s="47" t="n">
+    <row r="151" hidden="1" customFormat="1" s="45">
+      <c r="B151" s="46" t="n">
         <v>150</v>
       </c>
-      <c r="C151" s="47" t="inlineStr">
+      <c r="C151" s="46" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D151" s="53" t="inlineStr">
+      <c r="D151" s="52" t="inlineStr">
         <is>
           <t>https://meli.la/2qiZA87</t>
         </is>
       </c>
-      <c r="E151" s="49" t="inlineStr">
+      <c r="E151" s="48" t="inlineStr">
         <is>
           <t>Pen Drive 128gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 128gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F151" s="47" t="n"/>
-      <c r="G151" s="50" t="inlineStr">
+      <c r="F151" s="46" t="n"/>
+      <c r="G151" s="49" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H151" s="47" t="n"/>
+      <c r="H151" s="46" t="n"/>
     </row>
     <row r="152" hidden="1">
       <c r="A152" s="16" t="n"/>
-      <c r="B152" s="28" t="n">
+      <c r="B152" s="27" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="28" t="inlineStr">
+      <c r="C152" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D152" s="40" t="inlineStr">
+      <c r="D152" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1zAUW82</t>
         </is>
       </c>
-      <c r="E152" s="30" t="inlineStr">
+      <c r="E152" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 32gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F152" s="30" t="n"/>
-      <c r="G152" s="31" t="inlineStr">
+      <c r="F152" s="29" t="n"/>
+      <c r="G152" s="30" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H152" s="28" t="n"/>
+      <c r="H152" s="27" t="n"/>
     </row>
     <row r="153" hidden="1" ht="21.95" customHeight="1">
       <c r="A153" s="16" t="n"/>
-      <c r="B153" s="28" t="n">
+      <c r="B153" s="27" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="28" t="inlineStr">
+      <c r="C153" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D153" s="40" t="inlineStr">
+      <c r="D153" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1LuoL3b</t>
         </is>
       </c>
-      <c r="E153" s="30" t="inlineStr">
+      <c r="E153" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 16gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F153" s="43" t="n"/>
-      <c r="G153" s="31" t="inlineStr">
+      <c r="F153" s="42" t="n"/>
+      <c r="G153" s="30" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H153" s="28" t="n"/>
+      <c r="H153" s="27" t="n"/>
     </row>
     <row r="154" hidden="1">
       <c r="A154" s="16" t="n"/>
-      <c r="B154" s="28" t="n">
+      <c r="B154" s="27" t="n">
         <v>153</v>
       </c>
-      <c r="C154" s="28" t="inlineStr">
+      <c r="C154" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D154" s="40" t="inlineStr">
+      <c r="D154" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1Q1hTC1</t>
         </is>
       </c>
-      <c r="E154" s="30" t="inlineStr">
+      <c r="E154" s="29" t="inlineStr">
         <is>
           <t>Pendrive Flash Drive 2 Em 1 Usb C E Usb 3.0 32gb Metal Pro</t>
         </is>
       </c>
-      <c r="F154" s="30" t="n"/>
-      <c r="G154" s="31" t="inlineStr">
+      <c r="F154" s="29" t="n"/>
+      <c r="G154" s="30" t="inlineStr">
         <is>
           <t>Pen Drive Celular Mini Pequeno Hrebos</t>
         </is>
       </c>
-      <c r="H154" s="28" t="n"/>
+      <c r="H154" s="27" t="n"/>
     </row>
     <row r="155" hidden="1" ht="21.95" customHeight="1">
       <c r="A155" s="9" t="n"/>
-      <c r="B155" s="55" t="n">
+      <c r="B155" s="54" t="n">
         <v>154</v>
       </c>
-      <c r="C155" s="36" t="inlineStr">
+      <c r="C155" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D155" s="42" t="inlineStr">
+      <c r="D155" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2EC1D2e</t>
         </is>
       </c>
-      <c r="E155" s="38" t="inlineStr">
+      <c r="E155" s="37" t="inlineStr">
         <is>
           <t>Pendrive Altomex AL-U-32 memória 32gb pc notebook usb cor preto liso</t>
         </is>
       </c>
-      <c r="F155" s="44" t="n"/>
-      <c r="G155" s="39" t="inlineStr">
+      <c r="F155" s="43" t="n"/>
+      <c r="G155" s="38" t="inlineStr">
         <is>
           <t>Altomex</t>
         </is>
       </c>
-      <c r="H155" s="36" t="inlineStr">
+      <c r="H155" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5753,7 +5772,7 @@
     </row>
     <row r="156" hidden="1">
       <c r="A156" s="3" t="n"/>
-      <c r="B156" s="54" t="n">
+      <c r="B156" s="53" t="n">
         <v>155</v>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -5778,151 +5797,151 @@
     </row>
     <row r="157" hidden="1">
       <c r="A157" s="16" t="n"/>
-      <c r="B157" s="28" t="n">
+      <c r="B157" s="27" t="n">
         <v>156</v>
       </c>
-      <c r="C157" s="28" t="inlineStr">
+      <c r="C157" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D157" s="40" t="inlineStr">
+      <c r="D157" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1qNb23D</t>
         </is>
       </c>
-      <c r="E157" s="30" t="inlineStr">
+      <c r="E157" s="29" t="inlineStr">
         <is>
           <t>Kingston USB Datatraveler Exodia S 64Gb USB-A 3.2 Gen 1</t>
         </is>
       </c>
-      <c r="F157" s="28" t="n"/>
-      <c r="G157" s="28" t="n"/>
-      <c r="H157" s="28" t="n"/>
+      <c r="F157" s="27" t="n"/>
+      <c r="G157" s="27" t="n"/>
+      <c r="H157" s="27" t="n"/>
     </row>
     <row r="158" hidden="1">
-      <c r="B158" s="28" t="n">
+      <c r="B158" s="27" t="n">
         <v>157</v>
       </c>
-      <c r="C158" s="28" t="inlineStr">
+      <c r="C158" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D158" s="40" t="inlineStr">
+      <c r="D158" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2LbfSKF</t>
         </is>
       </c>
-      <c r="E158" s="30" t="inlineStr">
+      <c r="E158" s="29" t="inlineStr">
         <is>
           <t>Pendrive Kingston Datatraveler Exodia Dtx/64 64gb 3.2 Gen 1</t>
         </is>
       </c>
-      <c r="F158" s="28" t="n"/>
-      <c r="G158" s="28" t="n"/>
-      <c r="H158" s="28" t="n"/>
+      <c r="F158" s="27" t="n"/>
+      <c r="G158" s="27" t="n"/>
+      <c r="H158" s="27" t="n"/>
     </row>
     <row r="159" hidden="1">
-      <c r="B159" s="55" t="n">
+      <c r="B159" s="54" t="n">
         <v>158</v>
       </c>
-      <c r="C159" s="36" t="inlineStr">
+      <c r="C159" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D159" s="42" t="inlineStr">
+      <c r="D159" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2YZWcPv</t>
         </is>
       </c>
-      <c r="E159" s="38" t="inlineStr">
+      <c r="E159" s="37" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Ultra Shift Preto 32gb Usb 3.2</t>
         </is>
       </c>
-      <c r="F159" s="36" t="n"/>
-      <c r="G159" s="36" t="n"/>
-      <c r="H159" s="36" t="inlineStr">
+      <c r="F159" s="35" t="n"/>
+      <c r="G159" s="35" t="n"/>
+      <c r="H159" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
     <row r="160" hidden="1">
-      <c r="B160" s="55" t="n">
+      <c r="B160" s="54" t="n">
         <v>159</v>
       </c>
-      <c r="C160" s="36" t="inlineStr">
+      <c r="C160" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D160" s="42" t="inlineStr">
+      <c r="D160" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/11UGXL4</t>
         </is>
       </c>
-      <c r="E160" s="38" t="inlineStr">
+      <c r="E160" s="37" t="inlineStr">
         <is>
           <t>SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido</t>
         </is>
       </c>
-      <c r="F160" s="36" t="n"/>
-      <c r="G160" s="36" t="n"/>
-      <c r="H160" s="36" t="inlineStr">
+      <c r="F160" s="35" t="n"/>
+      <c r="G160" s="35" t="n"/>
+      <c r="H160" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
     <row r="161" hidden="1">
-      <c r="B161" s="28" t="n">
+      <c r="B161" s="27" t="n">
         <v>160</v>
       </c>
-      <c r="C161" s="28" t="inlineStr">
+      <c r="C161" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D161" s="40" t="inlineStr">
+      <c r="D161" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1XfkXY4</t>
         </is>
       </c>
-      <c r="E161" s="30" t="inlineStr">
+      <c r="E161" s="29" t="inlineStr">
         <is>
           <t>Pendrive 64gb Usb 3.0 Tipo C Metal Plug &amp; Play Android Vers</t>
         </is>
       </c>
-      <c r="F161" s="30" t="n"/>
-      <c r="G161" s="30" t="n"/>
-      <c r="H161" s="30" t="n"/>
+      <c r="F161" s="29" t="n"/>
+      <c r="G161" s="29" t="n"/>
+      <c r="H161" s="29" t="n"/>
       <c r="I161" s="5" t="n"/>
     </row>
     <row r="162" hidden="1">
-      <c r="B162" s="55" t="n">
+      <c r="B162" s="54" t="n">
         <v>161</v>
       </c>
-      <c r="C162" s="36" t="inlineStr">
+      <c r="C162" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D162" s="42" t="inlineStr">
+      <c r="D162" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/15oUo1F</t>
         </is>
       </c>
-      <c r="E162" s="38" t="inlineStr">
+      <c r="E162" s="37" t="inlineStr">
         <is>
           <t>Pen Drive Sandisk Usb 3.2 Geração 1 Ultra Luxe 128gb</t>
         </is>
       </c>
-      <c r="F162" s="38" t="n"/>
-      <c r="G162" s="38" t="n"/>
-      <c r="H162" s="38" t="inlineStr">
+      <c r="F162" s="37" t="n"/>
+      <c r="G162" s="37" t="n"/>
+      <c r="H162" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5949,7 +5968,7 @@
     </row>
     <row r="163" hidden="1">
       <c r="A163" s="3" t="n"/>
-      <c r="B163" s="54" t="n">
+      <c r="B163" s="53" t="n">
         <v>162</v>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -5957,7 +5976,7 @@
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D163" s="25" t="inlineStr">
+      <c r="D163" s="24" t="inlineStr">
         <is>
           <t>https://meli.la/23sKPyN</t>
         </is>
@@ -5991,28 +6010,28 @@
       <c r="AA163" s="5" t="n"/>
     </row>
     <row r="164" hidden="1" customFormat="1" s="3">
-      <c r="A164" s="26" t="n"/>
-      <c r="B164" s="55" t="n">
+      <c r="A164" s="25" t="n"/>
+      <c r="B164" s="54" t="n">
         <v>163</v>
       </c>
-      <c r="C164" s="36" t="inlineStr">
+      <c r="C164" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D164" s="42" t="inlineStr">
+      <c r="D164" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2LoeExa</t>
         </is>
       </c>
-      <c r="E164" s="38" t="inlineStr">
+      <c r="E164" s="37" t="inlineStr">
         <is>
           <t>Pen Drive SanDisk Ultra Shift 128 GB USB 3.0 Violeta</t>
         </is>
       </c>
-      <c r="F164" s="38" t="n"/>
-      <c r="G164" s="38" t="n"/>
-      <c r="H164" s="38" t="inlineStr">
+      <c r="F164" s="37" t="n"/>
+      <c r="G164" s="37" t="n"/>
+      <c r="H164" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6037,28 +6056,28 @@
       <c r="Z164" s="5" t="n"/>
       <c r="AA164" s="5" t="n"/>
     </row>
-    <row r="165" hidden="1" customFormat="1" s="26">
-      <c r="B165" s="28" t="n">
+    <row r="165" hidden="1" customFormat="1" s="25">
+      <c r="B165" s="27" t="n">
         <v>164</v>
       </c>
-      <c r="C165" s="28" t="inlineStr">
+      <c r="C165" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D165" s="40" t="inlineStr">
+      <c r="D165" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1iL54rx</t>
         </is>
       </c>
-      <c r="E165" s="30" t="inlineStr">
+      <c r="E165" s="29" t="inlineStr">
         <is>
           <t>Kapbom Ka-a-16 Kit C/ 2 Pen-drive De 16 Gb Penmax Usb 2.0 Pc</t>
         </is>
       </c>
-      <c r="F165" s="30" t="n"/>
-      <c r="G165" s="30" t="n"/>
-      <c r="H165" s="30" t="n"/>
+      <c r="F165" s="29" t="n"/>
+      <c r="G165" s="29" t="n"/>
+      <c r="H165" s="29" t="n"/>
       <c r="I165" s="5" t="n"/>
       <c r="J165" s="5" t="n"/>
       <c r="K165" s="5" t="n"/>
@@ -6080,27 +6099,27 @@
       <c r="AA165" s="5" t="n"/>
     </row>
     <row r="166" hidden="1">
-      <c r="B166" s="28" t="n">
+      <c r="B166" s="27" t="n">
         <v>165</v>
       </c>
-      <c r="C166" s="28" t="inlineStr">
+      <c r="C166" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D166" s="40" t="inlineStr">
+      <c r="D166" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1j345xd</t>
         </is>
       </c>
-      <c r="E166" s="30" t="inlineStr">
+      <c r="E166" s="29" t="inlineStr">
         <is>
           <t>Pendrive Altomex Al-u-4 4 4gb 2.0 Preto</t>
         </is>
       </c>
-      <c r="F166" s="30" t="n"/>
-      <c r="G166" s="30" t="n"/>
-      <c r="H166" s="30" t="n"/>
+      <c r="F166" s="29" t="n"/>
+      <c r="G166" s="29" t="n"/>
+      <c r="H166" s="29" t="n"/>
       <c r="I166" s="5" t="n"/>
       <c r="J166" s="5" t="n"/>
       <c r="K166" s="5" t="n"/>
@@ -6122,27 +6141,27 @@
       <c r="AA166" s="5" t="n"/>
     </row>
     <row r="167" hidden="1">
-      <c r="B167" s="28" t="n">
+      <c r="B167" s="27" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="28" t="inlineStr">
+      <c r="C167" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D167" s="40" t="inlineStr">
+      <c r="D167" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1e35itv</t>
         </is>
       </c>
-      <c r="E167" s="30" t="inlineStr">
+      <c r="E167" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 64gb Usb 3.0 De Duplo 2 Em 1 Usb/usb-c 140mb/s</t>
         </is>
       </c>
-      <c r="F167" s="30" t="n"/>
-      <c r="G167" s="30" t="n"/>
-      <c r="H167" s="30" t="n"/>
+      <c r="F167" s="29" t="n"/>
+      <c r="G167" s="29" t="n"/>
+      <c r="H167" s="29" t="n"/>
       <c r="I167" s="5" t="n"/>
       <c r="J167" s="5" t="n"/>
       <c r="K167" s="5" t="n"/>
@@ -6164,27 +6183,27 @@
       <c r="AA167" s="5" t="n"/>
     </row>
     <row r="168" hidden="1">
-      <c r="B168" s="28" t="n">
+      <c r="B168" s="27" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="28" t="inlineStr">
+      <c r="C168" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D168" s="40" t="inlineStr">
+      <c r="D168" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1qjgyca</t>
         </is>
       </c>
-      <c r="E168" s="30" t="inlineStr">
+      <c r="E168" s="29" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Cruzer Blade 32gb 2.0 Usb Original Lacrado</t>
         </is>
       </c>
-      <c r="F168" s="30" t="n"/>
-      <c r="G168" s="30" t="n"/>
-      <c r="H168" s="30" t="n"/>
+      <c r="F168" s="29" t="n"/>
+      <c r="G168" s="29" t="n"/>
+      <c r="H168" s="29" t="n"/>
       <c r="I168" s="5" t="n"/>
       <c r="J168" s="5" t="n"/>
       <c r="K168" s="5" t="n"/>
@@ -6206,27 +6225,27 @@
       <c r="AA168" s="5" t="n"/>
     </row>
     <row r="169" hidden="1">
-      <c r="B169" s="55" t="n">
+      <c r="B169" s="54" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="36" t="inlineStr">
+      <c r="C169" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D169" s="42" t="inlineStr">
+      <c r="D169" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2bUd8Qi</t>
         </is>
       </c>
-      <c r="E169" s="38" t="inlineStr">
+      <c r="E169" s="37" t="inlineStr">
         <is>
           <t>Pendrive SanDisk Cruzer Blade 8GB 2.0 preto e vermelho</t>
         </is>
       </c>
-      <c r="F169" s="38" t="n"/>
-      <c r="G169" s="38" t="n"/>
-      <c r="H169" s="38" t="inlineStr">
+      <c r="F169" s="37" t="n"/>
+      <c r="G169" s="37" t="n"/>
+      <c r="H169" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6252,27 +6271,27 @@
       <c r="AA169" s="5" t="n"/>
     </row>
     <row r="170" hidden="1">
-      <c r="B170" s="28" t="n">
+      <c r="B170" s="27" t="n">
         <v>169</v>
       </c>
-      <c r="C170" s="28" t="inlineStr">
+      <c r="C170" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D170" s="40" t="inlineStr">
+      <c r="D170" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1rPATiL</t>
         </is>
       </c>
-      <c r="E170" s="30" t="inlineStr">
+      <c r="E170" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 16gb Multilaser Twist - Pd588</t>
         </is>
       </c>
-      <c r="F170" s="30" t="n"/>
-      <c r="G170" s="30" t="n"/>
-      <c r="H170" s="30" t="n"/>
+      <c r="F170" s="29" t="n"/>
+      <c r="G170" s="29" t="n"/>
+      <c r="H170" s="29" t="n"/>
       <c r="I170" s="5" t="n"/>
       <c r="J170" s="5" t="n"/>
       <c r="K170" s="5" t="n"/>
@@ -6294,27 +6313,27 @@
       <c r="AA170" s="5" t="n"/>
     </row>
     <row r="171" hidden="1">
-      <c r="B171" s="28" t="n">
+      <c r="B171" s="27" t="n">
         <v>170</v>
       </c>
-      <c r="C171" s="28" t="inlineStr">
+      <c r="C171" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D171" s="40" t="inlineStr">
+      <c r="D171" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2Z5fhDF</t>
         </is>
       </c>
-      <c r="E171" s="30" t="inlineStr">
+      <c r="E171" s="29" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Madeira Redondo Ecológico Personalizado Cor Marrom-claro</t>
         </is>
       </c>
-      <c r="F171" s="30" t="n"/>
-      <c r="G171" s="30" t="n"/>
-      <c r="H171" s="30" t="n"/>
+      <c r="F171" s="29" t="n"/>
+      <c r="G171" s="29" t="n"/>
+      <c r="H171" s="29" t="n"/>
       <c r="I171" s="5" t="n"/>
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="5" t="n"/>
@@ -6336,27 +6355,27 @@
       <c r="AA171" s="5" t="n"/>
     </row>
     <row r="172" hidden="1">
-      <c r="B172" s="55" t="n">
+      <c r="B172" s="54" t="n">
         <v>171</v>
       </c>
-      <c r="C172" s="36" t="inlineStr">
+      <c r="C172" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D172" s="42" t="inlineStr">
+      <c r="D172" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1Ny9BQg</t>
         </is>
       </c>
-      <c r="E172" s="38" t="inlineStr">
+      <c r="E172" s="37" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Ultra Flair Usb 3.0 Metal 150mbs Z73 Sandisk</t>
         </is>
       </c>
-      <c r="F172" s="38" t="n"/>
-      <c r="G172" s="38" t="n"/>
-      <c r="H172" s="38" t="inlineStr">
+      <c r="F172" s="37" t="n"/>
+      <c r="G172" s="37" t="n"/>
+      <c r="H172" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6382,27 +6401,27 @@
       <c r="AA172" s="5" t="n"/>
     </row>
     <row r="173" hidden="1">
-      <c r="B173" s="55" t="n">
+      <c r="B173" s="54" t="n">
         <v>172</v>
       </c>
-      <c r="C173" s="36" t="inlineStr">
+      <c r="C173" s="35" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D173" s="42" t="inlineStr">
+      <c r="D173" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1MHXAZo</t>
         </is>
       </c>
-      <c r="E173" s="38" t="inlineStr">
+      <c r="E173" s="37" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Ultra Shift 256gb Usb 3.2 Gen 1 100mbs Roxo Violeta</t>
         </is>
       </c>
-      <c r="F173" s="38" t="n"/>
-      <c r="G173" s="38" t="n"/>
-      <c r="H173" s="38" t="inlineStr">
+      <c r="F173" s="37" t="n"/>
+      <c r="G173" s="37" t="n"/>
+      <c r="H173" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6428,27 +6447,27 @@
       <c r="AA173" s="5" t="n"/>
     </row>
     <row r="174" hidden="1">
-      <c r="B174" s="54" t="n">
+      <c r="B174" s="53" t="n">
         <v>173</v>
       </c>
-      <c r="C174" s="32" t="inlineStr">
+      <c r="C174" s="31" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D174" s="45" t="inlineStr">
+      <c r="D174" s="44" t="inlineStr">
         <is>
           <t>https://meli.la/2u6BAdS</t>
         </is>
       </c>
-      <c r="E174" s="34" t="inlineStr">
+      <c r="E174" s="33" t="inlineStr">
         <is>
           <t>Pendrive 32gb 2 Em 1 Usb 3.0 Tipo-c Para Celular Pc Tablet</t>
         </is>
       </c>
-      <c r="F174" s="34" t="n"/>
-      <c r="G174" s="34" t="n"/>
-      <c r="H174" s="34" t="inlineStr">
+      <c r="F174" s="33" t="n"/>
+      <c r="G174" s="33" t="n"/>
+      <c r="H174" s="33" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -6474,27 +6493,27 @@
       <c r="AA174" s="5" t="n"/>
     </row>
     <row r="175" hidden="1">
-      <c r="B175" s="28" t="n">
+      <c r="B175" s="27" t="n">
         <v>174</v>
       </c>
-      <c r="C175" s="28" t="inlineStr">
+      <c r="C175" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D175" s="40" t="inlineStr">
+      <c r="D175" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2KYJowg</t>
         </is>
       </c>
-      <c r="E175" s="30" t="inlineStr">
+      <c r="E175" s="29" t="inlineStr">
         <is>
           <t>Pendrive Altomex 128gb Usb 2.0 Al-u-128 Alta Velocidade - Preto</t>
         </is>
       </c>
-      <c r="F175" s="30" t="n"/>
-      <c r="G175" s="30" t="n"/>
-      <c r="H175" s="30" t="n"/>
+      <c r="F175" s="29" t="n"/>
+      <c r="G175" s="29" t="n"/>
+      <c r="H175" s="29" t="n"/>
       <c r="I175" s="5" t="n"/>
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="5" t="n"/>
@@ -6516,27 +6535,27 @@
       <c r="AA175" s="5" t="n"/>
     </row>
     <row r="176" hidden="1">
-      <c r="B176" s="28" t="n">
+      <c r="B176" s="27" t="n">
         <v>175</v>
       </c>
-      <c r="C176" s="28" t="inlineStr">
+      <c r="C176" s="27" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D176" s="40" t="inlineStr">
+      <c r="D176" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2niAQ49</t>
         </is>
       </c>
-      <c r="E176" s="30" t="inlineStr">
+      <c r="E176" s="29" t="inlineStr">
         <is>
           <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 128gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
         </is>
       </c>
-      <c r="F176" s="30" t="n"/>
-      <c r="G176" s="30" t="n"/>
-      <c r="H176" s="30" t="n"/>
+      <c r="F176" s="29" t="n"/>
+      <c r="G176" s="29" t="n"/>
+      <c r="H176" s="29" t="n"/>
       <c r="I176" s="5" t="n"/>
       <c r="J176" s="5" t="n"/>
       <c r="K176" s="5" t="n"/>
@@ -6558,27 +6577,27 @@
       <c r="AA176" s="5" t="n"/>
     </row>
     <row r="177" hidden="1">
-      <c r="B177" s="28" t="n">
+      <c r="B177" s="27" t="n">
         <v>176</v>
       </c>
-      <c r="C177" s="28" t="inlineStr">
+      <c r="C177" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D177" s="40" t="inlineStr">
+      <c r="D177" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1Z5VJQ6</t>
         </is>
       </c>
-      <c r="E177" s="30" t="inlineStr">
+      <c r="E177" s="29" t="inlineStr">
         <is>
           <t>Mousepad De Escritório Pequeno Preto Tecido Simples Fortrek</t>
         </is>
       </c>
-      <c r="F177" s="30" t="n"/>
-      <c r="G177" s="30" t="n"/>
-      <c r="H177" s="30" t="n"/>
+      <c r="F177" s="29" t="n"/>
+      <c r="G177" s="29" t="n"/>
+      <c r="H177" s="29" t="n"/>
       <c r="I177" s="5" t="n"/>
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="5" t="n"/>
@@ -6600,27 +6619,27 @@
       <c r="AA177" s="5" t="n"/>
     </row>
     <row r="178" hidden="1">
-      <c r="B178" s="28" t="n">
+      <c r="B178" s="27" t="n">
         <v>177</v>
       </c>
-      <c r="C178" s="28" t="inlineStr">
+      <c r="C178" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D178" s="40" t="inlineStr">
+      <c r="D178" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1fheaUW</t>
         </is>
       </c>
-      <c r="E178" s="30" t="inlineStr">
+      <c r="E178" s="29" t="inlineStr">
         <is>
           <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Grafite Desenho impresso Courino</t>
         </is>
       </c>
-      <c r="F178" s="30" t="n"/>
-      <c r="G178" s="30" t="n"/>
-      <c r="H178" s="30" t="n"/>
+      <c r="F178" s="29" t="n"/>
+      <c r="G178" s="29" t="n"/>
+      <c r="H178" s="29" t="n"/>
       <c r="I178" s="5" t="n"/>
       <c r="J178" s="5" t="n"/>
       <c r="K178" s="5" t="n"/>
@@ -6642,27 +6661,27 @@
       <c r="AA178" s="5" t="n"/>
     </row>
     <row r="179" hidden="1">
-      <c r="B179" s="28" t="n">
+      <c r="B179" s="27" t="n">
         <v>178</v>
       </c>
-      <c r="C179" s="28" t="inlineStr">
+      <c r="C179" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D179" s="40" t="inlineStr">
+      <c r="D179" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1vKzJM3</t>
         </is>
       </c>
-      <c r="E179" s="30" t="inlineStr">
+      <c r="E179" s="29" t="inlineStr">
         <is>
           <t>Mouse Pad Com Apoio Ergonômico Em Espuma Para Punho Antiderrapante Confortável Para Escritório Gamer Estudo Trabalho Preto Megalodonte</t>
         </is>
       </c>
-      <c r="F179" s="30" t="n"/>
-      <c r="G179" s="30" t="n"/>
-      <c r="H179" s="30" t="n"/>
+      <c r="F179" s="29" t="n"/>
+      <c r="G179" s="29" t="n"/>
+      <c r="H179" s="29" t="n"/>
       <c r="I179" s="5" t="n"/>
       <c r="J179" s="5" t="n"/>
       <c r="K179" s="5" t="n"/>
@@ -6684,27 +6703,27 @@
       <c r="AA179" s="5" t="n"/>
     </row>
     <row r="180" hidden="1">
-      <c r="B180" s="55" t="n">
+      <c r="B180" s="54" t="n">
         <v>179</v>
       </c>
-      <c r="C180" s="36" t="inlineStr">
+      <c r="C180" s="35" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D180" s="42" t="inlineStr">
+      <c r="D180" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2NPo4eJ</t>
         </is>
       </c>
-      <c r="E180" s="38" t="inlineStr">
+      <c r="E180" s="37" t="inlineStr">
         <is>
           <t>Mousepad Mp-04pt Simples - Hoopso</t>
         </is>
       </c>
-      <c r="F180" s="38" t="n"/>
-      <c r="G180" s="38" t="n"/>
-      <c r="H180" s="38" t="inlineStr">
+      <c r="F180" s="37" t="n"/>
+      <c r="G180" s="37" t="n"/>
+      <c r="H180" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6730,27 +6749,27 @@
       <c r="AA180" s="5" t="n"/>
     </row>
     <row r="181" hidden="1">
-      <c r="B181" s="28" t="n">
+      <c r="B181" s="27" t="n">
         <v>180</v>
       </c>
-      <c r="C181" s="28" t="inlineStr">
+      <c r="C181" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D181" s="40" t="inlineStr">
+      <c r="D181" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1NCrcA6</t>
         </is>
       </c>
-      <c r="E181" s="30" t="inlineStr">
+      <c r="E181" s="29" t="inlineStr">
         <is>
           <t>Mousepad Gamer Speed Havit Pequeno Com Alta Qualidade Cor Preto</t>
         </is>
       </c>
-      <c r="F181" s="30" t="n"/>
-      <c r="G181" s="30" t="n"/>
-      <c r="H181" s="30" t="n"/>
+      <c r="F181" s="29" t="n"/>
+      <c r="G181" s="29" t="n"/>
+      <c r="H181" s="29" t="n"/>
       <c r="I181" s="5" t="n"/>
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="5" t="n"/>
@@ -6772,27 +6791,27 @@
       <c r="AA181" s="5" t="n"/>
     </row>
     <row r="182" hidden="1">
-      <c r="B182" s="28" t="n">
+      <c r="B182" s="27" t="n">
         <v>181</v>
       </c>
-      <c r="C182" s="28" t="inlineStr">
+      <c r="C182" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D182" s="40" t="inlineStr">
+      <c r="D182" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2ASehEZ</t>
         </is>
       </c>
-      <c r="E182" s="30" t="inlineStr">
+      <c r="E182" s="29" t="inlineStr">
         <is>
           <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Caramelo</t>
         </is>
       </c>
-      <c r="F182" s="30" t="n"/>
-      <c r="G182" s="30" t="n"/>
-      <c r="H182" s="30" t="n"/>
+      <c r="F182" s="29" t="n"/>
+      <c r="G182" s="29" t="n"/>
+      <c r="H182" s="29" t="n"/>
       <c r="I182" s="5" t="n"/>
       <c r="J182" s="5" t="n"/>
       <c r="K182" s="5" t="n"/>
@@ -6814,27 +6833,27 @@
       <c r="AA182" s="5" t="n"/>
     </row>
     <row r="183" hidden="1">
-      <c r="B183" s="28" t="n">
+      <c r="B183" s="27" t="n">
         <v>182</v>
       </c>
-      <c r="C183" s="28" t="inlineStr">
+      <c r="C183" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D183" s="40" t="inlineStr">
+      <c r="D183" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/13C2HTp</t>
         </is>
       </c>
-      <c r="E183" s="30" t="inlineStr">
+      <c r="E183" s="29" t="inlineStr">
         <is>
           <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Azul</t>
         </is>
       </c>
-      <c r="F183" s="30" t="n"/>
-      <c r="G183" s="30" t="n"/>
-      <c r="H183" s="30" t="n"/>
+      <c r="F183" s="29" t="n"/>
+      <c r="G183" s="29" t="n"/>
+      <c r="H183" s="29" t="n"/>
       <c r="I183" s="5" t="n"/>
       <c r="J183" s="5" t="n"/>
       <c r="K183" s="5" t="n"/>
@@ -6856,27 +6875,27 @@
       <c r="AA183" s="5" t="n"/>
     </row>
     <row r="184" hidden="1">
-      <c r="B184" s="28" t="n">
+      <c r="B184" s="27" t="n">
         <v>183</v>
       </c>
-      <c r="C184" s="28" t="inlineStr">
+      <c r="C184" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D184" s="40" t="inlineStr">
+      <c r="D184" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2e1VX7E</t>
         </is>
       </c>
-      <c r="E184" s="30" t="inlineStr">
+      <c r="E184" s="29" t="inlineStr">
         <is>
           <t>Mouse Pad Ziphome Preto 23x22.5cm Borracha Tecido Antiderrapante</t>
         </is>
       </c>
-      <c r="F184" s="30" t="n"/>
-      <c r="G184" s="30" t="n"/>
-      <c r="H184" s="30" t="n"/>
+      <c r="F184" s="29" t="n"/>
+      <c r="G184" s="29" t="n"/>
+      <c r="H184" s="29" t="n"/>
       <c r="I184" s="5" t="n"/>
       <c r="J184" s="5" t="n"/>
       <c r="K184" s="5" t="n"/>
@@ -6898,27 +6917,27 @@
       <c r="AA184" s="5" t="n"/>
     </row>
     <row r="185" hidden="1">
-      <c r="B185" s="28" t="n">
+      <c r="B185" s="27" t="n">
         <v>184</v>
       </c>
-      <c r="C185" s="28" t="inlineStr">
+      <c r="C185" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D185" s="40" t="inlineStr">
+      <c r="D185" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2Pn152u</t>
         </is>
       </c>
-      <c r="E185" s="30" t="inlineStr">
+      <c r="E185" s="29" t="inlineStr">
         <is>
           <t>Mouse Pad Pequeno 20x20cm Couro Sintetico Kit 2 Tapete Mesas Cor Quadrado MARFIM Desenho impresso Liso</t>
         </is>
       </c>
-      <c r="F185" s="30" t="n"/>
-      <c r="G185" s="30" t="n"/>
-      <c r="H185" s="30" t="n"/>
+      <c r="F185" s="29" t="n"/>
+      <c r="G185" s="29" t="n"/>
+      <c r="H185" s="29" t="n"/>
       <c r="I185" s="5" t="n"/>
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="5" t="n"/>
@@ -6940,27 +6959,27 @@
       <c r="AA185" s="5" t="n"/>
     </row>
     <row r="186" hidden="1">
-      <c r="B186" s="28" t="n">
+      <c r="B186" s="27" t="n">
         <v>185</v>
       </c>
-      <c r="C186" s="28" t="inlineStr">
+      <c r="C186" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D186" s="40" t="inlineStr">
+      <c r="D186" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1XfeDjK</t>
         </is>
       </c>
-      <c r="E186" s="30" t="inlineStr">
+      <c r="E186" s="29" t="inlineStr">
         <is>
           <t>Tapete Para Mouse Preto Liso Notebook E Escritório Borracha</t>
         </is>
       </c>
-      <c r="F186" s="30" t="n"/>
-      <c r="G186" s="30" t="n"/>
-      <c r="H186" s="30" t="n"/>
+      <c r="F186" s="29" t="n"/>
+      <c r="G186" s="29" t="n"/>
+      <c r="H186" s="29" t="n"/>
       <c r="I186" s="5" t="n"/>
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="5" t="n"/>
@@ -6982,27 +7001,27 @@
       <c r="AA186" s="5" t="n"/>
     </row>
     <row r="187" hidden="1">
-      <c r="B187" s="28" t="n">
+      <c r="B187" s="27" t="n">
         <v>186</v>
       </c>
-      <c r="C187" s="28" t="inlineStr">
+      <c r="C187" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D187" s="40" t="inlineStr">
+      <c r="D187" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2M889UE</t>
         </is>
       </c>
-      <c r="E187" s="30" t="inlineStr">
+      <c r="E187" s="29" t="inlineStr">
         <is>
           <t>Mousepad 20x20cm Couro Sintetico Slim Premium Impermeavel</t>
         </is>
       </c>
-      <c r="F187" s="30" t="n"/>
-      <c r="G187" s="30" t="n"/>
-      <c r="H187" s="30" t="n"/>
+      <c r="F187" s="29" t="n"/>
+      <c r="G187" s="29" t="n"/>
+      <c r="H187" s="29" t="n"/>
       <c r="I187" s="5" t="n"/>
       <c r="J187" s="5" t="n"/>
       <c r="K187" s="5" t="n"/>
@@ -7024,27 +7043,27 @@
       <c r="AA187" s="5" t="n"/>
     </row>
     <row r="188" hidden="1">
-      <c r="B188" s="28" t="n">
+      <c r="B188" s="27" t="n">
         <v>187</v>
       </c>
-      <c r="C188" s="28" t="inlineStr">
+      <c r="C188" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D188" s="40" t="inlineStr">
+      <c r="D188" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2K3HSeC</t>
         </is>
       </c>
-      <c r="E188" s="30" t="inlineStr">
+      <c r="E188" s="29" t="inlineStr">
         <is>
           <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Rosa Desenho impresso Courino</t>
         </is>
       </c>
-      <c r="F188" s="30" t="n"/>
-      <c r="G188" s="30" t="n"/>
-      <c r="H188" s="30" t="n"/>
+      <c r="F188" s="29" t="n"/>
+      <c r="G188" s="29" t="n"/>
+      <c r="H188" s="29" t="n"/>
       <c r="I188" s="5" t="n"/>
       <c r="J188" s="5" t="n"/>
       <c r="K188" s="5" t="n"/>
@@ -7066,27 +7085,27 @@
       <c r="AA188" s="5" t="n"/>
     </row>
     <row r="189" hidden="1">
-      <c r="B189" s="28" t="n">
+      <c r="B189" s="27" t="n">
         <v>188</v>
       </c>
-      <c r="C189" s="28" t="inlineStr">
+      <c r="C189" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D189" s="40" t="inlineStr">
+      <c r="D189" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1iM9KwJ</t>
         </is>
       </c>
-      <c r="E189" s="30" t="inlineStr">
+      <c r="E189" s="29" t="inlineStr">
         <is>
           <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Bege</t>
         </is>
       </c>
-      <c r="F189" s="30" t="n"/>
-      <c r="G189" s="30" t="n"/>
-      <c r="H189" s="30" t="n"/>
+      <c r="F189" s="29" t="n"/>
+      <c r="G189" s="29" t="n"/>
+      <c r="H189" s="29" t="n"/>
       <c r="I189" s="5" t="n"/>
       <c r="J189" s="5" t="n"/>
       <c r="K189" s="5" t="n"/>
@@ -7108,27 +7127,27 @@
       <c r="AA189" s="5" t="n"/>
     </row>
     <row r="190" hidden="1">
-      <c r="B190" s="28" t="n">
+      <c r="B190" s="27" t="n">
         <v>189</v>
       </c>
-      <c r="C190" s="28" t="inlineStr">
+      <c r="C190" s="27" t="inlineStr">
         <is>
           <t>Mousepad simples</t>
         </is>
       </c>
-      <c r="D190" s="40" t="inlineStr">
+      <c r="D190" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2jgnzuA</t>
         </is>
       </c>
-      <c r="E190" s="30" t="inlineStr">
+      <c r="E190" s="29" t="inlineStr">
         <is>
           <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Branco</t>
         </is>
       </c>
-      <c r="F190" s="30" t="n"/>
-      <c r="G190" s="30" t="n"/>
-      <c r="H190" s="30" t="n"/>
+      <c r="F190" s="29" t="n"/>
+      <c r="G190" s="29" t="n"/>
+      <c r="H190" s="29" t="n"/>
       <c r="I190" s="5" t="n"/>
       <c r="J190" s="5" t="n"/>
       <c r="K190" s="5" t="n"/>
@@ -7149,28 +7168,28 @@
       <c r="Z190" s="5" t="n"/>
       <c r="AA190" s="5" t="n"/>
     </row>
-    <row r="191">
-      <c r="B191" s="32" t="n">
+    <row r="191" hidden="1">
+      <c r="B191" s="31" t="n">
         <v>190</v>
       </c>
-      <c r="C191" s="32" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D191" s="45" t="inlineStr">
+      <c r="D191" s="44" t="inlineStr">
         <is>
           <t>https://meli.la/2cGbTdT</t>
         </is>
       </c>
-      <c r="E191" s="34" t="inlineStr">
+      <c r="E191" s="33" t="inlineStr">
         <is>
           <t>Fone Bluetooth 5.3 Tws Sem Fio Anti Ruido A Prova Dagua Compatível Iphone 7 8 X Xr 11 12 13 14 15 16 17 Xs Pro Max Plus Samsung S20 S23 S24 Xiaomi Motorola Android Prova DAgua Wireless Premium</t>
         </is>
       </c>
-      <c r="F191" s="34" t="n"/>
-      <c r="G191" s="34" t="n"/>
-      <c r="H191" s="34" t="inlineStr">
+      <c r="F191" s="33" t="n"/>
+      <c r="G191" s="33" t="n"/>
+      <c r="H191" s="33" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -7195,28 +7214,28 @@
       <c r="Z191" s="5" t="n"/>
       <c r="AA191" s="5" t="n"/>
     </row>
-    <row r="192">
-      <c r="B192" s="28" t="n">
+    <row r="192" hidden="1">
+      <c r="B192" s="27" t="n">
         <v>191</v>
       </c>
-      <c r="C192" s="28" t="inlineStr">
+      <c r="C192" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D192" s="40" t="inlineStr">
+      <c r="D192" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1NTtrP5</t>
         </is>
       </c>
-      <c r="E192" s="30" t="inlineStr">
+      <c r="E192" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth In Ear Touch À Prova D'água Inova</t>
         </is>
       </c>
-      <c r="F192" s="28" t="n"/>
-      <c r="G192" s="28" t="n"/>
-      <c r="H192" s="28" t="n"/>
+      <c r="F192" s="27" t="n"/>
+      <c r="G192" s="27" t="n"/>
+      <c r="H192" s="27" t="n"/>
       <c r="J192" s="5" t="n"/>
       <c r="K192" s="5" t="n"/>
       <c r="L192" s="5" t="n"/>
@@ -7236,419 +7255,419 @@
       <c r="Z192" s="5" t="n"/>
       <c r="AA192" s="5" t="n"/>
     </row>
-    <row r="193">
-      <c r="B193" s="28" t="n">
+    <row r="193" hidden="1">
+      <c r="B193" s="27" t="n">
         <v>192</v>
       </c>
-      <c r="C193" s="28" t="inlineStr">
+      <c r="C193" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D193" s="40" t="inlineStr">
+      <c r="D193" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2PLvtPH</t>
         </is>
       </c>
-      <c r="E193" s="30" t="inlineStr">
+      <c r="E193" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Azul</t>
         </is>
       </c>
-      <c r="F193" s="28" t="n"/>
-      <c r="G193" s="28" t="n"/>
-      <c r="H193" s="28" t="n"/>
-    </row>
-    <row r="194">
-      <c r="B194" s="28" t="n">
+      <c r="F193" s="27" t="n"/>
+      <c r="G193" s="27" t="n"/>
+      <c r="H193" s="27" t="n"/>
+    </row>
+    <row r="194" hidden="1">
+      <c r="B194" s="27" t="n">
         <v>193</v>
       </c>
-      <c r="C194" s="28" t="inlineStr">
+      <c r="C194" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D194" s="40" t="inlineStr">
+      <c r="D194" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2gbZpAz</t>
         </is>
       </c>
-      <c r="E194" s="30" t="inlineStr">
+      <c r="E194" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido Ows Bluetooth Design Aberto Kaidi 794 Cor Preto</t>
         </is>
       </c>
-      <c r="F194" s="28" t="n"/>
-      <c r="G194" s="28" t="n"/>
-      <c r="H194" s="28" t="inlineStr">
+      <c r="F194" s="27" t="n"/>
+      <c r="G194" s="27" t="n"/>
+      <c r="H194" s="27" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="B195" s="28" t="n">
+    <row r="195" hidden="1">
+      <c r="B195" s="27" t="n">
         <v>194</v>
       </c>
-      <c r="C195" s="28" t="inlineStr">
+      <c r="C195" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D195" s="40" t="inlineStr">
+      <c r="D195" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1NTUn6u</t>
         </is>
       </c>
-      <c r="E195" s="30" t="inlineStr">
+      <c r="E195" s="29" t="inlineStr">
         <is>
           <t>Fone Sem Fio Bluetooth 5.4 Compativel Iphone Ipx4 Microfone</t>
         </is>
       </c>
-      <c r="F195" s="28" t="n"/>
-      <c r="G195" s="28" t="n"/>
-      <c r="H195" s="28" t="n"/>
-    </row>
-    <row r="196">
-      <c r="B196" s="28" t="n">
+      <c r="F195" s="27" t="n"/>
+      <c r="G195" s="27" t="n"/>
+      <c r="H195" s="27" t="n"/>
+    </row>
+    <row r="196" hidden="1">
+      <c r="B196" s="27" t="n">
         <v>195</v>
       </c>
-      <c r="C196" s="28" t="inlineStr">
+      <c r="C196" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D196" s="40" t="inlineStr">
+      <c r="D196" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1KFgyz2</t>
         </is>
       </c>
-      <c r="E196" s="30" t="inlineStr">
+      <c r="E196" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido TWS B Basto Fone-TWS Bluetooth Sem Fio Com Cancelamento de Ruído e Microfone</t>
         </is>
       </c>
-      <c r="F196" s="28" t="n"/>
-      <c r="G196" s="28" t="n"/>
-      <c r="H196" s="28" t="n"/>
-    </row>
-    <row r="197">
-      <c r="B197" s="28" t="n">
+      <c r="F196" s="27" t="n"/>
+      <c r="G196" s="27" t="n"/>
+      <c r="H196" s="27" t="n"/>
+    </row>
+    <row r="197" hidden="1">
+      <c r="B197" s="27" t="n">
         <v>196</v>
       </c>
-      <c r="C197" s="28" t="inlineStr">
+      <c r="C197" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D197" s="40" t="inlineStr">
+      <c r="D197" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1XARpGa</t>
         </is>
       </c>
-      <c r="E197" s="30" t="inlineStr">
+      <c r="E197" s="29" t="inlineStr">
         <is>
           <t>Fone Bluetooth 5.4 Sem Fio Tws Kaidi Kd780 Graves Potentes</t>
         </is>
       </c>
-      <c r="F197" s="28" t="n"/>
-      <c r="G197" s="28" t="n"/>
-      <c r="H197" s="28" t="n"/>
-    </row>
-    <row r="198">
-      <c r="B198" s="28" t="n">
+      <c r="F197" s="27" t="n"/>
+      <c r="G197" s="27" t="n"/>
+      <c r="H197" s="27" t="n"/>
+    </row>
+    <row r="198" hidden="1">
+      <c r="B198" s="27" t="n">
         <v>197</v>
       </c>
-      <c r="C198" s="28" t="inlineStr">
+      <c r="C198" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D198" s="40" t="inlineStr">
+      <c r="D198" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/18AJ4f6</t>
         </is>
       </c>
-      <c r="E198" s="30" t="inlineStr">
+      <c r="E198" s="29" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth 5.1 Sem Fio Tws Wireless Bateria Longa Duração E Conexão Rápida Coolmusic</t>
         </is>
       </c>
-      <c r="F198" s="28" t="n"/>
-      <c r="G198" s="28" t="n"/>
-      <c r="H198" s="28" t="n"/>
-    </row>
-    <row r="199">
-      <c r="B199" s="28" t="n">
+      <c r="F198" s="27" t="n"/>
+      <c r="G198" s="27" t="n"/>
+      <c r="H198" s="27" t="n"/>
+    </row>
+    <row r="199" hidden="1">
+      <c r="B199" s="27" t="n">
         <v>198</v>
       </c>
-      <c r="C199" s="28" t="inlineStr">
+      <c r="C199" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D199" s="40" t="inlineStr">
+      <c r="D199" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2GHMGcW</t>
         </is>
       </c>
-      <c r="E199" s="30" t="inlineStr">
+      <c r="E199" s="29" t="inlineStr">
         <is>
           <t>Fone Qcy N30 Anc Bluetooth 5.4 Multiponto Ipx4 Cor Preto</t>
         </is>
       </c>
-      <c r="F199" s="28" t="n"/>
-      <c r="G199" s="28" t="n"/>
-      <c r="H199" s="28" t="n"/>
-    </row>
-    <row r="200">
-      <c r="B200" s="36" t="n">
+      <c r="F199" s="27" t="n"/>
+      <c r="G199" s="27" t="n"/>
+      <c r="H199" s="27" t="n"/>
+    </row>
+    <row r="200" hidden="1">
+      <c r="B200" s="35" t="n">
         <v>199</v>
       </c>
-      <c r="C200" s="36" t="inlineStr">
+      <c r="C200" s="35" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D200" s="42" t="inlineStr">
+      <c r="D200" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1jGZwC3</t>
         </is>
       </c>
-      <c r="E200" s="38" t="inlineStr">
+      <c r="E200" s="37" t="inlineStr">
         <is>
           <t>Fone De Ouvido Esportivos Sem Fio Bluetooth Impermeável Ipx6</t>
         </is>
       </c>
-      <c r="F200" s="36" t="n"/>
-      <c r="G200" s="36" t="n"/>
-      <c r="H200" s="36" t="inlineStr">
+      <c r="F200" s="35" t="n"/>
+      <c r="G200" s="35" t="n"/>
+      <c r="H200" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="B201" s="28" t="n">
+    <row r="201" hidden="1">
+      <c r="B201" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="C201" s="28" t="inlineStr">
+      <c r="C201" s="27" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D201" s="40" t="inlineStr">
+      <c r="D201" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2G3uu5c</t>
         </is>
       </c>
-      <c r="E201" s="30" t="inlineStr">
+      <c r="E201" s="29" t="inlineStr">
         <is>
           <t>Fone de Ouvido Eardbud AIWA AWS-EB-04-B Bluetooth IPX4 ANC 26 Horas de bateria</t>
         </is>
       </c>
-      <c r="F201" s="28" t="n"/>
-      <c r="G201" s="28" t="n"/>
-      <c r="H201" s="28" t="inlineStr">
+      <c r="F201" s="27" t="n"/>
+      <c r="G201" s="27" t="n"/>
+      <c r="H201" s="27" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="B202" s="32" t="n">
+    <row r="202" hidden="1">
+      <c r="B202" s="31" t="n">
         <v>201</v>
       </c>
-      <c r="C202" s="32" t="inlineStr">
+      <c r="C202" s="31" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D202" s="45" t="inlineStr">
+      <c r="D202" s="44" t="inlineStr">
         <is>
           <t>https://meli.la/1A65TWL</t>
         </is>
       </c>
-      <c r="E202" s="34" t="inlineStr">
+      <c r="E202" s="33" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Redmi Buds 6 Play Xiaomi Sem Fio Cor Preto</t>
         </is>
       </c>
-      <c r="F202" s="32" t="n"/>
-      <c r="G202" s="32" t="n"/>
-      <c r="H202" s="32" t="inlineStr">
+      <c r="F202" s="31" t="n"/>
+      <c r="G202" s="31" t="n"/>
+      <c r="H202" s="31" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
       </c>
     </row>
     <row r="203" hidden="1">
-      <c r="B203" s="54" t="n">
+      <c r="B203" s="53" t="n">
         <v>202</v>
       </c>
-      <c r="C203" s="54" t="inlineStr">
+      <c r="C203" s="53" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D203" s="57" t="inlineStr">
+      <c r="D203" s="56" t="inlineStr">
         <is>
           <t>https://meli.la/1HyuGqq</t>
         </is>
       </c>
-      <c r="E203" s="58" t="inlineStr">
+      <c r="E203" s="57" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Dual Bluetooth 2.4GHz USB Recarregável Silencioso Para Notebook PC</t>
         </is>
       </c>
-      <c r="F203" s="54" t="n"/>
-      <c r="G203" s="54" t="n"/>
-      <c r="H203" s="54" t="n"/>
+      <c r="F203" s="53" t="n"/>
+      <c r="G203" s="53" t="n"/>
+      <c r="H203" s="53" t="n"/>
       <c r="I203" s="3" t="n"/>
     </row>
     <row r="204" hidden="1">
       <c r="A204" s="16" t="n"/>
-      <c r="B204" s="28" t="n">
+      <c r="B204" s="27" t="n">
         <v>203</v>
       </c>
-      <c r="C204" s="28" t="inlineStr">
+      <c r="C204" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D204" s="40" t="inlineStr">
+      <c r="D204" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2gZQECx</t>
         </is>
       </c>
-      <c r="E204" s="30" t="inlineStr">
+      <c r="E204" s="29" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Bluetooth Recarregável Hrebos IF-216 Prateado USB Para Windows</t>
         </is>
       </c>
-      <c r="F204" s="28" t="n"/>
-      <c r="G204" s="28" t="n"/>
-      <c r="H204" s="28" t="n"/>
+      <c r="F204" s="27" t="n"/>
+      <c r="G204" s="27" t="n"/>
+      <c r="H204" s="27" t="n"/>
     </row>
     <row r="205" hidden="1">
       <c r="A205" s="16" t="n"/>
-      <c r="B205" s="28" t="n">
+      <c r="B205" s="27" t="n">
         <v>204</v>
       </c>
-      <c r="C205" s="28" t="inlineStr">
+      <c r="C205" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D205" s="40" t="inlineStr">
+      <c r="D205" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1LM6zpe</t>
         </is>
       </c>
-      <c r="E205" s="30" t="inlineStr">
+      <c r="E205" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio Logitech M280 com Pilha Inclusa - Cinza</t>
         </is>
       </c>
-      <c r="F205" s="28" t="n"/>
-      <c r="G205" s="28" t="n"/>
-      <c r="H205" s="28" t="n"/>
+      <c r="F205" s="27" t="n"/>
+      <c r="G205" s="27" t="n"/>
+      <c r="H205" s="27" t="n"/>
     </row>
     <row r="206" hidden="1">
       <c r="A206" s="16" t="n"/>
-      <c r="B206" s="28" t="n">
+      <c r="B206" s="27" t="n">
         <v>205</v>
       </c>
-      <c r="C206" s="28" t="inlineStr">
+      <c r="C206" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D206" s="40" t="inlineStr">
+      <c r="D206" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/1ECoJrH</t>
         </is>
       </c>
-      <c r="E206" s="30" t="inlineStr">
+      <c r="E206" s="29" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Logitech M196 Com Conexão Bluetooth - Branco</t>
         </is>
       </c>
-      <c r="F206" s="28" t="n"/>
-      <c r="G206" s="28" t="n"/>
-      <c r="H206" s="28" t="n"/>
+      <c r="F206" s="27" t="n"/>
+      <c r="G206" s="27" t="n"/>
+      <c r="H206" s="27" t="n"/>
     </row>
     <row r="207" hidden="1">
       <c r="A207" s="16" t="n"/>
-      <c r="B207" s="28" t="n">
+      <c r="B207" s="27" t="n">
         <v>206</v>
       </c>
-      <c r="C207" s="28" t="inlineStr">
+      <c r="C207" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D207" s="40" t="inlineStr">
+      <c r="D207" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2B1DT57</t>
         </is>
       </c>
-      <c r="E207" s="30" t="inlineStr">
+      <c r="E207" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio Logitech M185 - Cinza</t>
         </is>
       </c>
-      <c r="F207" s="28" t="n"/>
-      <c r="G207" s="28" t="n"/>
-      <c r="H207" s="28" t="n"/>
+      <c r="F207" s="27" t="n"/>
+      <c r="G207" s="27" t="n"/>
+      <c r="H207" s="27" t="n"/>
     </row>
     <row r="208" hidden="1">
       <c r="A208" s="16" t="n"/>
-      <c r="B208" s="28" t="n">
+      <c r="B208" s="27" t="n">
         <v>207</v>
       </c>
-      <c r="C208" s="28" t="inlineStr">
+      <c r="C208" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D208" s="40" t="inlineStr">
+      <c r="D208" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2bjhTN4</t>
         </is>
       </c>
-      <c r="E208" s="30" t="inlineStr">
+      <c r="E208" s="29" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Preto Z3700 V0l79aa Hp</t>
         </is>
       </c>
-      <c r="F208" s="28" t="n"/>
-      <c r="G208" s="28" t="n"/>
-      <c r="H208" s="28" t="n"/>
+      <c r="F208" s="27" t="n"/>
+      <c r="G208" s="27" t="n"/>
+      <c r="H208" s="27" t="n"/>
     </row>
     <row r="209" hidden="1">
       <c r="A209" s="16" t="n"/>
-      <c r="B209" s="55" t="n">
+      <c r="B209" s="54" t="n">
         <v>208</v>
       </c>
-      <c r="C209" s="36" t="inlineStr">
+      <c r="C209" s="35" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D209" s="42" t="inlineStr">
+      <c r="D209" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2UKmjJK</t>
         </is>
       </c>
-      <c r="E209" s="38" t="inlineStr">
+      <c r="E209" s="37" t="inlineStr">
         <is>
           <t>Mouse Oriente Sem Fio 1600 Dpi Maxprint Branco</t>
         </is>
       </c>
-      <c r="F209" s="36" t="n"/>
-      <c r="G209" s="36" t="n"/>
-      <c r="H209" s="36" t="inlineStr">
+      <c r="F209" s="35" t="n"/>
+      <c r="G209" s="35" t="n"/>
+      <c r="H209" s="35" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -7656,431 +7675,431 @@
     </row>
     <row r="210" hidden="1">
       <c r="A210" s="16" t="n"/>
-      <c r="B210" s="28" t="n">
+      <c r="B210" s="27" t="n">
         <v>209</v>
       </c>
-      <c r="C210" s="28" t="inlineStr">
+      <c r="C210" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D210" s="40" t="inlineStr">
+      <c r="D210" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/2mZP8Mf</t>
         </is>
       </c>
-      <c r="E210" s="30" t="inlineStr">
+      <c r="E210" s="29" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Compacto Lenovo 300 Cinza Claro Gy51l15677</t>
         </is>
       </c>
-      <c r="F210" s="28" t="n"/>
-      <c r="G210" s="28" t="n"/>
-      <c r="H210" s="28" t="n"/>
+      <c r="F210" s="27" t="n"/>
+      <c r="G210" s="27" t="n"/>
+      <c r="H210" s="27" t="n"/>
     </row>
     <row r="211" hidden="1">
       <c r="A211" s="16" t="n"/>
-      <c r="B211" s="28" t="n">
+      <c r="B211" s="27" t="n">
         <v>210</v>
       </c>
-      <c r="C211" s="28" t="inlineStr">
+      <c r="C211" s="27" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D211" s="40" t="inlineStr">
+      <c r="D211" s="39" t="inlineStr">
         <is>
           <t>https://meli.la/18G4RGk</t>
         </is>
       </c>
-      <c r="E211" s="30" t="inlineStr">
+      <c r="E211" s="29" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Multilaser Office - Design Ergonômico e Conexão 2.4GHz - MO251</t>
         </is>
       </c>
-      <c r="F211" s="28" t="n"/>
-      <c r="G211" s="28" t="n"/>
-      <c r="H211" s="28" t="n"/>
+      <c r="F211" s="27" t="n"/>
+      <c r="G211" s="27" t="n"/>
+      <c r="H211" s="27" t="n"/>
     </row>
     <row r="212" hidden="1">
-      <c r="B212" s="28" t="n">
+      <c r="B212" s="27" t="n">
         <v>211</v>
       </c>
-      <c r="E212" s="20" t="n"/>
+      <c r="E212" s="19" t="n"/>
     </row>
     <row r="213" hidden="1">
-      <c r="B213" s="28" t="n">
+      <c r="B213" s="27" t="n">
         <v>212</v>
       </c>
-      <c r="E213" s="20" t="n"/>
+      <c r="E213" s="19" t="n"/>
     </row>
     <row r="214" hidden="1">
-      <c r="B214" s="28" t="n">
+      <c r="B214" s="27" t="n">
         <v>213</v>
       </c>
-      <c r="E214" s="22" t="n"/>
+      <c r="E214" s="21" t="n"/>
     </row>
     <row r="215" hidden="1">
-      <c r="B215" s="28" t="n">
+      <c r="B215" s="27" t="n">
         <v>214</v>
       </c>
-      <c r="E215" s="22" t="n"/>
+      <c r="E215" s="21" t="n"/>
     </row>
     <row r="216" hidden="1">
-      <c r="B216" s="28" t="n">
+      <c r="B216" s="27" t="n">
         <v>215</v>
       </c>
-      <c r="E216" s="20" t="n"/>
+      <c r="E216" s="19" t="n"/>
     </row>
     <row r="217" hidden="1" ht="15.6" customHeight="1">
-      <c r="B217" s="28" t="n">
+      <c r="B217" s="27" t="n">
         <v>216</v>
       </c>
-      <c r="E217" s="21" t="n"/>
+      <c r="E217" s="20" t="n"/>
     </row>
     <row r="218" hidden="1">
-      <c r="B218" s="28" t="n">
+      <c r="B218" s="27" t="n">
         <v>217</v>
       </c>
-      <c r="E218" s="20" t="n"/>
+      <c r="E218" s="19" t="n"/>
     </row>
     <row r="219" hidden="1">
-      <c r="B219" s="28" t="n">
+      <c r="B219" s="27" t="n">
         <v>218</v>
       </c>
-      <c r="E219" s="20" t="n"/>
+      <c r="E219" s="19" t="n"/>
     </row>
     <row r="220" hidden="1">
-      <c r="B220" s="28" t="n">
+      <c r="B220" s="27" t="n">
         <v>219</v>
       </c>
-      <c r="E220" s="20" t="n"/>
+      <c r="E220" s="19" t="n"/>
     </row>
     <row r="221" hidden="1">
-      <c r="B221" s="28" t="n">
+      <c r="B221" s="27" t="n">
         <v>220</v>
       </c>
-      <c r="E221" s="20" t="n"/>
+      <c r="E221" s="19" t="n"/>
     </row>
     <row r="222" hidden="1">
-      <c r="B222" s="28" t="n">
+      <c r="B222" s="27" t="n">
         <v>221</v>
       </c>
-      <c r="E222" s="20" t="n"/>
+      <c r="E222" s="19" t="n"/>
     </row>
     <row r="223" hidden="1">
-      <c r="B223" s="28" t="n">
+      <c r="B223" s="27" t="n">
         <v>222</v>
       </c>
-      <c r="E223" s="20" t="n"/>
+      <c r="E223" s="19" t="n"/>
     </row>
     <row r="224" hidden="1">
-      <c r="B224" s="28" t="n">
+      <c r="B224" s="27" t="n">
         <v>223</v>
       </c>
-      <c r="E224" s="20" t="n"/>
+      <c r="E224" s="19" t="n"/>
     </row>
     <row r="225" hidden="1">
-      <c r="B225" s="28" t="n">
+      <c r="B225" s="27" t="n">
         <v>224</v>
       </c>
-      <c r="E225" s="20" t="n"/>
+      <c r="E225" s="19" t="n"/>
     </row>
     <row r="226" hidden="1">
-      <c r="B226" s="28" t="n">
+      <c r="B226" s="27" t="n">
         <v>225</v>
       </c>
-      <c r="E226" s="20" t="n"/>
+      <c r="E226" s="19" t="n"/>
     </row>
     <row r="227" hidden="1">
-      <c r="B227" s="28" t="n">
+      <c r="B227" s="27" t="n">
         <v>226</v>
       </c>
-      <c r="E227" s="20" t="n"/>
+      <c r="E227" s="19" t="n"/>
     </row>
     <row r="228" hidden="1">
-      <c r="B228" s="28" t="n">
+      <c r="B228" s="27" t="n">
         <v>227</v>
       </c>
-      <c r="E228" s="20" t="n"/>
+      <c r="E228" s="19" t="n"/>
     </row>
     <row r="229" hidden="1">
-      <c r="B229" s="28" t="n">
+      <c r="B229" s="27" t="n">
         <v>228</v>
       </c>
-      <c r="E229" s="20" t="n"/>
+      <c r="E229" s="19" t="n"/>
     </row>
     <row r="230" hidden="1">
-      <c r="B230" s="28" t="n">
+      <c r="B230" s="27" t="n">
         <v>229</v>
       </c>
-      <c r="E230" s="20" t="n"/>
+      <c r="E230" s="19" t="n"/>
     </row>
     <row r="231" hidden="1">
-      <c r="B231" s="28" t="n">
+      <c r="B231" s="27" t="n">
         <v>230</v>
       </c>
-      <c r="E231" s="20" t="n"/>
+      <c r="E231" s="19" t="n"/>
     </row>
     <row r="232" hidden="1">
-      <c r="B232" s="28" t="n">
+      <c r="B232" s="27" t="n">
         <v>231</v>
       </c>
-      <c r="E232" s="20" t="n"/>
+      <c r="E232" s="19" t="n"/>
     </row>
     <row r="233" hidden="1">
-      <c r="B233" s="28" t="n">
+      <c r="B233" s="27" t="n">
         <v>232</v>
       </c>
-      <c r="E233" s="20" t="n"/>
+      <c r="E233" s="19" t="n"/>
     </row>
     <row r="234" hidden="1">
-      <c r="B234" s="28" t="n">
+      <c r="B234" s="27" t="n">
         <v>233</v>
       </c>
-      <c r="E234" s="20" t="n"/>
+      <c r="E234" s="19" t="n"/>
     </row>
     <row r="235" hidden="1">
-      <c r="B235" s="28" t="n">
+      <c r="B235" s="27" t="n">
         <v>234</v>
       </c>
-      <c r="E235" s="20" t="n"/>
+      <c r="E235" s="19" t="n"/>
     </row>
     <row r="236" hidden="1">
-      <c r="B236" s="28" t="n">
+      <c r="B236" s="27" t="n">
         <v>235</v>
       </c>
-      <c r="E236" s="20" t="n"/>
+      <c r="E236" s="19" t="n"/>
     </row>
     <row r="237" hidden="1">
-      <c r="B237" s="28" t="n">
+      <c r="B237" s="27" t="n">
         <v>236</v>
       </c>
-      <c r="E237" s="20" t="n"/>
+      <c r="E237" s="19" t="n"/>
     </row>
     <row r="238" hidden="1">
-      <c r="B238" s="28" t="n">
+      <c r="B238" s="27" t="n">
         <v>237</v>
       </c>
-      <c r="E238" s="20" t="n"/>
+      <c r="E238" s="19" t="n"/>
     </row>
     <row r="239" hidden="1">
-      <c r="B239" s="28" t="n">
+      <c r="B239" s="27" t="n">
         <v>238</v>
       </c>
-      <c r="E239" s="20" t="n"/>
+      <c r="E239" s="19" t="n"/>
     </row>
     <row r="240" hidden="1">
-      <c r="B240" s="28" t="n">
+      <c r="B240" s="27" t="n">
         <v>239</v>
       </c>
-      <c r="E240" s="20" t="n"/>
+      <c r="E240" s="19" t="n"/>
     </row>
     <row r="241" hidden="1">
-      <c r="B241" s="28" t="n">
+      <c r="B241" s="27" t="n">
         <v>240</v>
       </c>
-      <c r="E241" s="22" t="n"/>
+      <c r="E241" s="21" t="n"/>
     </row>
     <row r="242" hidden="1">
-      <c r="B242" s="28" t="n">
+      <c r="B242" s="27" t="n">
         <v>241</v>
       </c>
-      <c r="E242" s="22" t="n"/>
+      <c r="E242" s="21" t="n"/>
     </row>
     <row r="243" hidden="1">
-      <c r="B243" s="28" t="n">
+      <c r="B243" s="27" t="n">
         <v>242</v>
       </c>
-      <c r="E243" s="20" t="n"/>
+      <c r="E243" s="19" t="n"/>
     </row>
     <row r="244" hidden="1" ht="15.6" customHeight="1">
-      <c r="B244" s="28" t="n">
+      <c r="B244" s="27" t="n">
         <v>243</v>
       </c>
-      <c r="E244" s="21" t="n"/>
+      <c r="E244" s="20" t="n"/>
     </row>
     <row r="245" hidden="1">
-      <c r="B245" s="28" t="n">
+      <c r="B245" s="27" t="n">
         <v>244</v>
       </c>
-      <c r="E245" s="20" t="n"/>
+      <c r="E245" s="19" t="n"/>
     </row>
     <row r="246" hidden="1">
-      <c r="B246" s="28" t="n">
+      <c r="B246" s="27" t="n">
         <v>245</v>
       </c>
-      <c r="E246" s="20" t="n"/>
+      <c r="E246" s="19" t="n"/>
     </row>
     <row r="247" hidden="1">
-      <c r="B247" s="28" t="n">
+      <c r="B247" s="27" t="n">
         <v>246</v>
       </c>
-      <c r="E247" s="20" t="n"/>
+      <c r="E247" s="19" t="n"/>
     </row>
     <row r="248" hidden="1">
-      <c r="B248" s="28" t="n">
+      <c r="B248" s="27" t="n">
         <v>247</v>
       </c>
-      <c r="E248" s="20" t="n"/>
+      <c r="E248" s="19" t="n"/>
     </row>
     <row r="249" hidden="1">
-      <c r="B249" s="28" t="n">
+      <c r="B249" s="27" t="n">
         <v>248</v>
       </c>
-      <c r="E249" s="20" t="n"/>
+      <c r="E249" s="19" t="n"/>
     </row>
     <row r="250" hidden="1">
-      <c r="B250" s="28" t="n">
+      <c r="B250" s="27" t="n">
         <v>249</v>
       </c>
-      <c r="E250" s="20" t="n"/>
+      <c r="E250" s="19" t="n"/>
     </row>
     <row r="251" hidden="1">
-      <c r="B251" s="28" t="n">
+      <c r="B251" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="E251" s="20" t="n"/>
+      <c r="E251" s="19" t="n"/>
     </row>
     <row r="252" hidden="1">
-      <c r="B252" s="28" t="n">
+      <c r="B252" s="27" t="n">
         <v>251</v>
       </c>
-      <c r="E252" s="20" t="n"/>
+      <c r="E252" s="19" t="n"/>
     </row>
     <row r="253" hidden="1">
-      <c r="B253" s="28" t="n">
+      <c r="B253" s="27" t="n">
         <v>252</v>
       </c>
-      <c r="E253" s="20" t="n"/>
+      <c r="E253" s="19" t="n"/>
     </row>
     <row r="254">
-      <c r="E254" s="20" t="n"/>
+      <c r="E254" s="19" t="n"/>
     </row>
     <row r="255">
-      <c r="E255" s="20" t="n"/>
+      <c r="E255" s="19" t="n"/>
     </row>
     <row r="256">
-      <c r="E256" s="20" t="n"/>
+      <c r="E256" s="19" t="n"/>
     </row>
     <row r="257">
-      <c r="E257" s="20" t="n"/>
+      <c r="E257" s="19" t="n"/>
     </row>
     <row r="258">
-      <c r="E258" s="20" t="n"/>
+      <c r="E258" s="19" t="n"/>
     </row>
     <row r="259">
-      <c r="E259" s="20" t="n"/>
+      <c r="E259" s="19" t="n"/>
     </row>
     <row r="260">
-      <c r="E260" s="20" t="n"/>
+      <c r="E260" s="19" t="n"/>
     </row>
     <row r="261">
-      <c r="E261" s="20" t="n"/>
+      <c r="E261" s="19" t="n"/>
     </row>
     <row r="262">
-      <c r="E262" s="20" t="n"/>
+      <c r="E262" s="19" t="n"/>
     </row>
     <row r="263">
-      <c r="E263" s="20" t="n"/>
+      <c r="E263" s="19" t="n"/>
     </row>
     <row r="264">
-      <c r="E264" s="20" t="n"/>
+      <c r="E264" s="19" t="n"/>
     </row>
     <row r="265">
-      <c r="E265" s="20" t="n"/>
+      <c r="E265" s="19" t="n"/>
     </row>
     <row r="266">
-      <c r="E266" s="20" t="n"/>
+      <c r="E266" s="19" t="n"/>
     </row>
     <row r="267">
-      <c r="E267" s="20" t="n"/>
+      <c r="E267" s="19" t="n"/>
     </row>
     <row r="268">
-      <c r="E268" s="22" t="n"/>
+      <c r="E268" s="21" t="n"/>
     </row>
     <row r="269">
-      <c r="E269" s="22" t="n"/>
+      <c r="E269" s="21" t="n"/>
     </row>
     <row r="270">
-      <c r="E270" s="20" t="n"/>
+      <c r="E270" s="19" t="n"/>
     </row>
     <row r="271" ht="15.6" customHeight="1">
-      <c r="E271" s="21" t="n"/>
+      <c r="E271" s="20" t="n"/>
     </row>
     <row r="272">
-      <c r="E272" s="20" t="n"/>
+      <c r="E272" s="19" t="n"/>
     </row>
     <row r="273">
-      <c r="E273" s="20" t="n"/>
+      <c r="E273" s="19" t="n"/>
     </row>
     <row r="274">
-      <c r="E274" s="20" t="n"/>
+      <c r="E274" s="19" t="n"/>
     </row>
     <row r="275">
-      <c r="E275" s="20" t="n"/>
+      <c r="E275" s="19" t="n"/>
     </row>
     <row r="276">
-      <c r="E276" s="20" t="n"/>
+      <c r="E276" s="19" t="n"/>
     </row>
     <row r="277">
-      <c r="E277" s="20" t="n"/>
+      <c r="E277" s="19" t="n"/>
     </row>
     <row r="278">
-      <c r="E278" s="20" t="n"/>
+      <c r="E278" s="19" t="n"/>
     </row>
     <row r="279">
-      <c r="E279" s="20" t="n"/>
+      <c r="E279" s="19" t="n"/>
     </row>
     <row r="280">
-      <c r="E280" s="20" t="n"/>
+      <c r="E280" s="19" t="n"/>
     </row>
     <row r="281">
-      <c r="E281" s="20" t="n"/>
+      <c r="E281" s="19" t="n"/>
     </row>
     <row r="282">
-      <c r="E282" s="20" t="n"/>
+      <c r="E282" s="19" t="n"/>
     </row>
     <row r="283">
-      <c r="E283" s="20" t="n"/>
+      <c r="E283" s="19" t="n"/>
     </row>
     <row r="284">
-      <c r="E284" s="20" t="n"/>
+      <c r="E284" s="19" t="n"/>
     </row>
     <row r="285">
-      <c r="E285" s="20" t="n"/>
+      <c r="E285" s="19" t="n"/>
     </row>
     <row r="286">
-      <c r="E286" s="20" t="n"/>
+      <c r="E286" s="19" t="n"/>
     </row>
     <row r="287">
-      <c r="E287" s="20" t="n"/>
+      <c r="E287" s="19" t="n"/>
     </row>
     <row r="288">
-      <c r="E288" s="20" t="n"/>
+      <c r="E288" s="19" t="n"/>
     </row>
     <row r="289"/>
     <row r="290">
-      <c r="E290" s="20" t="n"/>
+      <c r="E290" s="19" t="n"/>
     </row>
     <row r="291">
-      <c r="E291" s="20" t="n"/>
+      <c r="E291" s="19" t="n"/>
     </row>
     <row r="292"/>
     <row r="293"/>
     <row r="294">
-      <c r="D294" s="20" t="n"/>
-      <c r="E294" s="20" t="n"/>
+      <c r="D294" s="19" t="n"/>
+      <c r="E294" s="19" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="20" t="n"/>
-      <c r="E295" s="19" t="n"/>
+      <c r="D295" s="19" t="n"/>
+      <c r="E295" s="18" t="n"/>
     </row>
     <row r="296">
-      <c r="E296" s="23" t="n"/>
+      <c r="E296" s="22" t="n"/>
     </row>
     <row r="297" ht="21.95" customHeight="1">
-      <c r="E297" s="24" t="n"/>
+      <c r="E297" s="23" t="n"/>
     </row>
     <row r="298"/>
     <row r="299"/>
@@ -9767,7 +9786,7 @@
   <autoFilter ref="A1:I253">
     <filterColumn colId="2" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="Fone sem fio (bluetooth)"/>
+        <filter val="Fone com fio"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9995,7 +10014,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
   </cols>

--- a/Produtos_ml.xlsx
+++ b/Produtos_ml.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Produtos Renomear" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Como usar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos Renomear" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como usar" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos Renomear'!$A$1:$I$253</definedName>
@@ -248,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -271,6 +271,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -292,6 +293,7 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -329,7 +331,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,7 +712,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Validação</t>
         </is>
@@ -759,31 +760,31 @@
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="16" t="n"/>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/16Zu7aQ</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Rosa</t>
         </is>
       </c>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="30" t="inlineStr">
+      <c r="F2" s="29" t="n"/>
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H2" s="27" t="n"/>
+      <c r="H2" s="29" t="n"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -792,31 +793,31 @@
     </row>
     <row r="3" hidden="1">
       <c r="A3" s="16" t="n"/>
-      <c r="B3" s="27" t="n">
+      <c r="B3" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1FKVJ3z</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech Pebble 2 M350s Grafite</t>
         </is>
       </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H3" s="27" t="n"/>
+      <c r="H3" s="29" t="n"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -825,31 +826,31 @@
     </row>
     <row r="4" hidden="1">
       <c r="A4" s="16" t="n"/>
-      <c r="B4" s="27" t="n">
+      <c r="B4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1LJWhVZ</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Mouse Intelbras MSI50 Silencioso Preto</t>
         </is>
       </c>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="30" t="inlineStr">
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>Intelbras</t>
         </is>
       </c>
-      <c r="H4" s="27" t="n"/>
+      <c r="H4" s="29" t="n"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -858,7 +859,7 @@
     </row>
     <row r="5" hidden="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="53" t="n">
+      <c r="B5" s="55" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -887,31 +888,31 @@
     </row>
     <row r="6" hidden="1">
       <c r="A6" s="16" t="n"/>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/24v9AsX</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Azul Claro</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H6" s="27" t="n"/>
+      <c r="H6" s="29" t="n"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -920,31 +921,31 @@
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="16" t="n"/>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2Ax6kZC</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M280 Sem Fio Preto</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H7" s="27" t="n"/>
+      <c r="H7" s="29" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -953,31 +954,31 @@
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="17" t="n"/>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2QtqWZq</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M190 Sem Fio Cinza</t>
         </is>
       </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H8" s="27" t="n"/>
+      <c r="H8" s="29" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -986,31 +987,31 @@
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="16" t="n"/>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2QUUhTR</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Cinza e Preto</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H9" s="27" t="n"/>
+      <c r="H9" s="29" t="n"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1019,31 +1020,31 @@
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="16" t="n"/>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2rqAKxH</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M170 Sem Fio Preto</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H10" s="27" t="n"/>
+      <c r="H10" s="29" t="n"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1052,31 +1053,31 @@
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="16" t="n"/>
-      <c r="B11" s="53" t="n">
+      <c r="B11" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>https://meli.la/1zHhNjb</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Mouse USB 1200 DPI Ergonômico</t>
         </is>
       </c>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>Eduimports</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -1089,31 +1090,31 @@
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="16" t="n"/>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2BdXdPm</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Mouse HP 150 USB Preto</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="H12" s="27" t="n"/>
+      <c r="H12" s="29" t="n"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1122,31 +1123,31 @@
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="16" t="n"/>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1jy5H8M</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>Mouse HP 100 USB 1600 DPI</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="H13" s="27" t="n"/>
+      <c r="H13" s="29" t="n"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1155,31 +1156,31 @@
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="16" t="n"/>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2F8AUwW</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1600 DPI Preto</t>
         </is>
       </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>Megalodonte</t>
         </is>
       </c>
-      <c r="H14" s="27" t="n"/>
+      <c r="H14" s="29" t="n"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1188,31 +1189,31 @@
     </row>
     <row r="15" hidden="1" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="16" t="n"/>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1zquXcb</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1200 DPI Ergonômico</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>Exbom</t>
         </is>
       </c>
-      <c r="H15" s="27" t="n"/>
+      <c r="H15" s="29" t="n"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1221,31 +1222,31 @@
     </row>
     <row r="16" hidden="1" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="3" t="n"/>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>https://meli.la/12UNNBe</t>
         </is>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Mouse USB Óptico 1000 DPI Preto</t>
         </is>
       </c>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="58" t="inlineStr">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Grupo Ecommshops Pró</t>
         </is>
       </c>
-      <c r="H16" s="27" t="n"/>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1254,31 +1255,31 @@
     </row>
     <row r="17" hidden="1">
       <c r="A17" s="9" t="n"/>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="56" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>https://meli.la/1G5EfHd</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>Mouse Dell MS116 USB</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -1291,31 +1292,31 @@
     </row>
     <row r="18" hidden="1">
       <c r="A18" s="16" t="n"/>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1a7Rfrt</t>
         </is>
       </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>Mouse Multilaser Classic Box 1200 DPI</t>
         </is>
       </c>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H18" s="27" t="n"/>
+      <c r="H18" s="29" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1324,31 +1325,31 @@
     </row>
     <row r="19" hidden="1">
       <c r="A19" s="16" t="n"/>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/28xQ9VT</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>Mouse Logitech M90 Com Fio</t>
         </is>
       </c>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="30" t="inlineStr">
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H19" s="27" t="n"/>
+      <c r="H19" s="29" t="n"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1356,28 +1357,24 @@
       </c>
     </row>
     <row r="20" hidden="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="27" t="n">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Mouse com fio</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1cvqKkQ</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>Mouse Óptico com Fio Usb Black 03950 - MS-71 Exbom</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1386,35 +1383,31 @@
     </row>
     <row r="21" hidden="1">
       <c r="A21" s="16" t="n"/>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D21" s="39" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2eiaX1o</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Sem Fio</t>
         </is>
       </c>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H21" s="29" t="n"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1422,28 +1415,24 @@
       </c>
     </row>
     <row r="22" hidden="1">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="27" t="n">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1ieF2X8</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr">
-        <is>
-          <t>Mouse Gamer Redragon King Pro 1K Preto Preto - M916-PRO-1K</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
-      <c r="H22" s="27" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1452,35 +1441,31 @@
     </row>
     <row r="23" hidden="1">
       <c r="A23" s="16" t="n"/>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1ViXRN7</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Attack Shark R1 Branco</t>
         </is>
       </c>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="inlineStr">
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H23" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H23" s="29" t="n"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1488,32 +1473,32 @@
       </c>
     </row>
     <row r="24" hidden="1">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="27" t="n">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/15QeaEY</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Mouse Gamer Tri Mode 18000 DPI</t>
         </is>
       </c>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Fire Phoenix</t>
         </is>
       </c>
-      <c r="H24" s="27" t="n"/>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1521,28 +1506,24 @@
       </c>
     </row>
     <row r="25" hidden="1">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="35" t="n">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/2bq5uLu</t>
         </is>
       </c>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1551,31 +1532,31 @@
     </row>
     <row r="26" hidden="1">
       <c r="A26" s="16" t="n"/>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Bwj698</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 12000 DPI</t>
         </is>
       </c>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H26" s="27" t="n"/>
+      <c r="H26" s="29" t="n"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1584,35 +1565,31 @@
     </row>
     <row r="27" hidden="1">
       <c r="A27" s="16" t="n"/>
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D27" s="36" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2iuRXex</t>
         </is>
       </c>
-      <c r="E27" s="37" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 4K</t>
         </is>
       </c>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="35" t="inlineStr">
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H27" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H27" s="29" t="n"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1621,35 +1598,31 @@
     </row>
     <row r="28" hidden="1">
       <c r="A28" s="16" t="n"/>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/13eJLNw</t>
         </is>
       </c>
-      <c r="E28" s="37" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Shinka 3200 DPI Sem Fio</t>
         </is>
       </c>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="38" t="inlineStr">
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>Shinka</t>
         </is>
       </c>
-      <c r="H28" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H28" s="29" t="n"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1657,33 +1630,33 @@
       </c>
     </row>
     <row r="29" hidden="1">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="46" t="n">
+      <c r="A29" s="47" t="n"/>
+      <c r="B29" s="48" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="47" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D29" s="50" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>https://meli.la/2iuRXex</t>
         </is>
       </c>
-      <c r="E29" s="51" t="inlineStr">
+      <c r="E29" s="53" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro 4K Preto</t>
         </is>
       </c>
-      <c r="F29" s="45" t="n"/>
-      <c r="G29" s="45" t="inlineStr">
+      <c r="F29" s="47" t="n"/>
+      <c r="G29" s="47" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H29" s="45" t="n"/>
-      <c r="I29" s="45" t="inlineStr">
+      <c r="H29" s="47" t="n"/>
+      <c r="I29" s="47" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1691,35 +1664,31 @@
     </row>
     <row r="30" hidden="1">
       <c r="A30" s="16" t="n"/>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="29" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2kvFciT</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Paw3104 7200 DPI</t>
         </is>
       </c>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H30" s="27" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H30" s="29" t="n"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1728,105 +1697,101 @@
     </row>
     <row r="31" hidden="1">
       <c r="A31" s="16" t="n"/>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D31" s="36" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/241na5E</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon King Pro</t>
         </is>
       </c>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="38" t="inlineStr">
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr">
+      <c r="H31" s="29" t="n"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" hidden="1">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Mouse gamer sem fio</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="inlineStr">
+        <is>
+          <t>https://meli.la/2BZocDd</t>
+        </is>
+      </c>
+      <c r="E32" s="39" t="inlineStr">
+        <is>
+          <t>Mouse Gamer Redragon Fyzu Pro</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>Redragon</t>
+        </is>
+      </c>
+      <c r="H32" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" hidden="1">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="35" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" hidden="1">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="55" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>https://meli.la/2BZocDd</t>
-        </is>
-      </c>
-      <c r="E32" s="37" t="inlineStr">
-        <is>
-          <t>Mouse Gamer Redragon Fyzu Pro</t>
-        </is>
-      </c>
-      <c r="F32" s="35" t="n"/>
-      <c r="G32" s="38" t="inlineStr">
-        <is>
-          <t>Redragon</t>
-        </is>
-      </c>
-      <c r="H32" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" hidden="1">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>Mouse gamer sem fio</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/19CRJzw</t>
         </is>
       </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Mouse Gamer Fire Phoenix Sem Fio</t>
         </is>
       </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="inlineStr">
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Fire Phoenix</t>
         </is>
       </c>
-      <c r="H33" s="27" t="n"/>
+      <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1835,31 +1800,31 @@
     </row>
     <row r="34" hidden="1">
       <c r="A34" s="16" t="n"/>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2F4p8Fn</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 3311</t>
         </is>
       </c>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="30" t="inlineStr">
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="32" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H34" s="27" t="n"/>
+      <c r="H34" s="29" t="n"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1867,33 +1832,33 @@
       </c>
     </row>
     <row r="35" hidden="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="46" t="n">
+      <c r="A35" s="47" t="n"/>
+      <c r="B35" s="48" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C35" s="48" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="49" t="inlineStr">
         <is>
           <t>https://meli.la/1Bwj698</t>
         </is>
       </c>
-      <c r="E35" s="48" t="inlineStr">
+      <c r="E35" s="50" t="inlineStr">
         <is>
           <t>Mouse Gamer Titorion Pixart 3311 Sem Fio</t>
         </is>
       </c>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="49" t="inlineStr">
+      <c r="F35" s="48" t="n"/>
+      <c r="G35" s="51" t="inlineStr">
         <is>
           <t>Titorion</t>
         </is>
       </c>
-      <c r="H35" s="46" t="n"/>
-      <c r="I35" s="45" t="inlineStr">
+      <c r="H35" s="48" t="n"/>
+      <c r="I35" s="47" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1901,31 +1866,31 @@
     </row>
     <row r="36" hidden="1">
       <c r="A36" s="16" t="n"/>
-      <c r="B36" s="27" t="n">
+      <c r="B36" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1xnHcCq</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Knup Bluetooth 1600 DPI</t>
         </is>
       </c>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="30" t="inlineStr">
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H36" s="27" t="n"/>
+      <c r="H36" s="29" t="n"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1934,31 +1899,31 @@
     </row>
     <row r="37" hidden="1">
       <c r="A37" s="16" t="n"/>
-      <c r="B37" s="27" t="n">
+      <c r="B37" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2pnhc6K</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Recarregável Bluetooth</t>
         </is>
       </c>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="inlineStr">
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="inlineStr">
         <is>
           <t>Smailwolf Mouse Gamer</t>
         </is>
       </c>
-      <c r="H37" s="27" t="n"/>
+      <c r="H37" s="29" t="n"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -1967,35 +1932,31 @@
     </row>
     <row r="38" hidden="1">
       <c r="A38" s="16" t="n"/>
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/12Li269</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Machenike M7 Pro RGB</t>
         </is>
       </c>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>Machenike</t>
         </is>
       </c>
-      <c r="H38" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="H38" s="29" t="n"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2004,31 +1965,31 @@
     </row>
     <row r="39" hidden="1">
       <c r="A39" s="16" t="n"/>
-      <c r="B39" s="27" t="n">
+      <c r="B39" s="29" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2UTzmsY</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Warrior Dash 8 Botões</t>
         </is>
       </c>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="30" t="inlineStr">
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="H39" s="27" t="n"/>
+      <c r="H39" s="29" t="n"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2037,31 +1998,31 @@
     </row>
     <row r="40" hidden="1">
       <c r="A40" s="16" t="n"/>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1NTFM66</t>
         </is>
       </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Taipan Pro M810</t>
         </is>
       </c>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="F40" s="29" t="n"/>
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H40" s="27" t="n"/>
+      <c r="H40" s="29" t="n"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2070,31 +2031,31 @@
     </row>
     <row r="41" hidden="1">
       <c r="A41" s="16" t="n"/>
-      <c r="B41" s="27" t="n">
+      <c r="B41" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D41" s="28" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/28iFCs3</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Recarregável Bluetooth 2.4G</t>
         </is>
       </c>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="30" t="inlineStr">
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="32" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H41" s="27" t="n"/>
+      <c r="H41" s="29" t="n"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2102,8 +2063,8 @@
       </c>
     </row>
     <row r="42" hidden="1">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="53" t="n">
+      <c r="A42" s="3" t="n"/>
+      <c r="B42" s="55" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2128,31 +2089,31 @@
     </row>
     <row r="43" hidden="1">
       <c r="A43" s="16" t="n"/>
-      <c r="B43" s="27" t="n">
+      <c r="B43" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="27" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer sem fio</t>
         </is>
       </c>
-      <c r="D43" s="28" t="inlineStr">
+      <c r="D43" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1uhKd3R</t>
         </is>
       </c>
-      <c r="E43" s="40" t="inlineStr">
+      <c r="E43" s="42" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon M991 Sem Fio</t>
         </is>
       </c>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="30" t="inlineStr">
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="32" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H43" s="27" t="n"/>
+      <c r="H43" s="29" t="n"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2160,28 +2121,24 @@
       </c>
     </row>
     <row r="44" hidden="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="27" t="n">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="55" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="27" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D44" s="39" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>https://meli.la/321ZTMv</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
-        <is>
-          <t>Mouse Gamer M711 Cobra Chroma Redragon Com fio Para Jogos 12.400 DPI Com Led RGB Preto</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="27" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2190,31 +2147,31 @@
     </row>
     <row r="45" hidden="1">
       <c r="A45" s="16" t="n"/>
-      <c r="B45" s="27" t="n">
+      <c r="B45" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="27" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr">
+      <c r="D45" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2nikVNt</t>
         </is>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Viper Pro Naja 7200 DPI</t>
         </is>
       </c>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="inlineStr">
+      <c r="F45" s="29" t="n"/>
+      <c r="G45" s="29" t="inlineStr">
         <is>
           <t>Viper Pro</t>
         </is>
       </c>
-      <c r="H45" s="27" t="n"/>
+      <c r="H45" s="29" t="n"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2223,31 +2180,31 @@
     </row>
     <row r="46" hidden="1">
       <c r="A46" s="16" t="n"/>
-      <c r="B46" s="27" t="n">
+      <c r="B46" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="27" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2BkMNpg</t>
         </is>
       </c>
-      <c r="E46" s="29" t="inlineStr">
+      <c r="E46" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Machenike M7 Pro 12800 DPI</t>
         </is>
       </c>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="30" t="inlineStr">
+      <c r="F46" s="29" t="n"/>
+      <c r="G46" s="32" t="inlineStr">
         <is>
           <t>Machenike</t>
         </is>
       </c>
-      <c r="H46" s="27" t="n"/>
+      <c r="H46" s="29" t="n"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2256,35 +2213,31 @@
     </row>
     <row r="47" hidden="1">
       <c r="A47" s="3" t="n"/>
-      <c r="B47" s="35" t="n">
+      <c r="B47" s="55" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="35" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D47" s="36" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/2nK6CGd</t>
         </is>
       </c>
-      <c r="E47" s="37" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon M815 Ultraleve</t>
         </is>
       </c>
-      <c r="F47" s="35" t="n"/>
-      <c r="G47" s="38" t="inlineStr">
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H47" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2293,35 +2246,31 @@
     </row>
     <row r="48" hidden="1">
       <c r="A48" s="16" t="n"/>
-      <c r="B48" s="35" t="n">
+      <c r="B48" s="29" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D48" s="36" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1GyW82d</t>
         </is>
       </c>
-      <c r="E48" s="37" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Onikuma CW917 Com Fio</t>
         </is>
       </c>
-      <c r="F48" s="35" t="n"/>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="F48" s="29" t="n"/>
+      <c r="G48" s="29" t="inlineStr">
         <is>
           <t>Onikuma</t>
         </is>
       </c>
-      <c r="H48" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H48" s="29" t="n"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2330,31 +2279,23 @@
     </row>
     <row r="49" hidden="1">
       <c r="A49" s="3" t="n"/>
-      <c r="B49" s="35" t="n">
+      <c r="B49" s="55" t="n">
         <v>48</v>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D49" s="36" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/23wdZ7w</t>
         </is>
       </c>
-      <c r="E49" s="37" t="inlineStr">
-        <is>
-          <t>Mouse Gamer 6 Botões 12.800 Dpi Sensor Instantâneo Kp-mu026</t>
-        </is>
-      </c>
-      <c r="F49" s="35" t="n"/>
-      <c r="G49" s="35" t="n"/>
-      <c r="H49" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2363,31 +2304,31 @@
     </row>
     <row r="50" hidden="1">
       <c r="A50" s="16" t="n"/>
-      <c r="B50" s="27" t="n">
+      <c r="B50" s="29" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="27" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D50" s="28" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/15mY31Y</t>
         </is>
       </c>
-      <c r="E50" s="29" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Havit MS1036 RGB 7200 DPI</t>
         </is>
       </c>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="27" t="inlineStr">
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="29" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H50" s="27" t="n"/>
+      <c r="H50" s="29" t="n"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2396,31 +2337,31 @@
     </row>
     <row r="51" hidden="1">
       <c r="A51" s="16" t="n"/>
-      <c r="B51" s="27" t="n">
+      <c r="B51" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="C51" s="27" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D51" s="28" t="inlineStr">
+      <c r="D51" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2n5VFUw</t>
         </is>
       </c>
-      <c r="E51" s="29" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Hive RGB 16000 DPI</t>
         </is>
       </c>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="30" t="inlineStr">
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="32" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H51" s="27" t="n"/>
+      <c r="H51" s="29" t="n"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2429,35 +2370,31 @@
     </row>
     <row r="52" hidden="1">
       <c r="A52" s="16" t="n"/>
-      <c r="B52" s="35" t="n">
+      <c r="B52" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D52" s="36" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2BwBjiE</t>
         </is>
       </c>
-      <c r="E52" s="37" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Havit MS959S RGB 8 Botões</t>
         </is>
       </c>
-      <c r="F52" s="35" t="n"/>
-      <c r="G52" s="38" t="inlineStr">
+      <c r="F52" s="29" t="n"/>
+      <c r="G52" s="32" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H52" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H52" s="29" t="n"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2466,31 +2403,31 @@
     </row>
     <row r="53" hidden="1">
       <c r="A53" s="16" t="n"/>
-      <c r="B53" s="27" t="n">
+      <c r="B53" s="29" t="n">
         <v>52</v>
       </c>
-      <c r="C53" s="27" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D53" s="28" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1QTQPMY</t>
         </is>
       </c>
-      <c r="E53" s="29" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Rgb Fortrek Crusader White Edition 12800dpi</t>
         </is>
       </c>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="30" t="inlineStr">
+      <c r="F53" s="29" t="n"/>
+      <c r="G53" s="32" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H53" s="27" t="n"/>
+      <c r="H53" s="29" t="n"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2499,31 +2436,31 @@
     </row>
     <row r="54" hidden="1">
       <c r="A54" s="16" t="n"/>
-      <c r="B54" s="27" t="n">
+      <c r="B54" s="29" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D54" s="28" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2ZyCiGn</t>
         </is>
       </c>
-      <c r="E54" s="29" t="inlineStr">
+      <c r="E54" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Fortrek Crusader 12800 Dpi Com Led Switch Huano</t>
         </is>
       </c>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="30" t="inlineStr">
+      <c r="F54" s="29" t="n"/>
+      <c r="G54" s="32" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H54" s="27" t="n"/>
+      <c r="H54" s="29" t="n"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2532,35 +2469,31 @@
     </row>
     <row r="55" hidden="1">
       <c r="A55" s="16" t="n"/>
-      <c r="B55" s="35" t="n">
+      <c r="B55" s="29" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D55" s="36" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2ms6fTM</t>
         </is>
       </c>
-      <c r="E55" s="37" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Bomber M722 Redragon Preto</t>
         </is>
       </c>
-      <c r="F55" s="35" t="n"/>
-      <c r="G55" s="38" t="inlineStr">
+      <c r="F55" s="29" t="n"/>
+      <c r="G55" s="32" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H55" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H55" s="29" t="n"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2569,35 +2502,31 @@
     </row>
     <row r="56" hidden="1">
       <c r="A56" s="16" t="n"/>
-      <c r="B56" s="35" t="n">
+      <c r="B56" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>Mouse gamer com fio</t>
         </is>
       </c>
-      <c r="D56" s="36" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/23VvESt</t>
         </is>
       </c>
-      <c r="E56" s="37" t="inlineStr">
+      <c r="E56" s="31" t="inlineStr">
         <is>
           <t>Mouse Gamer Redragon Devourer Preto M993-rgb</t>
         </is>
       </c>
-      <c r="F56" s="35" t="n"/>
-      <c r="G56" s="38" t="inlineStr">
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="32" t="inlineStr">
         <is>
           <t>Redradon</t>
         </is>
       </c>
-      <c r="H56" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H56" s="29" t="n"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2606,35 +2535,31 @@
     </row>
     <row r="57" hidden="1">
       <c r="A57" s="16" t="n"/>
-      <c r="B57" s="35" t="n">
+      <c r="B57" s="29" t="n">
         <v>56</v>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D57" s="36" t="inlineStr">
+      <c r="D57" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Fy7WQv</t>
         </is>
       </c>
-      <c r="E57" s="37" t="inlineStr">
+      <c r="E57" s="31" t="inlineStr">
         <is>
           <t>Teclado Multimídia Com Fio Usb Teclas Silenciosas (abnt2)</t>
         </is>
       </c>
-      <c r="F57" s="35" t="n"/>
-      <c r="G57" s="38" t="inlineStr">
+      <c r="F57" s="29" t="n"/>
+      <c r="G57" s="32" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H57" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H57" s="29" t="n"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2643,31 +2568,31 @@
     </row>
     <row r="58" hidden="1">
       <c r="A58" s="16" t="n"/>
-      <c r="B58" s="27" t="n">
+      <c r="B58" s="29" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="27" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D58" s="28" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2e7gPck</t>
         </is>
       </c>
-      <c r="E58" s="29" t="inlineStr">
+      <c r="E58" s="31" t="inlineStr">
         <is>
           <t>Teclado Titanis USB com Fio Preto ABNT2 Ergonômico Plug &amp; Play Numérico PC Toque Suave para Computador Layout Qwerty Prático Ideal para Trabalho Escritório Office</t>
         </is>
       </c>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="30" t="inlineStr">
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="32" t="inlineStr">
         <is>
           <t>Titanis</t>
         </is>
       </c>
-      <c r="H58" s="27" t="n"/>
+      <c r="H58" s="29" t="n"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2676,31 +2601,31 @@
     </row>
     <row r="59" hidden="1">
       <c r="A59" s="16" t="n"/>
-      <c r="B59" s="27" t="n">
+      <c r="B59" s="29" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="27" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D59" s="28" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1kFH9iG</t>
         </is>
       </c>
-      <c r="E59" s="29" t="inlineStr">
+      <c r="E59" s="31" t="inlineStr">
         <is>
           <t>Teclado USB Hoopson TPC-058G com Fio Teclas Grandes Preto ABNT2</t>
         </is>
       </c>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="30" t="inlineStr">
+      <c r="F59" s="29" t="n"/>
+      <c r="G59" s="32" t="inlineStr">
         <is>
           <t>Hoopson</t>
         </is>
       </c>
-      <c r="H59" s="27" t="n"/>
+      <c r="H59" s="29" t="n"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2709,31 +2634,31 @@
     </row>
     <row r="60" hidden="1">
       <c r="A60" s="16" t="n"/>
-      <c r="B60" s="27" t="n">
+      <c r="B60" s="29" t="n">
         <v>59</v>
       </c>
-      <c r="C60" s="27" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D60" s="28" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/11EgXFE</t>
         </is>
       </c>
-      <c r="E60" s="29" t="inlineStr">
+      <c r="E60" s="31" t="inlineStr">
         <is>
           <t>Teclado Usb Com Fio Dgx Padrão Abnt2 Silencioso Ergonômico Preto Com Cabo Usb Escritorio</t>
         </is>
       </c>
-      <c r="F60" s="27" t="n"/>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="F60" s="29" t="n"/>
+      <c r="G60" s="32" t="inlineStr">
         <is>
           <t>Dgx</t>
         </is>
       </c>
-      <c r="H60" s="27" t="n"/>
+      <c r="H60" s="29" t="n"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2742,31 +2667,31 @@
     </row>
     <row r="61" hidden="1">
       <c r="A61" s="16" t="n"/>
-      <c r="B61" s="27" t="n">
+      <c r="B61" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="27" t="inlineStr">
+      <c r="C61" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D61" s="28" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2kFVGHA</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>Teclado Com Fio Usb Kb216 Dell Cor De Teclado Preto Idioma Português Brasil</t>
         </is>
       </c>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="F61" s="29" t="n"/>
+      <c r="G61" s="32" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="H61" s="27" t="n"/>
+      <c r="H61" s="29" t="n"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2775,31 +2700,31 @@
     </row>
     <row r="62" hidden="1">
       <c r="A62" s="16" t="n"/>
-      <c r="B62" s="27" t="n">
+      <c r="B62" s="29" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="27" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2s4v5j3</t>
         </is>
       </c>
-      <c r="E62" s="29" t="inlineStr">
+      <c r="E62" s="31" t="inlineStr">
         <is>
           <t>Teclado USB Exbom BK-102 Preto ABNT2 Para PC e Notebook PT-BR</t>
         </is>
       </c>
-      <c r="F62" s="27" t="n"/>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="F62" s="29" t="n"/>
+      <c r="G62" s="32" t="inlineStr">
         <is>
           <t>Exbom</t>
         </is>
       </c>
-      <c r="H62" s="27" t="n"/>
+      <c r="H62" s="29" t="n"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2808,7 +2733,7 @@
     </row>
     <row r="63" hidden="1">
       <c r="A63" s="3" t="n"/>
-      <c r="B63" s="53" t="n">
+      <c r="B63" s="55" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2833,31 +2758,31 @@
     </row>
     <row r="64" hidden="1">
       <c r="A64" s="16" t="n"/>
-      <c r="B64" s="27" t="n">
+      <c r="B64" s="29" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="27" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D64" s="28" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1eE7xym</t>
         </is>
       </c>
-      <c r="E64" s="29" t="inlineStr">
+      <c r="E64" s="31" t="inlineStr">
         <is>
           <t>Teclado Com Fio Usb Logitech K120 Com Layout Abnt2 Cor de teclado Preto Idioma Português Brasil QWERTY</t>
         </is>
       </c>
-      <c r="F64" s="27" t="n"/>
-      <c r="G64" s="30" t="inlineStr">
+      <c r="F64" s="29" t="n"/>
+      <c r="G64" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H64" s="27" t="n"/>
+      <c r="H64" s="29" t="n"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2866,31 +2791,31 @@
     </row>
     <row r="65" hidden="1">
       <c r="A65" s="3" t="n"/>
-      <c r="B65" s="27" t="n">
+      <c r="B65" s="55" t="n">
         <v>64</v>
       </c>
-      <c r="C65" s="27" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D65" s="28" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1PK6gym</t>
         </is>
       </c>
-      <c r="E65" s="29" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>Teclado Bahrein Para Pc Computador Notebook Com Fio Português Brasil Cor Preto</t>
         </is>
       </c>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="18" t="inlineStr">
         <is>
           <t>Rezzet</t>
         </is>
       </c>
-      <c r="H65" s="27" t="n"/>
+      <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2899,31 +2824,31 @@
     </row>
     <row r="66" hidden="1">
       <c r="A66" s="16" t="n"/>
-      <c r="B66" s="27" t="n">
+      <c r="B66" s="29" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="27" t="inlineStr">
+      <c r="C66" s="29" t="inlineStr">
         <is>
           <t>Teclado com fio</t>
         </is>
       </c>
-      <c r="D66" s="28" t="inlineStr">
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1YkqEkr</t>
         </is>
       </c>
-      <c r="E66" s="29" t="inlineStr">
+      <c r="E66" s="31" t="inlineStr">
         <is>
           <t>Teclado USB Com Fio B-Max BM-T02 ABNT2 Silencioso Ergonômico Preto</t>
         </is>
       </c>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="F66" s="29" t="n"/>
+      <c r="G66" s="32" t="inlineStr">
         <is>
           <t>B-Max</t>
         </is>
       </c>
-      <c r="H66" s="27" t="n"/>
+      <c r="H66" s="29" t="n"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2932,35 +2857,31 @@
     </row>
     <row r="67" hidden="1">
       <c r="A67" s="16" t="n"/>
-      <c r="B67" s="35" t="n">
+      <c r="B67" s="29" t="n">
         <v>66</v>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D67" s="36" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1RdrkMP</t>
         </is>
       </c>
-      <c r="E67" s="37" t="inlineStr">
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Mx Keys Mini Logitech Grafite Americano</t>
         </is>
       </c>
-      <c r="F67" s="35" t="n"/>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="F67" s="29" t="n"/>
+      <c r="G67" s="29" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H67" s="29" t="n"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -2969,31 +2890,31 @@
     </row>
     <row r="68" hidden="1">
       <c r="A68" s="16" t="n"/>
-      <c r="B68" s="27" t="n">
+      <c r="B68" s="29" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="27" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D68" s="28" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Qx1EEh</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E68" s="31" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Signature Slim K950 Branco Logitech</t>
         </is>
       </c>
-      <c r="F68" s="27" t="n"/>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H68" s="27" t="n"/>
+      <c r="H68" s="29" t="n"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3002,35 +2923,31 @@
     </row>
     <row r="69" hidden="1">
       <c r="A69" s="16" t="n"/>
-      <c r="B69" s="31" t="n">
+      <c r="B69" s="29" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="31" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/16PdgAV</t>
         </is>
       </c>
-      <c r="E69" s="33" t="inlineStr">
+      <c r="E69" s="31" t="inlineStr">
         <is>
           <t>Teclado Mecânico Aula F75 Preto Sem Fio RGB 75% Tri Mode Bluetooth, 2.4ghz, USB-C, Inglês Us</t>
         </is>
       </c>
-      <c r="F69" s="31" t="n"/>
-      <c r="G69" s="34" t="inlineStr">
+      <c r="F69" s="29" t="n"/>
+      <c r="G69" s="32" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H69" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="H69" s="29" t="n"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3039,35 +2956,31 @@
     </row>
     <row r="70" hidden="1">
       <c r="A70" s="16" t="n"/>
-      <c r="B70" s="35" t="n">
+      <c r="B70" s="29" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D70" s="36" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/138aRrU</t>
         </is>
       </c>
-      <c r="E70" s="37" t="inlineStr">
+      <c r="E70" s="31" t="inlineStr">
         <is>
           <t>Teclado Aula F75 Sem Fio Mecânico Thunder Black Tri Mode Gasket Hot Swapp Inglês US</t>
         </is>
       </c>
-      <c r="F70" s="35" t="n"/>
-      <c r="G70" s="38" t="inlineStr">
+      <c r="F70" s="29" t="n"/>
+      <c r="G70" s="32" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H70" s="29" t="n"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3076,23 +2989,23 @@
     </row>
     <row r="71" hidden="1">
       <c r="A71" s="3" t="n"/>
-      <c r="B71" s="27" t="n">
+      <c r="B71" s="55" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="27" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D71" s="28" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1gfyU2e</t>
         </is>
       </c>
-      <c r="E71" s="29" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3101,31 +3014,31 @@
     </row>
     <row r="72" hidden="1">
       <c r="A72" s="16" t="n"/>
-      <c r="B72" s="27" t="n">
+      <c r="B72" s="29" t="n">
         <v>71</v>
       </c>
-      <c r="C72" s="27" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1uRKdMf</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
+      <c r="E72" s="31" t="inlineStr">
         <is>
           <t>Teclado sem fio Logitech Pebble Keys 2 K380s - Branco</t>
         </is>
       </c>
-      <c r="F72" s="27" t="n"/>
-      <c r="G72" s="30" t="inlineStr">
+      <c r="F72" s="29" t="n"/>
+      <c r="G72" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H72" s="27" t="n"/>
+      <c r="H72" s="29" t="n"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3134,31 +3047,31 @@
     </row>
     <row r="73" hidden="1">
       <c r="A73" s="16" t="n"/>
-      <c r="B73" s="27" t="n">
+      <c r="B73" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="27" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D73" s="28" t="inlineStr">
+      <c r="D73" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Y9Djdq</t>
         </is>
       </c>
-      <c r="E73" s="29" t="inlineStr">
+      <c r="E73" s="31" t="inlineStr">
         <is>
           <t>Teclado Aula F75 Mecânico Sem Fio Tri Mode Gasket Hot Swapp Cor de teclado Branco Idioma Inglês US</t>
         </is>
       </c>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="30" t="inlineStr">
+      <c r="F73" s="29" t="n"/>
+      <c r="G73" s="32" t="inlineStr">
         <is>
           <t>Aula</t>
         </is>
       </c>
-      <c r="H73" s="27" t="n"/>
+      <c r="H73" s="29" t="n"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3167,31 +3080,31 @@
     </row>
     <row r="74" hidden="1">
       <c r="A74" s="16" t="n"/>
-      <c r="B74" s="27" t="n">
+      <c r="B74" s="29" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="27" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Teclado sem fio</t>
         </is>
       </c>
-      <c r="D74" s="28" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Gkykud</t>
         </is>
       </c>
-      <c r="E74" s="29" t="inlineStr">
+      <c r="E74" s="31" t="inlineStr">
         <is>
           <t>Teclado Sem Fio Logitech Signature K650 - Branco</t>
         </is>
       </c>
-      <c r="F74" s="27" t="n"/>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="F74" s="29" t="n"/>
+      <c r="G74" s="32" t="inlineStr">
         <is>
           <t>Logitech</t>
         </is>
       </c>
-      <c r="H74" s="27" t="n"/>
+      <c r="H74" s="29" t="n"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3200,31 +3113,31 @@
     </row>
     <row r="75" hidden="1">
       <c r="A75" s="16" t="n"/>
-      <c r="B75" s="27" t="n">
+      <c r="B75" s="29" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="27" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D75" s="28" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1s34Rp2</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>Teclado Gamer 60% Membrana Rgb Fio Usb Anti Ghosting Pt-br</t>
         </is>
       </c>
-      <c r="F75" s="27" t="n"/>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="F75" s="29" t="n"/>
+      <c r="G75" s="32" t="inlineStr">
         <is>
           <t>Teclado 60 por Cento Barato</t>
         </is>
       </c>
-      <c r="H75" s="27" t="n"/>
+      <c r="H75" s="29" t="n"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3232,23 +3145,23 @@
       </c>
     </row>
     <row r="76" hidden="1">
-      <c r="B76" s="35" t="n">
+      <c r="B76" s="37" t="n">
         <v>75</v>
       </c>
-      <c r="C76" s="35" t="inlineStr">
+      <c r="C76" s="37" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D76" s="36" t="inlineStr">
+      <c r="D76" s="38" t="inlineStr">
         <is>
           <t>https://meli.la/2G9hQwo</t>
         </is>
       </c>
-      <c r="E76" s="37" t="n"/>
-      <c r="F76" s="35" t="n"/>
-      <c r="G76" s="35" t="n"/>
-      <c r="H76" s="35" t="inlineStr">
+      <c r="E76" s="39" t="n"/>
+      <c r="F76" s="37" t="n"/>
+      <c r="G76" s="37" t="n"/>
+      <c r="H76" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -3261,31 +3174,31 @@
     </row>
     <row r="77" hidden="1">
       <c r="A77" s="16" t="n"/>
-      <c r="B77" s="27" t="n">
+      <c r="B77" s="29" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="27" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D77" s="28" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2WCTDDE</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E77" s="31" t="inlineStr">
         <is>
           <t>Teclado Mecânico Gamer Rgb Switch Azul Barulhent 63t Com Fio</t>
         </is>
       </c>
-      <c r="F77" s="27" t="n"/>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="F77" s="29" t="n"/>
+      <c r="G77" s="32" t="inlineStr">
         <is>
           <t>T-Wolf</t>
         </is>
       </c>
-      <c r="H77" s="27" t="n"/>
+      <c r="H77" s="29" t="n"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3294,31 +3207,31 @@
     </row>
     <row r="78" hidden="1">
       <c r="A78" s="16" t="n"/>
-      <c r="B78" s="27" t="n">
+      <c r="B78" s="29" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="27" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D78" s="28" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1ivXod3</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
+      <c r="E78" s="31" t="inlineStr">
         <is>
           <t>Bluetooth+2.4g+com Fio Rgb Gamer Teclado Silencioso Para Pc</t>
         </is>
       </c>
-      <c r="F78" s="27" t="n"/>
-      <c r="G78" s="30" t="inlineStr">
+      <c r="F78" s="29" t="n"/>
+      <c r="G78" s="32" t="inlineStr">
         <is>
           <t>SPLPLUS</t>
         </is>
       </c>
-      <c r="H78" s="27" t="n"/>
+      <c r="H78" s="29" t="n"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3327,31 +3240,31 @@
     </row>
     <row r="79" hidden="1">
       <c r="A79" s="16" t="n"/>
-      <c r="B79" s="27" t="n">
+      <c r="B79" s="29" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="27" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D79" s="28" t="inlineStr">
+      <c r="D79" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/34bmbbX</t>
         </is>
       </c>
-      <c r="E79" s="29" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>Teclado Mecânico Fio Gamer Rgb 60% Switch Blue Anti Ghosting</t>
         </is>
       </c>
-      <c r="F79" s="27" t="n"/>
-      <c r="G79" s="30" t="inlineStr">
+      <c r="F79" s="29" t="n"/>
+      <c r="G79" s="32" t="inlineStr">
         <is>
           <t>Master Gaming</t>
         </is>
       </c>
-      <c r="H79" s="27" t="n"/>
+      <c r="H79" s="29" t="n"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3360,7 +3273,7 @@
     </row>
     <row r="80" hidden="1">
       <c r="A80" s="3" t="n"/>
-      <c r="B80" s="53" t="n">
+      <c r="B80" s="55" t="n">
         <v>79</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3385,7 +3298,7 @@
     </row>
     <row r="81" hidden="1">
       <c r="A81" s="3" t="n"/>
-      <c r="B81" s="53" t="n">
+      <c r="B81" s="55" t="n">
         <v>80</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3414,31 +3327,31 @@
     </row>
     <row r="82" hidden="1">
       <c r="A82" s="16" t="n"/>
-      <c r="B82" s="27" t="n">
+      <c r="B82" s="29" t="n">
         <v>81</v>
       </c>
-      <c r="C82" s="27" t="inlineStr">
+      <c r="C82" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D82" s="28" t="inlineStr">
+      <c r="D82" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2wUJ3fr</t>
         </is>
       </c>
-      <c r="E82" s="29" t="inlineStr">
+      <c r="E82" s="31" t="inlineStr">
         <is>
           <t>Original Lenovo Teclado Gamer Com Led Rgb Ergonômico Com Fio</t>
         </is>
       </c>
-      <c r="F82" s="27" t="n"/>
-      <c r="G82" s="30" t="inlineStr">
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="32" t="inlineStr">
         <is>
           <t>Lenovo Legion</t>
         </is>
       </c>
-      <c r="H82" s="27" t="n"/>
+      <c r="H82" s="29" t="n"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3447,31 +3360,31 @@
     </row>
     <row r="83" hidden="1">
       <c r="A83" s="16" t="n"/>
-      <c r="B83" s="53" t="n">
+      <c r="B83" s="55" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="31" t="inlineStr">
+      <c r="C83" s="33" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="D83" s="34" t="inlineStr">
         <is>
           <t>https://meli.la/32SsR3d</t>
         </is>
       </c>
-      <c r="E83" s="33" t="inlineStr">
+      <c r="E83" s="35" t="inlineStr">
         <is>
           <t>Teclado Gamer Led Rgb Multimídia Com Fio Pt-br Qwerty Inova</t>
         </is>
       </c>
-      <c r="F83" s="31" t="n"/>
-      <c r="G83" s="34" t="inlineStr">
+      <c r="F83" s="33" t="n"/>
+      <c r="G83" s="36" t="inlineStr">
         <is>
           <t>Inova</t>
         </is>
       </c>
-      <c r="H83" s="31" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -3484,31 +3397,31 @@
     </row>
     <row r="84" hidden="1">
       <c r="A84" s="16" t="n"/>
-      <c r="B84" s="27" t="n">
+      <c r="B84" s="29" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="27" t="inlineStr">
+      <c r="C84" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D84" s="28" t="inlineStr">
+      <c r="D84" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1DNzGQi</t>
         </is>
       </c>
-      <c r="E84" s="29" t="inlineStr">
+      <c r="E84" s="31" t="inlineStr">
         <is>
           <t>Teclado Semi-mecânico Gamer Rgb Usb Shop Finos Pc Console</t>
         </is>
       </c>
-      <c r="F84" s="27" t="n"/>
-      <c r="G84" s="30" t="inlineStr">
+      <c r="F84" s="29" t="n"/>
+      <c r="G84" s="32" t="inlineStr">
         <is>
           <t>Shop Finos</t>
         </is>
       </c>
-      <c r="H84" s="27" t="n"/>
+      <c r="H84" s="29" t="n"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3517,31 +3430,31 @@
     </row>
     <row r="85" hidden="1">
       <c r="A85" s="16" t="n"/>
-      <c r="B85" s="27" t="n">
+      <c r="B85" s="29" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="27" t="inlineStr">
+      <c r="C85" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D85" s="28" t="inlineStr">
+      <c r="D85" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2xBx1Tq</t>
         </is>
       </c>
-      <c r="E85" s="29" t="inlineStr">
+      <c r="E85" s="31" t="inlineStr">
         <is>
           <t>Teclado Pro X Tkl Rapid Gamer Com Fio Branco Logitech G</t>
         </is>
       </c>
-      <c r="F85" s="27" t="n"/>
-      <c r="G85" s="30" t="inlineStr">
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="32" t="inlineStr">
         <is>
           <t>Shop Finos</t>
         </is>
       </c>
-      <c r="H85" s="27" t="n"/>
+      <c r="H85" s="29" t="n"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3550,31 +3463,31 @@
     </row>
     <row r="86" hidden="1">
       <c r="A86" s="16" t="n"/>
-      <c r="B86" s="27" t="n">
+      <c r="B86" s="29" t="n">
         <v>85</v>
       </c>
-      <c r="C86" s="27" t="inlineStr">
+      <c r="C86" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D86" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2NhJeVD</t>
         </is>
       </c>
-      <c r="E86" s="29" t="inlineStr">
+      <c r="E86" s="31" t="inlineStr">
         <is>
           <t>Teclado Gamer Switch Magnético Attack Shark 8000hz X68 He</t>
         </is>
       </c>
-      <c r="F86" s="27" t="n"/>
-      <c r="G86" s="30" t="inlineStr">
+      <c r="F86" s="29" t="n"/>
+      <c r="G86" s="32" t="inlineStr">
         <is>
           <t>Attack Shark</t>
         </is>
       </c>
-      <c r="H86" s="27" t="n"/>
+      <c r="H86" s="29" t="n"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3583,31 +3496,31 @@
     </row>
     <row r="87" hidden="1">
       <c r="A87" s="16" t="n"/>
-      <c r="B87" s="27" t="n">
+      <c r="B87" s="29" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="27" t="inlineStr">
+      <c r="C87" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D87" s="28" t="inlineStr">
+      <c r="D87" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2RGpCCn</t>
         </is>
       </c>
-      <c r="E87" s="29" t="inlineStr">
+      <c r="E87" s="31" t="inlineStr">
         <is>
           <t>Teclado E Mouse Mecânico Com Fio De 98 Teclas Para Jogos+rgb</t>
         </is>
       </c>
-      <c r="F87" s="27" t="n"/>
-      <c r="G87" s="30" t="inlineStr">
+      <c r="F87" s="29" t="n"/>
+      <c r="G87" s="32" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H87" s="27" t="n"/>
+      <c r="H87" s="29" t="n"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3616,31 +3529,31 @@
     </row>
     <row r="88" hidden="1">
       <c r="A88" s="16" t="n"/>
-      <c r="B88" s="27" t="n">
+      <c r="B88" s="29" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="27" t="inlineStr">
+      <c r="C88" s="29" t="inlineStr">
         <is>
           <t>Teclado gamer com fio</t>
         </is>
       </c>
-      <c r="D88" s="28" t="inlineStr">
+      <c r="D88" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1WKzhP5</t>
         </is>
       </c>
-      <c r="E88" s="29" t="inlineStr">
+      <c r="E88" s="31" t="inlineStr">
         <is>
           <t>Teclado Mecânico Com Fio Conjunto De Mouse Luz De Fundo Rgb</t>
         </is>
       </c>
-      <c r="F88" s="27" t="n"/>
-      <c r="G88" s="30" t="inlineStr">
+      <c r="F88" s="29" t="n"/>
+      <c r="G88" s="32" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H88" s="27" t="n"/>
+      <c r="H88" s="29" t="n"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3649,31 +3562,31 @@
     </row>
     <row r="89" hidden="1">
       <c r="A89" s="16" t="n"/>
-      <c r="B89" s="27" t="n">
+      <c r="B89" s="29" t="n">
         <v>88</v>
       </c>
-      <c r="C89" s="27" t="inlineStr">
+      <c r="C89" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D89" s="28" t="inlineStr">
+      <c r="D89" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1EHHo28</t>
         </is>
       </c>
-      <c r="E89" s="29" t="inlineStr">
+      <c r="E89" s="31" t="inlineStr">
         <is>
           <t>Fone Ouvido Bluetooth 5.4 Sem Fio Estojo De Carregamento Anti Ruido A Prova Dagua Compatível Com Ios Samsung Galaxy Android Tws Wireless Air Premium Microfone Touch Marca Pro Phone See</t>
         </is>
       </c>
-      <c r="F89" s="27" t="n"/>
-      <c r="G89" s="30" t="inlineStr">
+      <c r="F89" s="29" t="n"/>
+      <c r="G89" s="32" t="inlineStr">
         <is>
           <t>PRO PHONE SEE</t>
         </is>
       </c>
-      <c r="H89" s="27" t="n"/>
+      <c r="H89" s="29" t="n"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3682,35 +3595,31 @@
     </row>
     <row r="90" hidden="1">
       <c r="A90" s="16" t="n"/>
-      <c r="B90" s="35" t="n">
+      <c r="B90" s="29" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="35" t="inlineStr">
+      <c r="C90" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D90" s="36" t="inlineStr">
+      <c r="D90" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1vyVnBY</t>
         </is>
       </c>
-      <c r="E90" s="37" t="inlineStr">
+      <c r="E90" s="31" t="inlineStr">
         <is>
           <t>Fones de ouvido Bluetooth esportivos sem fio Ipx7 5.3.650 mAh, Bluetooth 5.3, cancelamento de ruído Enc, tela LED, resistência à água IPX7, para negócios, entretenimento e corrida</t>
         </is>
       </c>
-      <c r="F90" s="35" t="n"/>
-      <c r="G90" s="38" t="inlineStr">
+      <c r="F90" s="29" t="n"/>
+      <c r="G90" s="32" t="inlineStr">
         <is>
           <t>MerttoBX28</t>
         </is>
       </c>
-      <c r="H90" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H90" s="29" t="n"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3719,31 +3628,31 @@
     </row>
     <row r="91" hidden="1">
       <c r="A91" s="16" t="n"/>
-      <c r="B91" s="27" t="n">
+      <c r="B91" s="29" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="27" t="inlineStr">
+      <c r="C91" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D91" s="28" t="inlineStr">
+      <c r="D91" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2ZmHugN</t>
         </is>
       </c>
-      <c r="E91" s="29" t="inlineStr">
+      <c r="E91" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Sem Fio Bluetooth Esportivo Gancho De Orelha Beexcellent</t>
         </is>
       </c>
-      <c r="F91" s="27" t="n"/>
-      <c r="G91" s="30" t="inlineStr">
+      <c r="F91" s="29" t="n"/>
+      <c r="G91" s="32" t="inlineStr">
         <is>
           <t>Beexcellent</t>
         </is>
       </c>
-      <c r="H91" s="27" t="n"/>
+      <c r="H91" s="29" t="n"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3752,31 +3661,31 @@
     </row>
     <row r="92" hidden="1">
       <c r="A92" s="16" t="n"/>
-      <c r="B92" s="27" t="n">
+      <c r="B92" s="29" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="27" t="inlineStr">
+      <c r="C92" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D92" s="28" t="inlineStr">
+      <c r="D92" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1y3PyiV</t>
         </is>
       </c>
-      <c r="E92" s="29" t="inlineStr">
+      <c r="E92" s="31" t="inlineStr">
         <is>
           <t>Fone de ouvido Tws Philips Tat1109bk/00 preto Ipx4</t>
         </is>
       </c>
-      <c r="F92" s="27" t="n"/>
-      <c r="G92" s="30" t="inlineStr">
+      <c r="F92" s="29" t="n"/>
+      <c r="G92" s="32" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H92" s="27" t="n"/>
+      <c r="H92" s="29" t="n"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3785,7 +3694,7 @@
     </row>
     <row r="93" hidden="1">
       <c r="A93" s="3" t="n"/>
-      <c r="B93" s="53" t="n">
+      <c r="B93" s="55" t="n">
         <v>92</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3810,31 +3719,31 @@
     </row>
     <row r="94" hidden="1">
       <c r="A94" s="16" t="n"/>
-      <c r="B94" s="27" t="n">
+      <c r="B94" s="29" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="27" t="inlineStr">
+      <c r="C94" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D94" s="28" t="inlineStr">
+      <c r="D94" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2Kr9VSQ</t>
         </is>
       </c>
-      <c r="E94" s="29" t="inlineStr">
+      <c r="E94" s="31" t="inlineStr">
         <is>
           <t>Fone de Ouvido In-ear Bluetooth Sem Fio TWS Branco air confortavel wireless charge case</t>
         </is>
       </c>
-      <c r="F94" s="27" t="n"/>
-      <c r="G94" s="30" t="inlineStr">
+      <c r="F94" s="29" t="n"/>
+      <c r="G94" s="32" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H94" s="27" t="n"/>
+      <c r="H94" s="29" t="n"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3843,31 +3752,31 @@
     </row>
     <row r="95" hidden="1">
       <c r="A95" s="16" t="n"/>
-      <c r="B95" s="27" t="n">
+      <c r="B95" s="29" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="27" t="inlineStr">
+      <c r="C95" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D95" s="28" t="inlineStr">
+      <c r="D95" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2haN2CW</t>
         </is>
       </c>
-      <c r="E95" s="29" t="inlineStr">
+      <c r="E95" s="31" t="inlineStr">
         <is>
           <t>Hivi Fone De Ouvido Bluetooth 5.0 Par Sem Fio Duplo Cor Preto</t>
         </is>
       </c>
-      <c r="F95" s="27" t="n"/>
-      <c r="G95" s="30" t="inlineStr">
+      <c r="F95" s="29" t="n"/>
+      <c r="G95" s="32" t="inlineStr">
         <is>
           <t>Hivi ltda</t>
         </is>
       </c>
-      <c r="H95" s="27" t="n"/>
+      <c r="H95" s="29" t="n"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3876,35 +3785,31 @@
     </row>
     <row r="96" hidden="1">
       <c r="A96" s="16" t="n"/>
-      <c r="B96" s="35" t="n">
+      <c r="B96" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="C96" s="35" t="inlineStr">
+      <c r="C96" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D96" s="36" t="inlineStr">
+      <c r="D96" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1G18uM3</t>
         </is>
       </c>
-      <c r="E96" s="37" t="inlineStr">
+      <c r="E96" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Jbl Tune Flex 2 Preto</t>
         </is>
       </c>
-      <c r="F96" s="35" t="n"/>
-      <c r="G96" s="38" t="inlineStr">
+      <c r="F96" s="29" t="n"/>
+      <c r="G96" s="32" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H96" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H96" s="29" t="n"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3913,31 +3818,31 @@
     </row>
     <row r="97" hidden="1">
       <c r="A97" s="16" t="n"/>
-      <c r="B97" s="27" t="n">
+      <c r="B97" s="29" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="27" t="inlineStr">
+      <c r="C97" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D97" s="28" t="inlineStr">
+      <c r="D97" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2wu3ra9</t>
         </is>
       </c>
-      <c r="E97" s="29" t="inlineStr">
+      <c r="E97" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Soundcore by Anker P20i Graves Poderosos e Impactantes Bluetooth 5.3 30H de Reprodução Resistência à Água 2 Mics IA para Chamadas Claras Personalização de Som via App Cor Preto</t>
         </is>
       </c>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="30" t="inlineStr">
+      <c r="F97" s="29" t="n"/>
+      <c r="G97" s="32" t="inlineStr">
         <is>
           <t>Soundcore</t>
         </is>
       </c>
-      <c r="H97" s="27" t="n"/>
+      <c r="H97" s="29" t="n"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -3946,7 +3851,7 @@
     </row>
     <row r="98" hidden="1">
       <c r="A98" s="3" t="n"/>
-      <c r="B98" s="53" t="n">
+      <c r="B98" s="55" t="n">
         <v>97</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3971,27 +3876,23 @@
     </row>
     <row r="99" hidden="1">
       <c r="A99" s="3" t="n"/>
-      <c r="B99" s="27" t="n">
+      <c r="B99" s="55" t="n">
         <v>98</v>
       </c>
-      <c r="C99" s="27" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D99" s="28" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/2L2DTy9</t>
         </is>
       </c>
-      <c r="E99" s="29" t="inlineStr">
-        <is>
-          <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Branco</t>
-        </is>
-      </c>
-      <c r="F99" s="27" t="n"/>
-      <c r="G99" s="27" t="n"/>
-      <c r="H99" s="27" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4000,31 +3901,31 @@
     </row>
     <row r="100" hidden="1">
       <c r="A100" s="16" t="n"/>
-      <c r="B100" s="27" t="n">
+      <c r="B100" s="29" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="27" t="inlineStr">
+      <c r="C100" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D100" s="28" t="inlineStr">
+      <c r="D100" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/19F238V</t>
         </is>
       </c>
-      <c r="E100" s="29" t="inlineStr">
+      <c r="E100" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Sem Fio Stage Hero6 TWS Bluetooth 5.2 Cancelamento De Ruído Ativo 35h IPX5 Para Academia, Corrida e Jogos - Stagesound</t>
         </is>
       </c>
-      <c r="F100" s="27" t="n"/>
-      <c r="G100" s="30" t="inlineStr">
+      <c r="F100" s="29" t="n"/>
+      <c r="G100" s="32" t="inlineStr">
         <is>
           <t>Coolme</t>
         </is>
       </c>
-      <c r="H100" s="27" t="n"/>
+      <c r="H100" s="29" t="n"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4033,35 +3934,31 @@
     </row>
     <row r="101" hidden="1">
       <c r="A101" s="16" t="n"/>
-      <c r="B101" s="31" t="n">
+      <c r="B101" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="C101" s="31" t="inlineStr">
+      <c r="C101" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D101" s="32" t="inlineStr">
+      <c r="D101" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1c6vAL2</t>
         </is>
       </c>
-      <c r="E101" s="33" t="inlineStr">
+      <c r="E101" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Aberto Indicador De Bateria Ipx7 Para Corrida,fone De Ouvido Bluetooth Com Ear Clip Tws Ows Hifi Esportivo 72h Bateria Ipx7 Prova D'água E Suor Enc Cancelamento Ruído</t>
         </is>
       </c>
-      <c r="F101" s="31" t="n"/>
-      <c r="G101" s="34" t="inlineStr">
+      <c r="F101" s="29" t="n"/>
+      <c r="G101" s="32" t="inlineStr">
         <is>
           <t>Inova Cases</t>
         </is>
       </c>
-      <c r="H101" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="H101" s="29" t="n"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4070,31 +3967,31 @@
     </row>
     <row r="102" hidden="1">
       <c r="A102" s="16" t="n"/>
-      <c r="B102" s="27" t="n">
+      <c r="B102" s="29" t="n">
         <v>101</v>
       </c>
-      <c r="C102" s="27" t="inlineStr">
+      <c r="C102" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D102" s="28" t="inlineStr">
+      <c r="D102" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2rbugtv</t>
         </is>
       </c>
-      <c r="E102" s="29" t="inlineStr">
+      <c r="E102" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Ear Cuff Ows Hifi 90 Horas Enc Ipx6</t>
         </is>
       </c>
-      <c r="F102" s="27" t="n"/>
-      <c r="G102" s="30" t="inlineStr">
+      <c r="F102" s="29" t="n"/>
+      <c r="G102" s="32" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H102" s="27" t="n"/>
+      <c r="H102" s="29" t="n"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4103,31 +4000,31 @@
     </row>
     <row r="103" hidden="1">
       <c r="A103" s="3" t="n"/>
-      <c r="B103" s="27" t="n">
+      <c r="B103" s="55" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="27" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D103" s="28" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1N2GQcc</t>
         </is>
       </c>
-      <c r="E103" s="29" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Sem Fio Wave Buds 2 JBL JBLWBUDS2BLK Preto</t>
         </is>
       </c>
-      <c r="F103" s="27" t="n"/>
-      <c r="G103" s="30" t="inlineStr">
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="18" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H103" s="27" t="n"/>
+      <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4136,44 +4033,40 @@
     </row>
     <row r="104" hidden="1">
       <c r="A104" s="16" t="n"/>
-      <c r="B104" s="31" t="n">
+      <c r="B104" s="29" t="n">
         <v>103</v>
       </c>
-      <c r="C104" s="31" t="inlineStr">
+      <c r="C104" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D104" s="32" t="inlineStr">
+      <c r="D104" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2wA6HkN</t>
         </is>
       </c>
-      <c r="E104" s="33" t="inlineStr">
+      <c r="E104" s="31" t="inlineStr">
         <is>
           <t>Basike Fone De Ouvido Sem Fio Esportivo Bluetooth5.4 TWS, Corrida Gancho, à prova d'água, Com Gan, Tela LED Dupla, Suporta chamadas de voz, adequadas para Android e IOS, Cor Branco</t>
         </is>
       </c>
-      <c r="F104" s="31" t="n"/>
-      <c r="G104" s="34" t="inlineStr">
+      <c r="F104" s="29" t="n"/>
+      <c r="G104" s="32" t="inlineStr">
         <is>
           <t>Basike</t>
         </is>
       </c>
-      <c r="H104" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="H104" s="29" t="n"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" s="3" t="n"/>
-      <c r="B105" s="53" t="n">
+      <c r="B105" s="55" t="n">
         <v>104</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4196,400 +4089,380 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106" s="16" t="n"/>
-      <c r="B106" s="35" t="n">
+      <c r="B106" s="29" t="n">
         <v>105</v>
       </c>
-      <c r="C106" s="35" t="inlineStr">
+      <c r="C106" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D106" s="36" t="inlineStr">
+      <c r="D106" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2kNgG1Z</t>
         </is>
       </c>
-      <c r="E106" s="37" t="inlineStr">
+      <c r="E106" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Baseus Encok H17 Com Fio P2 3.5mm Premium Cor Branco</t>
         </is>
       </c>
-      <c r="F106" s="35" t="n"/>
-      <c r="G106" s="38" t="inlineStr">
+      <c r="F106" s="29" t="n"/>
+      <c r="G106" s="32" t="inlineStr">
         <is>
           <t>Baseus</t>
         </is>
       </c>
-      <c r="H106" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H106" s="29" t="n"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" s="16" t="n"/>
-      <c r="B107" s="35" t="n">
+      <c r="B107" s="29" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="35" t="inlineStr">
+      <c r="C107" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D107" s="36" t="inlineStr">
+      <c r="D107" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2P1K5Eq</t>
         </is>
       </c>
-      <c r="E107" s="37" t="inlineStr">
+      <c r="E107" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Tae1126bk In Ear Com Microfone Philips Cor Preto</t>
         </is>
       </c>
-      <c r="F107" s="35" t="n"/>
-      <c r="G107" s="38" t="inlineStr">
+      <c r="F107" s="29" t="n"/>
+      <c r="G107" s="32" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H107" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H107" s="29" t="n"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" s="16" t="n"/>
-      <c r="B108" s="35" t="n">
+      <c r="B108" s="29" t="n">
         <v>107</v>
       </c>
-      <c r="C108" s="35" t="inlineStr">
+      <c r="C108" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D108" s="36" t="inlineStr">
+      <c r="D108" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1jMCFjN</t>
         </is>
       </c>
-      <c r="E108" s="37" t="inlineStr">
+      <c r="E108" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Com Fio Somic Tone Extra Bass Microfone S603 Preto</t>
         </is>
       </c>
-      <c r="F108" s="35" t="n"/>
-      <c r="G108" s="38" t="inlineStr">
+      <c r="F108" s="29" t="n"/>
+      <c r="G108" s="32" t="inlineStr">
         <is>
           <t>Somic Tone</t>
         </is>
       </c>
-      <c r="H108" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H108" s="29" t="n"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" s="3" t="n"/>
-      <c r="B109" s="27" t="n">
+      <c r="B109" s="55" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="27" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D109" s="28" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>https://meli.la/1Vj6R2V</t>
         </is>
       </c>
-      <c r="E109" s="29" t="n"/>
-      <c r="F109" s="27" t="n"/>
-      <c r="G109" s="27" t="n"/>
-      <c r="H109" s="27" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110" s="16" t="n"/>
-      <c r="B110" s="27" t="n">
+      <c r="B110" s="29" t="n">
         <v>109</v>
       </c>
-      <c r="C110" s="27" t="inlineStr">
+      <c r="C110" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D110" s="28" t="inlineStr">
+      <c r="D110" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2m5Y1hr</t>
         </is>
       </c>
-      <c r="E110" s="29" t="inlineStr">
+      <c r="E110" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Retorno Palco Edx Pro Dj In-ear + Case Cor Cristal</t>
         </is>
       </c>
-      <c r="F110" s="27" t="n"/>
-      <c r="G110" s="30" t="inlineStr">
+      <c r="F110" s="29" t="n"/>
+      <c r="G110" s="32" t="inlineStr">
         <is>
           <t>Mega digital eletronicos</t>
         </is>
       </c>
-      <c r="H110" s="27" t="n"/>
+      <c r="H110" s="29" t="n"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111" s="16" t="n"/>
-      <c r="B111" s="27" t="n">
+      <c r="B111" s="29" t="n">
         <v>110</v>
       </c>
-      <c r="C111" s="27" t="inlineStr">
+      <c r="C111" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D111" s="28" t="inlineStr">
+      <c r="D111" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/26bqnka</t>
         </is>
       </c>
-      <c r="E111" s="29" t="inlineStr">
+      <c r="E111" s="31" t="inlineStr">
         <is>
           <t>2pcs Fone De Ouvido 1.2m Com Fio 3.5mm Com Microfone Preto</t>
         </is>
       </c>
-      <c r="F111" s="27" t="n"/>
-      <c r="G111" s="30" t="inlineStr">
+      <c r="F111" s="29" t="n"/>
+      <c r="G111" s="32" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H111" s="27" t="n"/>
+      <c r="H111" s="29" t="n"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" s="16" t="n"/>
-      <c r="B112" s="27" t="n">
+      <c r="B112" s="29" t="n">
         <v>111</v>
       </c>
-      <c r="C112" s="27" t="inlineStr">
+      <c r="C112" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D112" s="28" t="inlineStr">
+      <c r="D112" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/14Hqw6W</t>
         </is>
       </c>
-      <c r="E112" s="29" t="inlineStr">
+      <c r="E112" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Com Fio 3.5mm Com Microfone Cor Preto S6</t>
         </is>
       </c>
-      <c r="F112" s="27" t="n"/>
-      <c r="G112" s="30" t="inlineStr">
+      <c r="F112" s="29" t="n"/>
+      <c r="G112" s="32" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H112" s="27" t="n"/>
+      <c r="H112" s="29" t="n"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" s="9" t="n"/>
-      <c r="B113" s="31" t="n">
+      <c r="B113" s="56" t="n">
         <v>112</v>
       </c>
-      <c r="C113" s="31" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D113" s="32" t="inlineStr">
+      <c r="D113" s="10" t="inlineStr">
         <is>
           <t>https://meli.la/2Kef7ag</t>
         </is>
       </c>
-      <c r="E113" s="33" t="n"/>
-      <c r="F113" s="31" t="n"/>
-      <c r="G113" s="31" t="n"/>
-      <c r="H113" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="E113" s="11" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="9" t="n"/>
       <c r="I113" s="9" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" s="16" t="n"/>
-      <c r="B114" s="27" t="n">
+      <c r="B114" s="29" t="n">
         <v>113</v>
       </c>
-      <c r="C114" s="27" t="inlineStr">
+      <c r="C114" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D114" s="28" t="inlineStr">
+      <c r="D114" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1WJac2f</t>
         </is>
       </c>
-      <c r="E114" s="29" t="inlineStr">
+      <c r="E114" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Intra-auricular Com Fio 1.2 Metros Original</t>
         </is>
       </c>
-      <c r="F114" s="27" t="n"/>
-      <c r="G114" s="30" t="inlineStr">
+      <c r="F114" s="29" t="n"/>
+      <c r="G114" s="32" t="inlineStr">
         <is>
           <t>H'maston</t>
         </is>
       </c>
-      <c r="H114" s="27" t="n"/>
+      <c r="H114" s="29" t="n"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115" s="16" t="n"/>
-      <c r="B115" s="35" t="n">
+      <c r="B115" s="29" t="n">
         <v>114</v>
       </c>
-      <c r="C115" s="35" t="inlineStr">
+      <c r="C115" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D115" s="36" t="inlineStr">
+      <c r="D115" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1KuHyGK</t>
         </is>
       </c>
-      <c r="E115" s="37" t="inlineStr">
+      <c r="E115" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Taue101bk/00 Com Microfone Philips Cor Preto</t>
         </is>
       </c>
-      <c r="F115" s="35" t="n"/>
-      <c r="G115" s="38" t="inlineStr">
+      <c r="F115" s="29" t="n"/>
+      <c r="G115" s="32" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H115" s="35" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
+      <c r="H115" s="29" t="n"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116" s="16" t="n"/>
-      <c r="B116" s="27" t="n">
+      <c r="B116" s="29" t="n">
         <v>115</v>
       </c>
-      <c r="C116" s="27" t="inlineStr">
+      <c r="C116" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D116" s="28" t="inlineStr">
+      <c r="D116" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1CpcDEH</t>
         </is>
       </c>
-      <c r="E116" s="29" t="inlineStr">
+      <c r="E116" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Silicone Com Fio 3.5mm Com Controle E Microfo</t>
         </is>
       </c>
-      <c r="F116" s="27" t="n"/>
-      <c r="G116" s="27" t="inlineStr">
+      <c r="F116" s="29" t="n"/>
+      <c r="G116" s="29" t="inlineStr">
         <is>
           <t>Bemmy</t>
         </is>
       </c>
-      <c r="H116" s="27" t="n"/>
+      <c r="H116" s="29" t="n"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117" s="16" t="n"/>
-      <c r="B117" s="27" t="n">
+      <c r="B117" s="29" t="n">
         <v>116</v>
       </c>
-      <c r="C117" s="27" t="inlineStr">
+      <c r="C117" s="29" t="inlineStr">
         <is>
           <t>Fone com fio</t>
         </is>
       </c>
-      <c r="D117" s="28" t="inlineStr">
+      <c r="D117" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1ttbaqV</t>
         </is>
       </c>
-      <c r="E117" s="29" t="inlineStr">
+      <c r="E117" s="31" t="inlineStr">
         <is>
           <t>Fone de Ouvido In-Ear QKZ AKX para Música e Jogo com Microfone e Cancelamento de Ruído</t>
         </is>
       </c>
-      <c r="F117" s="27" t="n"/>
-      <c r="G117" s="30" t="inlineStr">
+      <c r="F117" s="29" t="n"/>
+      <c r="G117" s="32" t="inlineStr">
         <is>
           <t>TECHSTORE-QKZ</t>
         </is>
       </c>
-      <c r="H117" s="27" t="n"/>
+      <c r="H117" s="29" t="n"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4598,12 +4471,12 @@
     </row>
     <row r="118" hidden="1">
       <c r="A118" s="3" t="n"/>
-      <c r="B118" s="53" t="n">
+      <c r="B118" s="55" t="n">
         <v>117</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Fone gamer (headset com fio)</t>
+          <t>Headset Gamer Com Fio</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -4623,31 +4496,31 @@
     </row>
     <row r="119" hidden="1">
       <c r="A119" s="16" t="n"/>
-      <c r="B119" s="27" t="n">
+      <c r="B119" s="29" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D119" s="28" t="inlineStr">
+      <c r="C119" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D119" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2unSB1K</t>
         </is>
       </c>
-      <c r="E119" s="29" t="inlineStr">
+      <c r="E119" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Gamer Headset Led Rgb Computador Microfone Pc</t>
         </is>
       </c>
-      <c r="F119" s="27" t="n"/>
-      <c r="G119" s="30" t="inlineStr">
+      <c r="F119" s="29" t="n"/>
+      <c r="G119" s="32" t="inlineStr">
         <is>
           <t>Knup</t>
         </is>
       </c>
-      <c r="H119" s="27" t="n"/>
+      <c r="H119" s="29" t="n"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4656,31 +4529,31 @@
     </row>
     <row r="120" hidden="1">
       <c r="A120" s="16" t="n"/>
-      <c r="B120" s="27" t="n">
+      <c r="B120" s="29" t="n">
         <v>119</v>
       </c>
-      <c r="C120" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D120" s="28" t="inlineStr">
+      <c r="C120" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D120" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1Rqma2o</t>
         </is>
       </c>
-      <c r="E120" s="29" t="inlineStr">
+      <c r="E120" s="31" t="inlineStr">
         <is>
           <t>Fone de ouvido Headset over-ear gamer Havit H2232D 2xP2, RGB - Preto</t>
         </is>
       </c>
-      <c r="F120" s="27" t="n"/>
-      <c r="G120" s="30" t="inlineStr">
+      <c r="F120" s="29" t="n"/>
+      <c r="G120" s="32" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H120" s="27" t="n"/>
+      <c r="H120" s="29" t="n"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4689,31 +4562,31 @@
     </row>
     <row r="121" hidden="1">
       <c r="A121" s="16" t="n"/>
-      <c r="B121" s="27" t="n">
+      <c r="B121" s="29" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D121" s="28" t="inlineStr">
+      <c r="C121" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D121" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2nSWHED</t>
         </is>
       </c>
-      <c r="E121" s="29" t="inlineStr">
+      <c r="E121" s="31" t="inlineStr">
         <is>
           <t>Fone Headset Gamer Profissional Mento Rgb H270-rgb Redragon Cor Preto</t>
         </is>
       </c>
-      <c r="F121" s="27" t="n"/>
-      <c r="G121" s="30" t="inlineStr">
+      <c r="F121" s="29" t="n"/>
+      <c r="G121" s="32" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H121" s="27" t="n"/>
+      <c r="H121" s="29" t="n"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4722,12 +4595,12 @@
     </row>
     <row r="122" hidden="1">
       <c r="A122" s="3" t="n"/>
-      <c r="B122" s="53" t="n">
+      <c r="B122" s="55" t="n">
         <v>121</v>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Fone gamer (headset com fio)</t>
+          <t>Headset Gamer Com Fio</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -4747,31 +4620,31 @@
     </row>
     <row r="123" hidden="1">
       <c r="A123" s="16" t="n"/>
-      <c r="B123" s="27" t="n">
+      <c r="B123" s="29" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D123" s="28" t="inlineStr">
+      <c r="C123" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/15fHoqk</t>
         </is>
       </c>
-      <c r="E123" s="29" t="inlineStr">
+      <c r="E123" s="31" t="inlineStr">
         <is>
           <t>Headset over-ear Gamer Quantum 400 Preto LED JBL</t>
         </is>
       </c>
-      <c r="F123" s="27" t="n"/>
-      <c r="G123" s="30" t="inlineStr">
+      <c r="F123" s="29" t="n"/>
+      <c r="G123" s="32" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="H123" s="27" t="n"/>
+      <c r="H123" s="29" t="n"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4780,31 +4653,31 @@
     </row>
     <row r="124" hidden="1">
       <c r="A124" s="16" t="n"/>
-      <c r="B124" s="27" t="n">
+      <c r="B124" s="29" t="n">
         <v>123</v>
       </c>
-      <c r="C124" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D124" s="28" t="inlineStr">
+      <c r="C124" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D124" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1wmU4zZ</t>
         </is>
       </c>
-      <c r="E124" s="29" t="inlineStr">
+      <c r="E124" s="31" t="inlineStr">
         <is>
           <t>Headset Gamer Mancer Twilight S, Rainbow, Drivers 40mm Preto</t>
         </is>
       </c>
-      <c r="F124" s="27" t="n"/>
-      <c r="G124" s="27" t="inlineStr">
+      <c r="F124" s="29" t="n"/>
+      <c r="G124" s="29" t="inlineStr">
         <is>
           <t>Mancer</t>
         </is>
       </c>
-      <c r="H124" s="27" t="n"/>
+      <c r="H124" s="29" t="n"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4813,12 +4686,12 @@
     </row>
     <row r="125" hidden="1">
       <c r="A125" s="12" t="n"/>
-      <c r="B125" s="27" t="n">
+      <c r="B125" s="29" t="n">
         <v>124</v>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Fone gamer (headset com fio)</t>
+          <t>Headset Gamer Com Fio</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr">
@@ -4846,31 +4719,31 @@
     </row>
     <row r="126" hidden="1">
       <c r="A126" s="16" t="n"/>
-      <c r="B126" s="27" t="n">
+      <c r="B126" s="29" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D126" s="28" t="inlineStr">
+      <c r="C126" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D126" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2tidt18</t>
         </is>
       </c>
-      <c r="E126" s="29" t="inlineStr">
+      <c r="E126" s="31" t="inlineStr">
         <is>
           <t>Headset Gamer Redragon Zeus Lite Preto P3 H510-lt Preto</t>
         </is>
       </c>
-      <c r="F126" s="27" t="n"/>
-      <c r="G126" s="27" t="inlineStr">
+      <c r="F126" s="29" t="n"/>
+      <c r="G126" s="29" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H126" s="27" t="n"/>
+      <c r="H126" s="29" t="n"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4879,31 +4752,31 @@
     </row>
     <row r="127" hidden="1">
       <c r="A127" s="16" t="n"/>
-      <c r="B127" s="27" t="n">
+      <c r="B127" s="29" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D127" s="28" t="inlineStr">
+      <c r="C127" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D127" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1eNRNSS</t>
         </is>
       </c>
-      <c r="E127" s="29" t="inlineStr">
+      <c r="E127" s="31" t="inlineStr">
         <is>
           <t>Fone Headset Gamer HAVIT H2230d P2 P3 3,5MM Microfone Removível Consoles PC Preto</t>
         </is>
       </c>
-      <c r="F127" s="27" t="n"/>
-      <c r="G127" s="30" t="inlineStr">
+      <c r="F127" s="29" t="n"/>
+      <c r="G127" s="32" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H127" s="27" t="n"/>
+      <c r="H127" s="29" t="n"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4912,31 +4785,31 @@
     </row>
     <row r="128" hidden="1">
       <c r="A128" s="16" t="n"/>
-      <c r="B128" s="27" t="n">
+      <c r="B128" s="29" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D128" s="28" t="inlineStr">
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D128" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1uLNe2m</t>
         </is>
       </c>
-      <c r="E128" s="29" t="inlineStr">
+      <c r="E128" s="31" t="inlineStr">
         <is>
           <t>Fone Headset Gamer Pro H2 Preto Fortrek</t>
         </is>
       </c>
-      <c r="F128" s="27" t="n"/>
-      <c r="G128" s="27" t="inlineStr">
+      <c r="F128" s="29" t="n"/>
+      <c r="G128" s="29" t="inlineStr">
         <is>
           <t>Fortrek</t>
         </is>
       </c>
-      <c r="H128" s="27" t="n"/>
+      <c r="H128" s="29" t="n"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4945,31 +4818,31 @@
     </row>
     <row r="129" hidden="1">
       <c r="A129" s="16" t="n"/>
-      <c r="B129" s="27" t="n">
+      <c r="B129" s="29" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D129" s="28" t="inlineStr">
+      <c r="C129" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D129" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2UUay16</t>
         </is>
       </c>
-      <c r="E129" s="29" t="inlineStr">
+      <c r="E129" s="31" t="inlineStr">
         <is>
           <t>Fone Nubwo® U3 Headset Gamer 3d Estéreo Ouvido Para Pc Ps4</t>
         </is>
       </c>
-      <c r="F129" s="27" t="n"/>
-      <c r="G129" s="30" t="inlineStr">
+      <c r="F129" s="29" t="n"/>
+      <c r="G129" s="32" t="inlineStr">
         <is>
           <t>Nubwo</t>
         </is>
       </c>
-      <c r="H129" s="27" t="n"/>
+      <c r="H129" s="29" t="n"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -4978,31 +4851,31 @@
     </row>
     <row r="130" hidden="1">
       <c r="A130" s="16" t="n"/>
-      <c r="B130" s="27" t="n">
+      <c r="B130" s="29" t="n">
         <v>129</v>
       </c>
-      <c r="C130" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D130" s="28" t="inlineStr">
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D130" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2Z5SEKB</t>
         </is>
       </c>
-      <c r="E130" s="27" t="inlineStr">
+      <c r="E130" s="29" t="inlineStr">
         <is>
           <t>Headset Gamer Profissional Onikuma X25 Fone De Ouvido Over-ear Compatível com Ps4/ps5/xbox/one/series/pc com Luz Led RGB Plug 3.5mm com Microfone Flexível Incorporado Cabo De 2.2m Confortável</t>
         </is>
       </c>
-      <c r="F130" s="27" t="n"/>
-      <c r="G130" s="30" t="inlineStr">
+      <c r="F130" s="29" t="n"/>
+      <c r="G130" s="32" t="inlineStr">
         <is>
           <t>Onikuma</t>
         </is>
       </c>
-      <c r="H130" s="27" t="n"/>
+      <c r="H130" s="29" t="n"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5011,31 +4884,31 @@
     </row>
     <row r="131" hidden="1">
       <c r="A131" s="16" t="n"/>
-      <c r="B131" s="27" t="n">
+      <c r="B131" s="29" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D131" s="28" t="inlineStr">
+      <c r="C131" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D131" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1dZBv92</t>
         </is>
       </c>
-      <c r="E131" s="27" t="inlineStr">
+      <c r="E131" s="29" t="inlineStr">
         <is>
           <t>Headset Gamer Havit H2002d Fone de ouvido over-ear gamer Vermelho Compatível com PS4/PS5/xbox/One/Series/pc</t>
         </is>
       </c>
-      <c r="F131" s="27" t="n"/>
-      <c r="G131" s="30" t="inlineStr">
+      <c r="F131" s="29" t="n"/>
+      <c r="G131" s="32" t="inlineStr">
         <is>
           <t>Havit</t>
         </is>
       </c>
-      <c r="H131" s="27" t="n"/>
+      <c r="H131" s="29" t="n"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5044,31 +4917,31 @@
     </row>
     <row r="132" hidden="1">
       <c r="A132" s="16" t="n"/>
-      <c r="B132" s="27" t="n">
+      <c r="B132" s="29" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D132" s="28" t="inlineStr">
+      <c r="C132" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D132" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2rBnTKy</t>
         </is>
       </c>
-      <c r="E132" s="29" t="inlineStr">
+      <c r="E132" s="31" t="inlineStr">
         <is>
           <t>Headset Fone Gamer Redragon Pandora 2 Rgb, H350rgb-1 Cor Preto</t>
         </is>
       </c>
-      <c r="F132" s="27" t="n"/>
-      <c r="G132" s="30" t="inlineStr">
+      <c r="F132" s="29" t="n"/>
+      <c r="G132" s="32" t="inlineStr">
         <is>
           <t>Redragon</t>
         </is>
       </c>
-      <c r="H132" s="27" t="n"/>
+      <c r="H132" s="29" t="n"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5077,31 +4950,31 @@
     </row>
     <row r="133" hidden="1">
       <c r="A133" s="16" t="n"/>
-      <c r="B133" s="27" t="n">
+      <c r="B133" s="29" t="n">
         <v>132</v>
       </c>
-      <c r="C133" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D133" s="28" t="inlineStr">
+      <c r="C133" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D133" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1D1stad</t>
         </is>
       </c>
-      <c r="E133" s="29" t="inlineStr">
+      <c r="E133" s="31" t="inlineStr">
         <is>
           <t>Headset Fifine Ampligame H6 Rgb 7.1 Surround Gamer Cor Preto</t>
         </is>
       </c>
-      <c r="F133" s="27" t="n"/>
-      <c r="G133" s="30" t="inlineStr">
+      <c r="F133" s="29" t="n"/>
+      <c r="G133" s="32" t="inlineStr">
         <is>
           <t>Fifine</t>
         </is>
       </c>
-      <c r="H133" s="27" t="n"/>
+      <c r="H133" s="29" t="n"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>⬜</t>
@@ -5110,374 +4983,374 @@
     </row>
     <row r="134" hidden="1">
       <c r="A134" s="16" t="n"/>
-      <c r="B134" s="27" t="n">
+      <c r="B134" s="29" t="n">
         <v>133</v>
       </c>
-      <c r="C134" s="27" t="inlineStr">
-        <is>
-          <t>Fone gamer (headset com fio)</t>
-        </is>
-      </c>
-      <c r="D134" s="28" t="inlineStr">
+      <c r="C134" s="29" t="inlineStr">
+        <is>
+          <t>Headset Gamer Com Fio</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1ZVVbE5</t>
         </is>
       </c>
-      <c r="E134" s="29" t="inlineStr">
+      <c r="E134" s="31" t="inlineStr">
         <is>
           <t>Headset Gamer Mizar ELG, 3D Surround 7.1, Drivers de 50mm, Microfone Omnidirecional, Earpads de Malha Esportiva, Iluminação RGB, Preto, HGMZ</t>
         </is>
       </c>
-      <c r="F134" s="27" t="n"/>
-      <c r="G134" s="30" t="inlineStr">
+      <c r="F134" s="29" t="n"/>
+      <c r="G134" s="32" t="inlineStr">
         <is>
           <t>ELG</t>
         </is>
       </c>
-      <c r="H134" s="27" t="n"/>
+      <c r="H134" s="29" t="n"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="135" hidden="1">
+    <row r="135">
       <c r="A135" s="16" t="n"/>
-      <c r="B135" s="27" t="n">
+      <c r="B135" s="29" t="n">
         <v>134</v>
       </c>
-      <c r="C135" s="27" t="inlineStr">
+      <c r="C135" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D135" s="28" t="inlineStr">
+      <c r="D135" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1xR2nNz</t>
         </is>
       </c>
-      <c r="E135" s="29" t="inlineStr">
+      <c r="E135" s="31" t="inlineStr">
         <is>
           <t>Cabo Carregador Usb Tipo C 6a Carregamento Rápido Alta Velocidade Compatível Celulares Smartphones Tablets Resistência Premium Para Xiaomi Samsung Ios Motorola 1 Metro Branco Ezsias Armarinhos</t>
         </is>
       </c>
-      <c r="F135" s="27" t="n"/>
-      <c r="G135" s="30" t="inlineStr">
+      <c r="F135" s="29" t="n"/>
+      <c r="G135" s="32" t="inlineStr">
         <is>
           <t>Ezsias Armarinhos</t>
         </is>
       </c>
-      <c r="H135" s="27" t="n"/>
+      <c r="H135" s="29" t="n"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="136" hidden="1">
+    <row r="136">
       <c r="A136" s="16" t="n"/>
-      <c r="B136" s="27" t="n">
+      <c r="B136" s="29" t="n">
         <v>135</v>
       </c>
-      <c r="C136" s="27" t="inlineStr">
+      <c r="C136" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D136" s="28" t="inlineStr">
+      <c r="D136" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1s6goJ3</t>
         </is>
       </c>
-      <c r="E136" s="29" t="inlineStr">
+      <c r="E136" s="31" t="inlineStr">
         <is>
           <t>Cabo Usb X Tipo C Turbo 60w - 2 Metros Celular Notebook 3.1</t>
         </is>
       </c>
-      <c r="F136" s="27" t="n"/>
-      <c r="G136" s="30" t="inlineStr">
+      <c r="F136" s="29" t="n"/>
+      <c r="G136" s="32" t="inlineStr">
         <is>
           <t>Hrebos</t>
         </is>
       </c>
-      <c r="H136" s="27" t="n"/>
+      <c r="H136" s="29" t="n"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="137" hidden="1">
+    <row r="137">
       <c r="A137" s="16" t="n"/>
-      <c r="B137" s="27" t="n">
+      <c r="B137" s="29" t="n">
         <v>136</v>
       </c>
-      <c r="C137" s="27" t="inlineStr">
+      <c r="C137" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D137" s="28" t="inlineStr">
+      <c r="D137" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1G4ky69</t>
         </is>
       </c>
-      <c r="E137" s="29" t="inlineStr">
+      <c r="E137" s="31" t="inlineStr">
         <is>
           <t>Cabo Usb Turbo Tipo C Philips Original Carregamento Rapido 1.2 Metro Nylon DLC2628N Cor Vermelho</t>
         </is>
       </c>
-      <c r="F137" s="27" t="n"/>
-      <c r="G137" s="30" t="inlineStr">
+      <c r="F137" s="29" t="n"/>
+      <c r="G137" s="32" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="H137" s="27" t="n"/>
+      <c r="H137" s="29" t="n"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="138" hidden="1">
+    <row r="138">
       <c r="A138" s="16" t="n"/>
-      <c r="B138" s="27" t="n">
+      <c r="B138" s="29" t="n">
         <v>137</v>
       </c>
-      <c r="C138" s="27" t="inlineStr">
+      <c r="C138" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D138" s="28" t="inlineStr">
+      <c r="D138" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1FATBkB</t>
         </is>
       </c>
-      <c r="E138" s="29" t="inlineStr">
+      <c r="E138" s="31" t="inlineStr">
         <is>
           <t>Cabo Usb Entrada Tipo C A 60w Turbo Ultra Rápido 2 Metros Longo Nylon Blindado Plus Max Trançado Reforçado Resistente Compatível Com Carregador De Celular Pd Qc Usbc Carga E Dados Marca Pro Phone See</t>
         </is>
       </c>
-      <c r="F138" s="27" t="n"/>
-      <c r="G138" s="30" t="inlineStr">
+      <c r="F138" s="29" t="n"/>
+      <c r="G138" s="32" t="inlineStr">
         <is>
           <t>PRO PHONE SEE</t>
         </is>
       </c>
-      <c r="H138" s="27" t="n"/>
+      <c r="H138" s="29" t="n"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="139" hidden="1">
+    <row r="139">
       <c r="A139" s="16" t="n"/>
-      <c r="B139" s="27" t="n">
+      <c r="B139" s="29" t="n">
         <v>138</v>
       </c>
-      <c r="C139" s="27" t="inlineStr">
+      <c r="C139" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D139" s="28" t="inlineStr">
+      <c r="D139" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/2z251cg</t>
         </is>
       </c>
-      <c r="E139" s="29" t="inlineStr">
+      <c r="E139" s="31" t="inlineStr">
         <is>
           <t>Cabo Usb Carregador Celular Usb C Tipo C 3 Metros Turbo 4.0</t>
         </is>
       </c>
-      <c r="F139" s="27" t="n"/>
-      <c r="G139" s="30" t="inlineStr">
+      <c r="F139" s="29" t="n"/>
+      <c r="G139" s="32" t="inlineStr">
         <is>
           <t>Hrebos</t>
         </is>
       </c>
-      <c r="H139" s="27" t="n"/>
+      <c r="H139" s="29" t="n"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="140" hidden="1">
+    <row r="140">
       <c r="A140" s="16" t="n"/>
-      <c r="B140" s="27" t="n">
+      <c r="B140" s="29" t="n">
         <v>139</v>
       </c>
-      <c r="C140" s="27" t="inlineStr">
+      <c r="C140" s="29" t="inlineStr">
         <is>
           <t>Cabo USB-C</t>
         </is>
       </c>
-      <c r="D140" s="28" t="inlineStr">
+      <c r="D140" s="30" t="inlineStr">
         <is>
           <t>https://meli.la/1rbUMsD</t>
         </is>
       </c>
-      <c r="E140" s="29" t="inlineStr">
+      <c r="E140" s="31" t="inlineStr">
         <is>
           <t>Cabo Usb Tipo C 2 Metros Carregador Turbo Compatível Com Motorola Moto G Samsung Galaxy Xiaomi Redmi iPhone 15 16 17 Pro Max Carplay Ps5 Super Rápido</t>
         </is>
       </c>
-      <c r="F140" s="27" t="n"/>
-      <c r="G140" s="30" t="inlineStr">
+      <c r="F140" s="29" t="n"/>
+      <c r="G140" s="32" t="inlineStr">
         <is>
           <t>rgbsgames e pipas</t>
         </is>
       </c>
-      <c r="H140" s="27" t="n"/>
+      <c r="H140" s="29" t="n"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="141" hidden="1" customFormat="1" s="55">
+    <row r="141" hidden="1" customFormat="1" s="57">
       <c r="A141" s="16" t="n"/>
-      <c r="B141" s="27" t="n">
+      <c r="B141" s="29" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="27" t="inlineStr">
+      <c r="C141" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D141" s="39" t="inlineStr">
+      <c r="D141" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2qiZA87</t>
         </is>
       </c>
-      <c r="E141" s="29" t="inlineStr">
+      <c r="E141" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 128gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 128gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F141" s="27" t="n"/>
-      <c r="G141" s="30" t="inlineStr">
+      <c r="F141" s="29" t="n"/>
+      <c r="G141" s="32" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H141" s="27" t="n"/>
+      <c r="H141" s="29" t="n"/>
     </row>
     <row r="142" hidden="1">
       <c r="A142" s="16" t="n"/>
-      <c r="B142" s="27" t="n">
+      <c r="B142" s="29" t="n">
         <v>141</v>
       </c>
-      <c r="C142" s="27" t="inlineStr">
+      <c r="C142" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D142" s="39" t="inlineStr">
+      <c r="D142" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2CViyMj</t>
         </is>
       </c>
-      <c r="E142" s="29" t="inlineStr">
+      <c r="E142" s="31" t="inlineStr">
         <is>
           <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 32gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
         </is>
       </c>
-      <c r="F142" s="27" t="n"/>
-      <c r="G142" s="30" t="inlineStr">
+      <c r="F142" s="29" t="n"/>
+      <c r="G142" s="32" t="inlineStr">
         <is>
           <t>Gurumania</t>
         </is>
       </c>
-      <c r="H142" s="27" t="n"/>
+      <c r="H142" s="29" t="n"/>
     </row>
     <row r="143" hidden="1">
       <c r="A143" s="16" t="n"/>
-      <c r="B143" s="27" t="n">
+      <c r="B143" s="29" t="n">
         <v>142</v>
       </c>
-      <c r="C143" s="27" t="inlineStr">
+      <c r="C143" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D143" s="39" t="inlineStr">
+      <c r="D143" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/16wgc76</t>
         </is>
       </c>
-      <c r="E143" s="29" t="inlineStr">
+      <c r="E143" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 64gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F143" s="27" t="n"/>
-      <c r="G143" s="30" t="inlineStr">
+      <c r="F143" s="29" t="n"/>
+      <c r="G143" s="32" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H143" s="27" t="n"/>
+      <c r="H143" s="29" t="n"/>
     </row>
     <row r="144" hidden="1">
       <c r="A144" s="16" t="n"/>
-      <c r="B144" s="27" t="n">
+      <c r="B144" s="29" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="27" t="inlineStr">
+      <c r="C144" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D144" s="39" t="inlineStr">
+      <c r="D144" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/11j9MNb</t>
         </is>
       </c>
-      <c r="E144" s="29" t="inlineStr">
+      <c r="E144" s="31" t="inlineStr">
         <is>
           <t>Pendrive Twist preto 64gb multilaser modelo PD590</t>
         </is>
       </c>
-      <c r="F144" s="27" t="n"/>
-      <c r="G144" s="30" t="inlineStr">
+      <c r="F144" s="29" t="n"/>
+      <c r="G144" s="32" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="H144" s="27" t="n"/>
+      <c r="H144" s="29" t="n"/>
     </row>
     <row r="145" hidden="1">
       <c r="A145" s="9" t="n"/>
-      <c r="B145" s="54" t="n">
+      <c r="B145" s="56" t="n">
         <v>144</v>
       </c>
-      <c r="C145" s="35" t="inlineStr">
+      <c r="C145" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D145" s="41" t="inlineStr">
+      <c r="D145" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/1HWTTfy</t>
         </is>
       </c>
-      <c r="E145" s="37" t="inlineStr">
+      <c r="E145" s="39" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Cruzer Blade 32gb Usb 2.0 Sdcz50-032g-b35 Cor Preto Sem tampa</t>
         </is>
       </c>
-      <c r="F145" s="35" t="n"/>
-      <c r="G145" s="38" t="inlineStr">
+      <c r="F145" s="37" t="n"/>
+      <c r="G145" s="40" t="inlineStr">
         <is>
           <t>SanDisk</t>
         </is>
       </c>
-      <c r="H145" s="35" t="inlineStr">
+      <c r="H145" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5485,286 +5358,286 @@
     </row>
     <row r="146" hidden="1">
       <c r="A146" s="16" t="n"/>
-      <c r="B146" s="27" t="n">
+      <c r="B146" s="29" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="27" t="inlineStr">
+      <c r="C146" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D146" s="39" t="inlineStr">
+      <c r="D146" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2zCrUDN</t>
         </is>
       </c>
-      <c r="E146" s="29" t="inlineStr">
+      <c r="E146" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F146" s="27" t="n"/>
-      <c r="G146" s="30" t="inlineStr">
+      <c r="F146" s="29" t="n"/>
+      <c r="G146" s="32" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H146" s="27" t="n"/>
+      <c r="H146" s="29" t="n"/>
     </row>
     <row r="147" hidden="1">
       <c r="A147" s="16" t="n"/>
-      <c r="B147" s="27" t="n">
+      <c r="B147" s="29" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="27" t="inlineStr">
+      <c r="C147" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D147" s="39" t="inlineStr">
+      <c r="D147" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/29Wfdp7</t>
         </is>
       </c>
-      <c r="E147" s="29" t="inlineStr">
+      <c r="E147" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Ótima De Armazenamento Pc Notebook Haixia Cor Prateado</t>
         </is>
       </c>
-      <c r="F147" s="27" t="n"/>
-      <c r="G147" s="30" t="inlineStr">
+      <c r="F147" s="29" t="n"/>
+      <c r="G147" s="32" t="inlineStr">
         <is>
           <t>Haixia</t>
         </is>
       </c>
-      <c r="H147" s="27" t="n"/>
+      <c r="H147" s="29" t="n"/>
     </row>
     <row r="148" hidden="1">
       <c r="A148" s="16" t="n"/>
-      <c r="B148" s="27" t="n">
+      <c r="B148" s="29" t="n">
         <v>147</v>
       </c>
-      <c r="C148" s="27" t="inlineStr">
+      <c r="C148" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D148" s="39" t="inlineStr">
+      <c r="D148" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1BhCm1B</t>
         </is>
       </c>
-      <c r="E148" s="29" t="inlineStr">
+      <c r="E148" s="31" t="inlineStr">
         <is>
           <t>Pendrive Kapbom 16gb Usb 2.0 Metal Prateado Compatível Wind</t>
         </is>
       </c>
-      <c r="F148" s="27" t="n"/>
-      <c r="G148" s="30" t="inlineStr">
+      <c r="F148" s="29" t="n"/>
+      <c r="G148" s="32" t="inlineStr">
         <is>
           <t>Kapbom</t>
         </is>
       </c>
-      <c r="H148" s="27" t="n"/>
+      <c r="H148" s="29" t="n"/>
     </row>
     <row r="149" hidden="1">
       <c r="A149" s="16" t="n"/>
-      <c r="B149" s="27" t="n">
+      <c r="B149" s="29" t="n">
         <v>148</v>
       </c>
-      <c r="C149" s="27" t="inlineStr">
+      <c r="C149" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D149" s="39" t="inlineStr">
+      <c r="D149" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2UUu5Ti</t>
         </is>
       </c>
-      <c r="E149" s="29" t="inlineStr">
+      <c r="E149" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 8gb Usb Compacto Alto Desempenho E Velocidade</t>
         </is>
       </c>
-      <c r="F149" s="27" t="n"/>
-      <c r="G149" s="30" t="inlineStr">
+      <c r="F149" s="29" t="n"/>
+      <c r="G149" s="32" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="H149" s="27" t="n"/>
+      <c r="H149" s="29" t="n"/>
     </row>
     <row r="150" hidden="1">
       <c r="A150" s="9" t="n"/>
-      <c r="B150" s="54" t="n">
+      <c r="B150" s="56" t="n">
         <v>149</v>
       </c>
-      <c r="C150" s="35" t="inlineStr">
+      <c r="C150" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D150" s="41" t="inlineStr">
+      <c r="D150" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/1Dv34H3</t>
         </is>
       </c>
-      <c r="E150" s="37" t="inlineStr">
+      <c r="E150" s="39" t="inlineStr">
         <is>
           <t>Pendrive 2tb Usb 3.0 Metalico</t>
         </is>
       </c>
-      <c r="F150" s="35" t="n"/>
-      <c r="G150" s="38" t="inlineStr">
+      <c r="F150" s="37" t="n"/>
+      <c r="G150" s="40" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
-      <c r="H150" s="35" t="inlineStr">
+      <c r="H150" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="151" hidden="1" customFormat="1" s="45">
-      <c r="B151" s="46" t="n">
+    <row r="151" hidden="1" customFormat="1" s="47">
+      <c r="B151" s="48" t="n">
         <v>150</v>
       </c>
-      <c r="C151" s="46" t="inlineStr">
+      <c r="C151" s="48" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D151" s="52" t="inlineStr">
+      <c r="D151" s="54" t="inlineStr">
         <is>
           <t>https://meli.la/2qiZA87</t>
         </is>
       </c>
-      <c r="E151" s="48" t="inlineStr">
+      <c r="E151" s="50" t="inlineStr">
         <is>
           <t>Pen Drive 128gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 128gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F151" s="46" t="n"/>
-      <c r="G151" s="49" t="inlineStr">
+      <c r="F151" s="48" t="n"/>
+      <c r="G151" s="51" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H151" s="46" t="n"/>
+      <c r="H151" s="48" t="n"/>
     </row>
     <row r="152" hidden="1">
       <c r="A152" s="16" t="n"/>
-      <c r="B152" s="27" t="n">
+      <c r="B152" s="29" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="27" t="inlineStr">
+      <c r="C152" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D152" s="39" t="inlineStr">
+      <c r="D152" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1zAUW82</t>
         </is>
       </c>
-      <c r="E152" s="29" t="inlineStr">
+      <c r="E152" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Mini Usb 2.0 Chaveiro Metalico Resistente Alta Velocidade Seguro Capacidade Capacidade Ótima 32gb De Armazenamento Pc Notebook Cor Prateado</t>
         </is>
       </c>
-      <c r="F152" s="29" t="n"/>
-      <c r="G152" s="30" t="inlineStr">
+      <c r="F152" s="31" t="n"/>
+      <c r="G152" s="32" t="inlineStr">
         <is>
           <t>RHEAD RED HIGH END STUDIOS</t>
         </is>
       </c>
-      <c r="H152" s="27" t="n"/>
+      <c r="H152" s="29" t="n"/>
     </row>
     <row r="153" hidden="1" ht="21.95" customHeight="1">
       <c r="A153" s="16" t="n"/>
-      <c r="B153" s="27" t="n">
+      <c r="B153" s="29" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="27" t="inlineStr">
+      <c r="C153" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D153" s="39" t="inlineStr">
+      <c r="D153" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1LuoL3b</t>
         </is>
       </c>
-      <c r="E153" s="29" t="inlineStr">
+      <c r="E153" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 16gb Mini Chaveiro Resistente Rápido Usb Metal Cor Prata Alta Velocidade Compatível Desktop Pc Notebook Som Automotivo Wmix Eletrônicos</t>
         </is>
       </c>
-      <c r="F153" s="42" t="n"/>
-      <c r="G153" s="30" t="inlineStr">
+      <c r="F153" s="44" t="n"/>
+      <c r="G153" s="32" t="inlineStr">
         <is>
           <t>WMIX ELETRÔNICOS</t>
         </is>
       </c>
-      <c r="H153" s="27" t="n"/>
+      <c r="H153" s="29" t="n"/>
     </row>
     <row r="154" hidden="1">
       <c r="A154" s="16" t="n"/>
-      <c r="B154" s="27" t="n">
+      <c r="B154" s="29" t="n">
         <v>153</v>
       </c>
-      <c r="C154" s="27" t="inlineStr">
+      <c r="C154" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D154" s="39" t="inlineStr">
+      <c r="D154" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1Q1hTC1</t>
         </is>
       </c>
-      <c r="E154" s="29" t="inlineStr">
+      <c r="E154" s="31" t="inlineStr">
         <is>
           <t>Pendrive Flash Drive 2 Em 1 Usb C E Usb 3.0 32gb Metal Pro</t>
         </is>
       </c>
-      <c r="F154" s="29" t="n"/>
-      <c r="G154" s="30" t="inlineStr">
+      <c r="F154" s="31" t="n"/>
+      <c r="G154" s="32" t="inlineStr">
         <is>
           <t>Pen Drive Celular Mini Pequeno Hrebos</t>
         </is>
       </c>
-      <c r="H154" s="27" t="n"/>
+      <c r="H154" s="29" t="n"/>
     </row>
     <row r="155" hidden="1" ht="21.95" customHeight="1">
       <c r="A155" s="9" t="n"/>
-      <c r="B155" s="54" t="n">
+      <c r="B155" s="56" t="n">
         <v>154</v>
       </c>
-      <c r="C155" s="35" t="inlineStr">
+      <c r="C155" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D155" s="41" t="inlineStr">
+      <c r="D155" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2EC1D2e</t>
         </is>
       </c>
-      <c r="E155" s="37" t="inlineStr">
+      <c r="E155" s="39" t="inlineStr">
         <is>
           <t>Pendrive Altomex AL-U-32 memória 32gb pc notebook usb cor preto liso</t>
         </is>
       </c>
-      <c r="F155" s="43" t="n"/>
-      <c r="G155" s="38" t="inlineStr">
+      <c r="F155" s="45" t="n"/>
+      <c r="G155" s="40" t="inlineStr">
         <is>
           <t>Altomex</t>
         </is>
       </c>
-      <c r="H155" s="35" t="inlineStr">
+      <c r="H155" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5772,7 +5645,7 @@
     </row>
     <row r="156" hidden="1">
       <c r="A156" s="3" t="n"/>
-      <c r="B156" s="53" t="n">
+      <c r="B156" s="55" t="n">
         <v>155</v>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -5797,151 +5670,151 @@
     </row>
     <row r="157" hidden="1">
       <c r="A157" s="16" t="n"/>
-      <c r="B157" s="27" t="n">
+      <c r="B157" s="29" t="n">
         <v>156</v>
       </c>
-      <c r="C157" s="27" t="inlineStr">
+      <c r="C157" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D157" s="39" t="inlineStr">
+      <c r="D157" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1qNb23D</t>
         </is>
       </c>
-      <c r="E157" s="29" t="inlineStr">
+      <c r="E157" s="31" t="inlineStr">
         <is>
           <t>Kingston USB Datatraveler Exodia S 64Gb USB-A 3.2 Gen 1</t>
         </is>
       </c>
-      <c r="F157" s="27" t="n"/>
-      <c r="G157" s="27" t="n"/>
-      <c r="H157" s="27" t="n"/>
+      <c r="F157" s="29" t="n"/>
+      <c r="G157" s="29" t="n"/>
+      <c r="H157" s="29" t="n"/>
     </row>
     <row r="158" hidden="1">
-      <c r="B158" s="27" t="n">
+      <c r="B158" s="29" t="n">
         <v>157</v>
       </c>
-      <c r="C158" s="27" t="inlineStr">
+      <c r="C158" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D158" s="39" t="inlineStr">
+      <c r="D158" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2LbfSKF</t>
         </is>
       </c>
-      <c r="E158" s="29" t="inlineStr">
+      <c r="E158" s="31" t="inlineStr">
         <is>
           <t>Pendrive Kingston Datatraveler Exodia Dtx/64 64gb 3.2 Gen 1</t>
         </is>
       </c>
-      <c r="F158" s="27" t="n"/>
-      <c r="G158" s="27" t="n"/>
-      <c r="H158" s="27" t="n"/>
+      <c r="F158" s="29" t="n"/>
+      <c r="G158" s="29" t="n"/>
+      <c r="H158" s="29" t="n"/>
     </row>
     <row r="159" hidden="1">
-      <c r="B159" s="54" t="n">
+      <c r="B159" s="56" t="n">
         <v>158</v>
       </c>
-      <c r="C159" s="35" t="inlineStr">
+      <c r="C159" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D159" s="41" t="inlineStr">
+      <c r="D159" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2YZWcPv</t>
         </is>
       </c>
-      <c r="E159" s="37" t="inlineStr">
+      <c r="E159" s="39" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Ultra Shift Preto 32gb Usb 3.2</t>
         </is>
       </c>
-      <c r="F159" s="35" t="n"/>
-      <c r="G159" s="35" t="n"/>
-      <c r="H159" s="35" t="inlineStr">
+      <c r="F159" s="37" t="n"/>
+      <c r="G159" s="37" t="n"/>
+      <c r="H159" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
     <row r="160" hidden="1">
-      <c r="B160" s="54" t="n">
+      <c r="B160" s="56" t="n">
         <v>159</v>
       </c>
-      <c r="C160" s="35" t="inlineStr">
+      <c r="C160" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D160" s="41" t="inlineStr">
+      <c r="D160" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/11UGXL4</t>
         </is>
       </c>
-      <c r="E160" s="37" t="inlineStr">
+      <c r="E160" s="39" t="inlineStr">
         <is>
           <t>SanDisk Ultra Shift pendrive 64 GB 3.0 / 3.2 preto 10x mais rapido</t>
         </is>
       </c>
-      <c r="F160" s="35" t="n"/>
-      <c r="G160" s="35" t="n"/>
-      <c r="H160" s="35" t="inlineStr">
+      <c r="F160" s="37" t="n"/>
+      <c r="G160" s="37" t="n"/>
+      <c r="H160" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
     <row r="161" hidden="1">
-      <c r="B161" s="27" t="n">
+      <c r="B161" s="29" t="n">
         <v>160</v>
       </c>
-      <c r="C161" s="27" t="inlineStr">
+      <c r="C161" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D161" s="39" t="inlineStr">
+      <c r="D161" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1XfkXY4</t>
         </is>
       </c>
-      <c r="E161" s="29" t="inlineStr">
+      <c r="E161" s="31" t="inlineStr">
         <is>
           <t>Pendrive 64gb Usb 3.0 Tipo C Metal Plug &amp; Play Android Vers</t>
         </is>
       </c>
-      <c r="F161" s="29" t="n"/>
-      <c r="G161" s="29" t="n"/>
-      <c r="H161" s="29" t="n"/>
+      <c r="F161" s="31" t="n"/>
+      <c r="G161" s="31" t="n"/>
+      <c r="H161" s="31" t="n"/>
       <c r="I161" s="5" t="n"/>
     </row>
     <row r="162" hidden="1">
-      <c r="B162" s="54" t="n">
+      <c r="B162" s="56" t="n">
         <v>161</v>
       </c>
-      <c r="C162" s="35" t="inlineStr">
+      <c r="C162" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D162" s="41" t="inlineStr">
+      <c r="D162" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/15oUo1F</t>
         </is>
       </c>
-      <c r="E162" s="37" t="inlineStr">
+      <c r="E162" s="39" t="inlineStr">
         <is>
           <t>Pen Drive Sandisk Usb 3.2 Geração 1 Ultra Luxe 128gb</t>
         </is>
       </c>
-      <c r="F162" s="37" t="n"/>
-      <c r="G162" s="37" t="n"/>
-      <c r="H162" s="37" t="inlineStr">
+      <c r="F162" s="39" t="n"/>
+      <c r="G162" s="39" t="n"/>
+      <c r="H162" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -5968,7 +5841,7 @@
     </row>
     <row r="163" hidden="1">
       <c r="A163" s="3" t="n"/>
-      <c r="B163" s="53" t="n">
+      <c r="B163" s="55" t="n">
         <v>162</v>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -5976,7 +5849,7 @@
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D163" s="24" t="inlineStr">
+      <c r="D163" s="25" t="inlineStr">
         <is>
           <t>https://meli.la/23sKPyN</t>
         </is>
@@ -6010,28 +5883,28 @@
       <c r="AA163" s="5" t="n"/>
     </row>
     <row r="164" hidden="1" customFormat="1" s="3">
-      <c r="A164" s="25" t="n"/>
-      <c r="B164" s="54" t="n">
+      <c r="A164" s="26" t="n"/>
+      <c r="B164" s="56" t="n">
         <v>163</v>
       </c>
-      <c r="C164" s="35" t="inlineStr">
+      <c r="C164" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D164" s="41" t="inlineStr">
+      <c r="D164" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2LoeExa</t>
         </is>
       </c>
-      <c r="E164" s="37" t="inlineStr">
+      <c r="E164" s="39" t="inlineStr">
         <is>
           <t>Pen Drive SanDisk Ultra Shift 128 GB USB 3.0 Violeta</t>
         </is>
       </c>
-      <c r="F164" s="37" t="n"/>
-      <c r="G164" s="37" t="n"/>
-      <c r="H164" s="37" t="inlineStr">
+      <c r="F164" s="39" t="n"/>
+      <c r="G164" s="39" t="n"/>
+      <c r="H164" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6056,28 +5929,28 @@
       <c r="Z164" s="5" t="n"/>
       <c r="AA164" s="5" t="n"/>
     </row>
-    <row r="165" hidden="1" customFormat="1" s="25">
-      <c r="B165" s="27" t="n">
+    <row r="165" hidden="1" customFormat="1" s="26">
+      <c r="B165" s="29" t="n">
         <v>164</v>
       </c>
-      <c r="C165" s="27" t="inlineStr">
+      <c r="C165" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D165" s="39" t="inlineStr">
+      <c r="D165" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1iL54rx</t>
         </is>
       </c>
-      <c r="E165" s="29" t="inlineStr">
+      <c r="E165" s="31" t="inlineStr">
         <is>
           <t>Kapbom Ka-a-16 Kit C/ 2 Pen-drive De 16 Gb Penmax Usb 2.0 Pc</t>
         </is>
       </c>
-      <c r="F165" s="29" t="n"/>
-      <c r="G165" s="29" t="n"/>
-      <c r="H165" s="29" t="n"/>
+      <c r="F165" s="31" t="n"/>
+      <c r="G165" s="31" t="n"/>
+      <c r="H165" s="31" t="n"/>
       <c r="I165" s="5" t="n"/>
       <c r="J165" s="5" t="n"/>
       <c r="K165" s="5" t="n"/>
@@ -6099,27 +5972,27 @@
       <c r="AA165" s="5" t="n"/>
     </row>
     <row r="166" hidden="1">
-      <c r="B166" s="27" t="n">
+      <c r="B166" s="29" t="n">
         <v>165</v>
       </c>
-      <c r="C166" s="27" t="inlineStr">
+      <c r="C166" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D166" s="39" t="inlineStr">
+      <c r="D166" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1j345xd</t>
         </is>
       </c>
-      <c r="E166" s="29" t="inlineStr">
+      <c r="E166" s="31" t="inlineStr">
         <is>
           <t>Pendrive Altomex Al-u-4 4 4gb 2.0 Preto</t>
         </is>
       </c>
-      <c r="F166" s="29" t="n"/>
-      <c r="G166" s="29" t="n"/>
-      <c r="H166" s="29" t="n"/>
+      <c r="F166" s="31" t="n"/>
+      <c r="G166" s="31" t="n"/>
+      <c r="H166" s="31" t="n"/>
       <c r="I166" s="5" t="n"/>
       <c r="J166" s="5" t="n"/>
       <c r="K166" s="5" t="n"/>
@@ -6141,27 +6014,27 @@
       <c r="AA166" s="5" t="n"/>
     </row>
     <row r="167" hidden="1">
-      <c r="B167" s="27" t="n">
+      <c r="B167" s="29" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="27" t="inlineStr">
+      <c r="C167" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D167" s="39" t="inlineStr">
+      <c r="D167" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1e35itv</t>
         </is>
       </c>
-      <c r="E167" s="29" t="inlineStr">
+      <c r="E167" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 64gb Usb 3.0 De Duplo 2 Em 1 Usb/usb-c 140mb/s</t>
         </is>
       </c>
-      <c r="F167" s="29" t="n"/>
-      <c r="G167" s="29" t="n"/>
-      <c r="H167" s="29" t="n"/>
+      <c r="F167" s="31" t="n"/>
+      <c r="G167" s="31" t="n"/>
+      <c r="H167" s="31" t="n"/>
       <c r="I167" s="5" t="n"/>
       <c r="J167" s="5" t="n"/>
       <c r="K167" s="5" t="n"/>
@@ -6183,27 +6056,27 @@
       <c r="AA167" s="5" t="n"/>
     </row>
     <row r="168" hidden="1">
-      <c r="B168" s="27" t="n">
+      <c r="B168" s="29" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="27" t="inlineStr">
+      <c r="C168" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D168" s="39" t="inlineStr">
+      <c r="D168" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1qjgyca</t>
         </is>
       </c>
-      <c r="E168" s="29" t="inlineStr">
+      <c r="E168" s="31" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Cruzer Blade 32gb 2.0 Usb Original Lacrado</t>
         </is>
       </c>
-      <c r="F168" s="29" t="n"/>
-      <c r="G168" s="29" t="n"/>
-      <c r="H168" s="29" t="n"/>
+      <c r="F168" s="31" t="n"/>
+      <c r="G168" s="31" t="n"/>
+      <c r="H168" s="31" t="n"/>
       <c r="I168" s="5" t="n"/>
       <c r="J168" s="5" t="n"/>
       <c r="K168" s="5" t="n"/>
@@ -6225,27 +6098,27 @@
       <c r="AA168" s="5" t="n"/>
     </row>
     <row r="169" hidden="1">
-      <c r="B169" s="54" t="n">
+      <c r="B169" s="56" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="35" t="inlineStr">
+      <c r="C169" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D169" s="41" t="inlineStr">
+      <c r="D169" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2bUd8Qi</t>
         </is>
       </c>
-      <c r="E169" s="37" t="inlineStr">
+      <c r="E169" s="39" t="inlineStr">
         <is>
           <t>Pendrive SanDisk Cruzer Blade 8GB 2.0 preto e vermelho</t>
         </is>
       </c>
-      <c r="F169" s="37" t="n"/>
-      <c r="G169" s="37" t="n"/>
-      <c r="H169" s="37" t="inlineStr">
+      <c r="F169" s="39" t="n"/>
+      <c r="G169" s="39" t="n"/>
+      <c r="H169" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6271,27 +6144,27 @@
       <c r="AA169" s="5" t="n"/>
     </row>
     <row r="170" hidden="1">
-      <c r="B170" s="27" t="n">
+      <c r="B170" s="29" t="n">
         <v>169</v>
       </c>
-      <c r="C170" s="27" t="inlineStr">
+      <c r="C170" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D170" s="39" t="inlineStr">
+      <c r="D170" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1rPATiL</t>
         </is>
       </c>
-      <c r="E170" s="29" t="inlineStr">
+      <c r="E170" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 16gb Multilaser Twist - Pd588</t>
         </is>
       </c>
-      <c r="F170" s="29" t="n"/>
-      <c r="G170" s="29" t="n"/>
-      <c r="H170" s="29" t="n"/>
+      <c r="F170" s="31" t="n"/>
+      <c r="G170" s="31" t="n"/>
+      <c r="H170" s="31" t="n"/>
       <c r="I170" s="5" t="n"/>
       <c r="J170" s="5" t="n"/>
       <c r="K170" s="5" t="n"/>
@@ -6313,27 +6186,27 @@
       <c r="AA170" s="5" t="n"/>
     </row>
     <row r="171" hidden="1">
-      <c r="B171" s="27" t="n">
+      <c r="B171" s="29" t="n">
         <v>170</v>
       </c>
-      <c r="C171" s="27" t="inlineStr">
+      <c r="C171" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D171" s="39" t="inlineStr">
+      <c r="D171" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2Z5fhDF</t>
         </is>
       </c>
-      <c r="E171" s="29" t="inlineStr">
+      <c r="E171" s="31" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Madeira Redondo Ecológico Personalizado Cor Marrom-claro</t>
         </is>
       </c>
-      <c r="F171" s="29" t="n"/>
-      <c r="G171" s="29" t="n"/>
-      <c r="H171" s="29" t="n"/>
+      <c r="F171" s="31" t="n"/>
+      <c r="G171" s="31" t="n"/>
+      <c r="H171" s="31" t="n"/>
       <c r="I171" s="5" t="n"/>
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="5" t="n"/>
@@ -6355,27 +6228,27 @@
       <c r="AA171" s="5" t="n"/>
     </row>
     <row r="172" hidden="1">
-      <c r="B172" s="54" t="n">
+      <c r="B172" s="56" t="n">
         <v>171</v>
       </c>
-      <c r="C172" s="35" t="inlineStr">
+      <c r="C172" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D172" s="41" t="inlineStr">
+      <c r="D172" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/1Ny9BQg</t>
         </is>
       </c>
-      <c r="E172" s="37" t="inlineStr">
+      <c r="E172" s="39" t="inlineStr">
         <is>
           <t>Pen Drive 32gb Ultra Flair Usb 3.0 Metal 150mbs Z73 Sandisk</t>
         </is>
       </c>
-      <c r="F172" s="37" t="n"/>
-      <c r="G172" s="37" t="n"/>
-      <c r="H172" s="37" t="inlineStr">
+      <c r="F172" s="39" t="n"/>
+      <c r="G172" s="39" t="n"/>
+      <c r="H172" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6401,27 +6274,27 @@
       <c r="AA172" s="5" t="n"/>
     </row>
     <row r="173" hidden="1">
-      <c r="B173" s="54" t="n">
+      <c r="B173" s="56" t="n">
         <v>172</v>
       </c>
-      <c r="C173" s="35" t="inlineStr">
+      <c r="C173" s="37" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D173" s="41" t="inlineStr">
+      <c r="D173" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/1MHXAZo</t>
         </is>
       </c>
-      <c r="E173" s="37" t="inlineStr">
+      <c r="E173" s="39" t="inlineStr">
         <is>
           <t>Pendrive Sandisk Ultra Shift 256gb Usb 3.2 Gen 1 100mbs Roxo Violeta</t>
         </is>
       </c>
-      <c r="F173" s="37" t="n"/>
-      <c r="G173" s="37" t="n"/>
-      <c r="H173" s="37" t="inlineStr">
+      <c r="F173" s="39" t="n"/>
+      <c r="G173" s="39" t="n"/>
+      <c r="H173" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6447,27 +6320,27 @@
       <c r="AA173" s="5" t="n"/>
     </row>
     <row r="174" hidden="1">
-      <c r="B174" s="53" t="n">
+      <c r="B174" s="55" t="n">
         <v>173</v>
       </c>
-      <c r="C174" s="31" t="inlineStr">
+      <c r="C174" s="33" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D174" s="44" t="inlineStr">
+      <c r="D174" s="46" t="inlineStr">
         <is>
           <t>https://meli.la/2u6BAdS</t>
         </is>
       </c>
-      <c r="E174" s="33" t="inlineStr">
+      <c r="E174" s="35" t="inlineStr">
         <is>
           <t>Pendrive 32gb 2 Em 1 Usb 3.0 Tipo-c Para Celular Pc Tablet</t>
         </is>
       </c>
-      <c r="F174" s="33" t="n"/>
-      <c r="G174" s="33" t="n"/>
-      <c r="H174" s="33" t="inlineStr">
+      <c r="F174" s="35" t="n"/>
+      <c r="G174" s="35" t="n"/>
+      <c r="H174" s="35" t="inlineStr">
         <is>
           <t>fora do ar</t>
         </is>
@@ -6493,27 +6366,27 @@
       <c r="AA174" s="5" t="n"/>
     </row>
     <row r="175" hidden="1">
-      <c r="B175" s="27" t="n">
+      <c r="B175" s="29" t="n">
         <v>174</v>
       </c>
-      <c r="C175" s="27" t="inlineStr">
+      <c r="C175" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D175" s="39" t="inlineStr">
+      <c r="D175" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2KYJowg</t>
         </is>
       </c>
-      <c r="E175" s="29" t="inlineStr">
+      <c r="E175" s="31" t="inlineStr">
         <is>
           <t>Pendrive Altomex 128gb Usb 2.0 Al-u-128 Alta Velocidade - Preto</t>
         </is>
       </c>
-      <c r="F175" s="29" t="n"/>
-      <c r="G175" s="29" t="n"/>
-      <c r="H175" s="29" t="n"/>
+      <c r="F175" s="31" t="n"/>
+      <c r="G175" s="31" t="n"/>
+      <c r="H175" s="31" t="n"/>
       <c r="I175" s="5" t="n"/>
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="5" t="n"/>
@@ -6535,27 +6408,27 @@
       <c r="AA175" s="5" t="n"/>
     </row>
     <row r="176" hidden="1">
-      <c r="B176" s="27" t="n">
+      <c r="B176" s="29" t="n">
         <v>175</v>
       </c>
-      <c r="C176" s="27" t="inlineStr">
+      <c r="C176" s="29" t="inlineStr">
         <is>
           <t>Pen drive</t>
         </is>
       </c>
-      <c r="D176" s="39" t="inlineStr">
+      <c r="D176" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2niAQ49</t>
         </is>
       </c>
-      <c r="E176" s="29" t="inlineStr">
+      <c r="E176" s="31" t="inlineStr">
         <is>
           <t>Pen Drive Dual Drive 2 Em 1 Usb-a E Usb-c 128gb Pendrive Tipo C Duplo Duas Entradas Gurumania</t>
         </is>
       </c>
-      <c r="F176" s="29" t="n"/>
-      <c r="G176" s="29" t="n"/>
-      <c r="H176" s="29" t="n"/>
+      <c r="F176" s="31" t="n"/>
+      <c r="G176" s="31" t="n"/>
+      <c r="H176" s="31" t="n"/>
       <c r="I176" s="5" t="n"/>
       <c r="J176" s="5" t="n"/>
       <c r="K176" s="5" t="n"/>
@@ -6577,27 +6450,27 @@
       <c r="AA176" s="5" t="n"/>
     </row>
     <row r="177" hidden="1">
-      <c r="B177" s="27" t="n">
+      <c r="B177" s="29" t="n">
         <v>176</v>
       </c>
-      <c r="C177" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D177" s="39" t="inlineStr">
+      <c r="C177" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D177" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1Z5VJQ6</t>
         </is>
       </c>
-      <c r="E177" s="29" t="inlineStr">
+      <c r="E177" s="31" t="inlineStr">
         <is>
           <t>Mousepad De Escritório Pequeno Preto Tecido Simples Fortrek</t>
         </is>
       </c>
-      <c r="F177" s="29" t="n"/>
-      <c r="G177" s="29" t="n"/>
-      <c r="H177" s="29" t="n"/>
+      <c r="F177" s="31" t="n"/>
+      <c r="G177" s="31" t="n"/>
+      <c r="H177" s="31" t="n"/>
       <c r="I177" s="5" t="n"/>
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="5" t="n"/>
@@ -6619,27 +6492,27 @@
       <c r="AA177" s="5" t="n"/>
     </row>
     <row r="178" hidden="1">
-      <c r="B178" s="27" t="n">
+      <c r="B178" s="29" t="n">
         <v>177</v>
       </c>
-      <c r="C178" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D178" s="39" t="inlineStr">
+      <c r="C178" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D178" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1fheaUW</t>
         </is>
       </c>
-      <c r="E178" s="29" t="inlineStr">
+      <c r="E178" s="31" t="inlineStr">
         <is>
           <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Grafite Desenho impresso Courino</t>
         </is>
       </c>
-      <c r="F178" s="29" t="n"/>
-      <c r="G178" s="29" t="n"/>
-      <c r="H178" s="29" t="n"/>
+      <c r="F178" s="31" t="n"/>
+      <c r="G178" s="31" t="n"/>
+      <c r="H178" s="31" t="n"/>
       <c r="I178" s="5" t="n"/>
       <c r="J178" s="5" t="n"/>
       <c r="K178" s="5" t="n"/>
@@ -6661,27 +6534,27 @@
       <c r="AA178" s="5" t="n"/>
     </row>
     <row r="179" hidden="1">
-      <c r="B179" s="27" t="n">
+      <c r="B179" s="29" t="n">
         <v>178</v>
       </c>
-      <c r="C179" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D179" s="39" t="inlineStr">
+      <c r="C179" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D179" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1vKzJM3</t>
         </is>
       </c>
-      <c r="E179" s="29" t="inlineStr">
+      <c r="E179" s="31" t="inlineStr">
         <is>
           <t>Mouse Pad Com Apoio Ergonômico Em Espuma Para Punho Antiderrapante Confortável Para Escritório Gamer Estudo Trabalho Preto Megalodonte</t>
         </is>
       </c>
-      <c r="F179" s="29" t="n"/>
-      <c r="G179" s="29" t="n"/>
-      <c r="H179" s="29" t="n"/>
+      <c r="F179" s="31" t="n"/>
+      <c r="G179" s="31" t="n"/>
+      <c r="H179" s="31" t="n"/>
       <c r="I179" s="5" t="n"/>
       <c r="J179" s="5" t="n"/>
       <c r="K179" s="5" t="n"/>
@@ -6703,27 +6576,27 @@
       <c r="AA179" s="5" t="n"/>
     </row>
     <row r="180" hidden="1">
-      <c r="B180" s="54" t="n">
+      <c r="B180" s="56" t="n">
         <v>179</v>
       </c>
-      <c r="C180" s="35" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D180" s="41" t="inlineStr">
+      <c r="C180" s="37" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D180" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2NPo4eJ</t>
         </is>
       </c>
-      <c r="E180" s="37" t="inlineStr">
+      <c r="E180" s="39" t="inlineStr">
         <is>
           <t>Mousepad Mp-04pt Simples - Hoopso</t>
         </is>
       </c>
-      <c r="F180" s="37" t="n"/>
-      <c r="G180" s="37" t="n"/>
-      <c r="H180" s="37" t="inlineStr">
+      <c r="F180" s="39" t="n"/>
+      <c r="G180" s="39" t="n"/>
+      <c r="H180" s="39" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -6749,27 +6622,27 @@
       <c r="AA180" s="5" t="n"/>
     </row>
     <row r="181" hidden="1">
-      <c r="B181" s="27" t="n">
+      <c r="B181" s="29" t="n">
         <v>180</v>
       </c>
-      <c r="C181" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D181" s="39" t="inlineStr">
+      <c r="C181" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D181" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1NCrcA6</t>
         </is>
       </c>
-      <c r="E181" s="29" t="inlineStr">
+      <c r="E181" s="31" t="inlineStr">
         <is>
           <t>Mousepad Gamer Speed Havit Pequeno Com Alta Qualidade Cor Preto</t>
         </is>
       </c>
-      <c r="F181" s="29" t="n"/>
-      <c r="G181" s="29" t="n"/>
-      <c r="H181" s="29" t="n"/>
+      <c r="F181" s="31" t="n"/>
+      <c r="G181" s="31" t="n"/>
+      <c r="H181" s="31" t="n"/>
       <c r="I181" s="5" t="n"/>
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="5" t="n"/>
@@ -6791,27 +6664,27 @@
       <c r="AA181" s="5" t="n"/>
     </row>
     <row r="182" hidden="1">
-      <c r="B182" s="27" t="n">
+      <c r="B182" s="29" t="n">
         <v>181</v>
       </c>
-      <c r="C182" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D182" s="39" t="inlineStr">
+      <c r="C182" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D182" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2ASehEZ</t>
         </is>
       </c>
-      <c r="E182" s="29" t="inlineStr">
+      <c r="E182" s="31" t="inlineStr">
         <is>
           <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Caramelo</t>
         </is>
       </c>
-      <c r="F182" s="29" t="n"/>
-      <c r="G182" s="29" t="n"/>
-      <c r="H182" s="29" t="n"/>
+      <c r="F182" s="31" t="n"/>
+      <c r="G182" s="31" t="n"/>
+      <c r="H182" s="31" t="n"/>
       <c r="I182" s="5" t="n"/>
       <c r="J182" s="5" t="n"/>
       <c r="K182" s="5" t="n"/>
@@ -6833,27 +6706,27 @@
       <c r="AA182" s="5" t="n"/>
     </row>
     <row r="183" hidden="1">
-      <c r="B183" s="27" t="n">
+      <c r="B183" s="29" t="n">
         <v>182</v>
       </c>
-      <c r="C183" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D183" s="39" t="inlineStr">
+      <c r="C183" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D183" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/13C2HTp</t>
         </is>
       </c>
-      <c r="E183" s="29" t="inlineStr">
+      <c r="E183" s="31" t="inlineStr">
         <is>
           <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Azul</t>
         </is>
       </c>
-      <c r="F183" s="29" t="n"/>
-      <c r="G183" s="29" t="n"/>
-      <c r="H183" s="29" t="n"/>
+      <c r="F183" s="31" t="n"/>
+      <c r="G183" s="31" t="n"/>
+      <c r="H183" s="31" t="n"/>
       <c r="I183" s="5" t="n"/>
       <c r="J183" s="5" t="n"/>
       <c r="K183" s="5" t="n"/>
@@ -6875,27 +6748,27 @@
       <c r="AA183" s="5" t="n"/>
     </row>
     <row r="184" hidden="1">
-      <c r="B184" s="27" t="n">
+      <c r="B184" s="29" t="n">
         <v>183</v>
       </c>
-      <c r="C184" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D184" s="39" t="inlineStr">
+      <c r="C184" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D184" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2e1VX7E</t>
         </is>
       </c>
-      <c r="E184" s="29" t="inlineStr">
+      <c r="E184" s="31" t="inlineStr">
         <is>
           <t>Mouse Pad Ziphome Preto 23x22.5cm Borracha Tecido Antiderrapante</t>
         </is>
       </c>
-      <c r="F184" s="29" t="n"/>
-      <c r="G184" s="29" t="n"/>
-      <c r="H184" s="29" t="n"/>
+      <c r="F184" s="31" t="n"/>
+      <c r="G184" s="31" t="n"/>
+      <c r="H184" s="31" t="n"/>
       <c r="I184" s="5" t="n"/>
       <c r="J184" s="5" t="n"/>
       <c r="K184" s="5" t="n"/>
@@ -6917,27 +6790,27 @@
       <c r="AA184" s="5" t="n"/>
     </row>
     <row r="185" hidden="1">
-      <c r="B185" s="27" t="n">
+      <c r="B185" s="29" t="n">
         <v>184</v>
       </c>
-      <c r="C185" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D185" s="39" t="inlineStr">
+      <c r="C185" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D185" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2Pn152u</t>
         </is>
       </c>
-      <c r="E185" s="29" t="inlineStr">
+      <c r="E185" s="31" t="inlineStr">
         <is>
           <t>Mouse Pad Pequeno 20x20cm Couro Sintetico Kit 2 Tapete Mesas Cor Quadrado MARFIM Desenho impresso Liso</t>
         </is>
       </c>
-      <c r="F185" s="29" t="n"/>
-      <c r="G185" s="29" t="n"/>
-      <c r="H185" s="29" t="n"/>
+      <c r="F185" s="31" t="n"/>
+      <c r="G185" s="31" t="n"/>
+      <c r="H185" s="31" t="n"/>
       <c r="I185" s="5" t="n"/>
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="5" t="n"/>
@@ -6959,27 +6832,27 @@
       <c r="AA185" s="5" t="n"/>
     </row>
     <row r="186" hidden="1">
-      <c r="B186" s="27" t="n">
+      <c r="B186" s="29" t="n">
         <v>185</v>
       </c>
-      <c r="C186" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D186" s="39" t="inlineStr">
+      <c r="C186" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D186" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1XfeDjK</t>
         </is>
       </c>
-      <c r="E186" s="29" t="inlineStr">
+      <c r="E186" s="31" t="inlineStr">
         <is>
           <t>Tapete Para Mouse Preto Liso Notebook E Escritório Borracha</t>
         </is>
       </c>
-      <c r="F186" s="29" t="n"/>
-      <c r="G186" s="29" t="n"/>
-      <c r="H186" s="29" t="n"/>
+      <c r="F186" s="31" t="n"/>
+      <c r="G186" s="31" t="n"/>
+      <c r="H186" s="31" t="n"/>
       <c r="I186" s="5" t="n"/>
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="5" t="n"/>
@@ -7001,27 +6874,27 @@
       <c r="AA186" s="5" t="n"/>
     </row>
     <row r="187" hidden="1">
-      <c r="B187" s="27" t="n">
+      <c r="B187" s="29" t="n">
         <v>186</v>
       </c>
-      <c r="C187" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D187" s="39" t="inlineStr">
+      <c r="C187" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D187" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2M889UE</t>
         </is>
       </c>
-      <c r="E187" s="29" t="inlineStr">
+      <c r="E187" s="31" t="inlineStr">
         <is>
           <t>Mousepad 20x20cm Couro Sintetico Slim Premium Impermeavel</t>
         </is>
       </c>
-      <c r="F187" s="29" t="n"/>
-      <c r="G187" s="29" t="n"/>
-      <c r="H187" s="29" t="n"/>
+      <c r="F187" s="31" t="n"/>
+      <c r="G187" s="31" t="n"/>
+      <c r="H187" s="31" t="n"/>
       <c r="I187" s="5" t="n"/>
       <c r="J187" s="5" t="n"/>
       <c r="K187" s="5" t="n"/>
@@ -7043,27 +6916,27 @@
       <c r="AA187" s="5" t="n"/>
     </row>
     <row r="188" hidden="1">
-      <c r="B188" s="27" t="n">
+      <c r="B188" s="29" t="n">
         <v>187</v>
       </c>
-      <c r="C188" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D188" s="39" t="inlineStr">
+      <c r="C188" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D188" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2K3HSeC</t>
         </is>
       </c>
-      <c r="E188" s="29" t="inlineStr">
+      <c r="E188" s="31" t="inlineStr">
         <is>
           <t>Mousepad Bullpad 20x20cm Cores Com Fundo Emborrachado Cor Rosa Desenho impresso Courino</t>
         </is>
       </c>
-      <c r="F188" s="29" t="n"/>
-      <c r="G188" s="29" t="n"/>
-      <c r="H188" s="29" t="n"/>
+      <c r="F188" s="31" t="n"/>
+      <c r="G188" s="31" t="n"/>
+      <c r="H188" s="31" t="n"/>
       <c r="I188" s="5" t="n"/>
       <c r="J188" s="5" t="n"/>
       <c r="K188" s="5" t="n"/>
@@ -7085,27 +6958,27 @@
       <c r="AA188" s="5" t="n"/>
     </row>
     <row r="189" hidden="1">
-      <c r="B189" s="27" t="n">
+      <c r="B189" s="29" t="n">
         <v>188</v>
       </c>
-      <c r="C189" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D189" s="39" t="inlineStr">
+      <c r="C189" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D189" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1iM9KwJ</t>
         </is>
       </c>
-      <c r="E189" s="29" t="inlineStr">
+      <c r="E189" s="31" t="inlineStr">
         <is>
           <t>Mouse Pad Mousepad Couro Legítimo Marca Volpe Cor Bege</t>
         </is>
       </c>
-      <c r="F189" s="29" t="n"/>
-      <c r="G189" s="29" t="n"/>
-      <c r="H189" s="29" t="n"/>
+      <c r="F189" s="31" t="n"/>
+      <c r="G189" s="31" t="n"/>
+      <c r="H189" s="31" t="n"/>
       <c r="I189" s="5" t="n"/>
       <c r="J189" s="5" t="n"/>
       <c r="K189" s="5" t="n"/>
@@ -7127,27 +7000,27 @@
       <c r="AA189" s="5" t="n"/>
     </row>
     <row r="190" hidden="1">
-      <c r="B190" s="27" t="n">
+      <c r="B190" s="29" t="n">
         <v>189</v>
       </c>
-      <c r="C190" s="27" t="inlineStr">
-        <is>
-          <t>Mousepad simples</t>
-        </is>
-      </c>
-      <c r="D190" s="39" t="inlineStr">
+      <c r="C190" s="29" t="inlineStr">
+        <is>
+          <t>Mouse pad pequeno</t>
+        </is>
+      </c>
+      <c r="D190" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2jgnzuA</t>
         </is>
       </c>
-      <c r="E190" s="29" t="inlineStr">
+      <c r="E190" s="31" t="inlineStr">
         <is>
           <t>Mousepad Dask Pad Gamer Pequeno Minimalista Moderno Prático Cor Branco</t>
         </is>
       </c>
-      <c r="F190" s="29" t="n"/>
-      <c r="G190" s="29" t="n"/>
-      <c r="H190" s="29" t="n"/>
+      <c r="F190" s="31" t="n"/>
+      <c r="G190" s="31" t="n"/>
+      <c r="H190" s="31" t="n"/>
       <c r="I190" s="5" t="n"/>
       <c r="J190" s="5" t="n"/>
       <c r="K190" s="5" t="n"/>
@@ -7169,31 +7042,27 @@
       <c r="AA190" s="5" t="n"/>
     </row>
     <row r="191" hidden="1">
-      <c r="B191" s="31" t="n">
+      <c r="B191" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="C191" s="31" t="inlineStr">
+      <c r="C191" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D191" s="44" t="inlineStr">
+      <c r="D191" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2cGbTdT</t>
         </is>
       </c>
-      <c r="E191" s="33" t="inlineStr">
+      <c r="E191" s="31" t="inlineStr">
         <is>
           <t>Fone Bluetooth 5.3 Tws Sem Fio Anti Ruido A Prova Dagua Compatível Iphone 7 8 X Xr 11 12 13 14 15 16 17 Xs Pro Max Plus Samsung S20 S23 S24 Xiaomi Motorola Android Prova DAgua Wireless Premium</t>
         </is>
       </c>
-      <c r="F191" s="33" t="n"/>
-      <c r="G191" s="33" t="n"/>
-      <c r="H191" s="33" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="F191" s="31" t="n"/>
+      <c r="G191" s="31" t="n"/>
+      <c r="H191" s="31" t="n"/>
       <c r="I191" s="5" t="n"/>
       <c r="J191" s="5" t="n"/>
       <c r="K191" s="5" t="n"/>
@@ -7215,27 +7084,27 @@
       <c r="AA191" s="5" t="n"/>
     </row>
     <row r="192" hidden="1">
-      <c r="B192" s="27" t="n">
+      <c r="B192" s="29" t="n">
         <v>191</v>
       </c>
-      <c r="C192" s="27" t="inlineStr">
+      <c r="C192" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D192" s="39" t="inlineStr">
+      <c r="D192" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1NTtrP5</t>
         </is>
       </c>
-      <c r="E192" s="29" t="inlineStr">
+      <c r="E192" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth In Ear Touch À Prova D'água Inova</t>
         </is>
       </c>
-      <c r="F192" s="27" t="n"/>
-      <c r="G192" s="27" t="n"/>
-      <c r="H192" s="27" t="n"/>
+      <c r="F192" s="29" t="n"/>
+      <c r="G192" s="29" t="n"/>
+      <c r="H192" s="29" t="n"/>
       <c r="J192" s="5" t="n"/>
       <c r="K192" s="5" t="n"/>
       <c r="L192" s="5" t="n"/>
@@ -7256,175 +7125,175 @@
       <c r="AA192" s="5" t="n"/>
     </row>
     <row r="193" hidden="1">
-      <c r="B193" s="27" t="n">
+      <c r="B193" s="29" t="n">
         <v>192</v>
       </c>
-      <c r="C193" s="27" t="inlineStr">
+      <c r="C193" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D193" s="39" t="inlineStr">
+      <c r="D193" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2PLvtPH</t>
         </is>
       </c>
-      <c r="E193" s="29" t="inlineStr">
+      <c r="E193" s="31" t="inlineStr">
         <is>
           <t>Fone de Ouvido Bluetooth 5.4 soundcore P30i da Anker, Cancelamento de Ruído Adaptativo, Graves Poderosos, 45H de Reprodução, Estojo 2-em-1 com Suporte para Celular, IP54, Fone sem fio TWS, Azul</t>
         </is>
       </c>
-      <c r="F193" s="27" t="n"/>
-      <c r="G193" s="27" t="n"/>
-      <c r="H193" s="27" t="n"/>
+      <c r="F193" s="29" t="n"/>
+      <c r="G193" s="29" t="n"/>
+      <c r="H193" s="29" t="n"/>
     </row>
     <row r="194" hidden="1">
-      <c r="B194" s="27" t="n">
+      <c r="B194" s="56" t="n">
         <v>193</v>
       </c>
-      <c r="C194" s="27" t="inlineStr">
+      <c r="C194" s="37" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D194" s="39" t="inlineStr">
+      <c r="D194" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2gbZpAz</t>
         </is>
       </c>
-      <c r="E194" s="29" t="inlineStr">
+      <c r="E194" s="39" t="inlineStr">
         <is>
           <t>Fone de Ouvido Ows Bluetooth Design Aberto Kaidi 794 Cor Preto</t>
         </is>
       </c>
-      <c r="F194" s="27" t="n"/>
-      <c r="G194" s="27" t="n"/>
-      <c r="H194" s="27" t="inlineStr">
+      <c r="F194" s="37" t="n"/>
+      <c r="G194" s="37" t="n"/>
+      <c r="H194" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
     <row r="195" hidden="1">
-      <c r="B195" s="27" t="n">
+      <c r="B195" s="29" t="n">
         <v>194</v>
       </c>
-      <c r="C195" s="27" t="inlineStr">
+      <c r="C195" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D195" s="39" t="inlineStr">
+      <c r="D195" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1NTUn6u</t>
         </is>
       </c>
-      <c r="E195" s="29" t="inlineStr">
+      <c r="E195" s="31" t="inlineStr">
         <is>
           <t>Fone Sem Fio Bluetooth 5.4 Compativel Iphone Ipx4 Microfone</t>
         </is>
       </c>
-      <c r="F195" s="27" t="n"/>
-      <c r="G195" s="27" t="n"/>
-      <c r="H195" s="27" t="n"/>
+      <c r="F195" s="29" t="n"/>
+      <c r="G195" s="29" t="n"/>
+      <c r="H195" s="29" t="n"/>
     </row>
     <row r="196" hidden="1">
-      <c r="B196" s="27" t="n">
+      <c r="B196" s="29" t="n">
         <v>195</v>
       </c>
-      <c r="C196" s="27" t="inlineStr">
+      <c r="C196" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D196" s="39" t="inlineStr">
+      <c r="D196" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1KFgyz2</t>
         </is>
       </c>
-      <c r="E196" s="29" t="inlineStr">
+      <c r="E196" s="31" t="inlineStr">
         <is>
           <t>Fone de Ouvido TWS B Basto Fone-TWS Bluetooth Sem Fio Com Cancelamento de Ruído e Microfone</t>
         </is>
       </c>
-      <c r="F196" s="27" t="n"/>
-      <c r="G196" s="27" t="n"/>
-      <c r="H196" s="27" t="n"/>
+      <c r="F196" s="29" t="n"/>
+      <c r="G196" s="29" t="n"/>
+      <c r="H196" s="29" t="n"/>
     </row>
     <row r="197" hidden="1">
-      <c r="B197" s="27" t="n">
+      <c r="B197" s="29" t="n">
         <v>196</v>
       </c>
-      <c r="C197" s="27" t="inlineStr">
+      <c r="C197" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D197" s="39" t="inlineStr">
+      <c r="D197" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1XARpGa</t>
         </is>
       </c>
-      <c r="E197" s="29" t="inlineStr">
+      <c r="E197" s="31" t="inlineStr">
         <is>
           <t>Fone Bluetooth 5.4 Sem Fio Tws Kaidi Kd780 Graves Potentes</t>
         </is>
       </c>
-      <c r="F197" s="27" t="n"/>
-      <c r="G197" s="27" t="n"/>
-      <c r="H197" s="27" t="n"/>
+      <c r="F197" s="29" t="n"/>
+      <c r="G197" s="29" t="n"/>
+      <c r="H197" s="29" t="n"/>
     </row>
     <row r="198" hidden="1">
-      <c r="B198" s="27" t="n">
+      <c r="B198" s="29" t="n">
         <v>197</v>
       </c>
-      <c r="C198" s="27" t="inlineStr">
+      <c r="C198" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D198" s="39" t="inlineStr">
+      <c r="D198" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/18AJ4f6</t>
         </is>
       </c>
-      <c r="E198" s="29" t="inlineStr">
+      <c r="E198" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth 5.1 Sem Fio Tws Wireless Bateria Longa Duração E Conexão Rápida Coolmusic</t>
         </is>
       </c>
-      <c r="F198" s="27" t="n"/>
-      <c r="G198" s="27" t="n"/>
-      <c r="H198" s="27" t="n"/>
+      <c r="F198" s="29" t="n"/>
+      <c r="G198" s="29" t="n"/>
+      <c r="H198" s="29" t="n"/>
     </row>
     <row r="199" hidden="1">
-      <c r="B199" s="27" t="n">
+      <c r="B199" s="29" t="n">
         <v>198</v>
       </c>
-      <c r="C199" s="27" t="inlineStr">
+      <c r="C199" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D199" s="39" t="inlineStr">
+      <c r="D199" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2GHMGcW</t>
         </is>
       </c>
-      <c r="E199" s="29" t="inlineStr">
+      <c r="E199" s="31" t="inlineStr">
         <is>
           <t>Fone Qcy N30 Anc Bluetooth 5.4 Multiponto Ipx4 Cor Preto</t>
         </is>
       </c>
-      <c r="F199" s="27" t="n"/>
-      <c r="G199" s="27" t="n"/>
-      <c r="H199" s="27" t="n"/>
+      <c r="F199" s="29" t="n"/>
+      <c r="G199" s="29" t="n"/>
+      <c r="H199" s="29" t="n"/>
     </row>
     <row r="200" hidden="1">
-      <c r="B200" s="35" t="n">
+      <c r="B200" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="C200" s="35" t="inlineStr">
+      <c r="C200" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
@@ -7434,240 +7303,232 @@
           <t>https://meli.la/1jGZwC3</t>
         </is>
       </c>
-      <c r="E200" s="37" t="inlineStr">
+      <c r="E200" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Esportivos Sem Fio Bluetooth Impermeável Ipx6</t>
         </is>
       </c>
-      <c r="F200" s="35" t="n"/>
-      <c r="G200" s="35" t="n"/>
-      <c r="H200" s="35" t="inlineStr">
+      <c r="F200" s="29" t="n"/>
+      <c r="G200" s="29" t="n"/>
+      <c r="H200" s="29" t="n"/>
+    </row>
+    <row r="201" hidden="1">
+      <c r="B201" s="56" t="n">
+        <v>200</v>
+      </c>
+      <c r="C201" s="37" t="inlineStr">
+        <is>
+          <t>Fone sem fio (bluetooth)</t>
+        </is>
+      </c>
+      <c r="D201" s="43" t="inlineStr">
+        <is>
+          <t>https://meli.la/2G3uu5c</t>
+        </is>
+      </c>
+      <c r="E201" s="39" t="inlineStr">
+        <is>
+          <t>Fone de Ouvido Eardbud AIWA AWS-EB-04-B Bluetooth IPX4 ANC 26 Horas de bateria</t>
+        </is>
+      </c>
+      <c r="F201" s="37" t="n"/>
+      <c r="G201" s="37" t="n"/>
+      <c r="H201" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
       </c>
     </row>
-    <row r="201" hidden="1">
-      <c r="B201" s="27" t="n">
-        <v>200</v>
-      </c>
-      <c r="C201" s="27" t="inlineStr">
+    <row r="202" hidden="1">
+      <c r="B202" s="29" t="n">
+        <v>201</v>
+      </c>
+      <c r="C202" s="29" t="inlineStr">
         <is>
           <t>Fone sem fio (bluetooth)</t>
         </is>
       </c>
-      <c r="D201" s="39" t="inlineStr">
-        <is>
-          <t>https://meli.la/2G3uu5c</t>
-        </is>
-      </c>
-      <c r="E201" s="29" t="inlineStr">
-        <is>
-          <t>Fone de Ouvido Eardbud AIWA AWS-EB-04-B Bluetooth IPX4 ANC 26 Horas de bateria</t>
-        </is>
-      </c>
-      <c r="F201" s="27" t="n"/>
-      <c r="G201" s="27" t="n"/>
-      <c r="H201" s="27" t="inlineStr">
-        <is>
-          <t>estoque baixo</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" hidden="1">
-      <c r="B202" s="31" t="n">
-        <v>201</v>
-      </c>
-      <c r="C202" s="31" t="inlineStr">
-        <is>
-          <t>Fone sem fio (bluetooth)</t>
-        </is>
-      </c>
-      <c r="D202" s="44" t="inlineStr">
+      <c r="D202" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1A65TWL</t>
         </is>
       </c>
-      <c r="E202" s="33" t="inlineStr">
+      <c r="E202" s="31" t="inlineStr">
         <is>
           <t>Fone De Ouvido Bluetooth Redmi Buds 6 Play Xiaomi Sem Fio Cor Preto</t>
         </is>
       </c>
-      <c r="F202" s="31" t="n"/>
-      <c r="G202" s="31" t="n"/>
-      <c r="H202" s="31" t="inlineStr">
-        <is>
-          <t>fora do ar</t>
-        </is>
-      </c>
+      <c r="F202" s="29" t="n"/>
+      <c r="G202" s="29" t="n"/>
+      <c r="H202" s="29" t="n"/>
     </row>
     <row r="203" hidden="1">
-      <c r="B203" s="53" t="n">
+      <c r="B203" s="55" t="n">
         <v>202</v>
       </c>
-      <c r="C203" s="53" t="inlineStr">
+      <c r="C203" s="55" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D203" s="56" t="inlineStr">
+      <c r="D203" s="58" t="inlineStr">
         <is>
           <t>https://meli.la/1HyuGqq</t>
         </is>
       </c>
-      <c r="E203" s="57" t="inlineStr">
+      <c r="E203" s="59" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Dual Bluetooth 2.4GHz USB Recarregável Silencioso Para Notebook PC</t>
         </is>
       </c>
-      <c r="F203" s="53" t="n"/>
-      <c r="G203" s="53" t="n"/>
-      <c r="H203" s="53" t="n"/>
+      <c r="F203" s="55" t="n"/>
+      <c r="G203" s="55" t="n"/>
+      <c r="H203" s="55" t="n"/>
       <c r="I203" s="3" t="n"/>
     </row>
     <row r="204" hidden="1">
       <c r="A204" s="16" t="n"/>
-      <c r="B204" s="27" t="n">
+      <c r="B204" s="29" t="n">
         <v>203</v>
       </c>
-      <c r="C204" s="27" t="inlineStr">
+      <c r="C204" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D204" s="39" t="inlineStr">
+      <c r="D204" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2gZQECx</t>
         </is>
       </c>
-      <c r="E204" s="29" t="inlineStr">
+      <c r="E204" s="31" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Bluetooth Recarregável Hrebos IF-216 Prateado USB Para Windows</t>
         </is>
       </c>
-      <c r="F204" s="27" t="n"/>
-      <c r="G204" s="27" t="n"/>
-      <c r="H204" s="27" t="n"/>
+      <c r="F204" s="29" t="n"/>
+      <c r="G204" s="29" t="n"/>
+      <c r="H204" s="29" t="n"/>
     </row>
     <row r="205" hidden="1">
       <c r="A205" s="16" t="n"/>
-      <c r="B205" s="27" t="n">
+      <c r="B205" s="29" t="n">
         <v>204</v>
       </c>
-      <c r="C205" s="27" t="inlineStr">
+      <c r="C205" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D205" s="39" t="inlineStr">
+      <c r="D205" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1LM6zpe</t>
         </is>
       </c>
-      <c r="E205" s="29" t="inlineStr">
+      <c r="E205" s="31" t="inlineStr">
         <is>
           <t>Mouse sem fio Logitech M280 com Pilha Inclusa - Cinza</t>
         </is>
       </c>
-      <c r="F205" s="27" t="n"/>
-      <c r="G205" s="27" t="n"/>
-      <c r="H205" s="27" t="n"/>
+      <c r="F205" s="29" t="n"/>
+      <c r="G205" s="29" t="n"/>
+      <c r="H205" s="29" t="n"/>
     </row>
     <row r="206" hidden="1">
       <c r="A206" s="16" t="n"/>
-      <c r="B206" s="27" t="n">
+      <c r="B206" s="29" t="n">
         <v>205</v>
       </c>
-      <c r="C206" s="27" t="inlineStr">
+      <c r="C206" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D206" s="39" t="inlineStr">
+      <c r="D206" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/1ECoJrH</t>
         </is>
       </c>
-      <c r="E206" s="29" t="inlineStr">
+      <c r="E206" s="31" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Logitech M196 Com Conexão Bluetooth - Branco</t>
         </is>
       </c>
-      <c r="F206" s="27" t="n"/>
-      <c r="G206" s="27" t="n"/>
-      <c r="H206" s="27" t="n"/>
+      <c r="F206" s="29" t="n"/>
+      <c r="G206" s="29" t="n"/>
+      <c r="H206" s="29" t="n"/>
     </row>
     <row r="207" hidden="1">
       <c r="A207" s="16" t="n"/>
-      <c r="B207" s="27" t="n">
+      <c r="B207" s="29" t="n">
         <v>206</v>
       </c>
-      <c r="C207" s="27" t="inlineStr">
+      <c r="C207" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D207" s="39" t="inlineStr">
+      <c r="D207" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2B1DT57</t>
         </is>
       </c>
-      <c r="E207" s="29" t="inlineStr">
+      <c r="E207" s="31" t="inlineStr">
         <is>
           <t>Mouse sem fio Logitech M185 - Cinza</t>
         </is>
       </c>
-      <c r="F207" s="27" t="n"/>
-      <c r="G207" s="27" t="n"/>
-      <c r="H207" s="27" t="n"/>
+      <c r="F207" s="29" t="n"/>
+      <c r="G207" s="29" t="n"/>
+      <c r="H207" s="29" t="n"/>
     </row>
     <row r="208" hidden="1">
       <c r="A208" s="16" t="n"/>
-      <c r="B208" s="27" t="n">
+      <c r="B208" s="29" t="n">
         <v>207</v>
       </c>
-      <c r="C208" s="27" t="inlineStr">
+      <c r="C208" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D208" s="39" t="inlineStr">
+      <c r="D208" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2bjhTN4</t>
         </is>
       </c>
-      <c r="E208" s="29" t="inlineStr">
+      <c r="E208" s="31" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Preto Z3700 V0l79aa Hp</t>
         </is>
       </c>
-      <c r="F208" s="27" t="n"/>
-      <c r="G208" s="27" t="n"/>
-      <c r="H208" s="27" t="n"/>
+      <c r="F208" s="29" t="n"/>
+      <c r="G208" s="29" t="n"/>
+      <c r="H208" s="29" t="n"/>
     </row>
     <row r="209" hidden="1">
       <c r="A209" s="16" t="n"/>
-      <c r="B209" s="54" t="n">
+      <c r="B209" s="56" t="n">
         <v>208</v>
       </c>
-      <c r="C209" s="35" t="inlineStr">
+      <c r="C209" s="37" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D209" s="41" t="inlineStr">
+      <c r="D209" s="43" t="inlineStr">
         <is>
           <t>https://meli.la/2UKmjJK</t>
         </is>
       </c>
-      <c r="E209" s="37" t="inlineStr">
+      <c r="E209" s="39" t="inlineStr">
         <is>
           <t>Mouse Oriente Sem Fio 1600 Dpi Maxprint Branco</t>
         </is>
       </c>
-      <c r="F209" s="35" t="n"/>
-      <c r="G209" s="35" t="n"/>
-      <c r="H209" s="35" t="inlineStr">
+      <c r="F209" s="37" t="n"/>
+      <c r="G209" s="37" t="n"/>
+      <c r="H209" s="37" t="inlineStr">
         <is>
           <t>estoque baixo</t>
         </is>
@@ -7675,431 +7536,431 @@
     </row>
     <row r="210" hidden="1">
       <c r="A210" s="16" t="n"/>
-      <c r="B210" s="27" t="n">
+      <c r="B210" s="29" t="n">
         <v>209</v>
       </c>
-      <c r="C210" s="27" t="inlineStr">
+      <c r="C210" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D210" s="39" t="inlineStr">
+      <c r="D210" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/2mZP8Mf</t>
         </is>
       </c>
-      <c r="E210" s="29" t="inlineStr">
+      <c r="E210" s="31" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Compacto Lenovo 300 Cinza Claro Gy51l15677</t>
         </is>
       </c>
-      <c r="F210" s="27" t="n"/>
-      <c r="G210" s="27" t="n"/>
-      <c r="H210" s="27" t="n"/>
+      <c r="F210" s="29" t="n"/>
+      <c r="G210" s="29" t="n"/>
+      <c r="H210" s="29" t="n"/>
     </row>
     <row r="211" hidden="1">
       <c r="A211" s="16" t="n"/>
-      <c r="B211" s="27" t="n">
+      <c r="B211" s="29" t="n">
         <v>210</v>
       </c>
-      <c r="C211" s="27" t="inlineStr">
+      <c r="C211" s="29" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="D211" s="39" t="inlineStr">
+      <c r="D211" s="41" t="inlineStr">
         <is>
           <t>https://meli.la/18G4RGk</t>
         </is>
       </c>
-      <c r="E211" s="29" t="inlineStr">
+      <c r="E211" s="31" t="inlineStr">
         <is>
           <t>Mouse Sem Fio Multilaser Office - Design Ergonômico e Conexão 2.4GHz - MO251</t>
         </is>
       </c>
-      <c r="F211" s="27" t="n"/>
-      <c r="G211" s="27" t="n"/>
-      <c r="H211" s="27" t="n"/>
+      <c r="F211" s="29" t="n"/>
+      <c r="G211" s="29" t="n"/>
+      <c r="H211" s="29" t="n"/>
     </row>
     <row r="212" hidden="1">
-      <c r="B212" s="27" t="n">
+      <c r="B212" s="29" t="n">
         <v>211</v>
       </c>
-      <c r="E212" s="19" t="n"/>
+      <c r="E212" s="20" t="n"/>
     </row>
     <row r="213" hidden="1">
-      <c r="B213" s="27" t="n">
+      <c r="B213" s="29" t="n">
         <v>212</v>
       </c>
-      <c r="E213" s="19" t="n"/>
+      <c r="E213" s="20" t="n"/>
     </row>
     <row r="214" hidden="1">
-      <c r="B214" s="27" t="n">
+      <c r="B214" s="29" t="n">
         <v>213</v>
       </c>
-      <c r="E214" s="21" t="n"/>
+      <c r="E214" s="22" t="n"/>
     </row>
     <row r="215" hidden="1">
-      <c r="B215" s="27" t="n">
+      <c r="B215" s="29" t="n">
         <v>214</v>
       </c>
-      <c r="E215" s="21" t="n"/>
+      <c r="E215" s="22" t="n"/>
     </row>
     <row r="216" hidden="1">
-      <c r="B216" s="27" t="n">
+      <c r="B216" s="29" t="n">
         <v>215</v>
       </c>
-      <c r="E216" s="19" t="n"/>
+      <c r="E216" s="20" t="n"/>
     </row>
     <row r="217" hidden="1" ht="15.6" customHeight="1">
-      <c r="B217" s="27" t="n">
+      <c r="B217" s="29" t="n">
         <v>216</v>
       </c>
-      <c r="E217" s="20" t="n"/>
+      <c r="E217" s="21" t="n"/>
     </row>
     <row r="218" hidden="1">
-      <c r="B218" s="27" t="n">
+      <c r="B218" s="29" t="n">
         <v>217</v>
       </c>
-      <c r="E218" s="19" t="n"/>
+      <c r="E218" s="20" t="n"/>
     </row>
     <row r="219" hidden="1">
-      <c r="B219" s="27" t="n">
+      <c r="B219" s="29" t="n">
         <v>218</v>
       </c>
-      <c r="E219" s="19" t="n"/>
+      <c r="E219" s="20" t="n"/>
     </row>
     <row r="220" hidden="1">
-      <c r="B220" s="27" t="n">
+      <c r="B220" s="29" t="n">
         <v>219</v>
       </c>
-      <c r="E220" s="19" t="n"/>
+      <c r="E220" s="20" t="n"/>
     </row>
     <row r="221" hidden="1">
-      <c r="B221" s="27" t="n">
+      <c r="B221" s="29" t="n">
         <v>220</v>
       </c>
-      <c r="E221" s="19" t="n"/>
+      <c r="E221" s="20" t="n"/>
     </row>
     <row r="222" hidden="1">
-      <c r="B222" s="27" t="n">
+      <c r="B222" s="29" t="n">
         <v>221</v>
       </c>
-      <c r="E222" s="19" t="n"/>
+      <c r="E222" s="20" t="n"/>
     </row>
     <row r="223" hidden="1">
-      <c r="B223" s="27" t="n">
+      <c r="B223" s="29" t="n">
         <v>222</v>
       </c>
-      <c r="E223" s="19" t="n"/>
+      <c r="E223" s="20" t="n"/>
     </row>
     <row r="224" hidden="1">
-      <c r="B224" s="27" t="n">
+      <c r="B224" s="29" t="n">
         <v>223</v>
       </c>
-      <c r="E224" s="19" t="n"/>
+      <c r="E224" s="20" t="n"/>
     </row>
     <row r="225" hidden="1">
-      <c r="B225" s="27" t="n">
+      <c r="B225" s="29" t="n">
         <v>224</v>
       </c>
-      <c r="E225" s="19" t="n"/>
+      <c r="E225" s="20" t="n"/>
     </row>
     <row r="226" hidden="1">
-      <c r="B226" s="27" t="n">
+      <c r="B226" s="29" t="n">
         <v>225</v>
       </c>
-      <c r="E226" s="19" t="n"/>
+      <c r="E226" s="20" t="n"/>
     </row>
     <row r="227" hidden="1">
-      <c r="B227" s="27" t="n">
+      <c r="B227" s="29" t="n">
         <v>226</v>
       </c>
-      <c r="E227" s="19" t="n"/>
+      <c r="E227" s="20" t="n"/>
     </row>
     <row r="228" hidden="1">
-      <c r="B228" s="27" t="n">
+      <c r="B228" s="29" t="n">
         <v>227</v>
       </c>
-      <c r="E228" s="19" t="n"/>
+      <c r="E228" s="20" t="n"/>
     </row>
     <row r="229" hidden="1">
-      <c r="B229" s="27" t="n">
+      <c r="B229" s="29" t="n">
         <v>228</v>
       </c>
-      <c r="E229" s="19" t="n"/>
+      <c r="E229" s="20" t="n"/>
     </row>
     <row r="230" hidden="1">
-      <c r="B230" s="27" t="n">
+      <c r="B230" s="29" t="n">
         <v>229</v>
       </c>
-      <c r="E230" s="19" t="n"/>
+      <c r="E230" s="20" t="n"/>
     </row>
     <row r="231" hidden="1">
-      <c r="B231" s="27" t="n">
+      <c r="B231" s="29" t="n">
         <v>230</v>
       </c>
-      <c r="E231" s="19" t="n"/>
+      <c r="E231" s="20" t="n"/>
     </row>
     <row r="232" hidden="1">
-      <c r="B232" s="27" t="n">
+      <c r="B232" s="29" t="n">
         <v>231</v>
       </c>
-      <c r="E232" s="19" t="n"/>
+      <c r="E232" s="20" t="n"/>
     </row>
     <row r="233" hidden="1">
-      <c r="B233" s="27" t="n">
+      <c r="B233" s="29" t="n">
         <v>232</v>
       </c>
-      <c r="E233" s="19" t="n"/>
+      <c r="E233" s="20" t="n"/>
     </row>
     <row r="234" hidden="1">
-      <c r="B234" s="27" t="n">
+      <c r="B234" s="29" t="n">
         <v>233</v>
       </c>
-      <c r="E234" s="19" t="n"/>
+      <c r="E234" s="20" t="n"/>
     </row>
     <row r="235" hidden="1">
-      <c r="B235" s="27" t="n">
+      <c r="B235" s="29" t="n">
         <v>234</v>
       </c>
-      <c r="E235" s="19" t="n"/>
+      <c r="E235" s="20" t="n"/>
     </row>
     <row r="236" hidden="1">
-      <c r="B236" s="27" t="n">
+      <c r="B236" s="29" t="n">
         <v>235</v>
       </c>
-      <c r="E236" s="19" t="n"/>
+      <c r="E236" s="20" t="n"/>
     </row>
     <row r="237" hidden="1">
-      <c r="B237" s="27" t="n">
+      <c r="B237" s="29" t="n">
         <v>236</v>
       </c>
-      <c r="E237" s="19" t="n"/>
+      <c r="E237" s="20" t="n"/>
     </row>
     <row r="238" hidden="1">
-      <c r="B238" s="27" t="n">
+      <c r="B238" s="29" t="n">
         <v>237</v>
       </c>
-      <c r="E238" s="19" t="n"/>
+      <c r="E238" s="20" t="n"/>
     </row>
     <row r="239" hidden="1">
-      <c r="B239" s="27" t="n">
+      <c r="B239" s="29" t="n">
         <v>238</v>
       </c>
-      <c r="E239" s="19" t="n"/>
+      <c r="E239" s="20" t="n"/>
     </row>
     <row r="240" hidden="1">
-      <c r="B240" s="27" t="n">
+      <c r="B240" s="29" t="n">
         <v>239</v>
       </c>
-      <c r="E240" s="19" t="n"/>
+      <c r="E240" s="20" t="n"/>
     </row>
     <row r="241" hidden="1">
-      <c r="B241" s="27" t="n">
+      <c r="B241" s="29" t="n">
         <v>240</v>
       </c>
-      <c r="E241" s="21" t="n"/>
+      <c r="E241" s="22" t="n"/>
     </row>
     <row r="242" hidden="1">
-      <c r="B242" s="27" t="n">
+      <c r="B242" s="29" t="n">
         <v>241</v>
       </c>
-      <c r="E242" s="21" t="n"/>
+      <c r="E242" s="22" t="n"/>
     </row>
     <row r="243" hidden="1">
-      <c r="B243" s="27" t="n">
+      <c r="B243" s="29" t="n">
         <v>242</v>
       </c>
-      <c r="E243" s="19" t="n"/>
+      <c r="E243" s="20" t="n"/>
     </row>
     <row r="244" hidden="1" ht="15.6" customHeight="1">
-      <c r="B244" s="27" t="n">
+      <c r="B244" s="29" t="n">
         <v>243</v>
       </c>
-      <c r="E244" s="20" t="n"/>
+      <c r="E244" s="21" t="n"/>
     </row>
     <row r="245" hidden="1">
-      <c r="B245" s="27" t="n">
+      <c r="B245" s="29" t="n">
         <v>244</v>
       </c>
-      <c r="E245" s="19" t="n"/>
+      <c r="E245" s="20" t="n"/>
     </row>
     <row r="246" hidden="1">
-      <c r="B246" s="27" t="n">
+      <c r="B246" s="29" t="n">
         <v>245</v>
       </c>
-      <c r="E246" s="19" t="n"/>
+      <c r="E246" s="20" t="n"/>
     </row>
     <row r="247" hidden="1">
-      <c r="B247" s="27" t="n">
+      <c r="B247" s="29" t="n">
         <v>246</v>
       </c>
-      <c r="E247" s="19" t="n"/>
+      <c r="E247" s="20" t="n"/>
     </row>
     <row r="248" hidden="1">
-      <c r="B248" s="27" t="n">
+      <c r="B248" s="29" t="n">
         <v>247</v>
       </c>
-      <c r="E248" s="19" t="n"/>
+      <c r="E248" s="20" t="n"/>
     </row>
     <row r="249" hidden="1">
-      <c r="B249" s="27" t="n">
+      <c r="B249" s="29" t="n">
         <v>248</v>
       </c>
-      <c r="E249" s="19" t="n"/>
+      <c r="E249" s="20" t="n"/>
     </row>
     <row r="250" hidden="1">
-      <c r="B250" s="27" t="n">
+      <c r="B250" s="29" t="n">
         <v>249</v>
       </c>
-      <c r="E250" s="19" t="n"/>
+      <c r="E250" s="20" t="n"/>
     </row>
     <row r="251" hidden="1">
-      <c r="B251" s="27" t="n">
+      <c r="B251" s="29" t="n">
         <v>250</v>
       </c>
-      <c r="E251" s="19" t="n"/>
+      <c r="E251" s="20" t="n"/>
     </row>
     <row r="252" hidden="1">
-      <c r="B252" s="27" t="n">
+      <c r="B252" s="29" t="n">
         <v>251</v>
       </c>
-      <c r="E252" s="19" t="n"/>
+      <c r="E252" s="20" t="n"/>
     </row>
     <row r="253" hidden="1">
-      <c r="B253" s="27" t="n">
+      <c r="B253" s="29" t="n">
         <v>252</v>
       </c>
-      <c r="E253" s="19" t="n"/>
+      <c r="E253" s="20" t="n"/>
     </row>
     <row r="254">
-      <c r="E254" s="19" t="n"/>
+      <c r="E254" s="20" t="n"/>
     </row>
     <row r="255">
-      <c r="E255" s="19" t="n"/>
+      <c r="E255" s="20" t="n"/>
     </row>
     <row r="256">
-      <c r="E256" s="19" t="n"/>
+      <c r="E256" s="20" t="n"/>
     </row>
     <row r="257">
-      <c r="E257" s="19" t="n"/>
+      <c r="E257" s="20" t="n"/>
     </row>
     <row r="258">
-      <c r="E258" s="19" t="n"/>
+      <c r="E258" s="20" t="n"/>
     </row>
     <row r="259">
-      <c r="E259" s="19" t="n"/>
+      <c r="E259" s="20" t="n"/>
     </row>
     <row r="260">
-      <c r="E260" s="19" t="n"/>
+      <c r="E260" s="20" t="n"/>
     </row>
     <row r="261">
-      <c r="E261" s="19" t="n"/>
+      <c r="E261" s="20" t="n"/>
     </row>
     <row r="262">
-      <c r="E262" s="19" t="n"/>
+      <c r="E262" s="20" t="n"/>
     </row>
     <row r="263">
-      <c r="E263" s="19" t="n"/>
+      <c r="E263" s="20" t="n"/>
     </row>
     <row r="264">
-      <c r="E264" s="19" t="n"/>
+      <c r="E264" s="20" t="n"/>
     </row>
     <row r="265">
-      <c r="E265" s="19" t="n"/>
+      <c r="E265" s="20" t="n"/>
     </row>
     <row r="266">
-      <c r="E266" s="19" t="n"/>
+      <c r="E266" s="20" t="n"/>
     </row>
     <row r="267">
-      <c r="E267" s="19" t="n"/>
+      <c r="E267" s="20" t="n"/>
     </row>
     <row r="268">
-      <c r="E268" s="21" t="n"/>
+      <c r="E268" s="22" t="n"/>
     </row>
     <row r="269">
-      <c r="E269" s="21" t="n"/>
+      <c r="E269" s="22" t="n"/>
     </row>
     <row r="270">
-      <c r="E270" s="19" t="n"/>
+      <c r="E270" s="20" t="n"/>
     </row>
     <row r="271" ht="15.6" customHeight="1">
-      <c r="E271" s="20" t="n"/>
+      <c r="E271" s="21" t="n"/>
     </row>
     <row r="272">
-      <c r="E272" s="19" t="n"/>
+      <c r="E272" s="20" t="n"/>
     </row>
     <row r="273">
-      <c r="E273" s="19" t="n"/>
+      <c r="E273" s="20" t="n"/>
     </row>
     <row r="274">
-      <c r="E274" s="19" t="n"/>
+      <c r="E274" s="20" t="n"/>
     </row>
     <row r="275">
-      <c r="E275" s="19" t="n"/>
+      <c r="E275" s="20" t="n"/>
     </row>
     <row r="276">
-      <c r="E276" s="19" t="n"/>
+      <c r="E276" s="20" t="n"/>
     </row>
     <row r="277">
-      <c r="E277" s="19" t="n"/>
+      <c r="E277" s="20" t="n"/>
     </row>
     <row r="278">
-      <c r="E278" s="19" t="n"/>
+      <c r="E278" s="20" t="n"/>
     </row>
     <row r="279">
-      <c r="E279" s="19" t="n"/>
+      <c r="E279" s="20" t="n"/>
     </row>
     <row r="280">
-      <c r="E280" s="19" t="n"/>
+      <c r="E280" s="20" t="n"/>
     </row>
     <row r="281">
-      <c r="E281" s="19" t="n"/>
+      <c r="E281" s="20" t="n"/>
     </row>
     <row r="282">
-      <c r="E282" s="19" t="n"/>
+      <c r="E282" s="20" t="n"/>
     </row>
     <row r="283">
-      <c r="E283" s="19" t="n"/>
+      <c r="E283" s="20" t="n"/>
     </row>
     <row r="284">
-      <c r="E284" s="19" t="n"/>
+      <c r="E284" s="20" t="n"/>
     </row>
     <row r="285">
-      <c r="E285" s="19" t="n"/>
+      <c r="E285" s="20" t="n"/>
     </row>
     <row r="286">
-      <c r="E286" s="19" t="n"/>
+      <c r="E286" s="20" t="n"/>
     </row>
     <row r="287">
-      <c r="E287" s="19" t="n"/>
+      <c r="E287" s="20" t="n"/>
     </row>
     <row r="288">
-      <c r="E288" s="19" t="n"/>
+      <c r="E288" s="20" t="n"/>
     </row>
     <row r="289"/>
     <row r="290">
-      <c r="E290" s="19" t="n"/>
+      <c r="E290" s="20" t="n"/>
     </row>
     <row r="291">
-      <c r="E291" s="19" t="n"/>
+      <c r="E291" s="20" t="n"/>
     </row>
     <row r="292"/>
     <row r="293"/>
     <row r="294">
-      <c r="D294" s="19" t="n"/>
-      <c r="E294" s="19" t="n"/>
+      <c r="D294" s="20" t="n"/>
+      <c r="E294" s="20" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="19" t="n"/>
-      <c r="E295" s="18" t="n"/>
+      <c r="D295" s="20" t="n"/>
+      <c r="E295" s="19" t="n"/>
     </row>
     <row r="296">
-      <c r="E296" s="22" t="n"/>
+      <c r="E296" s="23" t="n"/>
     </row>
     <row r="297" ht="21.95" customHeight="1">
-      <c r="E297" s="23" t="n"/>
+      <c r="E297" s="24" t="n"/>
     </row>
     <row r="298"/>
     <row r="299"/>
@@ -9786,7 +9647,7 @@
   <autoFilter ref="A1:I253">
     <filterColumn colId="2" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="Fone com fio"/>
+        <filter val="Cabo USB-C"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -10003,7 +9864,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
